--- a/data/target_dispatch/파보겔_실제발송_최종정제명단.xlsx
+++ b/data/target_dispatch/파보겔_실제발송_최종정제명단.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="452" uniqueCount="361">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="572" uniqueCount="454">
   <si>
     <t>순번</t>
   </si>
@@ -304,6 +304,78 @@
     <t>Parachiwo pom</t>
   </si>
   <si>
+    <t>삼성켄넬</t>
+  </si>
+  <si>
+    <t>더조은 펫타운1.2.3.4.5동</t>
+  </si>
+  <si>
+    <t>허니펫</t>
+  </si>
+  <si>
+    <t>멍스펫</t>
+  </si>
+  <si>
+    <t>캣츠비</t>
+  </si>
+  <si>
+    <t>펫샵/비비냥</t>
+  </si>
+  <si>
+    <t>경남고성군 거류면동해로447-15</t>
+  </si>
+  <si>
+    <t>폼스홀릭</t>
+  </si>
+  <si>
+    <t>댕구르냥</t>
+  </si>
+  <si>
+    <t>캣독365 청주점 강아지분양 고양이분양</t>
+  </si>
+  <si>
+    <t>보듬캣</t>
+  </si>
+  <si>
+    <t>코코캔넬</t>
+  </si>
+  <si>
+    <t>티니리안</t>
+  </si>
+  <si>
+    <t>도그하우스 대구점</t>
+  </si>
+  <si>
+    <t>대성독하우스</t>
+  </si>
+  <si>
+    <t>박달농장</t>
+  </si>
+  <si>
+    <t>포근하개도그하우스</t>
+  </si>
+  <si>
+    <t>지예</t>
+  </si>
+  <si>
+    <t>지용주</t>
+  </si>
+  <si>
+    <t>머머켄넬</t>
+  </si>
+  <si>
+    <t>이정훈강아지 하남본점</t>
+  </si>
+  <si>
+    <t>브리더하우스</t>
+  </si>
+  <si>
+    <t>댕댕러브펫 (ADAMS PET) 구리점</t>
+  </si>
+  <si>
+    <t>블랙 앤 화이트</t>
+  </si>
+  <si>
     <t>정원정</t>
   </si>
   <si>
@@ -538,6 +610,66 @@
     <t>유지혜</t>
   </si>
   <si>
+    <t>김성학</t>
+  </si>
+  <si>
+    <t>박명규외 3인</t>
+  </si>
+  <si>
+    <t>강동규</t>
+  </si>
+  <si>
+    <t>설수진</t>
+  </si>
+  <si>
+    <t>한병현</t>
+  </si>
+  <si>
+    <t>염주빈</t>
+  </si>
+  <si>
+    <t>함금순</t>
+  </si>
+  <si>
+    <t>박현구</t>
+  </si>
+  <si>
+    <t>현가영</t>
+  </si>
+  <si>
+    <t>이아름</t>
+  </si>
+  <si>
+    <t>심형진</t>
+  </si>
+  <si>
+    <t>박태순</t>
+  </si>
+  <si>
+    <t>이성욱</t>
+  </si>
+  <si>
+    <t>신용성</t>
+  </si>
+  <si>
+    <t>조상국</t>
+  </si>
+  <si>
+    <t>김형욱</t>
+  </si>
+  <si>
+    <t>이경표</t>
+  </si>
+  <si>
+    <t>우지훈</t>
+  </si>
+  <si>
+    <t>댕댕러브펫</t>
+  </si>
+  <si>
+    <t>문수미</t>
+  </si>
+  <si>
     <t>010-3114-1100</t>
   </si>
   <si>
@@ -805,6 +937,75 @@
     <t>010-7575-1231</t>
   </si>
   <si>
+    <t>010-5544-5008</t>
+  </si>
+  <si>
+    <t>010-3228-1333</t>
+  </si>
+  <si>
+    <t>010-6616-6919</t>
+  </si>
+  <si>
+    <t>010-5757-6766</t>
+  </si>
+  <si>
+    <t>010-5667-3733</t>
+  </si>
+  <si>
+    <t>010-2987-5256</t>
+  </si>
+  <si>
+    <t>010-2481-4481</t>
+  </si>
+  <si>
+    <t>010-9022-3590</t>
+  </si>
+  <si>
+    <t>010-8112-6192</t>
+  </si>
+  <si>
+    <t>010-4338-3264</t>
+  </si>
+  <si>
+    <t>010-9268-1937</t>
+  </si>
+  <si>
+    <t>010-9324-5524</t>
+  </si>
+  <si>
+    <t>010-4521-1831</t>
+  </si>
+  <si>
+    <t>010-3933-1402</t>
+  </si>
+  <si>
+    <t>010-9065-5805</t>
+  </si>
+  <si>
+    <t>010-7712-7003</t>
+  </si>
+  <si>
+    <t>010-9362-3587</t>
+  </si>
+  <si>
+    <t>010-3036-6023</t>
+  </si>
+  <si>
+    <t>010-8574-3998</t>
+  </si>
+  <si>
+    <t>010-2913-7457</t>
+  </si>
+  <si>
+    <t>010-8054-7773</t>
+  </si>
+  <si>
+    <t>031-557-6767</t>
+  </si>
+  <si>
+    <t>010-9700-8733</t>
+  </si>
+  <si>
     <t>원주시 태장동 흥양로30  대흥아파트202-1202</t>
   </si>
   <si>
@@ -1072,6 +1273,78 @@
     <t>전남 나주시 금천면 신가신촌길 9-11</t>
   </si>
   <si>
+    <t>인천시 강화군 불은면 불은북로 430 2층</t>
+  </si>
+  <si>
+    <t>평창읍종부1길 211-27</t>
+  </si>
+  <si>
+    <t>경기도 김포시 대곶북로9 202호</t>
+  </si>
+  <si>
+    <t>충북 음성군 금왕읍 대금로 1499 1층 멍스펫</t>
+  </si>
+  <si>
+    <t>고창군고창읍 덕산리 966-1 캣츠비 맨안쪽</t>
+  </si>
+  <si>
+    <t>광주 북구 면앙로 14 . 1층</t>
+  </si>
+  <si>
+    <t>경남 고성군 거류면 동해로 447-15</t>
+  </si>
+  <si>
+    <t>도창동 114-5 애견</t>
+  </si>
+  <si>
+    <t>경기도 남양주시 경춘로1286번안길 27 1층</t>
+  </si>
+  <si>
+    <t>충북 청주시 율량동 1977 캣독365</t>
+  </si>
+  <si>
+    <t>경기도 이천시 창전동 167-1 오구은광빌딩 2층 고양이</t>
+  </si>
+  <si>
+    <t>고령군 운수면 잣밭길 213-45</t>
+  </si>
+  <si>
+    <t>경북 김천시 감문면 문화로 144-8번지</t>
+  </si>
+  <si>
+    <t>대구 북구 태전동246-9 1층 도그하우스</t>
+  </si>
+  <si>
+    <t>경북포항시북구청하면용산길209 ~64</t>
+  </si>
+  <si>
+    <t>경북 경주시 내남면 박달로348-59</t>
+  </si>
+  <si>
+    <t>경북포항시 북구 장량로31번길51 1층 102호 포근하개</t>
+  </si>
+  <si>
+    <t>경기도 포천시 영중면 호국로 3344</t>
+  </si>
+  <si>
+    <t>충남 서천군 마산면 삼일로 493번길 81-20</t>
+  </si>
+  <si>
+    <t>충북 옥천군 안남면 중봉 213-34</t>
+  </si>
+  <si>
+    <t>경기도 하남시 망월동 1098 203-1 이정훈강아지</t>
+  </si>
+  <si>
+    <t>경북 영천시 북안면 대경로2424</t>
+  </si>
+  <si>
+    <t>경기도 구리시 장자대로86번길 38, 새롬프라자11차 102호 (수택동)</t>
+  </si>
+  <si>
+    <t>광주광역시 서구 봉학길 38</t>
+  </si>
+  <si>
     <t>[MMS 문자 유입] 펫샵 본품 1병 무료 샘플 신청</t>
   </si>
   <si>
@@ -1097,6 +1370,12 @@
   </si>
   <si>
     <t>[문자 직통 신청] 핸드폰 문자 직접 신청 (전화번호 확인필요) / [문자 직통 신청] 전화번호 확인 필요</t>
+  </si>
+  <si>
+    <t>[명함 이미지 유입] 펫샵 본품 1병 무료 샘플 신청</t>
+  </si>
+  <si>
+    <t>[MMS 문자 유입] 펫샵 본품 1병 무료 샘플 신청 / [쿠팡 2병 유료 주문 확인]</t>
   </si>
 </sst>
 </file>
@@ -1428,7 +1707,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G90"/>
+  <dimension ref="A1:G114"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -1462,19 +1741,19 @@
         <v>7</v>
       </c>
       <c r="C2" t="s">
-        <v>96</v>
+        <v>120</v>
       </c>
       <c r="D2" t="s">
-        <v>174</v>
+        <v>218</v>
       </c>
       <c r="E2" t="s">
-        <v>263</v>
+        <v>330</v>
       </c>
       <c r="F2">
         <v>1</v>
       </c>
       <c r="G2" t="s">
-        <v>352</v>
+        <v>443</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -1485,19 +1764,19 @@
         <v>8</v>
       </c>
       <c r="C3" t="s">
-        <v>97</v>
+        <v>121</v>
       </c>
       <c r="D3" t="s">
-        <v>175</v>
+        <v>219</v>
       </c>
       <c r="E3" t="s">
-        <v>264</v>
+        <v>331</v>
       </c>
       <c r="F3">
         <v>1</v>
       </c>
       <c r="G3" t="s">
-        <v>352</v>
+        <v>443</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -1508,19 +1787,19 @@
         <v>9</v>
       </c>
       <c r="C4" t="s">
-        <v>98</v>
+        <v>122</v>
       </c>
       <c r="D4" t="s">
-        <v>176</v>
+        <v>220</v>
       </c>
       <c r="E4" t="s">
-        <v>265</v>
+        <v>332</v>
       </c>
       <c r="F4">
         <v>1</v>
       </c>
       <c r="G4" t="s">
-        <v>352</v>
+        <v>443</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -1531,19 +1810,19 @@
         <v>10</v>
       </c>
       <c r="C5" t="s">
-        <v>99</v>
+        <v>123</v>
       </c>
       <c r="D5" t="s">
-        <v>177</v>
+        <v>221</v>
       </c>
       <c r="E5" t="s">
-        <v>266</v>
+        <v>333</v>
       </c>
       <c r="F5">
         <v>1</v>
       </c>
       <c r="G5" t="s">
-        <v>352</v>
+        <v>443</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -1554,19 +1833,19 @@
         <v>11</v>
       </c>
       <c r="C6" t="s">
-        <v>100</v>
+        <v>124</v>
       </c>
       <c r="D6" t="s">
-        <v>178</v>
+        <v>222</v>
       </c>
       <c r="E6" t="s">
-        <v>267</v>
+        <v>334</v>
       </c>
       <c r="F6">
         <v>1</v>
       </c>
       <c r="G6" t="s">
-        <v>352</v>
+        <v>443</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -1577,19 +1856,19 @@
         <v>12</v>
       </c>
       <c r="C7" t="s">
-        <v>101</v>
+        <v>125</v>
       </c>
       <c r="D7" t="s">
-        <v>179</v>
+        <v>223</v>
       </c>
       <c r="E7" t="s">
-        <v>268</v>
+        <v>335</v>
       </c>
       <c r="F7">
         <v>1</v>
       </c>
       <c r="G7" t="s">
-        <v>352</v>
+        <v>443</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -1600,19 +1879,19 @@
         <v>13</v>
       </c>
       <c r="C8" t="s">
-        <v>102</v>
+        <v>126</v>
       </c>
       <c r="D8" t="s">
-        <v>180</v>
+        <v>224</v>
       </c>
       <c r="E8" t="s">
-        <v>269</v>
+        <v>336</v>
       </c>
       <c r="F8">
         <v>1</v>
       </c>
       <c r="G8" t="s">
-        <v>352</v>
+        <v>443</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -1623,19 +1902,19 @@
         <v>14</v>
       </c>
       <c r="C9" t="s">
-        <v>103</v>
+        <v>127</v>
       </c>
       <c r="D9" t="s">
-        <v>181</v>
+        <v>225</v>
       </c>
       <c r="E9" t="s">
-        <v>270</v>
+        <v>337</v>
       </c>
       <c r="F9">
         <v>1</v>
       </c>
       <c r="G9" t="s">
-        <v>352</v>
+        <v>443</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -1646,19 +1925,19 @@
         <v>15</v>
       </c>
       <c r="C10" t="s">
-        <v>104</v>
+        <v>128</v>
       </c>
       <c r="D10" t="s">
-        <v>182</v>
+        <v>226</v>
       </c>
       <c r="E10" t="s">
-        <v>271</v>
+        <v>338</v>
       </c>
       <c r="F10">
         <v>1</v>
       </c>
       <c r="G10" t="s">
-        <v>352</v>
+        <v>443</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -1669,19 +1948,19 @@
         <v>16</v>
       </c>
       <c r="C11" t="s">
-        <v>105</v>
+        <v>129</v>
       </c>
       <c r="D11" t="s">
-        <v>183</v>
+        <v>227</v>
       </c>
       <c r="E11" t="s">
-        <v>272</v>
+        <v>339</v>
       </c>
       <c r="F11">
         <v>1</v>
       </c>
       <c r="G11" t="s">
-        <v>352</v>
+        <v>443</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -1692,19 +1971,19 @@
         <v>17</v>
       </c>
       <c r="C12" t="s">
-        <v>106</v>
+        <v>130</v>
       </c>
       <c r="D12" t="s">
-        <v>184</v>
+        <v>228</v>
       </c>
       <c r="E12" t="s">
-        <v>273</v>
+        <v>340</v>
       </c>
       <c r="F12">
         <v>1</v>
       </c>
       <c r="G12" t="s">
-        <v>352</v>
+        <v>443</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -1715,19 +1994,19 @@
         <v>18</v>
       </c>
       <c r="C13" t="s">
-        <v>107</v>
+        <v>131</v>
       </c>
       <c r="D13" t="s">
-        <v>185</v>
+        <v>229</v>
       </c>
       <c r="E13" t="s">
-        <v>274</v>
+        <v>341</v>
       </c>
       <c r="F13">
         <v>1</v>
       </c>
       <c r="G13" t="s">
-        <v>352</v>
+        <v>443</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -1738,19 +2017,19 @@
         <v>19</v>
       </c>
       <c r="C14" t="s">
-        <v>108</v>
+        <v>132</v>
       </c>
       <c r="D14" t="s">
-        <v>186</v>
+        <v>230</v>
       </c>
       <c r="E14" t="s">
-        <v>275</v>
+        <v>342</v>
       </c>
       <c r="F14">
         <v>1</v>
       </c>
       <c r="G14" t="s">
-        <v>352</v>
+        <v>443</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -1761,19 +2040,19 @@
         <v>20</v>
       </c>
       <c r="C15" t="s">
-        <v>109</v>
+        <v>133</v>
       </c>
       <c r="D15" t="s">
-        <v>187</v>
+        <v>231</v>
       </c>
       <c r="E15" t="s">
-        <v>276</v>
+        <v>343</v>
       </c>
       <c r="F15">
         <v>1</v>
       </c>
       <c r="G15" t="s">
-        <v>352</v>
+        <v>443</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -1784,19 +2063,19 @@
         <v>21</v>
       </c>
       <c r="C16" t="s">
-        <v>110</v>
+        <v>134</v>
       </c>
       <c r="D16" t="s">
-        <v>188</v>
+        <v>232</v>
       </c>
       <c r="E16" t="s">
-        <v>277</v>
+        <v>344</v>
       </c>
       <c r="F16">
         <v>1</v>
       </c>
       <c r="G16" t="s">
-        <v>353</v>
+        <v>444</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -1807,19 +2086,19 @@
         <v>22</v>
       </c>
       <c r="C17" t="s">
-        <v>111</v>
+        <v>135</v>
       </c>
       <c r="D17" t="s">
-        <v>189</v>
+        <v>233</v>
       </c>
       <c r="E17" t="s">
-        <v>278</v>
+        <v>345</v>
       </c>
       <c r="F17">
         <v>1</v>
       </c>
       <c r="G17" t="s">
-        <v>352</v>
+        <v>443</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -1830,19 +2109,19 @@
         <v>23</v>
       </c>
       <c r="C18" t="s">
-        <v>112</v>
+        <v>136</v>
       </c>
       <c r="D18" t="s">
-        <v>190</v>
+        <v>234</v>
       </c>
       <c r="E18" t="s">
-        <v>279</v>
+        <v>346</v>
       </c>
       <c r="F18">
         <v>1</v>
       </c>
       <c r="G18" t="s">
-        <v>352</v>
+        <v>443</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -1853,19 +2132,19 @@
         <v>24</v>
       </c>
       <c r="C19" t="s">
-        <v>113</v>
+        <v>137</v>
       </c>
       <c r="D19" t="s">
-        <v>191</v>
+        <v>235</v>
       </c>
       <c r="E19" t="s">
-        <v>280</v>
+        <v>347</v>
       </c>
       <c r="F19">
         <v>1</v>
       </c>
       <c r="G19" t="s">
-        <v>352</v>
+        <v>443</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -1876,19 +2155,19 @@
         <v>25</v>
       </c>
       <c r="C20" t="s">
-        <v>114</v>
+        <v>138</v>
       </c>
       <c r="D20" t="s">
-        <v>192</v>
+        <v>236</v>
       </c>
       <c r="E20" t="s">
-        <v>281</v>
+        <v>348</v>
       </c>
       <c r="F20">
         <v>1</v>
       </c>
       <c r="G20" t="s">
-        <v>352</v>
+        <v>443</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -1899,19 +2178,19 @@
         <v>26</v>
       </c>
       <c r="C21" t="s">
-        <v>115</v>
+        <v>139</v>
       </c>
       <c r="D21" t="s">
-        <v>193</v>
+        <v>237</v>
       </c>
       <c r="E21" t="s">
-        <v>282</v>
+        <v>349</v>
       </c>
       <c r="F21">
         <v>1</v>
       </c>
       <c r="G21" t="s">
-        <v>352</v>
+        <v>443</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -1922,19 +2201,19 @@
         <v>27</v>
       </c>
       <c r="C22" t="s">
-        <v>116</v>
+        <v>140</v>
       </c>
       <c r="D22" t="s">
-        <v>194</v>
+        <v>238</v>
       </c>
       <c r="E22" t="s">
-        <v>283</v>
+        <v>350</v>
       </c>
       <c r="F22">
         <v>1</v>
       </c>
       <c r="G22" t="s">
-        <v>352</v>
+        <v>443</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -1945,19 +2224,19 @@
         <v>28</v>
       </c>
       <c r="C23" t="s">
-        <v>117</v>
+        <v>141</v>
       </c>
       <c r="D23" t="s">
-        <v>195</v>
+        <v>239</v>
       </c>
       <c r="E23" t="s">
-        <v>284</v>
+        <v>351</v>
       </c>
       <c r="F23">
         <v>1</v>
       </c>
       <c r="G23" t="s">
-        <v>352</v>
+        <v>443</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -1968,19 +2247,19 @@
         <v>29</v>
       </c>
       <c r="C24" t="s">
-        <v>118</v>
+        <v>142</v>
       </c>
       <c r="D24" t="s">
-        <v>196</v>
+        <v>240</v>
       </c>
       <c r="E24" t="s">
-        <v>285</v>
+        <v>352</v>
       </c>
       <c r="F24">
         <v>1</v>
       </c>
       <c r="G24" t="s">
-        <v>352</v>
+        <v>443</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -1991,19 +2270,19 @@
         <v>30</v>
       </c>
       <c r="C25" t="s">
-        <v>119</v>
+        <v>143</v>
       </c>
       <c r="D25" t="s">
-        <v>197</v>
+        <v>241</v>
       </c>
       <c r="E25" t="s">
-        <v>286</v>
+        <v>353</v>
       </c>
       <c r="F25">
         <v>1</v>
       </c>
       <c r="G25" t="s">
-        <v>352</v>
+        <v>443</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -2014,19 +2293,19 @@
         <v>31</v>
       </c>
       <c r="C26" t="s">
-        <v>120</v>
+        <v>144</v>
       </c>
       <c r="D26" t="s">
-        <v>198</v>
+        <v>242</v>
       </c>
       <c r="E26" t="s">
-        <v>287</v>
+        <v>354</v>
       </c>
       <c r="F26">
         <v>1</v>
       </c>
       <c r="G26" t="s">
-        <v>352</v>
+        <v>443</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -2037,19 +2316,19 @@
         <v>32</v>
       </c>
       <c r="C27" t="s">
-        <v>121</v>
+        <v>145</v>
       </c>
       <c r="D27" t="s">
-        <v>199</v>
+        <v>243</v>
       </c>
       <c r="E27" t="s">
-        <v>288</v>
+        <v>355</v>
       </c>
       <c r="F27">
         <v>1</v>
       </c>
       <c r="G27" t="s">
-        <v>352</v>
+        <v>443</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -2060,19 +2339,19 @@
         <v>33</v>
       </c>
       <c r="C28" t="s">
-        <v>122</v>
+        <v>146</v>
       </c>
       <c r="D28" t="s">
-        <v>200</v>
+        <v>244</v>
       </c>
       <c r="E28" t="s">
-        <v>289</v>
+        <v>356</v>
       </c>
       <c r="F28">
         <v>1</v>
       </c>
       <c r="G28" t="s">
-        <v>352</v>
+        <v>443</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -2083,19 +2362,19 @@
         <v>34</v>
       </c>
       <c r="C29" t="s">
-        <v>123</v>
+        <v>147</v>
       </c>
       <c r="D29" t="s">
-        <v>201</v>
+        <v>245</v>
       </c>
       <c r="E29" t="s">
-        <v>290</v>
+        <v>357</v>
       </c>
       <c r="F29">
         <v>1</v>
       </c>
       <c r="G29" t="s">
-        <v>352</v>
+        <v>443</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -2106,19 +2385,19 @@
         <v>35</v>
       </c>
       <c r="C30" t="s">
-        <v>124</v>
+        <v>148</v>
       </c>
       <c r="D30" t="s">
-        <v>202</v>
+        <v>246</v>
       </c>
       <c r="E30" t="s">
-        <v>291</v>
+        <v>358</v>
       </c>
       <c r="F30">
         <v>1</v>
       </c>
       <c r="G30" t="s">
-        <v>352</v>
+        <v>443</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -2129,19 +2408,19 @@
         <v>36</v>
       </c>
       <c r="C31" t="s">
-        <v>125</v>
+        <v>149</v>
       </c>
       <c r="D31" t="s">
-        <v>203</v>
+        <v>247</v>
       </c>
       <c r="E31" t="s">
-        <v>292</v>
+        <v>359</v>
       </c>
       <c r="F31">
         <v>1</v>
       </c>
       <c r="G31" t="s">
-        <v>352</v>
+        <v>443</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -2152,19 +2431,19 @@
         <v>37</v>
       </c>
       <c r="C32" t="s">
-        <v>126</v>
+        <v>150</v>
       </c>
       <c r="D32" t="s">
-        <v>204</v>
+        <v>248</v>
       </c>
       <c r="E32" t="s">
-        <v>293</v>
+        <v>360</v>
       </c>
       <c r="F32">
         <v>1</v>
       </c>
       <c r="G32" t="s">
-        <v>352</v>
+        <v>443</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -2175,19 +2454,19 @@
         <v>38</v>
       </c>
       <c r="C33" t="s">
-        <v>127</v>
+        <v>151</v>
       </c>
       <c r="D33" t="s">
-        <v>205</v>
+        <v>249</v>
       </c>
       <c r="E33" t="s">
-        <v>294</v>
+        <v>361</v>
       </c>
       <c r="F33">
         <v>1</v>
       </c>
       <c r="G33" t="s">
-        <v>352</v>
+        <v>443</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -2198,19 +2477,19 @@
         <v>39</v>
       </c>
       <c r="C34" t="s">
-        <v>128</v>
+        <v>152</v>
       </c>
       <c r="D34" t="s">
-        <v>206</v>
+        <v>250</v>
       </c>
       <c r="E34" t="s">
-        <v>295</v>
+        <v>362</v>
       </c>
       <c r="F34">
         <v>1</v>
       </c>
       <c r="G34" t="s">
-        <v>352</v>
+        <v>443</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -2221,19 +2500,19 @@
         <v>40</v>
       </c>
       <c r="C35" t="s">
-        <v>129</v>
+        <v>153</v>
       </c>
       <c r="D35" t="s">
-        <v>207</v>
+        <v>251</v>
       </c>
       <c r="E35" t="s">
-        <v>296</v>
+        <v>363</v>
       </c>
       <c r="F35">
         <v>1</v>
       </c>
       <c r="G35" t="s">
-        <v>352</v>
+        <v>443</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -2244,19 +2523,19 @@
         <v>41</v>
       </c>
       <c r="C36" t="s">
-        <v>130</v>
+        <v>154</v>
       </c>
       <c r="D36" t="s">
-        <v>208</v>
+        <v>252</v>
       </c>
       <c r="E36" t="s">
-        <v>297</v>
+        <v>364</v>
       </c>
       <c r="F36">
         <v>1</v>
       </c>
       <c r="G36" t="s">
-        <v>352</v>
+        <v>443</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -2267,19 +2546,19 @@
         <v>42</v>
       </c>
       <c r="C37" t="s">
-        <v>131</v>
+        <v>155</v>
       </c>
       <c r="D37" t="s">
-        <v>209</v>
+        <v>253</v>
       </c>
       <c r="E37" t="s">
-        <v>298</v>
+        <v>365</v>
       </c>
       <c r="F37">
         <v>1</v>
       </c>
       <c r="G37" t="s">
-        <v>352</v>
+        <v>443</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -2290,19 +2569,19 @@
         <v>43</v>
       </c>
       <c r="C38" t="s">
-        <v>132</v>
+        <v>156</v>
       </c>
       <c r="D38" t="s">
-        <v>210</v>
+        <v>254</v>
       </c>
       <c r="E38" t="s">
-        <v>299</v>
+        <v>366</v>
       </c>
       <c r="F38">
         <v>1</v>
       </c>
       <c r="G38" t="s">
-        <v>352</v>
+        <v>443</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -2313,19 +2592,19 @@
         <v>44</v>
       </c>
       <c r="C39" t="s">
-        <v>133</v>
+        <v>157</v>
       </c>
       <c r="D39" t="s">
-        <v>211</v>
+        <v>255</v>
       </c>
       <c r="E39" t="s">
-        <v>300</v>
+        <v>367</v>
       </c>
       <c r="F39">
         <v>1</v>
       </c>
       <c r="G39" t="s">
-        <v>352</v>
+        <v>443</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -2336,19 +2615,19 @@
         <v>45</v>
       </c>
       <c r="C40" t="s">
-        <v>134</v>
+        <v>158</v>
       </c>
       <c r="D40" t="s">
-        <v>212</v>
+        <v>256</v>
       </c>
       <c r="E40" t="s">
-        <v>301</v>
+        <v>368</v>
       </c>
       <c r="F40">
         <v>1</v>
       </c>
       <c r="G40" t="s">
-        <v>354</v>
+        <v>445</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -2359,19 +2638,19 @@
         <v>46</v>
       </c>
       <c r="C41" t="s">
-        <v>135</v>
+        <v>159</v>
       </c>
       <c r="D41" t="s">
-        <v>213</v>
+        <v>257</v>
       </c>
       <c r="E41" t="s">
-        <v>302</v>
+        <v>369</v>
       </c>
       <c r="F41">
         <v>1</v>
       </c>
       <c r="G41" t="s">
-        <v>353</v>
+        <v>444</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -2382,19 +2661,19 @@
         <v>47</v>
       </c>
       <c r="C42" t="s">
-        <v>136</v>
+        <v>160</v>
       </c>
       <c r="D42" t="s">
-        <v>214</v>
+        <v>258</v>
       </c>
       <c r="E42" t="s">
-        <v>303</v>
+        <v>370</v>
       </c>
       <c r="F42">
         <v>1</v>
       </c>
       <c r="G42" t="s">
-        <v>352</v>
+        <v>443</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -2405,19 +2684,19 @@
         <v>48</v>
       </c>
       <c r="C43" t="s">
-        <v>137</v>
+        <v>161</v>
       </c>
       <c r="D43" t="s">
-        <v>215</v>
+        <v>259</v>
       </c>
       <c r="E43" t="s">
-        <v>304</v>
+        <v>371</v>
       </c>
       <c r="F43">
         <v>1</v>
       </c>
       <c r="G43" t="s">
-        <v>352</v>
+        <v>443</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -2428,19 +2707,19 @@
         <v>49</v>
       </c>
       <c r="C44" t="s">
-        <v>138</v>
+        <v>162</v>
       </c>
       <c r="D44" t="s">
-        <v>216</v>
+        <v>260</v>
       </c>
       <c r="E44" t="s">
-        <v>305</v>
+        <v>372</v>
       </c>
       <c r="F44">
         <v>1</v>
       </c>
       <c r="G44" t="s">
-        <v>352</v>
+        <v>443</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -2451,19 +2730,19 @@
         <v>50</v>
       </c>
       <c r="C45" t="s">
-        <v>139</v>
+        <v>163</v>
       </c>
       <c r="D45" t="s">
-        <v>217</v>
+        <v>261</v>
       </c>
       <c r="E45" t="s">
-        <v>306</v>
+        <v>373</v>
       </c>
       <c r="F45">
         <v>1</v>
       </c>
       <c r="G45" t="s">
-        <v>352</v>
+        <v>443</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -2474,19 +2753,19 @@
         <v>51</v>
       </c>
       <c r="C46" t="s">
-        <v>140</v>
+        <v>164</v>
       </c>
       <c r="D46" t="s">
-        <v>218</v>
+        <v>262</v>
       </c>
       <c r="E46" t="s">
-        <v>307</v>
+        <v>374</v>
       </c>
       <c r="F46">
         <v>1</v>
       </c>
       <c r="G46" t="s">
-        <v>352</v>
+        <v>443</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -2497,19 +2776,19 @@
         <v>52</v>
       </c>
       <c r="C47" t="s">
-        <v>141</v>
+        <v>165</v>
       </c>
       <c r="D47" t="s">
-        <v>219</v>
+        <v>263</v>
       </c>
       <c r="E47" t="s">
-        <v>308</v>
+        <v>375</v>
       </c>
       <c r="F47">
         <v>1</v>
       </c>
       <c r="G47" t="s">
-        <v>352</v>
+        <v>443</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -2520,19 +2799,19 @@
         <v>53</v>
       </c>
       <c r="C48" t="s">
-        <v>142</v>
+        <v>166</v>
       </c>
       <c r="D48" t="s">
-        <v>220</v>
+        <v>264</v>
       </c>
       <c r="E48" t="s">
-        <v>309</v>
+        <v>376</v>
       </c>
       <c r="F48">
         <v>1</v>
       </c>
       <c r="G48" t="s">
-        <v>352</v>
+        <v>443</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -2543,19 +2822,19 @@
         <v>54</v>
       </c>
       <c r="C49" t="s">
-        <v>143</v>
+        <v>167</v>
       </c>
       <c r="D49" t="s">
-        <v>221</v>
+        <v>265</v>
       </c>
       <c r="E49" t="s">
-        <v>310</v>
+        <v>377</v>
       </c>
       <c r="F49">
         <v>1</v>
       </c>
       <c r="G49" t="s">
-        <v>352</v>
+        <v>443</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -2566,19 +2845,19 @@
         <v>55</v>
       </c>
       <c r="C50" t="s">
-        <v>144</v>
+        <v>168</v>
       </c>
       <c r="D50" t="s">
-        <v>222</v>
+        <v>266</v>
       </c>
       <c r="E50" t="s">
-        <v>311</v>
+        <v>378</v>
       </c>
       <c r="F50">
         <v>1</v>
       </c>
       <c r="G50" t="s">
-        <v>352</v>
+        <v>443</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -2589,19 +2868,19 @@
         <v>56</v>
       </c>
       <c r="C51" t="s">
-        <v>145</v>
+        <v>169</v>
       </c>
       <c r="D51" t="s">
-        <v>223</v>
+        <v>267</v>
       </c>
       <c r="E51" t="s">
-        <v>312</v>
+        <v>379</v>
       </c>
       <c r="F51">
         <v>1</v>
       </c>
       <c r="G51" t="s">
-        <v>352</v>
+        <v>443</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -2612,19 +2891,19 @@
         <v>57</v>
       </c>
       <c r="C52" t="s">
-        <v>146</v>
+        <v>170</v>
       </c>
       <c r="D52" t="s">
-        <v>224</v>
+        <v>268</v>
       </c>
       <c r="E52" t="s">
-        <v>313</v>
+        <v>380</v>
       </c>
       <c r="F52">
         <v>1</v>
       </c>
       <c r="G52" t="s">
-        <v>352</v>
+        <v>443</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -2635,19 +2914,19 @@
         <v>58</v>
       </c>
       <c r="C53" t="s">
-        <v>147</v>
+        <v>171</v>
       </c>
       <c r="D53" t="s">
-        <v>225</v>
+        <v>269</v>
       </c>
       <c r="E53" t="s">
-        <v>314</v>
+        <v>381</v>
       </c>
       <c r="F53">
         <v>1</v>
       </c>
       <c r="G53" t="s">
-        <v>352</v>
+        <v>443</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -2658,19 +2937,19 @@
         <v>59</v>
       </c>
       <c r="C54" t="s">
-        <v>148</v>
+        <v>172</v>
       </c>
       <c r="D54" t="s">
-        <v>226</v>
+        <v>270</v>
       </c>
       <c r="E54" t="s">
-        <v>315</v>
+        <v>382</v>
       </c>
       <c r="F54">
         <v>1</v>
       </c>
       <c r="G54" t="s">
-        <v>352</v>
+        <v>443</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -2681,19 +2960,19 @@
         <v>60</v>
       </c>
       <c r="C55" t="s">
-        <v>149</v>
+        <v>173</v>
       </c>
       <c r="D55" t="s">
-        <v>227</v>
+        <v>271</v>
       </c>
       <c r="E55" t="s">
-        <v>316</v>
+        <v>383</v>
       </c>
       <c r="F55">
         <v>1</v>
       </c>
       <c r="G55" t="s">
-        <v>352</v>
+        <v>443</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -2704,19 +2983,19 @@
         <v>61</v>
       </c>
       <c r="C56" t="s">
-        <v>150</v>
+        <v>174</v>
       </c>
       <c r="D56" t="s">
-        <v>228</v>
+        <v>272</v>
       </c>
       <c r="E56" t="s">
-        <v>317</v>
+        <v>384</v>
       </c>
       <c r="F56">
         <v>1</v>
       </c>
       <c r="G56" t="s">
-        <v>352</v>
+        <v>443</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -2727,19 +3006,19 @@
         <v>62</v>
       </c>
       <c r="C57" t="s">
-        <v>151</v>
+        <v>175</v>
       </c>
       <c r="D57" t="s">
-        <v>229</v>
+        <v>273</v>
       </c>
       <c r="E57" t="s">
-        <v>318</v>
+        <v>385</v>
       </c>
       <c r="F57">
         <v>1</v>
       </c>
       <c r="G57" t="s">
-        <v>355</v>
+        <v>446</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -2750,19 +3029,19 @@
         <v>63</v>
       </c>
       <c r="C58" t="s">
-        <v>152</v>
+        <v>176</v>
       </c>
       <c r="D58" t="s">
-        <v>230</v>
+        <v>274</v>
       </c>
       <c r="E58" t="s">
-        <v>319</v>
+        <v>386</v>
       </c>
       <c r="F58">
         <v>1</v>
       </c>
       <c r="G58" t="s">
-        <v>352</v>
+        <v>443</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -2773,19 +3052,19 @@
         <v>64</v>
       </c>
       <c r="C59" t="s">
-        <v>153</v>
+        <v>177</v>
       </c>
       <c r="D59" t="s">
-        <v>231</v>
+        <v>275</v>
       </c>
       <c r="E59" t="s">
-        <v>320</v>
+        <v>387</v>
       </c>
       <c r="F59">
         <v>1</v>
       </c>
       <c r="G59" t="s">
-        <v>352</v>
+        <v>443</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -2796,19 +3075,19 @@
         <v>65</v>
       </c>
       <c r="C60" t="s">
-        <v>154</v>
+        <v>178</v>
       </c>
       <c r="D60" t="s">
-        <v>232</v>
+        <v>276</v>
       </c>
       <c r="E60" t="s">
-        <v>321</v>
+        <v>388</v>
       </c>
       <c r="F60">
         <v>1</v>
       </c>
       <c r="G60" t="s">
-        <v>352</v>
+        <v>443</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -2819,19 +3098,19 @@
         <v>66</v>
       </c>
       <c r="C61" t="s">
-        <v>155</v>
+        <v>179</v>
       </c>
       <c r="D61" t="s">
-        <v>233</v>
+        <v>277</v>
       </c>
       <c r="E61" t="s">
-        <v>322</v>
+        <v>389</v>
       </c>
       <c r="F61">
         <v>1</v>
       </c>
       <c r="G61" t="s">
-        <v>352</v>
+        <v>443</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -2842,19 +3121,19 @@
         <v>67</v>
       </c>
       <c r="C62" t="s">
-        <v>156</v>
+        <v>180</v>
       </c>
       <c r="D62" t="s">
-        <v>234</v>
+        <v>278</v>
       </c>
       <c r="E62" t="s">
-        <v>323</v>
+        <v>390</v>
       </c>
       <c r="F62">
         <v>1</v>
       </c>
       <c r="G62" t="s">
-        <v>352</v>
+        <v>443</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -2865,19 +3144,19 @@
         <v>68</v>
       </c>
       <c r="C63" t="s">
-        <v>157</v>
+        <v>181</v>
       </c>
       <c r="D63" t="s">
-        <v>235</v>
+        <v>279</v>
       </c>
       <c r="E63" t="s">
-        <v>324</v>
+        <v>391</v>
       </c>
       <c r="F63">
         <v>1</v>
       </c>
       <c r="G63" t="s">
-        <v>352</v>
+        <v>443</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -2888,19 +3167,19 @@
         <v>69</v>
       </c>
       <c r="C64" t="s">
-        <v>158</v>
+        <v>182</v>
       </c>
       <c r="D64" t="s">
-        <v>236</v>
+        <v>280</v>
       </c>
       <c r="E64" t="s">
-        <v>325</v>
+        <v>392</v>
       </c>
       <c r="F64">
         <v>1</v>
       </c>
       <c r="G64" t="s">
-        <v>352</v>
+        <v>443</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -2911,19 +3190,19 @@
         <v>70</v>
       </c>
       <c r="C65" t="s">
-        <v>159</v>
+        <v>183</v>
       </c>
       <c r="D65" t="s">
-        <v>237</v>
+        <v>281</v>
       </c>
       <c r="E65" t="s">
-        <v>326</v>
+        <v>393</v>
       </c>
       <c r="F65">
         <v>3</v>
       </c>
       <c r="G65" t="s">
-        <v>356</v>
+        <v>447</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -2934,19 +3213,19 @@
         <v>71</v>
       </c>
       <c r="C66" t="s">
-        <v>160</v>
+        <v>184</v>
       </c>
       <c r="D66" t="s">
-        <v>238</v>
+        <v>282</v>
       </c>
       <c r="E66" t="s">
-        <v>327</v>
+        <v>394</v>
       </c>
       <c r="F66">
         <v>1</v>
       </c>
       <c r="G66" t="s">
-        <v>352</v>
+        <v>443</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -2957,19 +3236,19 @@
         <v>72</v>
       </c>
       <c r="C67" t="s">
-        <v>161</v>
+        <v>185</v>
       </c>
       <c r="D67" t="s">
-        <v>239</v>
+        <v>283</v>
       </c>
       <c r="E67" t="s">
-        <v>328</v>
+        <v>395</v>
       </c>
       <c r="F67">
         <v>1</v>
       </c>
       <c r="G67" t="s">
-        <v>352</v>
+        <v>443</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -2980,19 +3259,19 @@
         <v>73</v>
       </c>
       <c r="C68" t="s">
-        <v>162</v>
+        <v>186</v>
       </c>
       <c r="D68" t="s">
-        <v>240</v>
+        <v>284</v>
       </c>
       <c r="E68" t="s">
-        <v>329</v>
+        <v>396</v>
       </c>
       <c r="F68">
         <v>1</v>
       </c>
       <c r="G68" t="s">
-        <v>352</v>
+        <v>443</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -3003,19 +3282,19 @@
         <v>74</v>
       </c>
       <c r="C69" t="s">
-        <v>163</v>
+        <v>187</v>
       </c>
       <c r="D69" t="s">
-        <v>241</v>
+        <v>285</v>
       </c>
       <c r="E69" t="s">
-        <v>330</v>
+        <v>397</v>
       </c>
       <c r="F69">
         <v>1</v>
       </c>
       <c r="G69" t="s">
-        <v>352</v>
+        <v>443</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -3026,19 +3305,19 @@
         <v>75</v>
       </c>
       <c r="C70" t="s">
-        <v>164</v>
+        <v>188</v>
       </c>
       <c r="D70" t="s">
-        <v>242</v>
+        <v>286</v>
       </c>
       <c r="E70" t="s">
-        <v>331</v>
+        <v>398</v>
       </c>
       <c r="F70">
         <v>1</v>
       </c>
       <c r="G70" t="s">
-        <v>352</v>
+        <v>443</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -3049,19 +3328,19 @@
         <v>76</v>
       </c>
       <c r="C71" t="s">
-        <v>165</v>
+        <v>189</v>
       </c>
       <c r="D71" t="s">
-        <v>243</v>
+        <v>287</v>
       </c>
       <c r="E71" t="s">
-        <v>332</v>
+        <v>399</v>
       </c>
       <c r="F71">
         <v>1</v>
       </c>
       <c r="G71" t="s">
-        <v>352</v>
+        <v>443</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -3072,19 +3351,19 @@
         <v>77</v>
       </c>
       <c r="C72" t="s">
-        <v>166</v>
+        <v>190</v>
       </c>
       <c r="D72" t="s">
-        <v>244</v>
+        <v>288</v>
       </c>
       <c r="E72" t="s">
-        <v>333</v>
+        <v>400</v>
       </c>
       <c r="F72">
         <v>1</v>
       </c>
       <c r="G72" t="s">
-        <v>352</v>
+        <v>443</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -3095,19 +3374,19 @@
         <v>78</v>
       </c>
       <c r="C73" t="s">
-        <v>167</v>
+        <v>191</v>
       </c>
       <c r="D73" t="s">
-        <v>245</v>
+        <v>289</v>
       </c>
       <c r="E73" t="s">
-        <v>334</v>
+        <v>401</v>
       </c>
       <c r="F73">
         <v>1</v>
       </c>
       <c r="G73" t="s">
-        <v>352</v>
+        <v>443</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -3118,19 +3397,19 @@
         <v>79</v>
       </c>
       <c r="C74" t="s">
-        <v>168</v>
+        <v>192</v>
       </c>
       <c r="D74" t="s">
-        <v>246</v>
+        <v>290</v>
       </c>
       <c r="E74" t="s">
-        <v>335</v>
+        <v>402</v>
       </c>
       <c r="F74">
         <v>1</v>
       </c>
       <c r="G74" t="s">
-        <v>352</v>
+        <v>443</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -3141,19 +3420,19 @@
         <v>80</v>
       </c>
       <c r="C75" t="s">
-        <v>169</v>
+        <v>193</v>
       </c>
       <c r="D75" t="s">
-        <v>247</v>
+        <v>291</v>
       </c>
       <c r="E75" t="s">
-        <v>336</v>
+        <v>403</v>
       </c>
       <c r="F75">
         <v>1</v>
       </c>
       <c r="G75" t="s">
-        <v>352</v>
+        <v>443</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -3164,19 +3443,19 @@
         <v>81</v>
       </c>
       <c r="C76" t="s">
-        <v>170</v>
+        <v>194</v>
       </c>
       <c r="D76" t="s">
-        <v>248</v>
+        <v>292</v>
       </c>
       <c r="E76" t="s">
-        <v>337</v>
+        <v>404</v>
       </c>
       <c r="F76">
         <v>1</v>
       </c>
       <c r="G76" t="s">
-        <v>352</v>
+        <v>443</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -3190,16 +3469,16 @@
         <v>82</v>
       </c>
       <c r="D77" t="s">
-        <v>249</v>
+        <v>293</v>
       </c>
       <c r="E77" t="s">
-        <v>338</v>
+        <v>405</v>
       </c>
       <c r="F77">
         <v>1</v>
       </c>
       <c r="G77" t="s">
-        <v>357</v>
+        <v>448</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -3213,16 +3492,16 @@
         <v>83</v>
       </c>
       <c r="D78" t="s">
-        <v>250</v>
+        <v>294</v>
       </c>
       <c r="E78" t="s">
-        <v>339</v>
+        <v>406</v>
       </c>
       <c r="F78">
         <v>1</v>
       </c>
       <c r="G78" t="s">
-        <v>357</v>
+        <v>448</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -3236,16 +3515,16 @@
         <v>84</v>
       </c>
       <c r="D79" t="s">
-        <v>251</v>
+        <v>295</v>
       </c>
       <c r="E79" t="s">
-        <v>340</v>
+        <v>407</v>
       </c>
       <c r="F79">
         <v>1</v>
       </c>
       <c r="G79" t="s">
-        <v>357</v>
+        <v>448</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -3259,16 +3538,16 @@
         <v>85</v>
       </c>
       <c r="D80" t="s">
-        <v>252</v>
+        <v>296</v>
       </c>
       <c r="E80" t="s">
-        <v>341</v>
+        <v>408</v>
       </c>
       <c r="F80">
         <v>1</v>
       </c>
       <c r="G80" t="s">
-        <v>357</v>
+        <v>448</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -3282,16 +3561,16 @@
         <v>86</v>
       </c>
       <c r="D81" t="s">
-        <v>253</v>
+        <v>297</v>
       </c>
       <c r="E81" t="s">
-        <v>342</v>
+        <v>409</v>
       </c>
       <c r="F81">
         <v>1</v>
       </c>
       <c r="G81" t="s">
-        <v>358</v>
+        <v>449</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -3305,16 +3584,16 @@
         <v>87</v>
       </c>
       <c r="D82" t="s">
-        <v>254</v>
+        <v>298</v>
       </c>
       <c r="E82" t="s">
-        <v>343</v>
+        <v>410</v>
       </c>
       <c r="F82">
         <v>1</v>
       </c>
       <c r="G82" t="s">
-        <v>359</v>
+        <v>450</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -3328,16 +3607,16 @@
         <v>88</v>
       </c>
       <c r="D83" t="s">
-        <v>255</v>
+        <v>299</v>
       </c>
       <c r="E83" t="s">
-        <v>344</v>
+        <v>411</v>
       </c>
       <c r="F83">
         <v>1</v>
       </c>
       <c r="G83" t="s">
-        <v>357</v>
+        <v>448</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -3351,16 +3630,16 @@
         <v>89</v>
       </c>
       <c r="D84" t="s">
-        <v>256</v>
+        <v>300</v>
       </c>
       <c r="E84" t="s">
-        <v>345</v>
+        <v>412</v>
       </c>
       <c r="F84">
         <v>1</v>
       </c>
       <c r="G84" t="s">
-        <v>357</v>
+        <v>448</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -3374,16 +3653,16 @@
         <v>90</v>
       </c>
       <c r="D85" t="s">
-        <v>257</v>
+        <v>301</v>
       </c>
       <c r="E85" t="s">
-        <v>346</v>
+        <v>413</v>
       </c>
       <c r="F85">
         <v>1</v>
       </c>
       <c r="G85" t="s">
-        <v>357</v>
+        <v>448</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -3394,19 +3673,19 @@
         <v>91</v>
       </c>
       <c r="C86" t="s">
-        <v>171</v>
+        <v>195</v>
       </c>
       <c r="D86" t="s">
-        <v>258</v>
+        <v>302</v>
       </c>
       <c r="E86" t="s">
-        <v>347</v>
+        <v>414</v>
       </c>
       <c r="F86">
         <v>1</v>
       </c>
       <c r="G86" t="s">
-        <v>357</v>
+        <v>448</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -3420,16 +3699,16 @@
         <v>92</v>
       </c>
       <c r="D87" t="s">
-        <v>259</v>
+        <v>303</v>
       </c>
       <c r="E87" t="s">
-        <v>348</v>
+        <v>415</v>
       </c>
       <c r="F87">
         <v>1</v>
       </c>
       <c r="G87" t="s">
-        <v>360</v>
+        <v>451</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -3443,16 +3722,16 @@
         <v>93</v>
       </c>
       <c r="D88" t="s">
-        <v>260</v>
+        <v>304</v>
       </c>
       <c r="E88" t="s">
-        <v>349</v>
+        <v>416</v>
       </c>
       <c r="F88">
         <v>1</v>
       </c>
       <c r="G88" t="s">
-        <v>357</v>
+        <v>448</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -3463,19 +3742,19 @@
         <v>94</v>
       </c>
       <c r="C89" t="s">
-        <v>172</v>
+        <v>196</v>
       </c>
       <c r="D89" t="s">
-        <v>261</v>
+        <v>305</v>
       </c>
       <c r="E89" t="s">
-        <v>350</v>
+        <v>417</v>
       </c>
       <c r="F89">
         <v>1</v>
       </c>
       <c r="G89" t="s">
-        <v>355</v>
+        <v>446</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -3486,19 +3765,571 @@
         <v>95</v>
       </c>
       <c r="C90" t="s">
-        <v>173</v>
+        <v>197</v>
       </c>
       <c r="D90" t="s">
-        <v>262</v>
+        <v>306</v>
       </c>
       <c r="E90" t="s">
-        <v>351</v>
+        <v>418</v>
       </c>
       <c r="F90">
         <v>1</v>
       </c>
       <c r="G90" t="s">
-        <v>352</v>
+        <v>443</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7">
+      <c r="A91">
+        <v>90</v>
+      </c>
+      <c r="B91" t="s">
+        <v>96</v>
+      </c>
+      <c r="C91" t="s">
+        <v>198</v>
+      </c>
+      <c r="D91" t="s">
+        <v>307</v>
+      </c>
+      <c r="E91" t="s">
+        <v>419</v>
+      </c>
+      <c r="F91">
+        <v>1</v>
+      </c>
+      <c r="G91" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7">
+      <c r="A92">
+        <v>91</v>
+      </c>
+      <c r="B92" t="s">
+        <v>97</v>
+      </c>
+      <c r="C92" t="s">
+        <v>199</v>
+      </c>
+      <c r="D92" t="s">
+        <v>244</v>
+      </c>
+      <c r="E92" t="s">
+        <v>420</v>
+      </c>
+      <c r="F92">
+        <v>1</v>
+      </c>
+      <c r="G92" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7">
+      <c r="A93">
+        <v>92</v>
+      </c>
+      <c r="B93" t="s">
+        <v>98</v>
+      </c>
+      <c r="C93" t="s">
+        <v>200</v>
+      </c>
+      <c r="D93" t="s">
+        <v>308</v>
+      </c>
+      <c r="E93" t="s">
+        <v>421</v>
+      </c>
+      <c r="F93">
+        <v>1</v>
+      </c>
+      <c r="G93" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7">
+      <c r="A94">
+        <v>93</v>
+      </c>
+      <c r="B94" t="s">
+        <v>99</v>
+      </c>
+      <c r="C94" t="s">
+        <v>201</v>
+      </c>
+      <c r="D94" t="s">
+        <v>309</v>
+      </c>
+      <c r="E94" t="s">
+        <v>422</v>
+      </c>
+      <c r="F94">
+        <v>1</v>
+      </c>
+      <c r="G94" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7">
+      <c r="A95">
+        <v>94</v>
+      </c>
+      <c r="B95" t="s">
+        <v>100</v>
+      </c>
+      <c r="C95" t="s">
+        <v>202</v>
+      </c>
+      <c r="D95" t="s">
+        <v>310</v>
+      </c>
+      <c r="E95" t="s">
+        <v>423</v>
+      </c>
+      <c r="F95">
+        <v>1</v>
+      </c>
+      <c r="G95" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7">
+      <c r="A96">
+        <v>95</v>
+      </c>
+      <c r="B96" t="s">
+        <v>101</v>
+      </c>
+      <c r="C96" t="s">
+        <v>203</v>
+      </c>
+      <c r="D96" t="s">
+        <v>311</v>
+      </c>
+      <c r="E96" t="s">
+        <v>424</v>
+      </c>
+      <c r="F96">
+        <v>1</v>
+      </c>
+      <c r="G96" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7">
+      <c r="A97">
+        <v>96</v>
+      </c>
+      <c r="B97" t="s">
+        <v>102</v>
+      </c>
+      <c r="C97" t="s">
+        <v>204</v>
+      </c>
+      <c r="D97" t="s">
+        <v>312</v>
+      </c>
+      <c r="E97" t="s">
+        <v>425</v>
+      </c>
+      <c r="F97">
+        <v>1</v>
+      </c>
+      <c r="G97" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7">
+      <c r="A98">
+        <v>97</v>
+      </c>
+      <c r="B98" t="s">
+        <v>103</v>
+      </c>
+      <c r="C98" t="s">
+        <v>182</v>
+      </c>
+      <c r="D98" t="s">
+        <v>313</v>
+      </c>
+      <c r="E98" t="s">
+        <v>426</v>
+      </c>
+      <c r="F98">
+        <v>1</v>
+      </c>
+      <c r="G98" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7">
+      <c r="A99">
+        <v>98</v>
+      </c>
+      <c r="B99" t="s">
+        <v>104</v>
+      </c>
+      <c r="C99" t="s">
+        <v>205</v>
+      </c>
+      <c r="D99" t="s">
+        <v>314</v>
+      </c>
+      <c r="E99" t="s">
+        <v>427</v>
+      </c>
+      <c r="F99">
+        <v>1</v>
+      </c>
+      <c r="G99" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7">
+      <c r="A100">
+        <v>99</v>
+      </c>
+      <c r="B100" t="s">
+        <v>105</v>
+      </c>
+      <c r="C100" t="s">
+        <v>206</v>
+      </c>
+      <c r="D100" t="s">
+        <v>315</v>
+      </c>
+      <c r="E100" t="s">
+        <v>428</v>
+      </c>
+      <c r="F100">
+        <v>1</v>
+      </c>
+      <c r="G100" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7">
+      <c r="A101">
+        <v>100</v>
+      </c>
+      <c r="B101" t="s">
+        <v>106</v>
+      </c>
+      <c r="C101" t="s">
+        <v>207</v>
+      </c>
+      <c r="D101" t="s">
+        <v>316</v>
+      </c>
+      <c r="E101" t="s">
+        <v>429</v>
+      </c>
+      <c r="F101">
+        <v>1</v>
+      </c>
+      <c r="G101" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7">
+      <c r="A102">
+        <v>101</v>
+      </c>
+      <c r="B102" t="s">
+        <v>107</v>
+      </c>
+      <c r="C102" t="s">
+        <v>208</v>
+      </c>
+      <c r="D102" t="s">
+        <v>317</v>
+      </c>
+      <c r="E102" t="s">
+        <v>430</v>
+      </c>
+      <c r="F102">
+        <v>1</v>
+      </c>
+      <c r="G102" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7">
+      <c r="A103">
+        <v>102</v>
+      </c>
+      <c r="B103" t="s">
+        <v>108</v>
+      </c>
+      <c r="C103" t="s">
+        <v>209</v>
+      </c>
+      <c r="D103" t="s">
+        <v>318</v>
+      </c>
+      <c r="E103" t="s">
+        <v>431</v>
+      </c>
+      <c r="F103">
+        <v>1</v>
+      </c>
+      <c r="G103" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7">
+      <c r="A104">
+        <v>103</v>
+      </c>
+      <c r="B104" t="s">
+        <v>109</v>
+      </c>
+      <c r="C104" t="s">
+        <v>210</v>
+      </c>
+      <c r="D104" t="s">
+        <v>319</v>
+      </c>
+      <c r="E104" t="s">
+        <v>432</v>
+      </c>
+      <c r="F104">
+        <v>1</v>
+      </c>
+      <c r="G104" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7">
+      <c r="A105">
+        <v>104</v>
+      </c>
+      <c r="B105" t="s">
+        <v>110</v>
+      </c>
+      <c r="C105" t="s">
+        <v>211</v>
+      </c>
+      <c r="D105" t="s">
+        <v>320</v>
+      </c>
+      <c r="E105" t="s">
+        <v>433</v>
+      </c>
+      <c r="F105">
+        <v>1</v>
+      </c>
+      <c r="G105" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="106" spans="1:7">
+      <c r="A106">
+        <v>105</v>
+      </c>
+      <c r="B106" t="s">
+        <v>111</v>
+      </c>
+      <c r="C106" t="s">
+        <v>212</v>
+      </c>
+      <c r="D106" t="s">
+        <v>321</v>
+      </c>
+      <c r="E106" t="s">
+        <v>434</v>
+      </c>
+      <c r="F106">
+        <v>1</v>
+      </c>
+      <c r="G106" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7">
+      <c r="A107">
+        <v>106</v>
+      </c>
+      <c r="B107" t="s">
+        <v>112</v>
+      </c>
+      <c r="C107" t="s">
+        <v>213</v>
+      </c>
+      <c r="D107" t="s">
+        <v>322</v>
+      </c>
+      <c r="E107" t="s">
+        <v>435</v>
+      </c>
+      <c r="F107">
+        <v>1</v>
+      </c>
+      <c r="G107" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="108" spans="1:7">
+      <c r="A108">
+        <v>107</v>
+      </c>
+      <c r="B108" t="s">
+        <v>113</v>
+      </c>
+      <c r="C108" t="s">
+        <v>113</v>
+      </c>
+      <c r="D108" t="s">
+        <v>323</v>
+      </c>
+      <c r="E108" t="s">
+        <v>436</v>
+      </c>
+      <c r="F108">
+        <v>1</v>
+      </c>
+      <c r="G108" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="109" spans="1:7">
+      <c r="A109">
+        <v>108</v>
+      </c>
+      <c r="B109" t="s">
+        <v>114</v>
+      </c>
+      <c r="C109" t="s">
+        <v>114</v>
+      </c>
+      <c r="D109" t="s">
+        <v>324</v>
+      </c>
+      <c r="E109" t="s">
+        <v>437</v>
+      </c>
+      <c r="F109">
+        <v>1</v>
+      </c>
+      <c r="G109" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="110" spans="1:7">
+      <c r="A110">
+        <v>109</v>
+      </c>
+      <c r="B110" t="s">
+        <v>115</v>
+      </c>
+      <c r="C110" t="s">
+        <v>115</v>
+      </c>
+      <c r="D110" t="s">
+        <v>325</v>
+      </c>
+      <c r="E110" t="s">
+        <v>438</v>
+      </c>
+      <c r="F110">
+        <v>1</v>
+      </c>
+      <c r="G110" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="111" spans="1:7">
+      <c r="A111">
+        <v>110</v>
+      </c>
+      <c r="B111" t="s">
+        <v>116</v>
+      </c>
+      <c r="C111" t="s">
+        <v>214</v>
+      </c>
+      <c r="D111" t="s">
+        <v>326</v>
+      </c>
+      <c r="E111" t="s">
+        <v>439</v>
+      </c>
+      <c r="F111">
+        <v>1</v>
+      </c>
+      <c r="G111" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="112" spans="1:7">
+      <c r="A112">
+        <v>111</v>
+      </c>
+      <c r="B112" t="s">
+        <v>117</v>
+      </c>
+      <c r="C112" t="s">
+        <v>215</v>
+      </c>
+      <c r="D112" t="s">
+        <v>327</v>
+      </c>
+      <c r="E112" t="s">
+        <v>440</v>
+      </c>
+      <c r="F112">
+        <v>1</v>
+      </c>
+      <c r="G112" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="113" spans="1:7">
+      <c r="A113">
+        <v>112</v>
+      </c>
+      <c r="B113" t="s">
+        <v>118</v>
+      </c>
+      <c r="C113" t="s">
+        <v>216</v>
+      </c>
+      <c r="D113" t="s">
+        <v>328</v>
+      </c>
+      <c r="E113" t="s">
+        <v>441</v>
+      </c>
+      <c r="F113">
+        <v>1</v>
+      </c>
+      <c r="G113" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="114" spans="1:7">
+      <c r="A114">
+        <v>113</v>
+      </c>
+      <c r="B114" t="s">
+        <v>119</v>
+      </c>
+      <c r="C114" t="s">
+        <v>217</v>
+      </c>
+      <c r="D114" t="s">
+        <v>329</v>
+      </c>
+      <c r="E114" t="s">
+        <v>442</v>
+      </c>
+      <c r="F114">
+        <v>1</v>
+      </c>
+      <c r="G114" t="s">
+        <v>453</v>
       </c>
     </row>
   </sheetData>

--- a/data/target_dispatch/파보겔_실제발송_최종정제명단.xlsx
+++ b/data/target_dispatch/파보겔_실제발송_최종정제명단.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="572" uniqueCount="454">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="577" uniqueCount="459">
   <si>
     <t>순번</t>
   </si>
@@ -376,6 +376,9 @@
     <t>블랙 앤 화이트</t>
   </si>
   <si>
+    <t>베프경매장</t>
+  </si>
+  <si>
     <t>정원정</t>
   </si>
   <si>
@@ -670,6 +673,9 @@
     <t>문수미</t>
   </si>
   <si>
+    <t>황상필</t>
+  </si>
+  <si>
     <t>010-3114-1100</t>
   </si>
   <si>
@@ -1006,6 +1012,9 @@
     <t>010-9700-8733</t>
   </si>
   <si>
+    <t>010-9283-7582</t>
+  </si>
+  <si>
     <t>원주시 태장동 흥양로30  대흥아파트202-1202</t>
   </si>
   <si>
@@ -1345,6 +1354,9 @@
     <t>광주광역시 서구 봉학길 38</t>
   </si>
   <si>
+    <t>경기도 용인시 처인구 원삼면 좌항리 579 나동(원양로577번길 23)</t>
+  </si>
+  <si>
     <t>[MMS 문자 유입] 펫샵 본품 1병 무료 샘플 신청</t>
   </si>
   <si>
@@ -1376,6 +1388,9 @@
   </si>
   <si>
     <t>[MMS 문자 유입] 펫샵 본품 1병 무료 샘플 신청 / [쿠팡 2병 유료 주문 확인]</t>
+  </si>
+  <si>
+    <t>[홍대표 직통 유입] 전화 및 문자 신청 (애견경매장 본품 1병 무료 샘플)</t>
   </si>
 </sst>
 </file>
@@ -1707,7 +1722,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G114"/>
+  <dimension ref="A1:G115"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -1741,19 +1756,19 @@
         <v>7</v>
       </c>
       <c r="C2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D2" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="E2" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="F2">
         <v>1</v>
       </c>
       <c r="G2" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -1764,19 +1779,19 @@
         <v>8</v>
       </c>
       <c r="C3" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D3" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="E3" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="F3">
         <v>1</v>
       </c>
       <c r="G3" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -1787,19 +1802,19 @@
         <v>9</v>
       </c>
       <c r="C4" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D4" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="E4" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="F4">
         <v>1</v>
       </c>
       <c r="G4" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -1810,19 +1825,19 @@
         <v>10</v>
       </c>
       <c r="C5" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D5" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="E5" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="F5">
         <v>1</v>
       </c>
       <c r="G5" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -1833,19 +1848,19 @@
         <v>11</v>
       </c>
       <c r="C6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D6" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="E6" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="F6">
         <v>1</v>
       </c>
       <c r="G6" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -1856,19 +1871,19 @@
         <v>12</v>
       </c>
       <c r="C7" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D7" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="E7" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="F7">
         <v>1</v>
       </c>
       <c r="G7" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -1879,19 +1894,19 @@
         <v>13</v>
       </c>
       <c r="C8" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D8" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="E8" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="F8">
         <v>1</v>
       </c>
       <c r="G8" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -1902,19 +1917,19 @@
         <v>14</v>
       </c>
       <c r="C9" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D9" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="E9" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="F9">
         <v>1</v>
       </c>
       <c r="G9" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -1925,19 +1940,19 @@
         <v>15</v>
       </c>
       <c r="C10" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D10" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="E10" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="F10">
         <v>1</v>
       </c>
       <c r="G10" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -1948,19 +1963,19 @@
         <v>16</v>
       </c>
       <c r="C11" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D11" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="E11" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="F11">
         <v>1</v>
       </c>
       <c r="G11" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -1971,19 +1986,19 @@
         <v>17</v>
       </c>
       <c r="C12" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="E12" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="F12">
         <v>1</v>
       </c>
       <c r="G12" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -1994,19 +2009,19 @@
         <v>18</v>
       </c>
       <c r="C13" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D13" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="E13" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="F13">
         <v>1</v>
       </c>
       <c r="G13" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -2017,19 +2032,19 @@
         <v>19</v>
       </c>
       <c r="C14" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D14" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="E14" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="F14">
         <v>1</v>
       </c>
       <c r="G14" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -2040,19 +2055,19 @@
         <v>20</v>
       </c>
       <c r="C15" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D15" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="E15" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="F15">
         <v>1</v>
       </c>
       <c r="G15" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -2063,19 +2078,19 @@
         <v>21</v>
       </c>
       <c r="C16" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D16" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="E16" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="F16">
         <v>1</v>
       </c>
       <c r="G16" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -2086,19 +2101,19 @@
         <v>22</v>
       </c>
       <c r="C17" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D17" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="E17" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="F17">
         <v>1</v>
       </c>
       <c r="G17" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -2109,19 +2124,19 @@
         <v>23</v>
       </c>
       <c r="C18" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D18" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="E18" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="F18">
         <v>1</v>
       </c>
       <c r="G18" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -2132,19 +2147,19 @@
         <v>24</v>
       </c>
       <c r="C19" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D19" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="E19" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="F19">
         <v>1</v>
       </c>
       <c r="G19" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -2155,19 +2170,19 @@
         <v>25</v>
       </c>
       <c r="C20" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D20" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="E20" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="F20">
         <v>1</v>
       </c>
       <c r="G20" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -2178,19 +2193,19 @@
         <v>26</v>
       </c>
       <c r="C21" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D21" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="E21" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="F21">
         <v>1</v>
       </c>
       <c r="G21" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -2201,19 +2216,19 @@
         <v>27</v>
       </c>
       <c r="C22" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D22" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="E22" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="F22">
         <v>1</v>
       </c>
       <c r="G22" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -2224,19 +2239,19 @@
         <v>28</v>
       </c>
       <c r="C23" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D23" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="E23" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="F23">
         <v>1</v>
       </c>
       <c r="G23" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -2247,19 +2262,19 @@
         <v>29</v>
       </c>
       <c r="C24" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D24" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="E24" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="F24">
         <v>1</v>
       </c>
       <c r="G24" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -2270,19 +2285,19 @@
         <v>30</v>
       </c>
       <c r="C25" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D25" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E25" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="F25">
         <v>1</v>
       </c>
       <c r="G25" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -2293,19 +2308,19 @@
         <v>31</v>
       </c>
       <c r="C26" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D26" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="E26" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="F26">
         <v>1</v>
       </c>
       <c r="G26" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -2316,19 +2331,19 @@
         <v>32</v>
       </c>
       <c r="C27" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D27" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="E27" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="F27">
         <v>1</v>
       </c>
       <c r="G27" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -2339,19 +2354,19 @@
         <v>33</v>
       </c>
       <c r="C28" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D28" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="E28" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="F28">
         <v>1</v>
       </c>
       <c r="G28" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -2362,19 +2377,19 @@
         <v>34</v>
       </c>
       <c r="C29" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D29" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="E29" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="F29">
         <v>1</v>
       </c>
       <c r="G29" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -2385,19 +2400,19 @@
         <v>35</v>
       </c>
       <c r="C30" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D30" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="E30" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="F30">
         <v>1</v>
       </c>
       <c r="G30" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -2408,19 +2423,19 @@
         <v>36</v>
       </c>
       <c r="C31" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D31" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="E31" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="F31">
         <v>1</v>
       </c>
       <c r="G31" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -2431,19 +2446,19 @@
         <v>37</v>
       </c>
       <c r="C32" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D32" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="E32" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="F32">
         <v>1</v>
       </c>
       <c r="G32" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -2454,19 +2469,19 @@
         <v>38</v>
       </c>
       <c r="C33" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D33" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="E33" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="F33">
         <v>1</v>
       </c>
       <c r="G33" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -2477,19 +2492,19 @@
         <v>39</v>
       </c>
       <c r="C34" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D34" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="E34" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="F34">
         <v>1</v>
       </c>
       <c r="G34" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -2500,19 +2515,19 @@
         <v>40</v>
       </c>
       <c r="C35" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D35" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="E35" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="F35">
         <v>1</v>
       </c>
       <c r="G35" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -2523,19 +2538,19 @@
         <v>41</v>
       </c>
       <c r="C36" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D36" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="E36" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="F36">
         <v>1</v>
       </c>
       <c r="G36" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -2546,19 +2561,19 @@
         <v>42</v>
       </c>
       <c r="C37" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D37" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="E37" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="F37">
         <v>1</v>
       </c>
       <c r="G37" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -2569,19 +2584,19 @@
         <v>43</v>
       </c>
       <c r="C38" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D38" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="E38" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="F38">
         <v>1</v>
       </c>
       <c r="G38" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -2592,19 +2607,19 @@
         <v>44</v>
       </c>
       <c r="C39" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D39" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="E39" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="F39">
         <v>1</v>
       </c>
       <c r="G39" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -2615,19 +2630,19 @@
         <v>45</v>
       </c>
       <c r="C40" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D40" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="E40" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="F40">
         <v>1</v>
       </c>
       <c r="G40" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -2638,19 +2653,19 @@
         <v>46</v>
       </c>
       <c r="C41" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D41" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="E41" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="F41">
         <v>1</v>
       </c>
       <c r="G41" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -2661,19 +2676,19 @@
         <v>47</v>
       </c>
       <c r="C42" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D42" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="E42" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="F42">
         <v>1</v>
       </c>
       <c r="G42" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -2684,19 +2699,19 @@
         <v>48</v>
       </c>
       <c r="C43" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D43" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="E43" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="F43">
         <v>1</v>
       </c>
       <c r="G43" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -2707,19 +2722,19 @@
         <v>49</v>
       </c>
       <c r="C44" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D44" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="E44" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="F44">
         <v>1</v>
       </c>
       <c r="G44" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -2730,19 +2745,19 @@
         <v>50</v>
       </c>
       <c r="C45" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D45" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="E45" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="F45">
         <v>1</v>
       </c>
       <c r="G45" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -2753,19 +2768,19 @@
         <v>51</v>
       </c>
       <c r="C46" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D46" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="E46" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="F46">
         <v>1</v>
       </c>
       <c r="G46" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -2776,19 +2791,19 @@
         <v>52</v>
       </c>
       <c r="C47" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D47" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="E47" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="F47">
         <v>1</v>
       </c>
       <c r="G47" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -2799,19 +2814,19 @@
         <v>53</v>
       </c>
       <c r="C48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D48" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="E48" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="F48">
         <v>1</v>
       </c>
       <c r="G48" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -2822,19 +2837,19 @@
         <v>54</v>
       </c>
       <c r="C49" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D49" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="E49" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="F49">
         <v>1</v>
       </c>
       <c r="G49" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -2845,19 +2860,19 @@
         <v>55</v>
       </c>
       <c r="C50" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D50" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="E50" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="F50">
         <v>1</v>
       </c>
       <c r="G50" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -2868,19 +2883,19 @@
         <v>56</v>
       </c>
       <c r="C51" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D51" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="E51" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="F51">
         <v>1</v>
       </c>
       <c r="G51" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -2891,19 +2906,19 @@
         <v>57</v>
       </c>
       <c r="C52" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D52" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="E52" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="F52">
         <v>1</v>
       </c>
       <c r="G52" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -2914,19 +2929,19 @@
         <v>58</v>
       </c>
       <c r="C53" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D53" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="E53" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="F53">
         <v>1</v>
       </c>
       <c r="G53" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -2937,19 +2952,19 @@
         <v>59</v>
       </c>
       <c r="C54" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D54" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="E54" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="F54">
         <v>1</v>
       </c>
       <c r="G54" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -2960,19 +2975,19 @@
         <v>60</v>
       </c>
       <c r="C55" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D55" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="E55" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="F55">
         <v>1</v>
       </c>
       <c r="G55" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -2983,19 +2998,19 @@
         <v>61</v>
       </c>
       <c r="C56" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D56" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="E56" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="F56">
         <v>1</v>
       </c>
       <c r="G56" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -3006,19 +3021,19 @@
         <v>62</v>
       </c>
       <c r="C57" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D57" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="E57" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="F57">
         <v>1</v>
       </c>
       <c r="G57" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -3029,19 +3044,19 @@
         <v>63</v>
       </c>
       <c r="C58" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D58" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="E58" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="F58">
         <v>1</v>
       </c>
       <c r="G58" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -3052,19 +3067,19 @@
         <v>64</v>
       </c>
       <c r="C59" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D59" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="E59" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="F59">
         <v>1</v>
       </c>
       <c r="G59" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -3075,19 +3090,19 @@
         <v>65</v>
       </c>
       <c r="C60" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D60" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="E60" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="F60">
         <v>1</v>
       </c>
       <c r="G60" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -3098,19 +3113,19 @@
         <v>66</v>
       </c>
       <c r="C61" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D61" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E61" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="F61">
         <v>1</v>
       </c>
       <c r="G61" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -3121,19 +3136,19 @@
         <v>67</v>
       </c>
       <c r="C62" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D62" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="E62" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="F62">
         <v>1</v>
       </c>
       <c r="G62" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -3144,19 +3159,19 @@
         <v>68</v>
       </c>
       <c r="C63" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="D63" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E63" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="F63">
         <v>1</v>
       </c>
       <c r="G63" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -3167,19 +3182,19 @@
         <v>69</v>
       </c>
       <c r="C64" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D64" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="E64" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="F64">
         <v>1</v>
       </c>
       <c r="G64" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -3190,19 +3205,19 @@
         <v>70</v>
       </c>
       <c r="C65" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D65" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="E65" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="F65">
         <v>3</v>
       </c>
       <c r="G65" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -3213,19 +3228,19 @@
         <v>71</v>
       </c>
       <c r="C66" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D66" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="E66" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="F66">
         <v>1</v>
       </c>
       <c r="G66" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -3236,19 +3251,19 @@
         <v>72</v>
       </c>
       <c r="C67" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D67" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="E67" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="F67">
         <v>1</v>
       </c>
       <c r="G67" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -3259,19 +3274,19 @@
         <v>73</v>
       </c>
       <c r="C68" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D68" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="E68" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="F68">
         <v>1</v>
       </c>
       <c r="G68" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -3282,19 +3297,19 @@
         <v>74</v>
       </c>
       <c r="C69" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D69" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="E69" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="F69">
         <v>1</v>
       </c>
       <c r="G69" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -3305,19 +3320,19 @@
         <v>75</v>
       </c>
       <c r="C70" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D70" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="E70" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="F70">
         <v>1</v>
       </c>
       <c r="G70" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -3328,19 +3343,19 @@
         <v>76</v>
       </c>
       <c r="C71" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D71" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="E71" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="F71">
         <v>1</v>
       </c>
       <c r="G71" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -3351,19 +3366,19 @@
         <v>77</v>
       </c>
       <c r="C72" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="D72" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="E72" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="F72">
         <v>1</v>
       </c>
       <c r="G72" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -3374,19 +3389,19 @@
         <v>78</v>
       </c>
       <c r="C73" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D73" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="E73" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="F73">
         <v>1</v>
       </c>
       <c r="G73" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -3397,19 +3412,19 @@
         <v>79</v>
       </c>
       <c r="C74" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="D74" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="E74" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="F74">
         <v>1</v>
       </c>
       <c r="G74" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -3420,19 +3435,19 @@
         <v>80</v>
       </c>
       <c r="C75" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D75" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="E75" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="F75">
         <v>1</v>
       </c>
       <c r="G75" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -3443,19 +3458,19 @@
         <v>81</v>
       </c>
       <c r="C76" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="D76" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="E76" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="F76">
         <v>1</v>
       </c>
       <c r="G76" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -3469,16 +3484,16 @@
         <v>82</v>
       </c>
       <c r="D77" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="E77" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="F77">
         <v>1</v>
       </c>
       <c r="G77" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -3492,16 +3507,16 @@
         <v>83</v>
       </c>
       <c r="D78" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="E78" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="F78">
         <v>1</v>
       </c>
       <c r="G78" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -3515,16 +3530,16 @@
         <v>84</v>
       </c>
       <c r="D79" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="E79" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="F79">
         <v>1</v>
       </c>
       <c r="G79" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -3538,16 +3553,16 @@
         <v>85</v>
       </c>
       <c r="D80" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="E80" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="F80">
         <v>1</v>
       </c>
       <c r="G80" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -3561,16 +3576,16 @@
         <v>86</v>
       </c>
       <c r="D81" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="E81" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="F81">
         <v>1</v>
       </c>
       <c r="G81" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -3584,16 +3599,16 @@
         <v>87</v>
       </c>
       <c r="D82" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="E82" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="F82">
         <v>1</v>
       </c>
       <c r="G82" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -3607,16 +3622,16 @@
         <v>88</v>
       </c>
       <c r="D83" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="E83" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="F83">
         <v>1</v>
       </c>
       <c r="G83" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -3630,16 +3645,16 @@
         <v>89</v>
       </c>
       <c r="D84" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="E84" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="F84">
         <v>1</v>
       </c>
       <c r="G84" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -3653,16 +3668,16 @@
         <v>90</v>
       </c>
       <c r="D85" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="E85" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="F85">
         <v>1</v>
       </c>
       <c r="G85" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -3673,19 +3688,19 @@
         <v>91</v>
       </c>
       <c r="C86" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="D86" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="E86" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="F86">
         <v>1</v>
       </c>
       <c r="G86" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -3699,16 +3714,16 @@
         <v>92</v>
       </c>
       <c r="D87" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="E87" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="F87">
         <v>1</v>
       </c>
       <c r="G87" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -3722,16 +3737,16 @@
         <v>93</v>
       </c>
       <c r="D88" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="E88" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="F88">
         <v>1</v>
       </c>
       <c r="G88" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -3742,19 +3757,19 @@
         <v>94</v>
       </c>
       <c r="C89" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="D89" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="E89" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="F89">
         <v>1</v>
       </c>
       <c r="G89" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -3765,19 +3780,19 @@
         <v>95</v>
       </c>
       <c r="C90" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D90" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="E90" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="F90">
         <v>1</v>
       </c>
       <c r="G90" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -3788,19 +3803,19 @@
         <v>96</v>
       </c>
       <c r="C91" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D91" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="E91" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="F91">
         <v>1</v>
       </c>
       <c r="G91" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -3811,19 +3826,19 @@
         <v>97</v>
       </c>
       <c r="C92" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D92" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="E92" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="F92">
         <v>1</v>
       </c>
       <c r="G92" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -3834,19 +3849,19 @@
         <v>98</v>
       </c>
       <c r="C93" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D93" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="E93" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="F93">
         <v>1</v>
       </c>
       <c r="G93" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -3857,19 +3872,19 @@
         <v>99</v>
       </c>
       <c r="C94" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D94" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="E94" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="F94">
         <v>1</v>
       </c>
       <c r="G94" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -3880,19 +3895,19 @@
         <v>100</v>
       </c>
       <c r="C95" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D95" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="E95" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="F95">
         <v>1</v>
       </c>
       <c r="G95" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -3903,19 +3918,19 @@
         <v>101</v>
       </c>
       <c r="C96" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D96" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="E96" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="F96">
         <v>1</v>
       </c>
       <c r="G96" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -3926,19 +3941,19 @@
         <v>102</v>
       </c>
       <c r="C97" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D97" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="E97" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="F97">
         <v>1</v>
       </c>
       <c r="G97" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -3949,19 +3964,19 @@
         <v>103</v>
       </c>
       <c r="C98" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D98" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="E98" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="F98">
         <v>1</v>
       </c>
       <c r="G98" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -3972,19 +3987,19 @@
         <v>104</v>
       </c>
       <c r="C99" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D99" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="E99" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="F99">
         <v>1</v>
       </c>
       <c r="G99" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -3995,19 +4010,19 @@
         <v>105</v>
       </c>
       <c r="C100" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="D100" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="E100" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="F100">
         <v>1</v>
       </c>
       <c r="G100" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -4018,19 +4033,19 @@
         <v>106</v>
       </c>
       <c r="C101" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D101" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="E101" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="F101">
         <v>1</v>
       </c>
       <c r="G101" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -4041,19 +4056,19 @@
         <v>107</v>
       </c>
       <c r="C102" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D102" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="E102" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="F102">
         <v>1</v>
       </c>
       <c r="G102" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
     </row>
     <row r="103" spans="1:7">
@@ -4064,19 +4079,19 @@
         <v>108</v>
       </c>
       <c r="C103" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="D103" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="E103" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="F103">
         <v>1</v>
       </c>
       <c r="G103" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
     </row>
     <row r="104" spans="1:7">
@@ -4087,19 +4102,19 @@
         <v>109</v>
       </c>
       <c r="C104" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D104" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="E104" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="F104">
         <v>1</v>
       </c>
       <c r="G104" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
     </row>
     <row r="105" spans="1:7">
@@ -4110,19 +4125,19 @@
         <v>110</v>
       </c>
       <c r="C105" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="D105" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="E105" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="F105">
         <v>1</v>
       </c>
       <c r="G105" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
     </row>
     <row r="106" spans="1:7">
@@ -4133,19 +4148,19 @@
         <v>111</v>
       </c>
       <c r="C106" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="D106" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="E106" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="F106">
         <v>1</v>
       </c>
       <c r="G106" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
     </row>
     <row r="107" spans="1:7">
@@ -4156,19 +4171,19 @@
         <v>112</v>
       </c>
       <c r="C107" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D107" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="E107" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="F107">
         <v>1</v>
       </c>
       <c r="G107" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
     </row>
     <row r="108" spans="1:7">
@@ -4182,16 +4197,16 @@
         <v>113</v>
       </c>
       <c r="D108" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="E108" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="F108">
         <v>1</v>
       </c>
       <c r="G108" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
     </row>
     <row r="109" spans="1:7">
@@ -4205,16 +4220,16 @@
         <v>114</v>
       </c>
       <c r="D109" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="E109" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="F109">
         <v>1</v>
       </c>
       <c r="G109" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
     </row>
     <row r="110" spans="1:7">
@@ -4228,16 +4243,16 @@
         <v>115</v>
       </c>
       <c r="D110" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="E110" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="F110">
         <v>1</v>
       </c>
       <c r="G110" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
     </row>
     <row r="111" spans="1:7">
@@ -4248,19 +4263,19 @@
         <v>116</v>
       </c>
       <c r="C111" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="D111" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="E111" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="F111">
         <v>1</v>
       </c>
       <c r="G111" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
     </row>
     <row r="112" spans="1:7">
@@ -4271,19 +4286,19 @@
         <v>117</v>
       </c>
       <c r="C112" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="D112" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="E112" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="F112">
         <v>1</v>
       </c>
       <c r="G112" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
     </row>
     <row r="113" spans="1:7">
@@ -4294,19 +4309,19 @@
         <v>118</v>
       </c>
       <c r="C113" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="D113" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="E113" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="F113">
         <v>1</v>
       </c>
       <c r="G113" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
     </row>
     <row r="114" spans="1:7">
@@ -4317,19 +4332,42 @@
         <v>119</v>
       </c>
       <c r="C114" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D114" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="E114" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="F114">
         <v>1</v>
       </c>
       <c r="G114" t="s">
-        <v>453</v>
+        <v>457</v>
+      </c>
+    </row>
+    <row r="115" spans="1:7">
+      <c r="A115">
+        <v>114</v>
+      </c>
+      <c r="B115" t="s">
+        <v>120</v>
+      </c>
+      <c r="C115" t="s">
+        <v>219</v>
+      </c>
+      <c r="D115" t="s">
+        <v>332</v>
+      </c>
+      <c r="E115" t="s">
+        <v>446</v>
+      </c>
+      <c r="F115">
+        <v>1</v>
+      </c>
+      <c r="G115" t="s">
+        <v>458</v>
       </c>
     </row>
   </sheetData>

--- a/data/target_dispatch/파보겔_실제발송_최종정제명단.xlsx
+++ b/data/target_dispatch/파보겔_실제발송_최종정제명단.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="577" uniqueCount="459">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="582" uniqueCount="464">
   <si>
     <t>순번</t>
   </si>
@@ -379,6 +379,9 @@
     <t>베프경매장</t>
   </si>
   <si>
+    <t>우포켄넬</t>
+  </si>
+  <si>
     <t>정원정</t>
   </si>
   <si>
@@ -676,6 +679,9 @@
     <t>황상필</t>
   </si>
   <si>
+    <t>서유석</t>
+  </si>
+  <si>
     <t>010-3114-1100</t>
   </si>
   <si>
@@ -1015,6 +1021,9 @@
     <t>010-9283-7582</t>
   </si>
   <si>
+    <t>010-3533-1104</t>
+  </si>
+  <si>
     <t>원주시 태장동 흥양로30  대흥아파트202-1202</t>
   </si>
   <si>
@@ -1357,6 +1366,9 @@
     <t>경기도 용인시 처인구 원삼면 좌항리 579 나동(원양로577번길 23)</t>
   </si>
   <si>
+    <t>경남 창녕군 창녕읍 우포유어농로 643번지</t>
+  </si>
+  <si>
     <t>[MMS 문자 유입] 펫샵 본품 1병 무료 샘플 신청</t>
   </si>
   <si>
@@ -1391,6 +1403,9 @@
   </si>
   <si>
     <t>[홍대표 직통 유입] 전화 및 문자 신청 (애견경매장 본품 1병 무료 샘플)</t>
+  </si>
+  <si>
+    <t>[홍대표 직통 유입] 켄넬/브리더 본품 1병 무료 샘플 신청</t>
   </si>
 </sst>
 </file>
@@ -1722,7 +1737,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G115"/>
+  <dimension ref="A1:G116"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -1756,19 +1771,19 @@
         <v>7</v>
       </c>
       <c r="C2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D2" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="E2" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="F2">
         <v>1</v>
       </c>
       <c r="G2" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -1779,19 +1794,19 @@
         <v>8</v>
       </c>
       <c r="C3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D3" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="E3" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="F3">
         <v>1</v>
       </c>
       <c r="G3" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -1802,19 +1817,19 @@
         <v>9</v>
       </c>
       <c r="C4" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D4" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="E4" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="F4">
         <v>1</v>
       </c>
       <c r="G4" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -1825,19 +1840,19 @@
         <v>10</v>
       </c>
       <c r="C5" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D5" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="E5" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="F5">
         <v>1</v>
       </c>
       <c r="G5" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -1848,19 +1863,19 @@
         <v>11</v>
       </c>
       <c r="C6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D6" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="E6" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="F6">
         <v>1</v>
       </c>
       <c r="G6" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -1871,19 +1886,19 @@
         <v>12</v>
       </c>
       <c r="C7" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D7" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="E7" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="F7">
         <v>1</v>
       </c>
       <c r="G7" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -1894,19 +1909,19 @@
         <v>13</v>
       </c>
       <c r="C8" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D8" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="E8" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="F8">
         <v>1</v>
       </c>
       <c r="G8" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -1917,19 +1932,19 @@
         <v>14</v>
       </c>
       <c r="C9" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D9" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="E9" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="F9">
         <v>1</v>
       </c>
       <c r="G9" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -1940,19 +1955,19 @@
         <v>15</v>
       </c>
       <c r="C10" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D10" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="E10" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="F10">
         <v>1</v>
       </c>
       <c r="G10" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -1963,19 +1978,19 @@
         <v>16</v>
       </c>
       <c r="C11" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D11" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="E11" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="F11">
         <v>1</v>
       </c>
       <c r="G11" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -1986,19 +2001,19 @@
         <v>17</v>
       </c>
       <c r="C12" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D12" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="E12" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="F12">
         <v>1</v>
       </c>
       <c r="G12" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -2009,19 +2024,19 @@
         <v>18</v>
       </c>
       <c r="C13" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D13" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="E13" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="F13">
         <v>1</v>
       </c>
       <c r="G13" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -2032,19 +2047,19 @@
         <v>19</v>
       </c>
       <c r="C14" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D14" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="E14" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="F14">
         <v>1</v>
       </c>
       <c r="G14" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -2055,19 +2070,19 @@
         <v>20</v>
       </c>
       <c r="C15" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D15" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="E15" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="F15">
         <v>1</v>
       </c>
       <c r="G15" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -2078,19 +2093,19 @@
         <v>21</v>
       </c>
       <c r="C16" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D16" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="E16" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="F16">
         <v>1</v>
       </c>
       <c r="G16" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -2101,19 +2116,19 @@
         <v>22</v>
       </c>
       <c r="C17" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D17" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="E17" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="F17">
         <v>1</v>
       </c>
       <c r="G17" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -2124,19 +2139,19 @@
         <v>23</v>
       </c>
       <c r="C18" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D18" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="E18" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="F18">
         <v>1</v>
       </c>
       <c r="G18" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -2147,19 +2162,19 @@
         <v>24</v>
       </c>
       <c r="C19" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D19" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="E19" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="F19">
         <v>1</v>
       </c>
       <c r="G19" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -2170,19 +2185,19 @@
         <v>25</v>
       </c>
       <c r="C20" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D20" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="E20" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="F20">
         <v>1</v>
       </c>
       <c r="G20" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -2193,19 +2208,19 @@
         <v>26</v>
       </c>
       <c r="C21" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D21" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="E21" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="F21">
         <v>1</v>
       </c>
       <c r="G21" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -2216,19 +2231,19 @@
         <v>27</v>
       </c>
       <c r="C22" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D22" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="E22" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="F22">
         <v>1</v>
       </c>
       <c r="G22" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -2239,19 +2254,19 @@
         <v>28</v>
       </c>
       <c r="C23" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D23" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E23" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="F23">
         <v>1</v>
       </c>
       <c r="G23" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -2262,19 +2277,19 @@
         <v>29</v>
       </c>
       <c r="C24" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D24" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="E24" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="F24">
         <v>1</v>
       </c>
       <c r="G24" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -2285,19 +2300,19 @@
         <v>30</v>
       </c>
       <c r="C25" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D25" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="E25" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="F25">
         <v>1</v>
       </c>
       <c r="G25" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -2308,19 +2323,19 @@
         <v>31</v>
       </c>
       <c r="C26" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D26" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="E26" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="F26">
         <v>1</v>
       </c>
       <c r="G26" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -2331,19 +2346,19 @@
         <v>32</v>
       </c>
       <c r="C27" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D27" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="E27" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="F27">
         <v>1</v>
       </c>
       <c r="G27" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -2354,19 +2369,19 @@
         <v>33</v>
       </c>
       <c r="C28" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D28" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="E28" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="F28">
         <v>1</v>
       </c>
       <c r="G28" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -2377,19 +2392,19 @@
         <v>34</v>
       </c>
       <c r="C29" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D29" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="E29" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="F29">
         <v>1</v>
       </c>
       <c r="G29" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -2400,19 +2415,19 @@
         <v>35</v>
       </c>
       <c r="C30" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D30" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="E30" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="F30">
         <v>1</v>
       </c>
       <c r="G30" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -2423,19 +2438,19 @@
         <v>36</v>
       </c>
       <c r="C31" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D31" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="E31" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="F31">
         <v>1</v>
       </c>
       <c r="G31" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -2446,19 +2461,19 @@
         <v>37</v>
       </c>
       <c r="C32" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D32" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="E32" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="F32">
         <v>1</v>
       </c>
       <c r="G32" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -2469,19 +2484,19 @@
         <v>38</v>
       </c>
       <c r="C33" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D33" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="E33" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="F33">
         <v>1</v>
       </c>
       <c r="G33" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -2492,19 +2507,19 @@
         <v>39</v>
       </c>
       <c r="C34" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D34" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="E34" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="F34">
         <v>1</v>
       </c>
       <c r="G34" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -2515,19 +2530,19 @@
         <v>40</v>
       </c>
       <c r="C35" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D35" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="E35" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="F35">
         <v>1</v>
       </c>
       <c r="G35" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -2538,19 +2553,19 @@
         <v>41</v>
       </c>
       <c r="C36" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D36" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="E36" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="F36">
         <v>1</v>
       </c>
       <c r="G36" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -2561,19 +2576,19 @@
         <v>42</v>
       </c>
       <c r="C37" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D37" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="E37" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="F37">
         <v>1</v>
       </c>
       <c r="G37" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -2584,19 +2599,19 @@
         <v>43</v>
       </c>
       <c r="C38" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D38" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="E38" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="F38">
         <v>1</v>
       </c>
       <c r="G38" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -2607,19 +2622,19 @@
         <v>44</v>
       </c>
       <c r="C39" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D39" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="E39" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="F39">
         <v>1</v>
       </c>
       <c r="G39" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -2630,19 +2645,19 @@
         <v>45</v>
       </c>
       <c r="C40" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D40" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="E40" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="F40">
         <v>1</v>
       </c>
       <c r="G40" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -2653,19 +2668,19 @@
         <v>46</v>
       </c>
       <c r="C41" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D41" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="E41" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="F41">
         <v>1</v>
       </c>
       <c r="G41" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -2676,19 +2691,19 @@
         <v>47</v>
       </c>
       <c r="C42" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D42" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="E42" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="F42">
         <v>1</v>
       </c>
       <c r="G42" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -2699,19 +2714,19 @@
         <v>48</v>
       </c>
       <c r="C43" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D43" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="E43" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="F43">
         <v>1</v>
       </c>
       <c r="G43" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -2722,19 +2737,19 @@
         <v>49</v>
       </c>
       <c r="C44" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D44" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="E44" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="F44">
         <v>1</v>
       </c>
       <c r="G44" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -2745,19 +2760,19 @@
         <v>50</v>
       </c>
       <c r="C45" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D45" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="E45" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="F45">
         <v>1</v>
       </c>
       <c r="G45" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -2768,19 +2783,19 @@
         <v>51</v>
       </c>
       <c r="C46" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D46" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="E46" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="F46">
         <v>1</v>
       </c>
       <c r="G46" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -2791,19 +2806,19 @@
         <v>52</v>
       </c>
       <c r="C47" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D47" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="E47" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="F47">
         <v>1</v>
       </c>
       <c r="G47" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -2814,19 +2829,19 @@
         <v>53</v>
       </c>
       <c r="C48" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D48" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="E48" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="F48">
         <v>1</v>
       </c>
       <c r="G48" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -2837,19 +2852,19 @@
         <v>54</v>
       </c>
       <c r="C49" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D49" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="E49" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="F49">
         <v>1</v>
       </c>
       <c r="G49" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -2860,19 +2875,19 @@
         <v>55</v>
       </c>
       <c r="C50" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D50" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="E50" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="F50">
         <v>1</v>
       </c>
       <c r="G50" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -2883,19 +2898,19 @@
         <v>56</v>
       </c>
       <c r="C51" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D51" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="E51" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="F51">
         <v>1</v>
       </c>
       <c r="G51" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -2906,19 +2921,19 @@
         <v>57</v>
       </c>
       <c r="C52" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D52" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="E52" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="F52">
         <v>1</v>
       </c>
       <c r="G52" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -2929,19 +2944,19 @@
         <v>58</v>
       </c>
       <c r="C53" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D53" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="E53" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="F53">
         <v>1</v>
       </c>
       <c r="G53" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -2952,19 +2967,19 @@
         <v>59</v>
       </c>
       <c r="C54" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D54" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="E54" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="F54">
         <v>1</v>
       </c>
       <c r="G54" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -2975,19 +2990,19 @@
         <v>60</v>
       </c>
       <c r="C55" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D55" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="E55" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="F55">
         <v>1</v>
       </c>
       <c r="G55" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -2998,19 +3013,19 @@
         <v>61</v>
       </c>
       <c r="C56" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D56" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="E56" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="F56">
         <v>1</v>
       </c>
       <c r="G56" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -3021,19 +3036,19 @@
         <v>62</v>
       </c>
       <c r="C57" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D57" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="E57" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="F57">
         <v>1</v>
       </c>
       <c r="G57" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -3044,19 +3059,19 @@
         <v>63</v>
       </c>
       <c r="C58" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D58" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="E58" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="F58">
         <v>1</v>
       </c>
       <c r="G58" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -3067,19 +3082,19 @@
         <v>64</v>
       </c>
       <c r="C59" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D59" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E59" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="F59">
         <v>1</v>
       </c>
       <c r="G59" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -3090,19 +3105,19 @@
         <v>65</v>
       </c>
       <c r="C60" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D60" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="E60" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="F60">
         <v>1</v>
       </c>
       <c r="G60" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -3113,19 +3128,19 @@
         <v>66</v>
       </c>
       <c r="C61" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D61" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E61" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="F61">
         <v>1</v>
       </c>
       <c r="G61" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -3136,19 +3151,19 @@
         <v>67</v>
       </c>
       <c r="C62" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="D62" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="E62" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="F62">
         <v>1</v>
       </c>
       <c r="G62" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -3159,19 +3174,19 @@
         <v>68</v>
       </c>
       <c r="C63" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D63" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="E63" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="F63">
         <v>1</v>
       </c>
       <c r="G63" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -3182,19 +3197,19 @@
         <v>69</v>
       </c>
       <c r="C64" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D64" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="E64" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="F64">
         <v>1</v>
       </c>
       <c r="G64" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -3205,19 +3220,19 @@
         <v>70</v>
       </c>
       <c r="C65" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D65" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="E65" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="F65">
         <v>3</v>
       </c>
       <c r="G65" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -3228,19 +3243,19 @@
         <v>71</v>
       </c>
       <c r="C66" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D66" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="E66" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="F66">
         <v>1</v>
       </c>
       <c r="G66" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -3251,19 +3266,19 @@
         <v>72</v>
       </c>
       <c r="C67" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D67" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="E67" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="F67">
         <v>1</v>
       </c>
       <c r="G67" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -3274,19 +3289,19 @@
         <v>73</v>
       </c>
       <c r="C68" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D68" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="E68" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="F68">
         <v>1</v>
       </c>
       <c r="G68" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -3297,19 +3312,19 @@
         <v>74</v>
       </c>
       <c r="C69" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D69" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="E69" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="F69">
         <v>1</v>
       </c>
       <c r="G69" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -3320,19 +3335,19 @@
         <v>75</v>
       </c>
       <c r="C70" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D70" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="E70" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="F70">
         <v>1</v>
       </c>
       <c r="G70" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -3343,19 +3358,19 @@
         <v>76</v>
       </c>
       <c r="C71" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="D71" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="E71" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="F71">
         <v>1</v>
       </c>
       <c r="G71" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -3366,19 +3381,19 @@
         <v>77</v>
       </c>
       <c r="C72" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D72" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="E72" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="F72">
         <v>1</v>
       </c>
       <c r="G72" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -3389,19 +3404,19 @@
         <v>78</v>
       </c>
       <c r="C73" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="D73" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="E73" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="F73">
         <v>1</v>
       </c>
       <c r="G73" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -3412,19 +3427,19 @@
         <v>79</v>
       </c>
       <c r="C74" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D74" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="E74" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="F74">
         <v>1</v>
       </c>
       <c r="G74" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -3435,19 +3450,19 @@
         <v>80</v>
       </c>
       <c r="C75" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="D75" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="E75" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="F75">
         <v>1</v>
       </c>
       <c r="G75" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -3458,19 +3473,19 @@
         <v>81</v>
       </c>
       <c r="C76" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="D76" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="E76" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="F76">
         <v>1</v>
       </c>
       <c r="G76" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -3484,16 +3499,16 @@
         <v>82</v>
       </c>
       <c r="D77" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="E77" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="F77">
         <v>1</v>
       </c>
       <c r="G77" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -3507,16 +3522,16 @@
         <v>83</v>
       </c>
       <c r="D78" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="E78" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="F78">
         <v>1</v>
       </c>
       <c r="G78" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -3530,16 +3545,16 @@
         <v>84</v>
       </c>
       <c r="D79" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="E79" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="F79">
         <v>1</v>
       </c>
       <c r="G79" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -3553,16 +3568,16 @@
         <v>85</v>
       </c>
       <c r="D80" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="E80" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="F80">
         <v>1</v>
       </c>
       <c r="G80" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -3576,16 +3591,16 @@
         <v>86</v>
       </c>
       <c r="D81" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="E81" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="F81">
         <v>1</v>
       </c>
       <c r="G81" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -3599,16 +3614,16 @@
         <v>87</v>
       </c>
       <c r="D82" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="E82" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="F82">
         <v>1</v>
       </c>
       <c r="G82" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -3622,16 +3637,16 @@
         <v>88</v>
       </c>
       <c r="D83" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="E83" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="F83">
         <v>1</v>
       </c>
       <c r="G83" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -3645,16 +3660,16 @@
         <v>89</v>
       </c>
       <c r="D84" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="E84" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="F84">
         <v>1</v>
       </c>
       <c r="G84" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -3668,16 +3683,16 @@
         <v>90</v>
       </c>
       <c r="D85" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="E85" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="F85">
         <v>1</v>
       </c>
       <c r="G85" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -3688,19 +3703,19 @@
         <v>91</v>
       </c>
       <c r="C86" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="D86" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="E86" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="F86">
         <v>1</v>
       </c>
       <c r="G86" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -3714,16 +3729,16 @@
         <v>92</v>
       </c>
       <c r="D87" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="E87" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="F87">
         <v>1</v>
       </c>
       <c r="G87" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -3737,16 +3752,16 @@
         <v>93</v>
       </c>
       <c r="D88" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="E88" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="F88">
         <v>1</v>
       </c>
       <c r="G88" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -3757,19 +3772,19 @@
         <v>94</v>
       </c>
       <c r="C89" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D89" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="E89" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="F89">
         <v>1</v>
       </c>
       <c r="G89" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -3780,19 +3795,19 @@
         <v>95</v>
       </c>
       <c r="C90" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D90" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="E90" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="F90">
         <v>1</v>
       </c>
       <c r="G90" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -3803,19 +3818,19 @@
         <v>96</v>
       </c>
       <c r="C91" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D91" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="E91" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="F91">
         <v>1</v>
       </c>
       <c r="G91" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -3826,19 +3841,19 @@
         <v>97</v>
       </c>
       <c r="C92" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D92" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="E92" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="F92">
         <v>1</v>
       </c>
       <c r="G92" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -3849,19 +3864,19 @@
         <v>98</v>
       </c>
       <c r="C93" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D93" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="E93" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="F93">
         <v>1</v>
       </c>
       <c r="G93" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -3872,19 +3887,19 @@
         <v>99</v>
       </c>
       <c r="C94" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D94" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="E94" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="F94">
         <v>1</v>
       </c>
       <c r="G94" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -3895,19 +3910,19 @@
         <v>100</v>
       </c>
       <c r="C95" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D95" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="E95" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="F95">
         <v>1</v>
       </c>
       <c r="G95" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -3918,19 +3933,19 @@
         <v>101</v>
       </c>
       <c r="C96" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D96" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="E96" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="F96">
         <v>1</v>
       </c>
       <c r="G96" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -3941,19 +3956,19 @@
         <v>102</v>
       </c>
       <c r="C97" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D97" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="E97" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="F97">
         <v>1</v>
       </c>
       <c r="G97" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -3964,19 +3979,19 @@
         <v>103</v>
       </c>
       <c r="C98" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D98" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="E98" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="F98">
         <v>1</v>
       </c>
       <c r="G98" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -3987,19 +4002,19 @@
         <v>104</v>
       </c>
       <c r="C99" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="D99" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="E99" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="F99">
         <v>1</v>
       </c>
       <c r="G99" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -4010,19 +4025,19 @@
         <v>105</v>
       </c>
       <c r="C100" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D100" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="E100" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="F100">
         <v>1</v>
       </c>
       <c r="G100" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -4033,19 +4048,19 @@
         <v>106</v>
       </c>
       <c r="C101" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D101" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="E101" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="F101">
         <v>1</v>
       </c>
       <c r="G101" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -4056,19 +4071,19 @@
         <v>107</v>
       </c>
       <c r="C102" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="D102" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="E102" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="F102">
         <v>1</v>
       </c>
       <c r="G102" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
     </row>
     <row r="103" spans="1:7">
@@ -4079,19 +4094,19 @@
         <v>108</v>
       </c>
       <c r="C103" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D103" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="E103" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="F103">
         <v>1</v>
       </c>
       <c r="G103" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
     </row>
     <row r="104" spans="1:7">
@@ -4102,19 +4117,19 @@
         <v>109</v>
       </c>
       <c r="C104" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="D104" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="E104" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="F104">
         <v>1</v>
       </c>
       <c r="G104" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
     </row>
     <row r="105" spans="1:7">
@@ -4125,19 +4140,19 @@
         <v>110</v>
       </c>
       <c r="C105" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="D105" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="E105" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="F105">
         <v>1</v>
       </c>
       <c r="G105" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
     </row>
     <row r="106" spans="1:7">
@@ -4148,19 +4163,19 @@
         <v>111</v>
       </c>
       <c r="C106" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D106" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="E106" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="F106">
         <v>1</v>
       </c>
       <c r="G106" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
     </row>
     <row r="107" spans="1:7">
@@ -4171,19 +4186,19 @@
         <v>112</v>
       </c>
       <c r="C107" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="D107" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="E107" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="F107">
         <v>1</v>
       </c>
       <c r="G107" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
     </row>
     <row r="108" spans="1:7">
@@ -4197,16 +4212,16 @@
         <v>113</v>
       </c>
       <c r="D108" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="E108" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="F108">
         <v>1</v>
       </c>
       <c r="G108" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
     </row>
     <row r="109" spans="1:7">
@@ -4220,16 +4235,16 @@
         <v>114</v>
       </c>
       <c r="D109" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="E109" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="F109">
         <v>1</v>
       </c>
       <c r="G109" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
     </row>
     <row r="110" spans="1:7">
@@ -4243,16 +4258,16 @@
         <v>115</v>
       </c>
       <c r="D110" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="E110" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="F110">
         <v>1</v>
       </c>
       <c r="G110" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
     </row>
     <row r="111" spans="1:7">
@@ -4263,19 +4278,19 @@
         <v>116</v>
       </c>
       <c r="C111" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="D111" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="E111" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="F111">
         <v>1</v>
       </c>
       <c r="G111" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
     </row>
     <row r="112" spans="1:7">
@@ -4286,19 +4301,19 @@
         <v>117</v>
       </c>
       <c r="C112" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="D112" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="E112" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="F112">
         <v>1</v>
       </c>
       <c r="G112" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
     </row>
     <row r="113" spans="1:7">
@@ -4309,19 +4324,19 @@
         <v>118</v>
       </c>
       <c r="C113" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D113" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="E113" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="F113">
         <v>1</v>
       </c>
       <c r="G113" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
     </row>
     <row r="114" spans="1:7">
@@ -4332,19 +4347,19 @@
         <v>119</v>
       </c>
       <c r="C114" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D114" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="E114" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="F114">
         <v>1</v>
       </c>
       <c r="G114" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
     </row>
     <row r="115" spans="1:7">
@@ -4355,19 +4370,42 @@
         <v>120</v>
       </c>
       <c r="C115" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D115" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="E115" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="F115">
         <v>1</v>
       </c>
       <c r="G115" t="s">
-        <v>458</v>
+        <v>462</v>
+      </c>
+    </row>
+    <row r="116" spans="1:7">
+      <c r="A116">
+        <v>115</v>
+      </c>
+      <c r="B116" t="s">
+        <v>121</v>
+      </c>
+      <c r="C116" t="s">
+        <v>221</v>
+      </c>
+      <c r="D116" t="s">
+        <v>335</v>
+      </c>
+      <c r="E116" t="s">
+        <v>450</v>
+      </c>
+      <c r="F116">
+        <v>1</v>
+      </c>
+      <c r="G116" t="s">
+        <v>463</v>
       </c>
     </row>
   </sheetData>

--- a/data/target_dispatch/파보겔_실제발송_최종정제명단.xlsx
+++ b/data/target_dispatch/파보겔_실제발송_최종정제명단.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="582" uniqueCount="464">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="587" uniqueCount="472">
   <si>
     <t>순번</t>
   </si>
@@ -115,7 +115,7 @@
     <t>애견샵</t>
   </si>
   <si>
-    <t>더조은 펫타운</t>
+    <t>더조은 펫타운 (1.2.3.4.5동)</t>
   </si>
   <si>
     <t>정읍하나</t>
@@ -307,9 +307,6 @@
     <t>삼성켄넬</t>
   </si>
   <si>
-    <t>더조은 펫타운1.2.3.4.5동</t>
-  </si>
-  <si>
     <t>허니펫</t>
   </si>
   <si>
@@ -382,6 +379,12 @@
     <t>우포켄넬</t>
   </si>
   <si>
+    <t>광주강아지분양 펫블리 애견 샵</t>
+  </si>
+  <si>
+    <t>화이트</t>
+  </si>
+  <si>
     <t>정원정</t>
   </si>
   <si>
@@ -460,7 +463,7 @@
     <t>하정숙</t>
   </si>
   <si>
-    <t>박명규</t>
+    <t>박명규외 3인</t>
   </si>
   <si>
     <t>채민선</t>
@@ -619,9 +622,6 @@
     <t>김성학</t>
   </si>
   <si>
-    <t>박명규외 3인</t>
-  </si>
-  <si>
     <t>강동규</t>
   </si>
   <si>
@@ -682,6 +682,12 @@
     <t>서유석</t>
   </si>
   <si>
+    <t>이왕신</t>
+  </si>
+  <si>
+    <t>서원재</t>
+  </si>
+  <si>
     <t>010-3114-1100</t>
   </si>
   <si>
@@ -928,7 +934,7 @@
     <t>010-2980-0180</t>
   </si>
   <si>
-    <t>010-9575-2577</t>
+    <t>010-9572-5776</t>
   </si>
   <si>
     <t>010-5262-6605</t>
@@ -1024,6 +1030,12 @@
     <t>010-3533-1104</t>
   </si>
   <si>
+    <t>010-6868-5999</t>
+  </si>
+  <si>
+    <t>010-3615-7058</t>
+  </si>
+  <si>
     <t>원주시 태장동 흥양로30  대흥아파트202-1202</t>
   </si>
   <si>
@@ -1102,7 +1114,7 @@
     <t>경남김해시분성로343</t>
   </si>
   <si>
-    <t>평창읍종부1길211-27</t>
+    <t>강원도 평창군 평창읍 종부1길 211-27</t>
   </si>
   <si>
     <t>전북특별자치도 정읍시 감곡면 계봉길 72-48</t>
@@ -1270,7 +1282,7 @@
     <t>경북 김천시 남면 연봉길 406-16</t>
   </si>
   <si>
-    <t>인천광역시 남동구 논현동 611-2</t>
+    <t>인천광역시 남동구 논현동 611-2 1층</t>
   </si>
   <si>
     <t>경기도 포천시 선마로 99번길 49-103</t>
@@ -1294,9 +1306,6 @@
     <t>인천시 강화군 불은면 불은북로 430 2층</t>
   </si>
   <si>
-    <t>평창읍종부1길 211-27</t>
-  </si>
-  <si>
     <t>경기도 김포시 대곶북로9 202호</t>
   </si>
   <si>
@@ -1369,12 +1378,21 @@
     <t>경남 창녕군 창녕읍 우포유어농로 643번지</t>
   </si>
   <si>
+    <t>광주광역시 광산구 장덕동 1653 번지 1층 펫블리</t>
+  </si>
+  <si>
+    <t>전남 영광군 묘량면 묘량로 226-36</t>
+  </si>
+  <si>
     <t>[MMS 문자 유입] 펫샵 본품 1병 무료 샘플 신청</t>
   </si>
   <si>
     <t>[MMS 문자 유입] 펫샵 본품 1병 무료 샘플 신청 / [문자 직통 신청] 핸드폰 문자 직접 신청</t>
   </si>
   <si>
+    <t>[MMS 문자 유입] 펫샵 본품 1병 무료 샘플 신청 (구 91번 중복 접수건 27번으로 단일화 통합)</t>
+  </si>
+  <si>
     <t>[히어로 배너 클릭] 펫샵/브리더 본품 1병 무료 샘플 신청 / [MMS 문자 유입] 펫샵 본품 1병 무료 샘플 신청</t>
   </si>
   <si>
@@ -1393,6 +1411,9 @@
     <t>[문자 직통 신청] 핸드폰 문자 직접 신청 (성명과 상호가 없음) / [문자 직통 신청] 성명과 상호가 없음</t>
   </si>
   <si>
+    <t>[전화번호 수정/재발송] 010-9572-5776 (기존 010-9575-2577 오기입 반송건 수정)</t>
+  </si>
+  <si>
     <t>[문자 직통 신청] 핸드폰 문자 직접 신청 (전화번호 확인필요) / [문자 직통 신청] 전화번호 확인 필요</t>
   </si>
   <si>
@@ -1406,6 +1427,9 @@
   </si>
   <si>
     <t>[홍대표 직통 유입] 켄넬/브리더 본품 1병 무료 샘플 신청</t>
+  </si>
+  <si>
+    <t>[이미지/문자 신청 유입] 펫샵 본품 1병 무료 샘플 신청</t>
   </si>
 </sst>
 </file>
@@ -1737,7 +1761,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G116"/>
+  <dimension ref="A1:G117"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -1771,19 +1795,19 @@
         <v>7</v>
       </c>
       <c r="C2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D2" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="E2" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="F2">
         <v>1</v>
       </c>
       <c r="G2" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -1794,19 +1818,19 @@
         <v>8</v>
       </c>
       <c r="C3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D3" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="E3" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="F3">
         <v>1</v>
       </c>
       <c r="G3" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -1817,19 +1841,19 @@
         <v>9</v>
       </c>
       <c r="C4" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D4" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="E4" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="F4">
         <v>1</v>
       </c>
       <c r="G4" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -1840,19 +1864,19 @@
         <v>10</v>
       </c>
       <c r="C5" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D5" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="E5" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="F5">
         <v>1</v>
       </c>
       <c r="G5" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -1863,19 +1887,19 @@
         <v>11</v>
       </c>
       <c r="C6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D6" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="E6" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="F6">
         <v>1</v>
       </c>
       <c r="G6" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -1886,19 +1910,19 @@
         <v>12</v>
       </c>
       <c r="C7" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D7" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="E7" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="F7">
         <v>1</v>
       </c>
       <c r="G7" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -1909,19 +1933,19 @@
         <v>13</v>
       </c>
       <c r="C8" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D8" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="E8" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="F8">
         <v>1</v>
       </c>
       <c r="G8" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -1932,19 +1956,19 @@
         <v>14</v>
       </c>
       <c r="C9" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D9" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="E9" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="F9">
         <v>1</v>
       </c>
       <c r="G9" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -1955,19 +1979,19 @@
         <v>15</v>
       </c>
       <c r="C10" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D10" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="E10" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="F10">
         <v>1</v>
       </c>
       <c r="G10" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -1978,19 +2002,19 @@
         <v>16</v>
       </c>
       <c r="C11" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D11" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="E11" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="F11">
         <v>1</v>
       </c>
       <c r="G11" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -2001,19 +2025,19 @@
         <v>17</v>
       </c>
       <c r="C12" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="E12" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="F12">
         <v>1</v>
       </c>
       <c r="G12" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -2024,19 +2048,19 @@
         <v>18</v>
       </c>
       <c r="C13" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D13" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="E13" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="F13">
         <v>1</v>
       </c>
       <c r="G13" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -2047,19 +2071,19 @@
         <v>19</v>
       </c>
       <c r="C14" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D14" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="E14" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="F14">
         <v>1</v>
       </c>
       <c r="G14" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -2070,19 +2094,19 @@
         <v>20</v>
       </c>
       <c r="C15" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D15" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="E15" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="F15">
         <v>1</v>
       </c>
       <c r="G15" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -2093,19 +2117,19 @@
         <v>21</v>
       </c>
       <c r="C16" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D16" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="E16" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="F16">
         <v>1</v>
       </c>
       <c r="G16" t="s">
-        <v>452</v>
+        <v>457</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -2116,19 +2140,19 @@
         <v>22</v>
       </c>
       <c r="C17" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D17" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="E17" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="F17">
         <v>1</v>
       </c>
       <c r="G17" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -2139,19 +2163,19 @@
         <v>23</v>
       </c>
       <c r="C18" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D18" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="E18" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="F18">
         <v>1</v>
       </c>
       <c r="G18" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -2162,19 +2186,19 @@
         <v>24</v>
       </c>
       <c r="C19" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D19" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="E19" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="F19">
         <v>1</v>
       </c>
       <c r="G19" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -2185,19 +2209,19 @@
         <v>25</v>
       </c>
       <c r="C20" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D20" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="E20" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="F20">
         <v>1</v>
       </c>
       <c r="G20" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -2208,19 +2232,19 @@
         <v>26</v>
       </c>
       <c r="C21" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D21" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E21" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="F21">
         <v>1</v>
       </c>
       <c r="G21" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -2231,19 +2255,19 @@
         <v>27</v>
       </c>
       <c r="C22" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D22" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="E22" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="F22">
         <v>1</v>
       </c>
       <c r="G22" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -2254,19 +2278,19 @@
         <v>28</v>
       </c>
       <c r="C23" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D23" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="E23" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="F23">
         <v>1</v>
       </c>
       <c r="G23" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -2277,19 +2301,19 @@
         <v>29</v>
       </c>
       <c r="C24" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D24" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="E24" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="F24">
         <v>1</v>
       </c>
       <c r="G24" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -2300,19 +2324,19 @@
         <v>30</v>
       </c>
       <c r="C25" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D25" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="E25" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="F25">
         <v>1</v>
       </c>
       <c r="G25" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -2323,19 +2347,19 @@
         <v>31</v>
       </c>
       <c r="C26" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D26" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="E26" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="F26">
         <v>1</v>
       </c>
       <c r="G26" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -2346,19 +2370,19 @@
         <v>32</v>
       </c>
       <c r="C27" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D27" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="E27" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="F27">
         <v>1</v>
       </c>
       <c r="G27" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -2369,19 +2393,19 @@
         <v>33</v>
       </c>
       <c r="C28" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D28" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="E28" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="F28">
         <v>1</v>
       </c>
       <c r="G28" t="s">
-        <v>451</v>
+        <v>458</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -2392,19 +2416,19 @@
         <v>34</v>
       </c>
       <c r="C29" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D29" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="E29" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="F29">
         <v>1</v>
       </c>
       <c r="G29" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -2415,19 +2439,19 @@
         <v>35</v>
       </c>
       <c r="C30" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D30" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="E30" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="F30">
         <v>1</v>
       </c>
       <c r="G30" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -2438,19 +2462,19 @@
         <v>36</v>
       </c>
       <c r="C31" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D31" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="E31" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="F31">
         <v>1</v>
       </c>
       <c r="G31" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -2461,19 +2485,19 @@
         <v>37</v>
       </c>
       <c r="C32" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D32" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="E32" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="F32">
         <v>1</v>
       </c>
       <c r="G32" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -2484,19 +2508,19 @@
         <v>38</v>
       </c>
       <c r="C33" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D33" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="E33" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="F33">
         <v>1</v>
       </c>
       <c r="G33" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -2507,19 +2531,19 @@
         <v>39</v>
       </c>
       <c r="C34" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D34" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="E34" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="F34">
         <v>1</v>
       </c>
       <c r="G34" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -2530,19 +2554,19 @@
         <v>40</v>
       </c>
       <c r="C35" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D35" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="E35" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="F35">
         <v>1</v>
       </c>
       <c r="G35" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -2553,19 +2577,19 @@
         <v>41</v>
       </c>
       <c r="C36" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D36" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="E36" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="F36">
         <v>1</v>
       </c>
       <c r="G36" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -2576,19 +2600,19 @@
         <v>42</v>
       </c>
       <c r="C37" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D37" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="E37" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="F37">
         <v>1</v>
       </c>
       <c r="G37" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -2599,19 +2623,19 @@
         <v>43</v>
       </c>
       <c r="C38" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D38" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="E38" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="F38">
         <v>1</v>
       </c>
       <c r="G38" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -2622,19 +2646,19 @@
         <v>44</v>
       </c>
       <c r="C39" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D39" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="E39" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="F39">
         <v>1</v>
       </c>
       <c r="G39" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -2645,19 +2669,19 @@
         <v>45</v>
       </c>
       <c r="C40" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D40" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="E40" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="F40">
         <v>1</v>
       </c>
       <c r="G40" t="s">
-        <v>453</v>
+        <v>459</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -2668,19 +2692,19 @@
         <v>46</v>
       </c>
       <c r="C41" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D41" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="E41" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="F41">
         <v>1</v>
       </c>
       <c r="G41" t="s">
-        <v>452</v>
+        <v>457</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -2691,19 +2715,19 @@
         <v>47</v>
       </c>
       <c r="C42" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D42" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="E42" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="F42">
         <v>1</v>
       </c>
       <c r="G42" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -2714,19 +2738,19 @@
         <v>48</v>
       </c>
       <c r="C43" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D43" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="E43" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="F43">
         <v>1</v>
       </c>
       <c r="G43" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -2737,19 +2761,19 @@
         <v>49</v>
       </c>
       <c r="C44" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D44" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="E44" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="F44">
         <v>1</v>
       </c>
       <c r="G44" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -2760,19 +2784,19 @@
         <v>50</v>
       </c>
       <c r="C45" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D45" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="E45" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="F45">
         <v>1</v>
       </c>
       <c r="G45" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -2783,19 +2807,19 @@
         <v>51</v>
       </c>
       <c r="C46" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D46" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="E46" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="F46">
         <v>1</v>
       </c>
       <c r="G46" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -2806,19 +2830,19 @@
         <v>52</v>
       </c>
       <c r="C47" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D47" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="E47" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="F47">
         <v>1</v>
       </c>
       <c r="G47" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -2829,19 +2853,19 @@
         <v>53</v>
       </c>
       <c r="C48" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D48" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="E48" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="F48">
         <v>1</v>
       </c>
       <c r="G48" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -2852,19 +2876,19 @@
         <v>54</v>
       </c>
       <c r="C49" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D49" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="E49" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="F49">
         <v>1</v>
       </c>
       <c r="G49" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -2875,19 +2899,19 @@
         <v>55</v>
       </c>
       <c r="C50" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D50" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="E50" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="F50">
         <v>1</v>
       </c>
       <c r="G50" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -2898,19 +2922,19 @@
         <v>56</v>
       </c>
       <c r="C51" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D51" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="E51" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="F51">
         <v>1</v>
       </c>
       <c r="G51" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -2921,19 +2945,19 @@
         <v>57</v>
       </c>
       <c r="C52" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D52" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="E52" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="F52">
         <v>1</v>
       </c>
       <c r="G52" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -2944,19 +2968,19 @@
         <v>58</v>
       </c>
       <c r="C53" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D53" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="E53" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="F53">
         <v>1</v>
       </c>
       <c r="G53" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -2967,19 +2991,19 @@
         <v>59</v>
       </c>
       <c r="C54" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D54" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="E54" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="F54">
         <v>1</v>
       </c>
       <c r="G54" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -2990,19 +3014,19 @@
         <v>60</v>
       </c>
       <c r="C55" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D55" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="E55" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="F55">
         <v>1</v>
       </c>
       <c r="G55" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -3013,19 +3037,19 @@
         <v>61</v>
       </c>
       <c r="C56" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D56" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="E56" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="F56">
         <v>1</v>
       </c>
       <c r="G56" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -3036,19 +3060,19 @@
         <v>62</v>
       </c>
       <c r="C57" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D57" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E57" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="F57">
         <v>1</v>
       </c>
       <c r="G57" t="s">
-        <v>454</v>
+        <v>460</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -3059,19 +3083,19 @@
         <v>63</v>
       </c>
       <c r="C58" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D58" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="E58" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="F58">
         <v>1</v>
       </c>
       <c r="G58" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -3082,19 +3106,19 @@
         <v>64</v>
       </c>
       <c r="C59" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D59" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E59" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="F59">
         <v>1</v>
       </c>
       <c r="G59" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -3105,19 +3129,19 @@
         <v>65</v>
       </c>
       <c r="C60" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D60" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="E60" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="F60">
         <v>1</v>
       </c>
       <c r="G60" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -3128,19 +3152,19 @@
         <v>66</v>
       </c>
       <c r="C61" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="D61" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="E61" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="F61">
         <v>1</v>
       </c>
       <c r="G61" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -3151,19 +3175,19 @@
         <v>67</v>
       </c>
       <c r="C62" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D62" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="E62" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="F62">
         <v>1</v>
       </c>
       <c r="G62" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -3174,19 +3198,19 @@
         <v>68</v>
       </c>
       <c r="C63" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D63" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="E63" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="F63">
         <v>1</v>
       </c>
       <c r="G63" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -3197,19 +3221,19 @@
         <v>69</v>
       </c>
       <c r="C64" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D64" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="E64" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="F64">
         <v>1</v>
       </c>
       <c r="G64" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -3220,19 +3244,19 @@
         <v>70</v>
       </c>
       <c r="C65" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D65" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="E65" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="F65">
         <v>3</v>
       </c>
       <c r="G65" t="s">
-        <v>455</v>
+        <v>461</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -3243,19 +3267,19 @@
         <v>71</v>
       </c>
       <c r="C66" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D66" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="E66" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="F66">
         <v>1</v>
       </c>
       <c r="G66" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -3266,19 +3290,19 @@
         <v>72</v>
       </c>
       <c r="C67" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D67" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="E67" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="F67">
         <v>1</v>
       </c>
       <c r="G67" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -3289,19 +3313,19 @@
         <v>73</v>
       </c>
       <c r="C68" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D68" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="E68" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="F68">
         <v>1</v>
       </c>
       <c r="G68" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -3312,19 +3336,19 @@
         <v>74</v>
       </c>
       <c r="C69" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D69" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="E69" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="F69">
         <v>1</v>
       </c>
       <c r="G69" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -3335,19 +3359,19 @@
         <v>75</v>
       </c>
       <c r="C70" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="D70" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="E70" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="F70">
         <v>1</v>
       </c>
       <c r="G70" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -3358,19 +3382,19 @@
         <v>76</v>
       </c>
       <c r="C71" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D71" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="E71" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="F71">
         <v>1</v>
       </c>
       <c r="G71" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -3381,19 +3405,19 @@
         <v>77</v>
       </c>
       <c r="C72" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="D72" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="E72" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="F72">
         <v>1</v>
       </c>
       <c r="G72" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -3404,19 +3428,19 @@
         <v>78</v>
       </c>
       <c r="C73" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D73" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="E73" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="F73">
         <v>1</v>
       </c>
       <c r="G73" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -3427,19 +3451,19 @@
         <v>79</v>
       </c>
       <c r="C74" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="D74" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="E74" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="F74">
         <v>1</v>
       </c>
       <c r="G74" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -3450,19 +3474,19 @@
         <v>80</v>
       </c>
       <c r="C75" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="D75" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="E75" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="F75">
         <v>1</v>
       </c>
       <c r="G75" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -3473,19 +3497,19 @@
         <v>81</v>
       </c>
       <c r="C76" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="D76" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="E76" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="F76">
         <v>1</v>
       </c>
       <c r="G76" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -3499,16 +3523,16 @@
         <v>82</v>
       </c>
       <c r="D77" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="E77" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="F77">
         <v>1</v>
       </c>
       <c r="G77" t="s">
-        <v>456</v>
+        <v>462</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -3522,16 +3546,16 @@
         <v>83</v>
       </c>
       <c r="D78" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="E78" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="F78">
         <v>1</v>
       </c>
       <c r="G78" t="s">
-        <v>456</v>
+        <v>462</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -3545,16 +3569,16 @@
         <v>84</v>
       </c>
       <c r="D79" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="E79" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="F79">
         <v>1</v>
       </c>
       <c r="G79" t="s">
-        <v>456</v>
+        <v>462</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -3568,16 +3592,16 @@
         <v>85</v>
       </c>
       <c r="D80" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="E80" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="F80">
         <v>1</v>
       </c>
       <c r="G80" t="s">
-        <v>456</v>
+        <v>462</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -3591,16 +3615,16 @@
         <v>86</v>
       </c>
       <c r="D81" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="E81" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="F81">
         <v>1</v>
       </c>
       <c r="G81" t="s">
-        <v>457</v>
+        <v>463</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -3614,16 +3638,16 @@
         <v>87</v>
       </c>
       <c r="D82" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="E82" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="F82">
         <v>1</v>
       </c>
       <c r="G82" t="s">
-        <v>458</v>
+        <v>464</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -3637,16 +3661,16 @@
         <v>88</v>
       </c>
       <c r="D83" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="E83" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="F83">
         <v>1</v>
       </c>
       <c r="G83" t="s">
-        <v>456</v>
+        <v>462</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -3660,16 +3684,16 @@
         <v>89</v>
       </c>
       <c r="D84" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="E84" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="F84">
         <v>1</v>
       </c>
       <c r="G84" t="s">
-        <v>456</v>
+        <v>465</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -3683,16 +3707,16 @@
         <v>90</v>
       </c>
       <c r="D85" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="E85" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="F85">
         <v>1</v>
       </c>
       <c r="G85" t="s">
-        <v>456</v>
+        <v>462</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -3703,19 +3727,19 @@
         <v>91</v>
       </c>
       <c r="C86" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D86" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="E86" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="F86">
         <v>1</v>
       </c>
       <c r="G86" t="s">
-        <v>456</v>
+        <v>462</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -3729,16 +3753,16 @@
         <v>92</v>
       </c>
       <c r="D87" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="E87" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="F87">
         <v>1</v>
       </c>
       <c r="G87" t="s">
-        <v>459</v>
+        <v>466</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -3752,16 +3776,16 @@
         <v>93</v>
       </c>
       <c r="D88" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="E88" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="F88">
         <v>1</v>
       </c>
       <c r="G88" t="s">
-        <v>456</v>
+        <v>462</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -3772,19 +3796,19 @@
         <v>94</v>
       </c>
       <c r="C89" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D89" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="E89" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="F89">
         <v>1</v>
       </c>
       <c r="G89" t="s">
-        <v>454</v>
+        <v>460</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -3795,19 +3819,19 @@
         <v>95</v>
       </c>
       <c r="C90" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D90" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="E90" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="F90">
         <v>1</v>
       </c>
       <c r="G90" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -3818,19 +3842,19 @@
         <v>96</v>
       </c>
       <c r="C91" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D91" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="E91" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="F91">
         <v>1</v>
       </c>
       <c r="G91" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -3841,19 +3865,19 @@
         <v>97</v>
       </c>
       <c r="C92" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D92" t="s">
-        <v>248</v>
+        <v>314</v>
       </c>
       <c r="E92" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="F92">
         <v>1</v>
       </c>
       <c r="G92" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -3864,19 +3888,19 @@
         <v>98</v>
       </c>
       <c r="C93" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D93" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="E93" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="F93">
         <v>1</v>
       </c>
       <c r="G93" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -3887,19 +3911,19 @@
         <v>99</v>
       </c>
       <c r="C94" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D94" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="E94" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="F94">
         <v>1</v>
       </c>
       <c r="G94" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -3910,19 +3934,19 @@
         <v>100</v>
       </c>
       <c r="C95" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D95" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="E95" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="F95">
         <v>1</v>
       </c>
       <c r="G95" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -3933,19 +3957,19 @@
         <v>101</v>
       </c>
       <c r="C96" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D96" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="E96" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="F96">
         <v>1</v>
       </c>
       <c r="G96" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -3956,19 +3980,19 @@
         <v>102</v>
       </c>
       <c r="C97" t="s">
-        <v>206</v>
+        <v>185</v>
       </c>
       <c r="D97" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="E97" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="F97">
         <v>1</v>
       </c>
       <c r="G97" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -3979,19 +4003,19 @@
         <v>103</v>
       </c>
       <c r="C98" t="s">
-        <v>184</v>
+        <v>207</v>
       </c>
       <c r="D98" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="E98" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="F98">
         <v>1</v>
       </c>
       <c r="G98" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -4002,19 +4026,19 @@
         <v>104</v>
       </c>
       <c r="C99" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D99" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="E99" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="F99">
         <v>1</v>
       </c>
       <c r="G99" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -4025,19 +4049,19 @@
         <v>105</v>
       </c>
       <c r="C100" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D100" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="E100" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="F100">
         <v>1</v>
       </c>
       <c r="G100" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -4048,19 +4072,19 @@
         <v>106</v>
       </c>
       <c r="C101" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="D101" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="E101" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="F101">
         <v>1</v>
       </c>
       <c r="G101" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -4071,19 +4095,19 @@
         <v>107</v>
       </c>
       <c r="C102" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D102" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="E102" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="F102">
         <v>1</v>
       </c>
       <c r="G102" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
     </row>
     <row r="103" spans="1:7">
@@ -4094,19 +4118,19 @@
         <v>108</v>
       </c>
       <c r="C103" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="D103" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="E103" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="F103">
         <v>1</v>
       </c>
       <c r="G103" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
     </row>
     <row r="104" spans="1:7">
@@ -4117,19 +4141,19 @@
         <v>109</v>
       </c>
       <c r="C104" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="D104" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="E104" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="F104">
         <v>1</v>
       </c>
       <c r="G104" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
     </row>
     <row r="105" spans="1:7">
@@ -4140,19 +4164,19 @@
         <v>110</v>
       </c>
       <c r="C105" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D105" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="E105" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="F105">
         <v>1</v>
       </c>
       <c r="G105" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
     </row>
     <row r="106" spans="1:7">
@@ -4163,19 +4187,19 @@
         <v>111</v>
       </c>
       <c r="C106" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="D106" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="E106" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="F106">
         <v>1</v>
       </c>
       <c r="G106" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
     </row>
     <row r="107" spans="1:7">
@@ -4186,19 +4210,19 @@
         <v>112</v>
       </c>
       <c r="C107" t="s">
-        <v>215</v>
+        <v>112</v>
       </c>
       <c r="D107" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="E107" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="F107">
         <v>1</v>
       </c>
       <c r="G107" t="s">
-        <v>451</v>
+        <v>462</v>
       </c>
     </row>
     <row r="108" spans="1:7">
@@ -4212,16 +4236,16 @@
         <v>113</v>
       </c>
       <c r="D108" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="E108" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="F108">
         <v>1</v>
       </c>
       <c r="G108" t="s">
-        <v>456</v>
+        <v>462</v>
       </c>
     </row>
     <row r="109" spans="1:7">
@@ -4235,16 +4259,16 @@
         <v>114</v>
       </c>
       <c r="D109" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="E109" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="F109">
         <v>1</v>
       </c>
       <c r="G109" t="s">
-        <v>456</v>
+        <v>462</v>
       </c>
     </row>
     <row r="110" spans="1:7">
@@ -4255,13 +4279,13 @@
         <v>115</v>
       </c>
       <c r="C110" t="s">
-        <v>115</v>
+        <v>216</v>
       </c>
       <c r="D110" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="E110" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="F110">
         <v>1</v>
@@ -4278,19 +4302,19 @@
         <v>116</v>
       </c>
       <c r="C111" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="D111" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="E111" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="F111">
         <v>1</v>
       </c>
       <c r="G111" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
     </row>
     <row r="112" spans="1:7">
@@ -4301,19 +4325,19 @@
         <v>117</v>
       </c>
       <c r="C112" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D112" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="E112" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="F112">
         <v>1</v>
       </c>
       <c r="G112" t="s">
-        <v>451</v>
+        <v>467</v>
       </c>
     </row>
     <row r="113" spans="1:7">
@@ -4324,19 +4348,19 @@
         <v>118</v>
       </c>
       <c r="C113" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D113" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="E113" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="F113">
         <v>1</v>
       </c>
       <c r="G113" t="s">
-        <v>460</v>
+        <v>468</v>
       </c>
     </row>
     <row r="114" spans="1:7">
@@ -4347,19 +4371,19 @@
         <v>119</v>
       </c>
       <c r="C114" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D114" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="E114" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="F114">
         <v>1</v>
       </c>
       <c r="G114" t="s">
-        <v>461</v>
+        <v>469</v>
       </c>
     </row>
     <row r="115" spans="1:7">
@@ -4370,19 +4394,19 @@
         <v>120</v>
       </c>
       <c r="C115" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="D115" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="E115" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="F115">
         <v>1</v>
       </c>
       <c r="G115" t="s">
-        <v>462</v>
+        <v>470</v>
       </c>
     </row>
     <row r="116" spans="1:7">
@@ -4393,19 +4417,42 @@
         <v>121</v>
       </c>
       <c r="C116" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D116" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="E116" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="F116">
         <v>1</v>
       </c>
       <c r="G116" t="s">
-        <v>463</v>
+        <v>456</v>
+      </c>
+    </row>
+    <row r="117" spans="1:7">
+      <c r="A117">
+        <v>116</v>
+      </c>
+      <c r="B117" t="s">
+        <v>122</v>
+      </c>
+      <c r="C117" t="s">
+        <v>223</v>
+      </c>
+      <c r="D117" t="s">
+        <v>339</v>
+      </c>
+      <c r="E117" t="s">
+        <v>455</v>
+      </c>
+      <c r="F117">
+        <v>1</v>
+      </c>
+      <c r="G117" t="s">
+        <v>471</v>
       </c>
     </row>
   </sheetData>

--- a/data/target_dispatch/파보겔_실제발송_최종정제명단.xlsx
+++ b/data/target_dispatch/파보겔_실제발송_최종정제명단.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="587" uniqueCount="472">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="940" uniqueCount="787">
   <si>
     <t>순번</t>
   </si>
@@ -115,7 +115,7 @@
     <t>애견샵</t>
   </si>
   <si>
-    <t>더조은 펫타운 (1.2.3.4.5동)</t>
+    <t>더조은 펫타운</t>
   </si>
   <si>
     <t>정읍하나</t>
@@ -385,6 +385,213 @@
     <t>화이트</t>
   </si>
   <si>
+    <t>천하양계</t>
+  </si>
+  <si>
+    <t>🌕 [추석지인선물] 박세은</t>
+  </si>
+  <si>
+    <t>🌕 [추석지인선물] 최치호</t>
+  </si>
+  <si>
+    <t>🌕 [추석지인선물] 지용현</t>
+  </si>
+  <si>
+    <t>🌕 [추석지인선물] 유은솔</t>
+  </si>
+  <si>
+    <t>🌕 [추석지인선물] 박종협</t>
+  </si>
+  <si>
+    <t>🌕 [추석지인선물] 김민철</t>
+  </si>
+  <si>
+    <t>🌕 [추석지인선물] 이채연</t>
+  </si>
+  <si>
+    <t>🌕 [추석지인선물] 박민서</t>
+  </si>
+  <si>
+    <t>🌕 [추석지인선물] 주미영</t>
+  </si>
+  <si>
+    <t>🌕 [추석지인선물] 이영설</t>
+  </si>
+  <si>
+    <t>🌕 [추석지인선물] 우지영</t>
+  </si>
+  <si>
+    <t>🌕 [추석지인선물] 오양근</t>
+  </si>
+  <si>
+    <t>🌕 [추석지인선물] 김성</t>
+  </si>
+  <si>
+    <t>🌕 [추석지인선물] 정연택</t>
+  </si>
+  <si>
+    <t>🌕 [추석지인선물] 류호상</t>
+  </si>
+  <si>
+    <t>🌕 [추석지인선물] 송선경</t>
+  </si>
+  <si>
+    <t>🌕 [추석지인선물] 감동근</t>
+  </si>
+  <si>
+    <t>🌕 [추석지인선물] 사악이</t>
+  </si>
+  <si>
+    <t>🌕 [추석지인선물] 정미진</t>
+  </si>
+  <si>
+    <t>🌕 [추석지인선물] 이종국</t>
+  </si>
+  <si>
+    <t>🌕 [추석지인선물] 박헌영</t>
+  </si>
+  <si>
+    <t>🌕 [추석지인선물] 허아리</t>
+  </si>
+  <si>
+    <t>🌕 [추석지인선물] 양희욱</t>
+  </si>
+  <si>
+    <t>🌕 [추석지인선물] 윤은해</t>
+  </si>
+  <si>
+    <t>🌕 [추석지인선물] 홍세화</t>
+  </si>
+  <si>
+    <t>🌕 [추석지인선물] 황미옥</t>
+  </si>
+  <si>
+    <t>🌕 [추석지인선물] 하재환</t>
+  </si>
+  <si>
+    <t>🌕 [추석지인선물] 한정희</t>
+  </si>
+  <si>
+    <t>퍼피하우스</t>
+  </si>
+  <si>
+    <t>루이몽</t>
+  </si>
+  <si>
+    <t>베어룸바이퍼피베어</t>
+  </si>
+  <si>
+    <t>루나</t>
+  </si>
+  <si>
+    <t>러브펫</t>
+  </si>
+  <si>
+    <t>어바웃독</t>
+  </si>
+  <si>
+    <t>봉화 김학봉농장</t>
+  </si>
+  <si>
+    <t>앙쥬펫</t>
+  </si>
+  <si>
+    <t>펫샵</t>
+  </si>
+  <si>
+    <t>니팅캣</t>
+  </si>
+  <si>
+    <t>빠찌애견</t>
+  </si>
+  <si>
+    <t>발리 애견호텔</t>
+  </si>
+  <si>
+    <t>정아켄넬</t>
+  </si>
+  <si>
+    <t>그리시아화이트매직</t>
+  </si>
+  <si>
+    <t>나루터켄넬</t>
+  </si>
+  <si>
+    <t>블루앤코</t>
+  </si>
+  <si>
+    <t>어도러블</t>
+  </si>
+  <si>
+    <t>익산귀엽개</t>
+  </si>
+  <si>
+    <t>컴투펫</t>
+  </si>
+  <si>
+    <t>마리켄넬</t>
+  </si>
+  <si>
+    <t>브랜드</t>
+  </si>
+  <si>
+    <t>피아켄넬</t>
+  </si>
+  <si>
+    <t>아리랑밸리켄넬</t>
+  </si>
+  <si>
+    <t>마루애견</t>
+  </si>
+  <si>
+    <t>FAPADOG KOREA (Galaxy Pom)</t>
+  </si>
+  <si>
+    <t>하이몽</t>
+  </si>
+  <si>
+    <t>상호미기재</t>
+  </si>
+  <si>
+    <t>반항</t>
+  </si>
+  <si>
+    <t>애견세계</t>
+  </si>
+  <si>
+    <t>동성농장</t>
+  </si>
+  <si>
+    <t>우리애견</t>
+  </si>
+  <si>
+    <t>윤진켄넬</t>
+  </si>
+  <si>
+    <t>홍정의 (브리더)</t>
+  </si>
+  <si>
+    <t>강아지나라</t>
+  </si>
+  <si>
+    <t>청통농장</t>
+  </si>
+  <si>
+    <t>정읍애견사랑</t>
+  </si>
+  <si>
+    <t>멍벤져스</t>
+  </si>
+  <si>
+    <t>오라애견</t>
+  </si>
+  <si>
+    <t>K타운</t>
+  </si>
+  <si>
+    <t>강아지대공원</t>
+  </si>
+  <si>
     <t>정원정</t>
   </si>
   <si>
@@ -463,7 +670,7 @@
     <t>하정숙</t>
   </si>
   <si>
-    <t>박명규외 3인</t>
+    <t>박명규</t>
   </si>
   <si>
     <t>채민선</t>
@@ -670,7 +877,7 @@
     <t>우지훈</t>
   </si>
   <si>
-    <t>댕댕러브펫</t>
+    <t>-</t>
   </si>
   <si>
     <t>문수미</t>
@@ -688,6 +895,219 @@
     <t>서원재</t>
   </si>
   <si>
+    <t>김태경</t>
+  </si>
+  <si>
+    <t>박세은</t>
+  </si>
+  <si>
+    <t>최치호</t>
+  </si>
+  <si>
+    <t>지용현</t>
+  </si>
+  <si>
+    <t>유은솔</t>
+  </si>
+  <si>
+    <t>박종협</t>
+  </si>
+  <si>
+    <t>김민철</t>
+  </si>
+  <si>
+    <t>이채연</t>
+  </si>
+  <si>
+    <t>박민서</t>
+  </si>
+  <si>
+    <t>주미영</t>
+  </si>
+  <si>
+    <t>이영설</t>
+  </si>
+  <si>
+    <t>우지영</t>
+  </si>
+  <si>
+    <t>오양근</t>
+  </si>
+  <si>
+    <t>김성</t>
+  </si>
+  <si>
+    <t>정연택</t>
+  </si>
+  <si>
+    <t>류호상</t>
+  </si>
+  <si>
+    <t>송선경</t>
+  </si>
+  <si>
+    <t>감동근</t>
+  </si>
+  <si>
+    <t>사악이</t>
+  </si>
+  <si>
+    <t>정미진</t>
+  </si>
+  <si>
+    <t>이종국</t>
+  </si>
+  <si>
+    <t>박헌영</t>
+  </si>
+  <si>
+    <t>허아리</t>
+  </si>
+  <si>
+    <t>양희욱</t>
+  </si>
+  <si>
+    <t>윤은해</t>
+  </si>
+  <si>
+    <t>홍세화</t>
+  </si>
+  <si>
+    <t>황미옥</t>
+  </si>
+  <si>
+    <t>하재환</t>
+  </si>
+  <si>
+    <t>한정희</t>
+  </si>
+  <si>
+    <t>류지민</t>
+  </si>
+  <si>
+    <t>이권영</t>
+  </si>
+  <si>
+    <t>박지연</t>
+  </si>
+  <si>
+    <t>이재호</t>
+  </si>
+  <si>
+    <t>조진혁</t>
+  </si>
+  <si>
+    <t>차기석</t>
+  </si>
+  <si>
+    <t>김학봉</t>
+  </si>
+  <si>
+    <t>강성민</t>
+  </si>
+  <si>
+    <t>김용일</t>
+  </si>
+  <si>
+    <t>이용섭</t>
+  </si>
+  <si>
+    <t>박송</t>
+  </si>
+  <si>
+    <t>유명애</t>
+  </si>
+  <si>
+    <t>배명란</t>
+  </si>
+  <si>
+    <t>강성아</t>
+  </si>
+  <si>
+    <t>노영조</t>
+  </si>
+  <si>
+    <t>김소화</t>
+  </si>
+  <si>
+    <t>정성일</t>
+  </si>
+  <si>
+    <t>이보영</t>
+  </si>
+  <si>
+    <t>박상석</t>
+  </si>
+  <si>
+    <t>김순희</t>
+  </si>
+  <si>
+    <t>이주연</t>
+  </si>
+  <si>
+    <t>박동주</t>
+  </si>
+  <si>
+    <t>임재명</t>
+  </si>
+  <si>
+    <t>여석래</t>
+  </si>
+  <si>
+    <t>김지훈</t>
+  </si>
+  <si>
+    <t>원누리</t>
+  </si>
+  <si>
+    <t>유선환</t>
+  </si>
+  <si>
+    <t>강대명</t>
+  </si>
+  <si>
+    <t>강경호</t>
+  </si>
+  <si>
+    <t>이승환</t>
+  </si>
+  <si>
+    <t>성명미상</t>
+  </si>
+  <si>
+    <t>유복남</t>
+  </si>
+  <si>
+    <t>문의호</t>
+  </si>
+  <si>
+    <t>이명순</t>
+  </si>
+  <si>
+    <t>홍정의</t>
+  </si>
+  <si>
+    <t>허영란</t>
+  </si>
+  <si>
+    <t>도병천</t>
+  </si>
+  <si>
+    <t>원태경</t>
+  </si>
+  <si>
+    <t>박정한</t>
+  </si>
+  <si>
+    <t>정미애</t>
+  </si>
+  <si>
+    <t>윤익수</t>
+  </si>
+  <si>
+    <t>이완구</t>
+  </si>
+  <si>
     <t>010-3114-1100</t>
   </si>
   <si>
@@ -934,7 +1354,7 @@
     <t>010-2980-0180</t>
   </si>
   <si>
-    <t>010-9572-5776</t>
+    <t>010-9575-2577</t>
   </si>
   <si>
     <t>010-5262-6605</t>
@@ -943,9 +1363,6 @@
     <t>010-2982-6849</t>
   </si>
   <si>
-    <t>010-3848-5709</t>
-  </si>
-  <si>
     <t>010-8433-6449</t>
   </si>
   <si>
@@ -1018,7 +1435,7 @@
     <t>010-8054-7773</t>
   </si>
   <si>
-    <t>031-557-6767</t>
+    <t>0315576767</t>
   </si>
   <si>
     <t>010-9700-8733</t>
@@ -1036,6 +1453,219 @@
     <t>010-3615-7058</t>
   </si>
   <si>
+    <t>010-4419-3110</t>
+  </si>
+  <si>
+    <t>010-2750-2269</t>
+  </si>
+  <si>
+    <t>010-9111-5418</t>
+  </si>
+  <si>
+    <t>010-8859-9413</t>
+  </si>
+  <si>
+    <t>010-3381-7317</t>
+  </si>
+  <si>
+    <t>010-4713-5943</t>
+  </si>
+  <si>
+    <t>010-7189-1657</t>
+  </si>
+  <si>
+    <t>010-9741-9967</t>
+  </si>
+  <si>
+    <t>010-4459-7662</t>
+  </si>
+  <si>
+    <t>010-7622-7628</t>
+  </si>
+  <si>
+    <t>010-8745-2283</t>
+  </si>
+  <si>
+    <t>010-6303-1261</t>
+  </si>
+  <si>
+    <t>010-3200-8380</t>
+  </si>
+  <si>
+    <t>010-7277-1972</t>
+  </si>
+  <si>
+    <t>010-3282-6427</t>
+  </si>
+  <si>
+    <t>010-9383-6110</t>
+  </si>
+  <si>
+    <t>010-3484-7745</t>
+  </si>
+  <si>
+    <t>010-9022-2784</t>
+  </si>
+  <si>
+    <t>010-9288-0852</t>
+  </si>
+  <si>
+    <t>010-7496-2344</t>
+  </si>
+  <si>
+    <t>010-4756-9450</t>
+  </si>
+  <si>
+    <t>010-9705-0560</t>
+  </si>
+  <si>
+    <t>010-3384-2606</t>
+  </si>
+  <si>
+    <t>010-6286-1108</t>
+  </si>
+  <si>
+    <t>010-8818-4592</t>
+  </si>
+  <si>
+    <t>010-6363-3754</t>
+  </si>
+  <si>
+    <t>010-6516-5528</t>
+  </si>
+  <si>
+    <t>010-7421-7275</t>
+  </si>
+  <si>
+    <t>010-7650-8657</t>
+  </si>
+  <si>
+    <t>010-8110-4118</t>
+  </si>
+  <si>
+    <t>010-9318-5338</t>
+  </si>
+  <si>
+    <t>010-8577-6461</t>
+  </si>
+  <si>
+    <t>010-6690-2105</t>
+  </si>
+  <si>
+    <t>010-4470-0322</t>
+  </si>
+  <si>
+    <t>010-9281-0077</t>
+  </si>
+  <si>
+    <t>010-3596-9099</t>
+  </si>
+  <si>
+    <t>010-3436-5240</t>
+  </si>
+  <si>
+    <t>010-6407-3176</t>
+  </si>
+  <si>
+    <t>010-3342-4447</t>
+  </si>
+  <si>
+    <t>010-3410-6044</t>
+  </si>
+  <si>
+    <t>010-6417-7820</t>
+  </si>
+  <si>
+    <t>010-9107-2223</t>
+  </si>
+  <si>
+    <t>010-7760-9970</t>
+  </si>
+  <si>
+    <t>010-8793-0014</t>
+  </si>
+  <si>
+    <t>010-8598-4625</t>
+  </si>
+  <si>
+    <t>010-8601-6515</t>
+  </si>
+  <si>
+    <t>010-9977-6315</t>
+  </si>
+  <si>
+    <t>010-5293-2396</t>
+  </si>
+  <si>
+    <t>010-5157-1555</t>
+  </si>
+  <si>
+    <t>010-6660-5647</t>
+  </si>
+  <si>
+    <t>010-9124-0820</t>
+  </si>
+  <si>
+    <t>010-8558-0015</t>
+  </si>
+  <si>
+    <t>010-8994-5414</t>
+  </si>
+  <si>
+    <t>010-2070-4433</t>
+  </si>
+  <si>
+    <t>010-5677-1222</t>
+  </si>
+  <si>
+    <t>010-3535-9663</t>
+  </si>
+  <si>
+    <t>010-5012-3969</t>
+  </si>
+  <si>
+    <t>010-5238-5485</t>
+  </si>
+  <si>
+    <t>010-4326-3513</t>
+  </si>
+  <si>
+    <t>010-8625-5999</t>
+  </si>
+  <si>
+    <t>010-9266-6351</t>
+  </si>
+  <si>
+    <t>010-6405-0089</t>
+  </si>
+  <si>
+    <t>010-2262-9267</t>
+  </si>
+  <si>
+    <t>010-7510-8246</t>
+  </si>
+  <si>
+    <t>010-4424-7972</t>
+  </si>
+  <si>
+    <t>010-3457-0354</t>
+  </si>
+  <si>
+    <t>010-6359-4019</t>
+  </si>
+  <si>
+    <t>010-2208-9245</t>
+  </si>
+  <si>
+    <t>010-2737-3032</t>
+  </si>
+  <si>
+    <t>010-8248-1048</t>
+  </si>
+  <si>
+    <t>010-2828-9779</t>
+  </si>
+  <si>
     <t>원주시 태장동 흥양로30  대흥아파트202-1202</t>
   </si>
   <si>
@@ -1114,7 +1744,7 @@
     <t>경남김해시분성로343</t>
   </si>
   <si>
-    <t>강원도 평창군 평창읍 종부1길 211-27</t>
+    <t>평창읍종부1길211-27</t>
   </si>
   <si>
     <t>전북특별자치도 정읍시 감곡면 계봉길 72-48</t>
@@ -1282,7 +1912,7 @@
     <t>경북 김천시 남면 연봉길 406-16</t>
   </si>
   <si>
-    <t>인천광역시 남동구 논현동 611-2 1층</t>
+    <t>인천광역시 남동구 논현동 611-2</t>
   </si>
   <si>
     <t>경기도 포천시 선마로 99번길 49-103</t>
@@ -1297,10 +1927,10 @@
     <t>인천광역시 연수구 먼우금로 197, 114호</t>
   </si>
   <si>
-    <t>경기도 구리시 검배로6번길 8 댕냥구리</t>
-  </si>
-  <si>
-    <t>전남 나주시 금천면 신가신촌길 9-11</t>
+    <t>경기도 구리시 검배로6번길8 댕냥구리</t>
+  </si>
+  <si>
+    <t>전남광주통합특별시 나주시 금천면 신가신촌길 9-11</t>
   </si>
   <si>
     <t>인천시 강화군 불은면 불은북로 430 2층</t>
@@ -1312,15 +1942,12 @@
     <t>충북 음성군 금왕읍 대금로 1499 1층 멍스펫</t>
   </si>
   <si>
-    <t>고창군고창읍 덕산리 966-1 캣츠비 맨안쪽</t>
+    <t>고창군고창읍 덕산리 966ㅡ1  캣츠비 맨안쪽</t>
   </si>
   <si>
     <t>광주 북구 면앙로 14 . 1층</t>
   </si>
   <si>
-    <t>경남 고성군 거류면 동해로 447-15</t>
-  </si>
-  <si>
     <t>도창동 114-5 애견</t>
   </si>
   <si>
@@ -1360,7 +1987,7 @@
     <t>충북 옥천군 안남면 중봉 213-34</t>
   </si>
   <si>
-    <t>경기도 하남시 망월동 1098 203-1 이정훈강아지</t>
+    <t>경기도  하남시 망월동 1098 203-1 이정훈강아지</t>
   </si>
   <si>
     <t>경북 영천시 북안면 대경로2424</t>
@@ -1384,15 +2011,225 @@
     <t>전남 영광군 묘량면 묘량로 226-36</t>
   </si>
   <si>
+    <t>경기도 평택시 비전동</t>
+  </si>
+  <si>
+    <t>대전광역시 옥천로 38 신흥마을아파트 101동 1103호</t>
+  </si>
+  <si>
+    <t>서울시 마포구 독막로42길 2 마포자이아파트 107동 1502호</t>
+  </si>
+  <si>
+    <t>충북 청주시 청원구 오창읍 2산단4로 20 503동1303호</t>
+  </si>
+  <si>
+    <t>전북특별자치도 익산시 고봉로34길 35 508동 708호</t>
+  </si>
+  <si>
+    <t>세종시 장군면 정자말길35 주택</t>
+  </si>
+  <si>
+    <t>안양시 운곡로 60 엘프라우드 207-301</t>
+  </si>
+  <si>
+    <t>울산 북구 송정동 1210-4 201호</t>
+  </si>
+  <si>
+    <t>북구 송정17길 5 이프커피</t>
+  </si>
+  <si>
+    <t>북구 송정17길 5 2층</t>
+  </si>
+  <si>
+    <t>수원시 권선구 효탑로50 우방파크타운 108동 501ㅎㆍ</t>
+  </si>
+  <si>
+    <t>해송로30번길19</t>
+  </si>
+  <si>
+    <t>충남 태안군 원북면 옥파로 226-60 1층</t>
+  </si>
+  <si>
+    <t>공항대로124 1102동903</t>
+  </si>
+  <si>
+    <t>서울시 서대문구 수색로100 303-903</t>
+  </si>
+  <si>
+    <t>동탄순환대로 12길 67 3652동 1204호</t>
+  </si>
+  <si>
+    <t>경기도 성남시 분당구 내정로165번길35 527동402호</t>
+  </si>
+  <si>
+    <t>서울시 강남구 개포로264 래미안포레스트 104-601</t>
+  </si>
+  <si>
+    <t>경기도 하남시 신장로 114 ICT하남 1215호</t>
+  </si>
+  <si>
+    <t>인천광역시 부평문화로116번길 28 비잔티움 오피스텔 1004호</t>
+  </si>
+  <si>
+    <t>평택시 소사3로 53 효성해링턴플레이스 106동 702호</t>
+  </si>
+  <si>
+    <t>천안시 서북구 두정역길48 두정역푸르지오 112동1602호</t>
+  </si>
+  <si>
+    <t>공항대로 49-2 신성빌딩 1층 매장</t>
+  </si>
+  <si>
+    <t>서울시 영등포구 영신로 247 106-1202</t>
+  </si>
+  <si>
+    <t>위례대로6길 45 7308-903</t>
+  </si>
+  <si>
+    <t>서울시 성북구 정릉로10길 107 2동 1층 더라운지 커피클럽</t>
+  </si>
+  <si>
+    <t>중곡로3길47 오늘맥주</t>
+  </si>
+  <si>
+    <t>창원시  마산회원구 합성북16길 197 롯데캐슬더퍼스트 101동 1201호</t>
+  </si>
+  <si>
+    <t>서울 송파구 올림픽로 135 리센츠아파트 229동 1801호</t>
+  </si>
+  <si>
+    <t>전남광주 광산구 하남대로275-1 ,1층</t>
+  </si>
+  <si>
+    <t>서울시 강남구 청담동 112-20 1층</t>
+  </si>
+  <si>
+    <t>경기도 성남시 중원구 둔촌대로 64번길 4-6 1층</t>
+  </si>
+  <si>
+    <t>경북 경산시 압량읍 대학로399-30 1층</t>
+  </si>
+  <si>
+    <t>경기도 안성시 삼죽면 용월리170-2</t>
+  </si>
+  <si>
+    <t>서울 강동구 성내동 386-18 2층 202호</t>
+  </si>
+  <si>
+    <t>경북 봉화군 법전면 보라로 621</t>
+  </si>
+  <si>
+    <t>서울 은평구 진관3로 33 꿈에그린 1층 129호</t>
+  </si>
+  <si>
+    <t>경기도 평택시 쇼핑로 22-1 펫샵</t>
+  </si>
+  <si>
+    <t>경기 김포시 통진읍 율마로384번길 77 니팅캣</t>
+  </si>
+  <si>
+    <t>청주시 서원구 사직대로255. 빠찌애견</t>
+  </si>
+  <si>
+    <t>아산시 배방읍 월천6길59, 4층</t>
+  </si>
+  <si>
+    <t>경상북도 예천군 지보면 어신2길 179번지</t>
+  </si>
+  <si>
+    <t>전남 나주시세남로1691-22</t>
+  </si>
+  <si>
+    <t>여주시세종대왕면 여술길36</t>
+  </si>
+  <si>
+    <t>경기도 화성시 장안면 장안리726</t>
+  </si>
+  <si>
+    <t>경기도 이천시 향교로40번길50 A동401호</t>
+  </si>
+  <si>
+    <t>전북 익산시 궁동로84 귀엽개</t>
+  </si>
+  <si>
+    <t>서울시 광진구 자양로54, 1층</t>
+  </si>
+  <si>
+    <t>경기도 고양시 덕양구 내유동 702-27 휴그린2차 215동401호</t>
+  </si>
+  <si>
+    <t>강원도 평창군 방림면 계촌리 1288</t>
+  </si>
+  <si>
+    <t>부산 기장군 기장읍 내리길 146-30, 1층</t>
+  </si>
+  <si>
+    <t>창원시 의창구 북면 무곡리883 (아리랑밸리켄넬)</t>
+  </si>
+  <si>
+    <t>경기도 이천시 모가면 신갈리312-3 우편번호17406</t>
+  </si>
+  <si>
+    <t>경기도 남양주시 화도읍 수레로1120번길 32, 2층</t>
+  </si>
+  <si>
+    <t>경기도 이천시 서희로 78, 1층 (창전동)</t>
+  </si>
+  <si>
+    <t>경기도 양평군 개군면 황서배길 62-16</t>
+  </si>
+  <si>
+    <t>경기도 이천시 설성면 설가로278번길 80-40</t>
+  </si>
+  <si>
+    <t>경기도 양평군 양동면 장만대길50</t>
+  </si>
+  <si>
+    <t>강원도 횡성군 우천면 산전리421-1번지</t>
+  </si>
+  <si>
+    <t>전라북도 정읍시 감곡면 계봉길 72-39</t>
+  </si>
+  <si>
+    <t>충청북도 영동군 용산면 부상2길91</t>
+  </si>
+  <si>
+    <t>경기도 평택시 팽성읍 안정순환로172번길57</t>
+  </si>
+  <si>
+    <t>경상남도 김해시 생림면 마사로473번길26.11</t>
+  </si>
+  <si>
+    <t>경기도 이천시 고담동 107-2</t>
+  </si>
+  <si>
+    <t>경기도 양평군 양평읍 충신로 18</t>
+  </si>
+  <si>
+    <t>경상북도 경산시 와촌면 상암길 37길124 (우: 38414)</t>
+  </si>
+  <si>
+    <t>전라북도 정읍시 감곡면 계봉길 72-42</t>
+  </si>
+  <si>
+    <t>인천광역시 남동구 간석동 234-4 트라움 108호</t>
+  </si>
+  <si>
+    <t>경기도 파주시 적성면 적암리 157 7동</t>
+  </si>
+  <si>
+    <t>경상북도 경산시 와촌면 상암길37길 124</t>
+  </si>
+  <si>
+    <t>경기도 양주시 옥정동로7다길 62 대길프라자 강아지대공원</t>
+  </si>
+  <si>
     <t>[MMS 문자 유입] 펫샵 본품 1병 무료 샘플 신청</t>
   </si>
   <si>
     <t>[MMS 문자 유입] 펫샵 본품 1병 무료 샘플 신청 / [문자 직통 신청] 핸드폰 문자 직접 신청</t>
   </si>
   <si>
-    <t>[MMS 문자 유입] 펫샵 본품 1병 무료 샘플 신청 (구 91번 중복 접수건 27번으로 단일화 통합)</t>
-  </si>
-  <si>
     <t>[히어로 배너 클릭] 펫샵/브리더 본품 1병 무료 샘플 신청 / [MMS 문자 유입] 펫샵 본품 1병 무료 샘플 신청</t>
   </si>
   <si>
@@ -1411,18 +2248,15 @@
     <t>[문자 직통 신청] 핸드폰 문자 직접 신청 (성명과 상호가 없음) / [문자 직통 신청] 성명과 상호가 없음</t>
   </si>
   <si>
-    <t>[전화번호 수정/재발송] 010-9572-5776 (기존 010-9575-2577 오기입 반송건 수정)</t>
-  </si>
-  <si>
     <t>[문자 직통 신청] 핸드폰 문자 직접 신청 (전화번호 확인필요) / [문자 직통 신청] 전화번호 확인 필요</t>
   </si>
   <si>
+    <t>MMS 문자 유입] 펫샵 본품 1병 무료 샘플 신청</t>
+  </si>
+  <si>
     <t>[명함 이미지 유입] 펫샵 본품 1병 무료 샘플 신청</t>
   </si>
   <si>
-    <t>[MMS 문자 유입] 펫샵 본품 1병 무료 샘플 신청 / [쿠팡 2병 유료 주문 확인]</t>
-  </si>
-  <si>
     <t>[홍대표 직통 유입] 전화 및 문자 신청 (애견경매장 본품 1병 무료 샘플)</t>
   </si>
   <si>
@@ -1430,6 +2264,117 @@
   </si>
   <si>
     <t>[이미지/문자 신청 유입] 펫샵 본품 1병 무료 샘플 신청</t>
+  </si>
+  <si>
+    <t>[신규 사업자 알림판 신청] 업종: vet, 사업자번호:</t>
+  </si>
+  <si>
+    <t>[추석지인선물] 초대코드: 달맞이100 | 반려가족: 🐶 강아지 (설기/7개월/비숑) | 덕담: 즐거운 명절 보내세요 :)</t>
+  </si>
+  <si>
+    <t>[추석지인선물] 초대코드: 달맞이100 | 반려가족: 🐶 강아지 (기을/9살/푸들변종) | 덕담: 감사합니다. 추석명절 풍요롭게 보내세요.</t>
+  </si>
+  <si>
+    <t>[추석지인선물] 초대코드: 달맞이100 | 반려가족: 🐶 강아지 (행복, 푸들) | 덕담: 없음</t>
+  </si>
+  <si>
+    <t>[추석지인선물] 초대코드: 달맞이100 | 반려가족: 🐱 고양이  | 덕담: 없음</t>
+  </si>
+  <si>
+    <t>[추석지인선물] 초대코드: 달맞이100 | 반려가족: 🐶 강아지 (18) | 덕담: 선배님 감사합니다</t>
+  </si>
+  <si>
+    <t>[추석지인선물] 초대코드: 달맞이100 | 반려가족: 🐱 고양이 (Nyang) | 덕담: 선물 감사드리고 사업 번창하세요</t>
+  </si>
+  <si>
+    <t>[추석지인선물] 초대코드: 달맞이100 | 반려가족: 🐶 강아지 (콩순이 4살 여자) | 덕담: 명절 행복하게 보내세요❤️</t>
+  </si>
+  <si>
+    <t>[추석지인선물] 초대코드: 달맞이100 | 반려가족: 🐶 강아지 (메리 4살) | 덕담: 저의 반려견이 건강히 아쁘지않게 사는 비결을 말씀해주세요</t>
+  </si>
+  <si>
+    <t>[추석지인선물] 초대코드: 달맞이100 | 반려가족: 🐶 강아지 (4살 해피 비숑) | 덕담: 없음</t>
+  </si>
+  <si>
+    <t>[추석지인선물] 초대코드: 달맞이100 | 반려가족: 🐶 강아지 (노아12세) | 덕담: 추석  명절  행복하길 바래요 ~</t>
+  </si>
+  <si>
+    <t>[추석지인선물] 초대코드: 달맞이100 | 반려가족: 🐶 강아지  | 덕담: 없음 / [상세주소 도착 업데이트] 해송로 30번길19 308-202호(송도동, 웰카운티3단지apt)</t>
+  </si>
+  <si>
+    <t>[추석지인선물] 초대코드: 달맞이100 | 반려가족: 🐶 강아지 (4살) | 덕담: 감사합니다 추석 잘 보내세요</t>
+  </si>
+  <si>
+    <t>[추석지인선물] 초대코드: 달맞이100 | 반려가족: 🐶 강아지 (김볼트) | 덕담: 풍요로운 명절되세요</t>
+  </si>
+  <si>
+    <t>[추석지인선물] 초대코드: 달맞이100 | 반려가족: 🐶 강아지 (이쁜이/치와와) | 덕담: 사업 번창하세요</t>
+  </si>
+  <si>
+    <t>[추석지인선물] 초대코드: 달맞이100 | 반려가족: 🐱 고양이 (시키/약 5살 추정/아메리칸컬) | 덕담: 아버지의 추천으로 전달받았습니다. 행복한 명절보내세요</t>
+  </si>
+  <si>
+    <t>[추석지인선물] 초대코드: 달맞이100 | 반려가족: 🐱 고양이 (레오/9살) | 덕담: 대표님 감사합니다! 항상 건강하시고 행복하세요!</t>
+  </si>
+  <si>
+    <t>[추석지인선물] 초대코드: 달맞이100 | 반려가족: 🐱 고양이 (호이/6/터키시앙고라, 레오/6세/아메리칸숏) | 덕담: 없음</t>
+  </si>
+  <si>
+    <t>[추석지인선물] 초대코드: 달맞이100 | 반려가족: 🐶 강아지 (타기/8살/믹스) | 덕담: 즐거운 명절 되세요 사악씨 :)</t>
+  </si>
+  <si>
+    <t>[추석지인선물] 초대코드: 달맞이100 | 반려가족: 🐶 강아지 (로키/4개월/말티푸) | 덕담: 없음</t>
+  </si>
+  <si>
+    <t>[추석지인선물] 초대코드: 달맞이100 | 반려가족: 🐶 강아지 (깜둘이/ 9세/ 요크셔테리어) | 덕담: 명절선물 잘받겠습니다.</t>
+  </si>
+  <si>
+    <t>[추석지인선물] 초대코드: 달맞이100 | 반려가족: 🐶 강아지 (9 개월 보더콜리 ) | 덕담:  늘 연구하는 대한민국 화이팅♡♡♡</t>
+  </si>
+  <si>
+    <t>[추석지인선물] 초대코드: 달맞이100 | 반려가족: 🐶 강아지 (푸/8/푸들) | 덕담: 해피 추석</t>
+  </si>
+  <si>
+    <t>[추석지인선물] 초대코드: 달맞이100 | 반려가족: 🐶 강아지 (마루/4살/말티푸) | 덕담: 감사해요</t>
+  </si>
+  <si>
+    <t>[추석지인선물] 초대코드: 달맞이100 | 반려가족: 🐶 강아지 (뽀또 15살 푸들) | 덕담: 없음</t>
+  </si>
+  <si>
+    <t>[추석지인선물] 초대코드: 달맞이100 | 반려가족: 🐱 고양이 (구름이) | 덕담: 감사합니다. 추석 명절 잘보내세요</t>
+  </si>
+  <si>
+    <t>[추석지인선물] 초대코드: 달맞이100 | 반려가족: 🐶 강아지 (2020년생 여 잡종 15키로) | 덕담: 선택되어서 감솨 드립니다</t>
+  </si>
+  <si>
+    <t>[추석지인선물] 초대코드: 달맞이100 | 반려가족: 🐶 강아지  | 덕담: 홍순일대표님! 잘 지내시죠? 자주 연락합시다.</t>
+  </si>
+  <si>
+    <t>[MMS 문자 유입] 펫샵 본품 1병 무료 샘플 신청 / [사진 인증 접수] 브리더 (동물생산업 허가증 확인완료)</t>
+  </si>
+  <si>
+    <t>[사진 인증 접수] 포메라니안 브리더 (동물생산업 허가증/견사호 확인완료)</t>
+  </si>
+  <si>
+    <t>[사진 인증 접수] 애견미용/호텔 (사업자등록증 확인완료)</t>
+  </si>
+  <si>
+    <t>[문자 직통 신청] 추가 8건 엑셀 캡처 접수 / [문자 직통 신청] 엑셀 캡처 접수 추가</t>
+  </si>
+  <si>
+    <t>[문자 직통 신청] 엑셀 캡처 접수 추가</t>
+  </si>
+  <si>
+    <t>[문자 접수] 전문 브리더 (파보겔 본품 1병 무료 샘플 신청)</t>
+  </si>
+  <si>
+    <t>[MMS 문자 유입] 펫샵 본품 1병 무료 샘플 신청 (인접 농장 분리 배송)</t>
+  </si>
+  <si>
+    <t>[문자 직통 신청] 펫샵 본품 1병 무료 샘플 신청</t>
+  </si>
+  <si>
+    <t>[MMS 문자 유입] 펫샵·켄넬 본품 1병 무료 샘플 신청 (동일 주소지 청통농장 인접 분리 배송)</t>
   </si>
 </sst>
 </file>
@@ -1761,7 +2706,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G117"/>
+  <dimension ref="A1:G188"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -1795,19 +2740,19 @@
         <v>7</v>
       </c>
       <c r="C2" t="s">
-        <v>123</v>
+        <v>192</v>
       </c>
       <c r="D2" t="s">
-        <v>224</v>
+        <v>364</v>
       </c>
       <c r="E2" t="s">
-        <v>340</v>
+        <v>550</v>
       </c>
       <c r="F2">
         <v>1</v>
       </c>
       <c r="G2" t="s">
-        <v>456</v>
+        <v>736</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -1818,19 +2763,19 @@
         <v>8</v>
       </c>
       <c r="C3" t="s">
-        <v>124</v>
+        <v>193</v>
       </c>
       <c r="D3" t="s">
-        <v>225</v>
+        <v>365</v>
       </c>
       <c r="E3" t="s">
-        <v>341</v>
+        <v>551</v>
       </c>
       <c r="F3">
         <v>1</v>
       </c>
       <c r="G3" t="s">
-        <v>456</v>
+        <v>736</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -1841,19 +2786,19 @@
         <v>9</v>
       </c>
       <c r="C4" t="s">
-        <v>125</v>
+        <v>194</v>
       </c>
       <c r="D4" t="s">
-        <v>226</v>
+        <v>366</v>
       </c>
       <c r="E4" t="s">
-        <v>342</v>
+        <v>552</v>
       </c>
       <c r="F4">
         <v>1</v>
       </c>
       <c r="G4" t="s">
-        <v>456</v>
+        <v>736</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -1864,19 +2809,19 @@
         <v>10</v>
       </c>
       <c r="C5" t="s">
-        <v>126</v>
+        <v>195</v>
       </c>
       <c r="D5" t="s">
-        <v>227</v>
+        <v>367</v>
       </c>
       <c r="E5" t="s">
-        <v>343</v>
+        <v>553</v>
       </c>
       <c r="F5">
         <v>1</v>
       </c>
       <c r="G5" t="s">
-        <v>456</v>
+        <v>736</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -1887,19 +2832,19 @@
         <v>11</v>
       </c>
       <c r="C6" t="s">
-        <v>127</v>
+        <v>196</v>
       </c>
       <c r="D6" t="s">
-        <v>228</v>
+        <v>368</v>
       </c>
       <c r="E6" t="s">
-        <v>344</v>
+        <v>554</v>
       </c>
       <c r="F6">
         <v>1</v>
       </c>
       <c r="G6" t="s">
-        <v>456</v>
+        <v>736</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -1910,19 +2855,19 @@
         <v>12</v>
       </c>
       <c r="C7" t="s">
-        <v>128</v>
+        <v>197</v>
       </c>
       <c r="D7" t="s">
-        <v>229</v>
+        <v>369</v>
       </c>
       <c r="E7" t="s">
-        <v>345</v>
+        <v>555</v>
       </c>
       <c r="F7">
         <v>1</v>
       </c>
       <c r="G7" t="s">
-        <v>456</v>
+        <v>736</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -1933,19 +2878,19 @@
         <v>13</v>
       </c>
       <c r="C8" t="s">
-        <v>129</v>
+        <v>198</v>
       </c>
       <c r="D8" t="s">
-        <v>230</v>
+        <v>370</v>
       </c>
       <c r="E8" t="s">
-        <v>346</v>
+        <v>556</v>
       </c>
       <c r="F8">
         <v>1</v>
       </c>
       <c r="G8" t="s">
-        <v>456</v>
+        <v>736</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -1956,19 +2901,19 @@
         <v>14</v>
       </c>
       <c r="C9" t="s">
-        <v>130</v>
+        <v>199</v>
       </c>
       <c r="D9" t="s">
-        <v>231</v>
+        <v>371</v>
       </c>
       <c r="E9" t="s">
-        <v>347</v>
+        <v>557</v>
       </c>
       <c r="F9">
         <v>1</v>
       </c>
       <c r="G9" t="s">
-        <v>456</v>
+        <v>736</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -1979,19 +2924,19 @@
         <v>15</v>
       </c>
       <c r="C10" t="s">
-        <v>131</v>
+        <v>200</v>
       </c>
       <c r="D10" t="s">
-        <v>232</v>
+        <v>372</v>
       </c>
       <c r="E10" t="s">
-        <v>348</v>
+        <v>558</v>
       </c>
       <c r="F10">
         <v>1</v>
       </c>
       <c r="G10" t="s">
-        <v>456</v>
+        <v>736</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -2002,19 +2947,16 @@
         <v>16</v>
       </c>
       <c r="C11" t="s">
-        <v>132</v>
+        <v>201</v>
       </c>
       <c r="D11" t="s">
-        <v>233</v>
+        <v>373</v>
       </c>
       <c r="E11" t="s">
-        <v>349</v>
+        <v>559</v>
       </c>
       <c r="F11">
         <v>1</v>
-      </c>
-      <c r="G11" t="s">
-        <v>456</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -2025,19 +2967,19 @@
         <v>17</v>
       </c>
       <c r="C12" t="s">
-        <v>133</v>
+        <v>202</v>
       </c>
       <c r="D12" t="s">
-        <v>234</v>
+        <v>374</v>
       </c>
       <c r="E12" t="s">
-        <v>350</v>
+        <v>560</v>
       </c>
       <c r="F12">
         <v>1</v>
       </c>
       <c r="G12" t="s">
-        <v>456</v>
+        <v>736</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -2048,19 +2990,19 @@
         <v>18</v>
       </c>
       <c r="C13" t="s">
-        <v>134</v>
+        <v>203</v>
       </c>
       <c r="D13" t="s">
-        <v>235</v>
+        <v>375</v>
       </c>
       <c r="E13" t="s">
-        <v>351</v>
+        <v>561</v>
       </c>
       <c r="F13">
         <v>1</v>
       </c>
       <c r="G13" t="s">
-        <v>456</v>
+        <v>736</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -2071,19 +3013,19 @@
         <v>19</v>
       </c>
       <c r="C14" t="s">
-        <v>135</v>
+        <v>204</v>
       </c>
       <c r="D14" t="s">
-        <v>236</v>
+        <v>376</v>
       </c>
       <c r="E14" t="s">
-        <v>352</v>
+        <v>562</v>
       </c>
       <c r="F14">
         <v>1</v>
       </c>
       <c r="G14" t="s">
-        <v>456</v>
+        <v>736</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -2094,19 +3036,19 @@
         <v>20</v>
       </c>
       <c r="C15" t="s">
-        <v>136</v>
+        <v>205</v>
       </c>
       <c r="D15" t="s">
-        <v>237</v>
+        <v>377</v>
       </c>
       <c r="E15" t="s">
-        <v>353</v>
+        <v>563</v>
       </c>
       <c r="F15">
         <v>1</v>
       </c>
       <c r="G15" t="s">
-        <v>456</v>
+        <v>736</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -2117,19 +3059,19 @@
         <v>21</v>
       </c>
       <c r="C16" t="s">
-        <v>137</v>
+        <v>206</v>
       </c>
       <c r="D16" t="s">
-        <v>238</v>
+        <v>378</v>
       </c>
       <c r="E16" t="s">
-        <v>354</v>
+        <v>564</v>
       </c>
       <c r="F16">
         <v>1</v>
       </c>
       <c r="G16" t="s">
-        <v>457</v>
+        <v>737</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -2140,19 +3082,19 @@
         <v>22</v>
       </c>
       <c r="C17" t="s">
-        <v>138</v>
+        <v>207</v>
       </c>
       <c r="D17" t="s">
-        <v>239</v>
+        <v>379</v>
       </c>
       <c r="E17" t="s">
-        <v>355</v>
+        <v>565</v>
       </c>
       <c r="F17">
         <v>1</v>
       </c>
       <c r="G17" t="s">
-        <v>456</v>
+        <v>736</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -2163,19 +3105,19 @@
         <v>23</v>
       </c>
       <c r="C18" t="s">
-        <v>139</v>
+        <v>208</v>
       </c>
       <c r="D18" t="s">
-        <v>240</v>
+        <v>380</v>
       </c>
       <c r="E18" t="s">
-        <v>356</v>
+        <v>566</v>
       </c>
       <c r="F18">
         <v>1</v>
       </c>
       <c r="G18" t="s">
-        <v>456</v>
+        <v>736</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -2186,19 +3128,19 @@
         <v>24</v>
       </c>
       <c r="C19" t="s">
-        <v>140</v>
+        <v>209</v>
       </c>
       <c r="D19" t="s">
-        <v>241</v>
+        <v>381</v>
       </c>
       <c r="E19" t="s">
-        <v>357</v>
+        <v>567</v>
       </c>
       <c r="F19">
         <v>1</v>
       </c>
       <c r="G19" t="s">
-        <v>456</v>
+        <v>736</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -2209,19 +3151,19 @@
         <v>25</v>
       </c>
       <c r="C20" t="s">
-        <v>141</v>
+        <v>210</v>
       </c>
       <c r="D20" t="s">
-        <v>242</v>
+        <v>382</v>
       </c>
       <c r="E20" t="s">
-        <v>358</v>
+        <v>568</v>
       </c>
       <c r="F20">
         <v>1</v>
       </c>
       <c r="G20" t="s">
-        <v>456</v>
+        <v>736</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -2232,19 +3174,19 @@
         <v>26</v>
       </c>
       <c r="C21" t="s">
-        <v>142</v>
+        <v>211</v>
       </c>
       <c r="D21" t="s">
-        <v>243</v>
+        <v>383</v>
       </c>
       <c r="E21" t="s">
-        <v>359</v>
+        <v>569</v>
       </c>
       <c r="F21">
         <v>1</v>
       </c>
       <c r="G21" t="s">
-        <v>456</v>
+        <v>736</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -2255,19 +3197,19 @@
         <v>27</v>
       </c>
       <c r="C22" t="s">
-        <v>143</v>
+        <v>212</v>
       </c>
       <c r="D22" t="s">
-        <v>244</v>
+        <v>384</v>
       </c>
       <c r="E22" t="s">
-        <v>360</v>
+        <v>570</v>
       </c>
       <c r="F22">
         <v>1</v>
       </c>
       <c r="G22" t="s">
-        <v>456</v>
+        <v>736</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -2278,19 +3220,19 @@
         <v>28</v>
       </c>
       <c r="C23" t="s">
-        <v>144</v>
+        <v>213</v>
       </c>
       <c r="D23" t="s">
-        <v>245</v>
+        <v>385</v>
       </c>
       <c r="E23" t="s">
-        <v>361</v>
+        <v>571</v>
       </c>
       <c r="F23">
         <v>1</v>
       </c>
       <c r="G23" t="s">
-        <v>456</v>
+        <v>736</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -2301,19 +3243,19 @@
         <v>29</v>
       </c>
       <c r="C24" t="s">
-        <v>145</v>
+        <v>214</v>
       </c>
       <c r="D24" t="s">
-        <v>246</v>
+        <v>386</v>
       </c>
       <c r="E24" t="s">
-        <v>362</v>
+        <v>572</v>
       </c>
       <c r="F24">
         <v>1</v>
       </c>
       <c r="G24" t="s">
-        <v>456</v>
+        <v>736</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -2324,19 +3266,19 @@
         <v>30</v>
       </c>
       <c r="C25" t="s">
-        <v>146</v>
+        <v>215</v>
       </c>
       <c r="D25" t="s">
-        <v>247</v>
+        <v>387</v>
       </c>
       <c r="E25" t="s">
-        <v>363</v>
+        <v>573</v>
       </c>
       <c r="F25">
         <v>1</v>
       </c>
       <c r="G25" t="s">
-        <v>456</v>
+        <v>736</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -2347,19 +3289,19 @@
         <v>31</v>
       </c>
       <c r="C26" t="s">
-        <v>147</v>
+        <v>216</v>
       </c>
       <c r="D26" t="s">
-        <v>248</v>
+        <v>388</v>
       </c>
       <c r="E26" t="s">
-        <v>364</v>
+        <v>574</v>
       </c>
       <c r="F26">
         <v>1</v>
       </c>
       <c r="G26" t="s">
-        <v>456</v>
+        <v>736</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -2370,19 +3312,19 @@
         <v>32</v>
       </c>
       <c r="C27" t="s">
-        <v>148</v>
+        <v>217</v>
       </c>
       <c r="D27" t="s">
-        <v>249</v>
+        <v>389</v>
       </c>
       <c r="E27" t="s">
-        <v>365</v>
+        <v>575</v>
       </c>
       <c r="F27">
         <v>1</v>
       </c>
       <c r="G27" t="s">
-        <v>456</v>
+        <v>736</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -2393,19 +3335,19 @@
         <v>33</v>
       </c>
       <c r="C28" t="s">
-        <v>149</v>
+        <v>218</v>
       </c>
       <c r="D28" t="s">
-        <v>250</v>
+        <v>390</v>
       </c>
       <c r="E28" t="s">
-        <v>366</v>
+        <v>576</v>
       </c>
       <c r="F28">
         <v>1</v>
       </c>
       <c r="G28" t="s">
-        <v>458</v>
+        <v>736</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -2416,19 +3358,19 @@
         <v>34</v>
       </c>
       <c r="C29" t="s">
-        <v>150</v>
+        <v>219</v>
       </c>
       <c r="D29" t="s">
-        <v>251</v>
+        <v>391</v>
       </c>
       <c r="E29" t="s">
-        <v>367</v>
+        <v>577</v>
       </c>
       <c r="F29">
         <v>1</v>
       </c>
       <c r="G29" t="s">
-        <v>456</v>
+        <v>736</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -2439,19 +3381,19 @@
         <v>35</v>
       </c>
       <c r="C30" t="s">
-        <v>151</v>
+        <v>220</v>
       </c>
       <c r="D30" t="s">
-        <v>252</v>
+        <v>392</v>
       </c>
       <c r="E30" t="s">
-        <v>368</v>
+        <v>578</v>
       </c>
       <c r="F30">
         <v>1</v>
       </c>
       <c r="G30" t="s">
-        <v>456</v>
+        <v>736</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -2462,19 +3404,19 @@
         <v>36</v>
       </c>
       <c r="C31" t="s">
-        <v>152</v>
+        <v>221</v>
       </c>
       <c r="D31" t="s">
-        <v>253</v>
+        <v>393</v>
       </c>
       <c r="E31" t="s">
-        <v>369</v>
+        <v>579</v>
       </c>
       <c r="F31">
         <v>1</v>
       </c>
       <c r="G31" t="s">
-        <v>456</v>
+        <v>736</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -2485,19 +3427,19 @@
         <v>37</v>
       </c>
       <c r="C32" t="s">
-        <v>153</v>
+        <v>222</v>
       </c>
       <c r="D32" t="s">
-        <v>254</v>
+        <v>394</v>
       </c>
       <c r="E32" t="s">
-        <v>370</v>
+        <v>580</v>
       </c>
       <c r="F32">
         <v>1</v>
       </c>
       <c r="G32" t="s">
-        <v>456</v>
+        <v>736</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -2508,19 +3450,19 @@
         <v>38</v>
       </c>
       <c r="C33" t="s">
-        <v>154</v>
+        <v>223</v>
       </c>
       <c r="D33" t="s">
-        <v>255</v>
+        <v>395</v>
       </c>
       <c r="E33" t="s">
-        <v>371</v>
+        <v>581</v>
       </c>
       <c r="F33">
         <v>1</v>
       </c>
       <c r="G33" t="s">
-        <v>456</v>
+        <v>736</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -2531,19 +3473,19 @@
         <v>39</v>
       </c>
       <c r="C34" t="s">
-        <v>155</v>
+        <v>224</v>
       </c>
       <c r="D34" t="s">
-        <v>256</v>
+        <v>396</v>
       </c>
       <c r="E34" t="s">
-        <v>372</v>
+        <v>582</v>
       </c>
       <c r="F34">
         <v>1</v>
       </c>
       <c r="G34" t="s">
-        <v>456</v>
+        <v>736</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -2554,19 +3496,19 @@
         <v>40</v>
       </c>
       <c r="C35" t="s">
-        <v>156</v>
+        <v>225</v>
       </c>
       <c r="D35" t="s">
-        <v>257</v>
+        <v>397</v>
       </c>
       <c r="E35" t="s">
-        <v>373</v>
+        <v>583</v>
       </c>
       <c r="F35">
         <v>1</v>
       </c>
       <c r="G35" t="s">
-        <v>456</v>
+        <v>736</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -2577,19 +3519,19 @@
         <v>41</v>
       </c>
       <c r="C36" t="s">
-        <v>157</v>
+        <v>226</v>
       </c>
       <c r="D36" t="s">
-        <v>258</v>
+        <v>398</v>
       </c>
       <c r="E36" t="s">
-        <v>374</v>
+        <v>584</v>
       </c>
       <c r="F36">
         <v>1</v>
       </c>
       <c r="G36" t="s">
-        <v>456</v>
+        <v>736</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -2600,19 +3542,19 @@
         <v>42</v>
       </c>
       <c r="C37" t="s">
-        <v>158</v>
+        <v>227</v>
       </c>
       <c r="D37" t="s">
-        <v>259</v>
+        <v>399</v>
       </c>
       <c r="E37" t="s">
-        <v>375</v>
+        <v>585</v>
       </c>
       <c r="F37">
         <v>1</v>
       </c>
       <c r="G37" t="s">
-        <v>456</v>
+        <v>736</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -2623,19 +3565,19 @@
         <v>43</v>
       </c>
       <c r="C38" t="s">
-        <v>159</v>
+        <v>228</v>
       </c>
       <c r="D38" t="s">
-        <v>260</v>
+        <v>400</v>
       </c>
       <c r="E38" t="s">
-        <v>376</v>
+        <v>586</v>
       </c>
       <c r="F38">
         <v>1</v>
       </c>
       <c r="G38" t="s">
-        <v>456</v>
+        <v>736</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -2646,19 +3588,19 @@
         <v>44</v>
       </c>
       <c r="C39" t="s">
-        <v>160</v>
+        <v>229</v>
       </c>
       <c r="D39" t="s">
-        <v>261</v>
+        <v>401</v>
       </c>
       <c r="E39" t="s">
-        <v>377</v>
+        <v>587</v>
       </c>
       <c r="F39">
         <v>1</v>
       </c>
       <c r="G39" t="s">
-        <v>456</v>
+        <v>736</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -2669,19 +3611,19 @@
         <v>45</v>
       </c>
       <c r="C40" t="s">
-        <v>161</v>
+        <v>230</v>
       </c>
       <c r="D40" t="s">
-        <v>262</v>
+        <v>402</v>
       </c>
       <c r="E40" t="s">
-        <v>378</v>
+        <v>588</v>
       </c>
       <c r="F40">
         <v>1</v>
       </c>
       <c r="G40" t="s">
-        <v>459</v>
+        <v>738</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -2692,19 +3634,19 @@
         <v>46</v>
       </c>
       <c r="C41" t="s">
-        <v>162</v>
+        <v>231</v>
       </c>
       <c r="D41" t="s">
-        <v>263</v>
+        <v>403</v>
       </c>
       <c r="E41" t="s">
-        <v>379</v>
+        <v>589</v>
       </c>
       <c r="F41">
         <v>1</v>
       </c>
       <c r="G41" t="s">
-        <v>457</v>
+        <v>737</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -2715,19 +3657,19 @@
         <v>47</v>
       </c>
       <c r="C42" t="s">
-        <v>163</v>
+        <v>232</v>
       </c>
       <c r="D42" t="s">
-        <v>264</v>
+        <v>404</v>
       </c>
       <c r="E42" t="s">
-        <v>380</v>
+        <v>590</v>
       </c>
       <c r="F42">
         <v>1</v>
       </c>
       <c r="G42" t="s">
-        <v>456</v>
+        <v>736</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -2738,19 +3680,19 @@
         <v>48</v>
       </c>
       <c r="C43" t="s">
-        <v>164</v>
+        <v>233</v>
       </c>
       <c r="D43" t="s">
-        <v>265</v>
+        <v>405</v>
       </c>
       <c r="E43" t="s">
-        <v>381</v>
+        <v>591</v>
       </c>
       <c r="F43">
         <v>1</v>
       </c>
       <c r="G43" t="s">
-        <v>456</v>
+        <v>736</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -2761,19 +3703,19 @@
         <v>49</v>
       </c>
       <c r="C44" t="s">
-        <v>165</v>
+        <v>234</v>
       </c>
       <c r="D44" t="s">
-        <v>266</v>
+        <v>406</v>
       </c>
       <c r="E44" t="s">
-        <v>382</v>
+        <v>592</v>
       </c>
       <c r="F44">
         <v>1</v>
       </c>
       <c r="G44" t="s">
-        <v>456</v>
+        <v>736</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -2784,19 +3726,19 @@
         <v>50</v>
       </c>
       <c r="C45" t="s">
-        <v>166</v>
+        <v>235</v>
       </c>
       <c r="D45" t="s">
-        <v>267</v>
+        <v>407</v>
       </c>
       <c r="E45" t="s">
-        <v>383</v>
+        <v>593</v>
       </c>
       <c r="F45">
         <v>1</v>
       </c>
       <c r="G45" t="s">
-        <v>456</v>
+        <v>736</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -2807,19 +3749,19 @@
         <v>51</v>
       </c>
       <c r="C46" t="s">
-        <v>167</v>
+        <v>236</v>
       </c>
       <c r="D46" t="s">
-        <v>268</v>
+        <v>408</v>
       </c>
       <c r="E46" t="s">
-        <v>384</v>
+        <v>594</v>
       </c>
       <c r="F46">
         <v>1</v>
       </c>
       <c r="G46" t="s">
-        <v>456</v>
+        <v>736</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -2830,19 +3772,19 @@
         <v>52</v>
       </c>
       <c r="C47" t="s">
-        <v>168</v>
+        <v>237</v>
       </c>
       <c r="D47" t="s">
-        <v>269</v>
+        <v>409</v>
       </c>
       <c r="E47" t="s">
-        <v>385</v>
+        <v>595</v>
       </c>
       <c r="F47">
         <v>1</v>
       </c>
       <c r="G47" t="s">
-        <v>456</v>
+        <v>736</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -2853,19 +3795,19 @@
         <v>53</v>
       </c>
       <c r="C48" t="s">
-        <v>169</v>
+        <v>238</v>
       </c>
       <c r="D48" t="s">
-        <v>270</v>
+        <v>410</v>
       </c>
       <c r="E48" t="s">
-        <v>386</v>
+        <v>596</v>
       </c>
       <c r="F48">
         <v>1</v>
       </c>
       <c r="G48" t="s">
-        <v>456</v>
+        <v>736</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -2876,19 +3818,19 @@
         <v>54</v>
       </c>
       <c r="C49" t="s">
-        <v>170</v>
+        <v>239</v>
       </c>
       <c r="D49" t="s">
-        <v>271</v>
+        <v>411</v>
       </c>
       <c r="E49" t="s">
-        <v>387</v>
+        <v>597</v>
       </c>
       <c r="F49">
         <v>1</v>
       </c>
       <c r="G49" t="s">
-        <v>456</v>
+        <v>736</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -2899,19 +3841,19 @@
         <v>55</v>
       </c>
       <c r="C50" t="s">
-        <v>171</v>
+        <v>240</v>
       </c>
       <c r="D50" t="s">
-        <v>272</v>
+        <v>412</v>
       </c>
       <c r="E50" t="s">
-        <v>388</v>
+        <v>598</v>
       </c>
       <c r="F50">
         <v>1</v>
       </c>
       <c r="G50" t="s">
-        <v>456</v>
+        <v>736</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -2922,19 +3864,19 @@
         <v>56</v>
       </c>
       <c r="C51" t="s">
-        <v>172</v>
+        <v>241</v>
       </c>
       <c r="D51" t="s">
-        <v>273</v>
+        <v>413</v>
       </c>
       <c r="E51" t="s">
-        <v>389</v>
+        <v>599</v>
       </c>
       <c r="F51">
         <v>1</v>
       </c>
       <c r="G51" t="s">
-        <v>456</v>
+        <v>736</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -2945,19 +3887,19 @@
         <v>57</v>
       </c>
       <c r="C52" t="s">
-        <v>173</v>
+        <v>242</v>
       </c>
       <c r="D52" t="s">
-        <v>274</v>
+        <v>414</v>
       </c>
       <c r="E52" t="s">
-        <v>390</v>
+        <v>600</v>
       </c>
       <c r="F52">
         <v>1</v>
       </c>
       <c r="G52" t="s">
-        <v>456</v>
+        <v>736</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -2968,19 +3910,19 @@
         <v>58</v>
       </c>
       <c r="C53" t="s">
-        <v>174</v>
+        <v>243</v>
       </c>
       <c r="D53" t="s">
-        <v>275</v>
+        <v>415</v>
       </c>
       <c r="E53" t="s">
-        <v>391</v>
+        <v>601</v>
       </c>
       <c r="F53">
         <v>1</v>
       </c>
       <c r="G53" t="s">
-        <v>456</v>
+        <v>736</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -2991,19 +3933,19 @@
         <v>59</v>
       </c>
       <c r="C54" t="s">
-        <v>175</v>
+        <v>244</v>
       </c>
       <c r="D54" t="s">
-        <v>276</v>
+        <v>416</v>
       </c>
       <c r="E54" t="s">
-        <v>392</v>
+        <v>602</v>
       </c>
       <c r="F54">
         <v>1</v>
       </c>
       <c r="G54" t="s">
-        <v>456</v>
+        <v>736</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -3014,19 +3956,19 @@
         <v>60</v>
       </c>
       <c r="C55" t="s">
-        <v>176</v>
+        <v>245</v>
       </c>
       <c r="D55" t="s">
-        <v>277</v>
+        <v>417</v>
       </c>
       <c r="E55" t="s">
-        <v>393</v>
+        <v>603</v>
       </c>
       <c r="F55">
         <v>1</v>
       </c>
       <c r="G55" t="s">
-        <v>456</v>
+        <v>736</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -3037,19 +3979,19 @@
         <v>61</v>
       </c>
       <c r="C56" t="s">
-        <v>177</v>
+        <v>246</v>
       </c>
       <c r="D56" t="s">
-        <v>278</v>
+        <v>418</v>
       </c>
       <c r="E56" t="s">
-        <v>394</v>
+        <v>604</v>
       </c>
       <c r="F56">
         <v>1</v>
       </c>
       <c r="G56" t="s">
-        <v>456</v>
+        <v>736</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -3060,19 +4002,19 @@
         <v>62</v>
       </c>
       <c r="C57" t="s">
-        <v>178</v>
+        <v>247</v>
       </c>
       <c r="D57" t="s">
-        <v>279</v>
+        <v>419</v>
       </c>
       <c r="E57" t="s">
-        <v>395</v>
+        <v>605</v>
       </c>
       <c r="F57">
         <v>1</v>
       </c>
       <c r="G57" t="s">
-        <v>460</v>
+        <v>739</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -3083,19 +4025,19 @@
         <v>63</v>
       </c>
       <c r="C58" t="s">
-        <v>179</v>
+        <v>248</v>
       </c>
       <c r="D58" t="s">
-        <v>280</v>
+        <v>420</v>
       </c>
       <c r="E58" t="s">
-        <v>396</v>
+        <v>606</v>
       </c>
       <c r="F58">
         <v>1</v>
       </c>
       <c r="G58" t="s">
-        <v>456</v>
+        <v>736</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -3106,19 +4048,19 @@
         <v>64</v>
       </c>
       <c r="C59" t="s">
-        <v>180</v>
+        <v>249</v>
       </c>
       <c r="D59" t="s">
-        <v>281</v>
+        <v>421</v>
       </c>
       <c r="E59" t="s">
-        <v>397</v>
+        <v>607</v>
       </c>
       <c r="F59">
         <v>1</v>
       </c>
       <c r="G59" t="s">
-        <v>456</v>
+        <v>736</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -3129,19 +4071,19 @@
         <v>65</v>
       </c>
       <c r="C60" t="s">
-        <v>181</v>
+        <v>250</v>
       </c>
       <c r="D60" t="s">
-        <v>282</v>
+        <v>422</v>
       </c>
       <c r="E60" t="s">
-        <v>398</v>
+        <v>608</v>
       </c>
       <c r="F60">
         <v>1</v>
       </c>
       <c r="G60" t="s">
-        <v>456</v>
+        <v>736</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -3152,19 +4094,19 @@
         <v>66</v>
       </c>
       <c r="C61" t="s">
-        <v>182</v>
+        <v>251</v>
       </c>
       <c r="D61" t="s">
-        <v>283</v>
+        <v>423</v>
       </c>
       <c r="E61" t="s">
-        <v>399</v>
+        <v>609</v>
       </c>
       <c r="F61">
         <v>1</v>
       </c>
       <c r="G61" t="s">
-        <v>456</v>
+        <v>736</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -3175,19 +4117,19 @@
         <v>67</v>
       </c>
       <c r="C62" t="s">
-        <v>183</v>
+        <v>252</v>
       </c>
       <c r="D62" t="s">
-        <v>284</v>
+        <v>424</v>
       </c>
       <c r="E62" t="s">
-        <v>400</v>
+        <v>610</v>
       </c>
       <c r="F62">
         <v>1</v>
       </c>
       <c r="G62" t="s">
-        <v>456</v>
+        <v>736</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -3198,19 +4140,19 @@
         <v>68</v>
       </c>
       <c r="C63" t="s">
-        <v>184</v>
+        <v>253</v>
       </c>
       <c r="D63" t="s">
-        <v>285</v>
+        <v>425</v>
       </c>
       <c r="E63" t="s">
-        <v>401</v>
+        <v>611</v>
       </c>
       <c r="F63">
         <v>1</v>
       </c>
       <c r="G63" t="s">
-        <v>456</v>
+        <v>736</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -3221,19 +4163,19 @@
         <v>69</v>
       </c>
       <c r="C64" t="s">
-        <v>185</v>
+        <v>254</v>
       </c>
       <c r="D64" t="s">
-        <v>286</v>
+        <v>426</v>
       </c>
       <c r="E64" t="s">
-        <v>402</v>
+        <v>612</v>
       </c>
       <c r="F64">
         <v>1</v>
       </c>
       <c r="G64" t="s">
-        <v>456</v>
+        <v>736</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -3244,19 +4186,19 @@
         <v>70</v>
       </c>
       <c r="C65" t="s">
-        <v>186</v>
+        <v>255</v>
       </c>
       <c r="D65" t="s">
-        <v>287</v>
+        <v>427</v>
       </c>
       <c r="E65" t="s">
-        <v>403</v>
+        <v>613</v>
       </c>
       <c r="F65">
         <v>3</v>
       </c>
       <c r="G65" t="s">
-        <v>461</v>
+        <v>740</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -3267,19 +4209,19 @@
         <v>71</v>
       </c>
       <c r="C66" t="s">
-        <v>187</v>
+        <v>256</v>
       </c>
       <c r="D66" t="s">
-        <v>288</v>
+        <v>428</v>
       </c>
       <c r="E66" t="s">
-        <v>404</v>
+        <v>614</v>
       </c>
       <c r="F66">
         <v>1</v>
       </c>
       <c r="G66" t="s">
-        <v>456</v>
+        <v>736</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -3290,19 +4232,19 @@
         <v>72</v>
       </c>
       <c r="C67" t="s">
-        <v>188</v>
+        <v>257</v>
       </c>
       <c r="D67" t="s">
-        <v>289</v>
+        <v>429</v>
       </c>
       <c r="E67" t="s">
-        <v>405</v>
+        <v>615</v>
       </c>
       <c r="F67">
         <v>1</v>
       </c>
       <c r="G67" t="s">
-        <v>456</v>
+        <v>736</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -3313,19 +4255,19 @@
         <v>73</v>
       </c>
       <c r="C68" t="s">
-        <v>189</v>
+        <v>258</v>
       </c>
       <c r="D68" t="s">
-        <v>290</v>
+        <v>430</v>
       </c>
       <c r="E68" t="s">
-        <v>406</v>
+        <v>616</v>
       </c>
       <c r="F68">
         <v>1</v>
       </c>
       <c r="G68" t="s">
-        <v>456</v>
+        <v>736</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -3336,19 +4278,19 @@
         <v>74</v>
       </c>
       <c r="C69" t="s">
-        <v>190</v>
+        <v>259</v>
       </c>
       <c r="D69" t="s">
-        <v>291</v>
+        <v>431</v>
       </c>
       <c r="E69" t="s">
-        <v>407</v>
+        <v>617</v>
       </c>
       <c r="F69">
         <v>1</v>
       </c>
       <c r="G69" t="s">
-        <v>456</v>
+        <v>736</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -3359,19 +4301,19 @@
         <v>75</v>
       </c>
       <c r="C70" t="s">
-        <v>191</v>
+        <v>260</v>
       </c>
       <c r="D70" t="s">
-        <v>292</v>
+        <v>432</v>
       </c>
       <c r="E70" t="s">
-        <v>408</v>
+        <v>618</v>
       </c>
       <c r="F70">
         <v>1</v>
       </c>
       <c r="G70" t="s">
-        <v>456</v>
+        <v>736</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -3382,19 +4324,19 @@
         <v>76</v>
       </c>
       <c r="C71" t="s">
-        <v>192</v>
+        <v>261</v>
       </c>
       <c r="D71" t="s">
-        <v>293</v>
+        <v>433</v>
       </c>
       <c r="E71" t="s">
-        <v>409</v>
+        <v>619</v>
       </c>
       <c r="F71">
         <v>1</v>
       </c>
       <c r="G71" t="s">
-        <v>456</v>
+        <v>736</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -3405,19 +4347,19 @@
         <v>77</v>
       </c>
       <c r="C72" t="s">
-        <v>193</v>
+        <v>262</v>
       </c>
       <c r="D72" t="s">
-        <v>294</v>
+        <v>434</v>
       </c>
       <c r="E72" t="s">
-        <v>410</v>
+        <v>620</v>
       </c>
       <c r="F72">
         <v>1</v>
       </c>
       <c r="G72" t="s">
-        <v>456</v>
+        <v>736</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -3428,19 +4370,19 @@
         <v>78</v>
       </c>
       <c r="C73" t="s">
-        <v>194</v>
+        <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>295</v>
+        <v>435</v>
       </c>
       <c r="E73" t="s">
-        <v>411</v>
+        <v>621</v>
       </c>
       <c r="F73">
         <v>1</v>
       </c>
       <c r="G73" t="s">
-        <v>456</v>
+        <v>736</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -3451,19 +4393,19 @@
         <v>79</v>
       </c>
       <c r="C74" t="s">
-        <v>195</v>
+        <v>264</v>
       </c>
       <c r="D74" t="s">
-        <v>296</v>
+        <v>436</v>
       </c>
       <c r="E74" t="s">
-        <v>412</v>
+        <v>622</v>
       </c>
       <c r="F74">
         <v>1</v>
       </c>
       <c r="G74" t="s">
-        <v>456</v>
+        <v>736</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -3474,19 +4416,19 @@
         <v>80</v>
       </c>
       <c r="C75" t="s">
-        <v>196</v>
+        <v>265</v>
       </c>
       <c r="D75" t="s">
-        <v>297</v>
+        <v>437</v>
       </c>
       <c r="E75" t="s">
-        <v>413</v>
+        <v>623</v>
       </c>
       <c r="F75">
         <v>1</v>
       </c>
       <c r="G75" t="s">
-        <v>456</v>
+        <v>736</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -3497,19 +4439,19 @@
         <v>81</v>
       </c>
       <c r="C76" t="s">
-        <v>197</v>
+        <v>266</v>
       </c>
       <c r="D76" t="s">
-        <v>298</v>
+        <v>438</v>
       </c>
       <c r="E76" t="s">
-        <v>414</v>
+        <v>624</v>
       </c>
       <c r="F76">
         <v>1</v>
       </c>
       <c r="G76" t="s">
-        <v>456</v>
+        <v>736</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -3523,16 +4465,16 @@
         <v>82</v>
       </c>
       <c r="D77" t="s">
-        <v>299</v>
+        <v>439</v>
       </c>
       <c r="E77" t="s">
-        <v>415</v>
+        <v>625</v>
       </c>
       <c r="F77">
         <v>1</v>
       </c>
       <c r="G77" t="s">
-        <v>462</v>
+        <v>741</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -3546,16 +4488,16 @@
         <v>83</v>
       </c>
       <c r="D78" t="s">
-        <v>300</v>
+        <v>440</v>
       </c>
       <c r="E78" t="s">
-        <v>416</v>
+        <v>626</v>
       </c>
       <c r="F78">
         <v>1</v>
       </c>
       <c r="G78" t="s">
-        <v>462</v>
+        <v>741</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -3569,16 +4511,16 @@
         <v>84</v>
       </c>
       <c r="D79" t="s">
-        <v>301</v>
+        <v>441</v>
       </c>
       <c r="E79" t="s">
-        <v>417</v>
+        <v>627</v>
       </c>
       <c r="F79">
         <v>1</v>
       </c>
       <c r="G79" t="s">
-        <v>462</v>
+        <v>741</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -3592,16 +4534,16 @@
         <v>85</v>
       </c>
       <c r="D80" t="s">
-        <v>302</v>
+        <v>442</v>
       </c>
       <c r="E80" t="s">
-        <v>418</v>
+        <v>628</v>
       </c>
       <c r="F80">
         <v>1</v>
       </c>
       <c r="G80" t="s">
-        <v>462</v>
+        <v>741</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -3615,16 +4557,16 @@
         <v>86</v>
       </c>
       <c r="D81" t="s">
-        <v>303</v>
+        <v>443</v>
       </c>
       <c r="E81" t="s">
-        <v>419</v>
+        <v>629</v>
       </c>
       <c r="F81">
         <v>1</v>
       </c>
       <c r="G81" t="s">
-        <v>463</v>
+        <v>742</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -3638,16 +4580,16 @@
         <v>87</v>
       </c>
       <c r="D82" t="s">
-        <v>304</v>
+        <v>444</v>
       </c>
       <c r="E82" t="s">
-        <v>420</v>
+        <v>630</v>
       </c>
       <c r="F82">
         <v>1</v>
       </c>
       <c r="G82" t="s">
-        <v>464</v>
+        <v>743</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -3661,16 +4603,16 @@
         <v>88</v>
       </c>
       <c r="D83" t="s">
-        <v>305</v>
+        <v>445</v>
       </c>
       <c r="E83" t="s">
-        <v>421</v>
+        <v>631</v>
       </c>
       <c r="F83">
         <v>1</v>
       </c>
       <c r="G83" t="s">
-        <v>462</v>
+        <v>741</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -3684,16 +4626,16 @@
         <v>89</v>
       </c>
       <c r="D84" t="s">
-        <v>306</v>
+        <v>446</v>
       </c>
       <c r="E84" t="s">
-        <v>422</v>
+        <v>632</v>
       </c>
       <c r="F84">
         <v>1</v>
       </c>
       <c r="G84" t="s">
-        <v>465</v>
+        <v>741</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -3707,16 +4649,16 @@
         <v>90</v>
       </c>
       <c r="D85" t="s">
-        <v>307</v>
+        <v>447</v>
       </c>
       <c r="E85" t="s">
-        <v>423</v>
+        <v>633</v>
       </c>
       <c r="F85">
         <v>1</v>
       </c>
       <c r="G85" t="s">
-        <v>462</v>
+        <v>741</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -3727,19 +4669,19 @@
         <v>91</v>
       </c>
       <c r="C86" t="s">
-        <v>198</v>
+        <v>267</v>
       </c>
       <c r="D86" t="s">
-        <v>308</v>
+        <v>448</v>
       </c>
       <c r="E86" t="s">
-        <v>424</v>
+        <v>634</v>
       </c>
       <c r="F86">
         <v>1</v>
       </c>
       <c r="G86" t="s">
-        <v>462</v>
+        <v>741</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -3753,16 +4695,16 @@
         <v>92</v>
       </c>
       <c r="D87" t="s">
-        <v>309</v>
+        <v>287</v>
       </c>
       <c r="E87" t="s">
-        <v>425</v>
+        <v>635</v>
       </c>
       <c r="F87">
         <v>1</v>
       </c>
       <c r="G87" t="s">
-        <v>466</v>
+        <v>744</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -3776,16 +4718,16 @@
         <v>93</v>
       </c>
       <c r="D88" t="s">
-        <v>310</v>
+        <v>449</v>
       </c>
       <c r="E88" t="s">
-        <v>426</v>
+        <v>636</v>
       </c>
       <c r="F88">
         <v>1</v>
       </c>
       <c r="G88" t="s">
-        <v>462</v>
+        <v>741</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -3796,19 +4738,19 @@
         <v>94</v>
       </c>
       <c r="C89" t="s">
-        <v>199</v>
+        <v>268</v>
       </c>
       <c r="D89" t="s">
-        <v>311</v>
+        <v>450</v>
       </c>
       <c r="E89" t="s">
-        <v>427</v>
+        <v>637</v>
       </c>
       <c r="F89">
         <v>1</v>
       </c>
       <c r="G89" t="s">
-        <v>460</v>
+        <v>739</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -3819,19 +4761,19 @@
         <v>95</v>
       </c>
       <c r="C90" t="s">
-        <v>200</v>
+        <v>269</v>
       </c>
       <c r="D90" t="s">
-        <v>312</v>
+        <v>451</v>
       </c>
       <c r="E90" t="s">
-        <v>428</v>
+        <v>638</v>
       </c>
       <c r="F90">
         <v>1</v>
       </c>
       <c r="G90" t="s">
-        <v>456</v>
+        <v>736</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -3842,19 +4784,19 @@
         <v>96</v>
       </c>
       <c r="C91" t="s">
-        <v>201</v>
+        <v>270</v>
       </c>
       <c r="D91" t="s">
-        <v>313</v>
+        <v>452</v>
       </c>
       <c r="E91" t="s">
-        <v>429</v>
+        <v>639</v>
       </c>
       <c r="F91">
         <v>1</v>
       </c>
       <c r="G91" t="s">
-        <v>456</v>
+        <v>736</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -3865,19 +4807,19 @@
         <v>97</v>
       </c>
       <c r="C92" t="s">
-        <v>202</v>
+        <v>271</v>
       </c>
       <c r="D92" t="s">
-        <v>314</v>
+        <v>453</v>
       </c>
       <c r="E92" t="s">
-        <v>430</v>
+        <v>640</v>
       </c>
       <c r="F92">
         <v>1</v>
       </c>
       <c r="G92" t="s">
-        <v>456</v>
+        <v>736</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -3888,19 +4830,19 @@
         <v>98</v>
       </c>
       <c r="C93" t="s">
-        <v>203</v>
+        <v>272</v>
       </c>
       <c r="D93" t="s">
-        <v>315</v>
+        <v>454</v>
       </c>
       <c r="E93" t="s">
-        <v>431</v>
+        <v>641</v>
       </c>
       <c r="F93">
         <v>1</v>
       </c>
       <c r="G93" t="s">
-        <v>456</v>
+        <v>736</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -3911,19 +4853,19 @@
         <v>99</v>
       </c>
       <c r="C94" t="s">
-        <v>204</v>
+        <v>273</v>
       </c>
       <c r="D94" t="s">
-        <v>316</v>
+        <v>455</v>
       </c>
       <c r="E94" t="s">
-        <v>432</v>
+        <v>642</v>
       </c>
       <c r="F94">
         <v>1</v>
       </c>
       <c r="G94" t="s">
-        <v>456</v>
+        <v>736</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -3934,19 +4876,19 @@
         <v>100</v>
       </c>
       <c r="C95" t="s">
-        <v>205</v>
+        <v>274</v>
       </c>
       <c r="D95" t="s">
-        <v>317</v>
+        <v>456</v>
       </c>
       <c r="E95" t="s">
-        <v>433</v>
+        <v>643</v>
       </c>
       <c r="F95">
         <v>1</v>
       </c>
       <c r="G95" t="s">
-        <v>456</v>
+        <v>745</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -3957,19 +4899,19 @@
         <v>101</v>
       </c>
       <c r="C96" t="s">
-        <v>206</v>
+        <v>275</v>
       </c>
       <c r="D96" t="s">
-        <v>318</v>
+        <v>457</v>
       </c>
       <c r="E96" t="s">
-        <v>434</v>
+        <v>101</v>
       </c>
       <c r="F96">
         <v>1</v>
       </c>
       <c r="G96" t="s">
-        <v>456</v>
+        <v>736</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -3980,19 +4922,19 @@
         <v>102</v>
       </c>
       <c r="C97" t="s">
-        <v>185</v>
+        <v>254</v>
       </c>
       <c r="D97" t="s">
-        <v>319</v>
+        <v>458</v>
       </c>
       <c r="E97" t="s">
-        <v>435</v>
+        <v>644</v>
       </c>
       <c r="F97">
         <v>1</v>
       </c>
       <c r="G97" t="s">
-        <v>456</v>
+        <v>736</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -4003,19 +4945,19 @@
         <v>103</v>
       </c>
       <c r="C98" t="s">
-        <v>207</v>
+        <v>276</v>
       </c>
       <c r="D98" t="s">
-        <v>320</v>
+        <v>459</v>
       </c>
       <c r="E98" t="s">
-        <v>436</v>
+        <v>645</v>
       </c>
       <c r="F98">
         <v>1</v>
       </c>
       <c r="G98" t="s">
-        <v>456</v>
+        <v>736</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -4026,19 +4968,19 @@
         <v>104</v>
       </c>
       <c r="C99" t="s">
-        <v>208</v>
+        <v>277</v>
       </c>
       <c r="D99" t="s">
-        <v>321</v>
+        <v>460</v>
       </c>
       <c r="E99" t="s">
-        <v>437</v>
+        <v>646</v>
       </c>
       <c r="F99">
         <v>1</v>
       </c>
       <c r="G99" t="s">
-        <v>456</v>
+        <v>736</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -4049,19 +4991,19 @@
         <v>105</v>
       </c>
       <c r="C100" t="s">
-        <v>209</v>
+        <v>278</v>
       </c>
       <c r="D100" t="s">
-        <v>322</v>
+        <v>461</v>
       </c>
       <c r="E100" t="s">
-        <v>438</v>
+        <v>647</v>
       </c>
       <c r="F100">
         <v>1</v>
       </c>
       <c r="G100" t="s">
-        <v>456</v>
+        <v>736</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -4072,19 +5014,19 @@
         <v>106</v>
       </c>
       <c r="C101" t="s">
-        <v>210</v>
+        <v>279</v>
       </c>
       <c r="D101" t="s">
-        <v>323</v>
+        <v>462</v>
       </c>
       <c r="E101" t="s">
-        <v>439</v>
+        <v>648</v>
       </c>
       <c r="F101">
         <v>1</v>
       </c>
       <c r="G101" t="s">
-        <v>456</v>
+        <v>736</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -4095,19 +5037,19 @@
         <v>107</v>
       </c>
       <c r="C102" t="s">
-        <v>211</v>
+        <v>280</v>
       </c>
       <c r="D102" t="s">
-        <v>324</v>
+        <v>463</v>
       </c>
       <c r="E102" t="s">
-        <v>440</v>
+        <v>649</v>
       </c>
       <c r="F102">
         <v>1</v>
       </c>
       <c r="G102" t="s">
-        <v>456</v>
+        <v>736</v>
       </c>
     </row>
     <row r="103" spans="1:7">
@@ -4118,19 +5060,19 @@
         <v>108</v>
       </c>
       <c r="C103" t="s">
-        <v>212</v>
+        <v>281</v>
       </c>
       <c r="D103" t="s">
-        <v>325</v>
+        <v>464</v>
       </c>
       <c r="E103" t="s">
-        <v>441</v>
+        <v>650</v>
       </c>
       <c r="F103">
         <v>1</v>
       </c>
       <c r="G103" t="s">
-        <v>456</v>
+        <v>736</v>
       </c>
     </row>
     <row r="104" spans="1:7">
@@ -4141,19 +5083,19 @@
         <v>109</v>
       </c>
       <c r="C104" t="s">
-        <v>213</v>
+        <v>282</v>
       </c>
       <c r="D104" t="s">
-        <v>326</v>
+        <v>465</v>
       </c>
       <c r="E104" t="s">
-        <v>442</v>
+        <v>651</v>
       </c>
       <c r="F104">
         <v>1</v>
       </c>
       <c r="G104" t="s">
-        <v>456</v>
+        <v>736</v>
       </c>
     </row>
     <row r="105" spans="1:7">
@@ -4164,19 +5106,19 @@
         <v>110</v>
       </c>
       <c r="C105" t="s">
-        <v>214</v>
+        <v>283</v>
       </c>
       <c r="D105" t="s">
-        <v>327</v>
+        <v>466</v>
       </c>
       <c r="E105" t="s">
-        <v>443</v>
+        <v>652</v>
       </c>
       <c r="F105">
         <v>1</v>
       </c>
       <c r="G105" t="s">
-        <v>456</v>
+        <v>736</v>
       </c>
     </row>
     <row r="106" spans="1:7">
@@ -4187,19 +5129,19 @@
         <v>111</v>
       </c>
       <c r="C106" t="s">
-        <v>215</v>
+        <v>284</v>
       </c>
       <c r="D106" t="s">
-        <v>328</v>
+        <v>467</v>
       </c>
       <c r="E106" t="s">
-        <v>444</v>
+        <v>653</v>
       </c>
       <c r="F106">
         <v>1</v>
       </c>
       <c r="G106" t="s">
-        <v>456</v>
+        <v>736</v>
       </c>
     </row>
     <row r="107" spans="1:7">
@@ -4213,16 +5155,16 @@
         <v>112</v>
       </c>
       <c r="D107" t="s">
-        <v>329</v>
+        <v>468</v>
       </c>
       <c r="E107" t="s">
-        <v>445</v>
+        <v>654</v>
       </c>
       <c r="F107">
         <v>1</v>
       </c>
       <c r="G107" t="s">
-        <v>462</v>
+        <v>741</v>
       </c>
     </row>
     <row r="108" spans="1:7">
@@ -4236,16 +5178,16 @@
         <v>113</v>
       </c>
       <c r="D108" t="s">
-        <v>330</v>
+        <v>469</v>
       </c>
       <c r="E108" t="s">
-        <v>446</v>
+        <v>655</v>
       </c>
       <c r="F108">
         <v>1</v>
       </c>
       <c r="G108" t="s">
-        <v>462</v>
+        <v>741</v>
       </c>
     </row>
     <row r="109" spans="1:7">
@@ -4259,16 +5201,16 @@
         <v>114</v>
       </c>
       <c r="D109" t="s">
-        <v>331</v>
+        <v>470</v>
       </c>
       <c r="E109" t="s">
-        <v>447</v>
+        <v>656</v>
       </c>
       <c r="F109">
         <v>1</v>
       </c>
       <c r="G109" t="s">
-        <v>462</v>
+        <v>741</v>
       </c>
     </row>
     <row r="110" spans="1:7">
@@ -4279,19 +5221,19 @@
         <v>115</v>
       </c>
       <c r="C110" t="s">
-        <v>216</v>
+        <v>285</v>
       </c>
       <c r="D110" t="s">
-        <v>332</v>
+        <v>471</v>
       </c>
       <c r="E110" t="s">
-        <v>448</v>
+        <v>657</v>
       </c>
       <c r="F110">
         <v>1</v>
       </c>
       <c r="G110" t="s">
-        <v>456</v>
+        <v>736</v>
       </c>
     </row>
     <row r="111" spans="1:7">
@@ -4302,19 +5244,19 @@
         <v>116</v>
       </c>
       <c r="C111" t="s">
-        <v>217</v>
+        <v>286</v>
       </c>
       <c r="D111" t="s">
-        <v>333</v>
+        <v>472</v>
       </c>
       <c r="E111" t="s">
-        <v>449</v>
+        <v>658</v>
       </c>
       <c r="F111">
         <v>1</v>
       </c>
       <c r="G111" t="s">
-        <v>456</v>
+        <v>736</v>
       </c>
     </row>
     <row r="112" spans="1:7">
@@ -4325,19 +5267,19 @@
         <v>117</v>
       </c>
       <c r="C112" t="s">
-        <v>218</v>
+        <v>287</v>
       </c>
       <c r="D112" t="s">
-        <v>334</v>
+        <v>473</v>
       </c>
       <c r="E112" t="s">
-        <v>450</v>
+        <v>659</v>
       </c>
       <c r="F112">
         <v>1</v>
       </c>
       <c r="G112" t="s">
-        <v>467</v>
+        <v>746</v>
       </c>
     </row>
     <row r="113" spans="1:7">
@@ -4348,19 +5290,19 @@
         <v>118</v>
       </c>
       <c r="C113" t="s">
-        <v>219</v>
+        <v>288</v>
       </c>
       <c r="D113" t="s">
-        <v>335</v>
+        <v>474</v>
       </c>
       <c r="E113" t="s">
-        <v>451</v>
+        <v>660</v>
       </c>
       <c r="F113">
         <v>1</v>
       </c>
       <c r="G113" t="s">
-        <v>468</v>
+        <v>736</v>
       </c>
     </row>
     <row r="114" spans="1:7">
@@ -4371,19 +5313,19 @@
         <v>119</v>
       </c>
       <c r="C114" t="s">
-        <v>220</v>
+        <v>289</v>
       </c>
       <c r="D114" t="s">
-        <v>336</v>
+        <v>475</v>
       </c>
       <c r="E114" t="s">
-        <v>452</v>
+        <v>661</v>
       </c>
       <c r="F114">
         <v>1</v>
       </c>
       <c r="G114" t="s">
-        <v>469</v>
+        <v>747</v>
       </c>
     </row>
     <row r="115" spans="1:7">
@@ -4394,19 +5336,19 @@
         <v>120</v>
       </c>
       <c r="C115" t="s">
-        <v>221</v>
+        <v>290</v>
       </c>
       <c r="D115" t="s">
-        <v>337</v>
+        <v>476</v>
       </c>
       <c r="E115" t="s">
-        <v>453</v>
+        <v>662</v>
       </c>
       <c r="F115">
         <v>1</v>
       </c>
       <c r="G115" t="s">
-        <v>470</v>
+        <v>748</v>
       </c>
     </row>
     <row r="116" spans="1:7">
@@ -4417,19 +5359,19 @@
         <v>121</v>
       </c>
       <c r="C116" t="s">
-        <v>222</v>
+        <v>291</v>
       </c>
       <c r="D116" t="s">
-        <v>338</v>
+        <v>477</v>
       </c>
       <c r="E116" t="s">
-        <v>454</v>
+        <v>663</v>
       </c>
       <c r="F116">
         <v>1</v>
       </c>
       <c r="G116" t="s">
-        <v>456</v>
+        <v>736</v>
       </c>
     </row>
     <row r="117" spans="1:7">
@@ -4440,19 +5382,1649 @@
         <v>122</v>
       </c>
       <c r="C117" t="s">
-        <v>223</v>
+        <v>292</v>
       </c>
       <c r="D117" t="s">
+        <v>478</v>
+      </c>
+      <c r="E117" t="s">
+        <v>664</v>
+      </c>
+      <c r="F117">
+        <v>1</v>
+      </c>
+      <c r="G117" t="s">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="118" spans="1:7">
+      <c r="A118">
+        <v>117</v>
+      </c>
+      <c r="B118" t="s">
+        <v>123</v>
+      </c>
+      <c r="C118" t="s">
+        <v>293</v>
+      </c>
+      <c r="D118" t="s">
+        <v>479</v>
+      </c>
+      <c r="E118" t="s">
+        <v>665</v>
+      </c>
+      <c r="F118">
+        <v>1</v>
+      </c>
+      <c r="G118" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="119" spans="1:7">
+      <c r="A119">
+        <v>118</v>
+      </c>
+      <c r="B119" t="s">
+        <v>124</v>
+      </c>
+      <c r="C119" t="s">
+        <v>294</v>
+      </c>
+      <c r="D119" t="s">
+        <v>480</v>
+      </c>
+      <c r="E119" t="s">
+        <v>666</v>
+      </c>
+      <c r="F119">
+        <v>1</v>
+      </c>
+      <c r="G119" t="s">
+        <v>751</v>
+      </c>
+    </row>
+    <row r="120" spans="1:7">
+      <c r="A120">
+        <v>119</v>
+      </c>
+      <c r="B120" t="s">
+        <v>125</v>
+      </c>
+      <c r="C120" t="s">
+        <v>295</v>
+      </c>
+      <c r="D120" t="s">
+        <v>481</v>
+      </c>
+      <c r="E120" t="s">
+        <v>667</v>
+      </c>
+      <c r="F120">
+        <v>1</v>
+      </c>
+      <c r="G120" t="s">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="121" spans="1:7">
+      <c r="A121">
+        <v>120</v>
+      </c>
+      <c r="B121" t="s">
+        <v>126</v>
+      </c>
+      <c r="C121" t="s">
+        <v>296</v>
+      </c>
+      <c r="D121" t="s">
+        <v>482</v>
+      </c>
+      <c r="E121" t="s">
+        <v>668</v>
+      </c>
+      <c r="F121">
+        <v>1</v>
+      </c>
+      <c r="G121" t="s">
+        <v>753</v>
+      </c>
+    </row>
+    <row r="122" spans="1:7">
+      <c r="A122">
+        <v>121</v>
+      </c>
+      <c r="B122" t="s">
+        <v>127</v>
+      </c>
+      <c r="C122" t="s">
+        <v>297</v>
+      </c>
+      <c r="D122" t="s">
+        <v>483</v>
+      </c>
+      <c r="E122" t="s">
+        <v>669</v>
+      </c>
+      <c r="F122">
+        <v>1</v>
+      </c>
+      <c r="G122" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="123" spans="1:7">
+      <c r="A123">
+        <v>122</v>
+      </c>
+      <c r="B123" t="s">
+        <v>128</v>
+      </c>
+      <c r="C123" t="s">
+        <v>298</v>
+      </c>
+      <c r="D123" t="s">
+        <v>484</v>
+      </c>
+      <c r="E123" t="s">
+        <v>670</v>
+      </c>
+      <c r="F123">
+        <v>1</v>
+      </c>
+      <c r="G123" t="s">
+        <v>755</v>
+      </c>
+    </row>
+    <row r="124" spans="1:7">
+      <c r="A124">
+        <v>123</v>
+      </c>
+      <c r="B124" t="s">
+        <v>129</v>
+      </c>
+      <c r="C124" t="s">
+        <v>299</v>
+      </c>
+      <c r="D124" t="s">
+        <v>485</v>
+      </c>
+      <c r="E124" t="s">
+        <v>671</v>
+      </c>
+      <c r="F124">
+        <v>1</v>
+      </c>
+      <c r="G124" t="s">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="125" spans="1:7">
+      <c r="A125">
+        <v>124</v>
+      </c>
+      <c r="B125" t="s">
+        <v>130</v>
+      </c>
+      <c r="C125" t="s">
+        <v>300</v>
+      </c>
+      <c r="D125" t="s">
+        <v>486</v>
+      </c>
+      <c r="E125" t="s">
+        <v>672</v>
+      </c>
+      <c r="F125">
+        <v>1</v>
+      </c>
+      <c r="G125" t="s">
+        <v>757</v>
+      </c>
+    </row>
+    <row r="126" spans="1:7">
+      <c r="A126">
+        <v>125</v>
+      </c>
+      <c r="B126" t="s">
+        <v>131</v>
+      </c>
+      <c r="C126" t="s">
+        <v>301</v>
+      </c>
+      <c r="D126" t="s">
+        <v>487</v>
+      </c>
+      <c r="E126" t="s">
+        <v>673</v>
+      </c>
+      <c r="F126">
+        <v>1</v>
+      </c>
+      <c r="G126" t="s">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="127" spans="1:7">
+      <c r="A127">
+        <v>126</v>
+      </c>
+      <c r="B127" t="s">
+        <v>132</v>
+      </c>
+      <c r="C127" t="s">
+        <v>302</v>
+      </c>
+      <c r="D127" t="s">
+        <v>488</v>
+      </c>
+      <c r="E127" t="s">
+        <v>674</v>
+      </c>
+      <c r="F127">
+        <v>1</v>
+      </c>
+      <c r="G127" t="s">
+        <v>759</v>
+      </c>
+    </row>
+    <row r="128" spans="1:7">
+      <c r="A128">
+        <v>127</v>
+      </c>
+      <c r="B128" t="s">
+        <v>133</v>
+      </c>
+      <c r="C128" t="s">
+        <v>303</v>
+      </c>
+      <c r="D128" t="s">
+        <v>489</v>
+      </c>
+      <c r="E128" t="s">
+        <v>675</v>
+      </c>
+      <c r="F128">
+        <v>1</v>
+      </c>
+      <c r="G128" t="s">
+        <v>760</v>
+      </c>
+    </row>
+    <row r="129" spans="1:7">
+      <c r="A129">
+        <v>128</v>
+      </c>
+      <c r="B129" t="s">
+        <v>134</v>
+      </c>
+      <c r="C129" t="s">
+        <v>304</v>
+      </c>
+      <c r="D129" t="s">
+        <v>490</v>
+      </c>
+      <c r="E129" t="s">
+        <v>676</v>
+      </c>
+      <c r="F129">
+        <v>1</v>
+      </c>
+      <c r="G129" t="s">
+        <v>761</v>
+      </c>
+    </row>
+    <row r="130" spans="1:7">
+      <c r="A130">
+        <v>129</v>
+      </c>
+      <c r="B130" t="s">
+        <v>135</v>
+      </c>
+      <c r="C130" t="s">
+        <v>305</v>
+      </c>
+      <c r="D130" t="s">
+        <v>491</v>
+      </c>
+      <c r="E130" t="s">
+        <v>677</v>
+      </c>
+      <c r="F130">
+        <v>1</v>
+      </c>
+      <c r="G130" t="s">
+        <v>762</v>
+      </c>
+    </row>
+    <row r="131" spans="1:7">
+      <c r="A131">
+        <v>130</v>
+      </c>
+      <c r="B131" t="s">
+        <v>136</v>
+      </c>
+      <c r="C131" t="s">
+        <v>306</v>
+      </c>
+      <c r="D131" t="s">
+        <v>492</v>
+      </c>
+      <c r="E131" t="s">
+        <v>678</v>
+      </c>
+      <c r="F131">
+        <v>1</v>
+      </c>
+      <c r="G131" t="s">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="132" spans="1:7">
+      <c r="A132">
+        <v>131</v>
+      </c>
+      <c r="B132" t="s">
+        <v>137</v>
+      </c>
+      <c r="C132" t="s">
+        <v>307</v>
+      </c>
+      <c r="D132" t="s">
+        <v>493</v>
+      </c>
+      <c r="E132" t="s">
+        <v>679</v>
+      </c>
+      <c r="F132">
+        <v>1</v>
+      </c>
+      <c r="G132" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="133" spans="1:7">
+      <c r="A133">
+        <v>132</v>
+      </c>
+      <c r="B133" t="s">
+        <v>138</v>
+      </c>
+      <c r="C133" t="s">
+        <v>308</v>
+      </c>
+      <c r="D133" t="s">
+        <v>494</v>
+      </c>
+      <c r="E133" t="s">
+        <v>680</v>
+      </c>
+      <c r="F133">
+        <v>1</v>
+      </c>
+      <c r="G133" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="134" spans="1:7">
+      <c r="A134">
+        <v>133</v>
+      </c>
+      <c r="B134" t="s">
+        <v>139</v>
+      </c>
+      <c r="C134" t="s">
+        <v>309</v>
+      </c>
+      <c r="D134" t="s">
+        <v>495</v>
+      </c>
+      <c r="E134" t="s">
+        <v>681</v>
+      </c>
+      <c r="F134">
+        <v>1</v>
+      </c>
+      <c r="G134" t="s">
+        <v>766</v>
+      </c>
+    </row>
+    <row r="135" spans="1:7">
+      <c r="A135">
+        <v>134</v>
+      </c>
+      <c r="B135" t="s">
+        <v>140</v>
+      </c>
+      <c r="C135" t="s">
+        <v>310</v>
+      </c>
+      <c r="D135" t="s">
+        <v>496</v>
+      </c>
+      <c r="E135" t="s">
+        <v>682</v>
+      </c>
+      <c r="F135">
+        <v>1</v>
+      </c>
+      <c r="G135" t="s">
+        <v>767</v>
+      </c>
+    </row>
+    <row r="136" spans="1:7">
+      <c r="A136">
+        <v>135</v>
+      </c>
+      <c r="B136" t="s">
+        <v>141</v>
+      </c>
+      <c r="C136" t="s">
+        <v>311</v>
+      </c>
+      <c r="D136" t="s">
+        <v>497</v>
+      </c>
+      <c r="E136" t="s">
+        <v>683</v>
+      </c>
+      <c r="F136">
+        <v>1</v>
+      </c>
+      <c r="G136" t="s">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="137" spans="1:7">
+      <c r="A137">
+        <v>136</v>
+      </c>
+      <c r="B137" t="s">
+        <v>142</v>
+      </c>
+      <c r="C137" t="s">
+        <v>312</v>
+      </c>
+      <c r="D137" t="s">
+        <v>498</v>
+      </c>
+      <c r="E137" t="s">
+        <v>684</v>
+      </c>
+      <c r="F137">
+        <v>1</v>
+      </c>
+      <c r="G137" t="s">
+        <v>769</v>
+      </c>
+    </row>
+    <row r="138" spans="1:7">
+      <c r="A138">
+        <v>137</v>
+      </c>
+      <c r="B138" t="s">
+        <v>143</v>
+      </c>
+      <c r="C138" t="s">
+        <v>313</v>
+      </c>
+      <c r="D138" t="s">
+        <v>499</v>
+      </c>
+      <c r="E138" t="s">
+        <v>685</v>
+      </c>
+      <c r="F138">
+        <v>1</v>
+      </c>
+      <c r="G138" t="s">
+        <v>770</v>
+      </c>
+    </row>
+    <row r="139" spans="1:7">
+      <c r="A139">
+        <v>138</v>
+      </c>
+      <c r="B139" t="s">
+        <v>144</v>
+      </c>
+      <c r="C139" t="s">
+        <v>314</v>
+      </c>
+      <c r="D139" t="s">
+        <v>500</v>
+      </c>
+      <c r="E139" t="s">
+        <v>686</v>
+      </c>
+      <c r="F139">
+        <v>1</v>
+      </c>
+      <c r="G139" t="s">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="140" spans="1:7">
+      <c r="A140">
+        <v>139</v>
+      </c>
+      <c r="B140" t="s">
+        <v>145</v>
+      </c>
+      <c r="C140" t="s">
+        <v>315</v>
+      </c>
+      <c r="D140" t="s">
+        <v>501</v>
+      </c>
+      <c r="E140" t="s">
+        <v>687</v>
+      </c>
+      <c r="F140">
+        <v>1</v>
+      </c>
+      <c r="G140" t="s">
+        <v>772</v>
+      </c>
+    </row>
+    <row r="141" spans="1:7">
+      <c r="A141">
+        <v>140</v>
+      </c>
+      <c r="B141" t="s">
+        <v>146</v>
+      </c>
+      <c r="C141" t="s">
+        <v>316</v>
+      </c>
+      <c r="D141" t="s">
+        <v>502</v>
+      </c>
+      <c r="E141" t="s">
+        <v>688</v>
+      </c>
+      <c r="F141">
+        <v>1</v>
+      </c>
+      <c r="G141" t="s">
+        <v>773</v>
+      </c>
+    </row>
+    <row r="142" spans="1:7">
+      <c r="A142">
+        <v>141</v>
+      </c>
+      <c r="B142" t="s">
+        <v>147</v>
+      </c>
+      <c r="C142" t="s">
+        <v>317</v>
+      </c>
+      <c r="D142" t="s">
+        <v>503</v>
+      </c>
+      <c r="E142" t="s">
+        <v>689</v>
+      </c>
+      <c r="F142">
+        <v>1</v>
+      </c>
+      <c r="G142" t="s">
+        <v>774</v>
+      </c>
+    </row>
+    <row r="143" spans="1:7">
+      <c r="A143">
+        <v>142</v>
+      </c>
+      <c r="B143" t="s">
+        <v>148</v>
+      </c>
+      <c r="C143" t="s">
+        <v>318</v>
+      </c>
+      <c r="D143" t="s">
+        <v>504</v>
+      </c>
+      <c r="E143" t="s">
+        <v>690</v>
+      </c>
+      <c r="F143">
+        <v>1</v>
+      </c>
+      <c r="G143" t="s">
+        <v>775</v>
+      </c>
+    </row>
+    <row r="144" spans="1:7">
+      <c r="A144">
+        <v>143</v>
+      </c>
+      <c r="B144" t="s">
+        <v>149</v>
+      </c>
+      <c r="C144" t="s">
+        <v>319</v>
+      </c>
+      <c r="D144" t="s">
+        <v>505</v>
+      </c>
+      <c r="E144" t="s">
+        <v>691</v>
+      </c>
+      <c r="F144">
+        <v>1</v>
+      </c>
+      <c r="G144" t="s">
+        <v>776</v>
+      </c>
+    </row>
+    <row r="145" spans="1:7">
+      <c r="A145">
+        <v>144</v>
+      </c>
+      <c r="B145" t="s">
+        <v>150</v>
+      </c>
+      <c r="C145" t="s">
+        <v>320</v>
+      </c>
+      <c r="D145" t="s">
+        <v>506</v>
+      </c>
+      <c r="E145" t="s">
+        <v>692</v>
+      </c>
+      <c r="F145">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="146" spans="1:7">
+      <c r="A146">
+        <v>145</v>
+      </c>
+      <c r="B146" t="s">
+        <v>151</v>
+      </c>
+      <c r="C146" t="s">
+        <v>321</v>
+      </c>
+      <c r="D146" t="s">
+        <v>507</v>
+      </c>
+      <c r="E146" t="s">
+        <v>693</v>
+      </c>
+      <c r="F146">
+        <v>1</v>
+      </c>
+      <c r="G146" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="147" spans="1:7">
+      <c r="A147">
+        <v>146</v>
+      </c>
+      <c r="B147" t="s">
+        <v>152</v>
+      </c>
+      <c r="C147" t="s">
+        <v>322</v>
+      </c>
+      <c r="D147" t="s">
+        <v>508</v>
+      </c>
+      <c r="E147" t="s">
+        <v>694</v>
+      </c>
+      <c r="F147">
+        <v>1</v>
+      </c>
+      <c r="G147" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="148" spans="1:7">
+      <c r="A148">
+        <v>147</v>
+      </c>
+      <c r="B148" t="s">
+        <v>153</v>
+      </c>
+      <c r="C148" t="s">
+        <v>323</v>
+      </c>
+      <c r="D148" t="s">
+        <v>509</v>
+      </c>
+      <c r="E148" t="s">
+        <v>695</v>
+      </c>
+      <c r="F148">
+        <v>1</v>
+      </c>
+      <c r="G148" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="149" spans="1:7">
+      <c r="A149">
+        <v>148</v>
+      </c>
+      <c r="B149" t="s">
+        <v>154</v>
+      </c>
+      <c r="C149" t="s">
+        <v>324</v>
+      </c>
+      <c r="D149" t="s">
+        <v>510</v>
+      </c>
+      <c r="E149" t="s">
+        <v>696</v>
+      </c>
+      <c r="F149">
+        <v>1</v>
+      </c>
+      <c r="G149" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="150" spans="1:7">
+      <c r="A150">
+        <v>149</v>
+      </c>
+      <c r="B150" t="s">
+        <v>155</v>
+      </c>
+      <c r="C150" t="s">
+        <v>325</v>
+      </c>
+      <c r="D150" t="s">
+        <v>511</v>
+      </c>
+      <c r="E150" t="s">
+        <v>697</v>
+      </c>
+      <c r="F150">
+        <v>1</v>
+      </c>
+      <c r="G150" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="151" spans="1:7">
+      <c r="A151">
+        <v>150</v>
+      </c>
+      <c r="B151" t="s">
+        <v>156</v>
+      </c>
+      <c r="C151" t="s">
+        <v>326</v>
+      </c>
+      <c r="D151" t="s">
+        <v>512</v>
+      </c>
+      <c r="E151" t="s">
+        <v>698</v>
+      </c>
+      <c r="F151">
+        <v>1</v>
+      </c>
+      <c r="G151" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="152" spans="1:7">
+      <c r="A152">
+        <v>151</v>
+      </c>
+      <c r="B152" t="s">
+        <v>157</v>
+      </c>
+      <c r="C152" t="s">
+        <v>327</v>
+      </c>
+      <c r="D152" t="s">
+        <v>513</v>
+      </c>
+      <c r="E152" t="s">
+        <v>699</v>
+      </c>
+      <c r="F152">
+        <v>1</v>
+      </c>
+      <c r="G152" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="153" spans="1:7">
+      <c r="A153">
+        <v>152</v>
+      </c>
+      <c r="B153" t="s">
+        <v>158</v>
+      </c>
+      <c r="C153" t="s">
+        <v>328</v>
+      </c>
+      <c r="D153" t="s">
+        <v>514</v>
+      </c>
+      <c r="E153" t="s">
+        <v>700</v>
+      </c>
+      <c r="F153">
+        <v>1</v>
+      </c>
+      <c r="G153" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="154" spans="1:7">
+      <c r="A154">
+        <v>153</v>
+      </c>
+      <c r="B154" t="s">
+        <v>159</v>
+      </c>
+      <c r="C154" t="s">
+        <v>329</v>
+      </c>
+      <c r="D154" t="s">
+        <v>515</v>
+      </c>
+      <c r="E154" t="s">
+        <v>701</v>
+      </c>
+      <c r="F154">
+        <v>1</v>
+      </c>
+      <c r="G154" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="155" spans="1:7">
+      <c r="A155">
+        <v>154</v>
+      </c>
+      <c r="B155" t="s">
+        <v>160</v>
+      </c>
+      <c r="C155" t="s">
+        <v>330</v>
+      </c>
+      <c r="D155" t="s">
+        <v>516</v>
+      </c>
+      <c r="E155" t="s">
+        <v>702</v>
+      </c>
+      <c r="F155">
+        <v>1</v>
+      </c>
+      <c r="G155" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="156" spans="1:7">
+      <c r="A156">
+        <v>155</v>
+      </c>
+      <c r="B156" t="s">
+        <v>161</v>
+      </c>
+      <c r="C156" t="s">
+        <v>331</v>
+      </c>
+      <c r="D156" t="s">
+        <v>517</v>
+      </c>
+      <c r="E156" t="s">
+        <v>703</v>
+      </c>
+      <c r="F156">
+        <v>1</v>
+      </c>
+      <c r="G156" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="157" spans="1:7">
+      <c r="A157">
+        <v>156</v>
+      </c>
+      <c r="B157" t="s">
+        <v>162</v>
+      </c>
+      <c r="C157" t="s">
+        <v>332</v>
+      </c>
+      <c r="D157" t="s">
+        <v>518</v>
+      </c>
+      <c r="E157" t="s">
+        <v>704</v>
+      </c>
+      <c r="F157">
+        <v>1</v>
+      </c>
+      <c r="G157" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="158" spans="1:7">
+      <c r="A158">
+        <v>157</v>
+      </c>
+      <c r="B158" t="s">
+        <v>163</v>
+      </c>
+      <c r="C158" t="s">
+        <v>333</v>
+      </c>
+      <c r="D158" t="s">
+        <v>519</v>
+      </c>
+      <c r="E158" t="s">
+        <v>705</v>
+      </c>
+      <c r="F158">
+        <v>1</v>
+      </c>
+      <c r="G158" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="159" spans="1:7">
+      <c r="A159">
+        <v>158</v>
+      </c>
+      <c r="B159" t="s">
+        <v>164</v>
+      </c>
+      <c r="C159" t="s">
+        <v>334</v>
+      </c>
+      <c r="D159" t="s">
+        <v>520</v>
+      </c>
+      <c r="E159" t="s">
+        <v>706</v>
+      </c>
+      <c r="F159">
+        <v>1</v>
+      </c>
+      <c r="G159" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="160" spans="1:7">
+      <c r="A160">
+        <v>159</v>
+      </c>
+      <c r="B160" t="s">
+        <v>165</v>
+      </c>
+      <c r="C160" t="s">
+        <v>335</v>
+      </c>
+      <c r="D160" t="s">
+        <v>521</v>
+      </c>
+      <c r="E160" t="s">
+        <v>707</v>
+      </c>
+      <c r="F160">
+        <v>1</v>
+      </c>
+      <c r="G160" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="161" spans="1:7">
+      <c r="A161">
+        <v>160</v>
+      </c>
+      <c r="B161" t="s">
+        <v>166</v>
+      </c>
+      <c r="C161" t="s">
+        <v>336</v>
+      </c>
+      <c r="D161" t="s">
+        <v>522</v>
+      </c>
+      <c r="E161" t="s">
+        <v>708</v>
+      </c>
+      <c r="F161">
+        <v>1</v>
+      </c>
+      <c r="G161" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="162" spans="1:7">
+      <c r="A162">
+        <v>161</v>
+      </c>
+      <c r="B162" t="s">
+        <v>167</v>
+      </c>
+      <c r="C162" t="s">
+        <v>337</v>
+      </c>
+      <c r="D162" t="s">
+        <v>523</v>
+      </c>
+      <c r="E162" t="s">
+        <v>709</v>
+      </c>
+      <c r="F162">
+        <v>1</v>
+      </c>
+      <c r="G162" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="163" spans="1:7">
+      <c r="A163">
+        <v>162</v>
+      </c>
+      <c r="B163" t="s">
+        <v>168</v>
+      </c>
+      <c r="C163" t="s">
+        <v>338</v>
+      </c>
+      <c r="D163" t="s">
+        <v>524</v>
+      </c>
+      <c r="E163" t="s">
+        <v>710</v>
+      </c>
+      <c r="F163">
+        <v>1</v>
+      </c>
+      <c r="G163" t="s">
+        <v>778</v>
+      </c>
+    </row>
+    <row r="164" spans="1:7">
+      <c r="A164">
+        <v>163</v>
+      </c>
+      <c r="B164" t="s">
+        <v>169</v>
+      </c>
+      <c r="C164" t="s">
         <v>339</v>
       </c>
-      <c r="E117" t="s">
-        <v>455</v>
-      </c>
-      <c r="F117">
-        <v>1</v>
-      </c>
-      <c r="G117" t="s">
-        <v>471</v>
+      <c r="D164" t="s">
+        <v>525</v>
+      </c>
+      <c r="E164" t="s">
+        <v>711</v>
+      </c>
+      <c r="F164">
+        <v>1</v>
+      </c>
+      <c r="G164" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="165" spans="1:7">
+      <c r="A165">
+        <v>164</v>
+      </c>
+      <c r="B165" t="s">
+        <v>170</v>
+      </c>
+      <c r="C165" t="s">
+        <v>340</v>
+      </c>
+      <c r="D165" t="s">
+        <v>526</v>
+      </c>
+      <c r="E165" t="s">
+        <v>712</v>
+      </c>
+      <c r="F165">
+        <v>1</v>
+      </c>
+      <c r="G165" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="166" spans="1:7">
+      <c r="A166">
+        <v>165</v>
+      </c>
+      <c r="B166" t="s">
+        <v>171</v>
+      </c>
+      <c r="C166" t="s">
+        <v>341</v>
+      </c>
+      <c r="D166" t="s">
+        <v>527</v>
+      </c>
+      <c r="E166" t="s">
+        <v>713</v>
+      </c>
+      <c r="F166">
+        <v>1</v>
+      </c>
+      <c r="G166" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="167" spans="1:7">
+      <c r="A167">
+        <v>166</v>
+      </c>
+      <c r="B167" t="s">
+        <v>172</v>
+      </c>
+      <c r="C167" t="s">
+        <v>342</v>
+      </c>
+      <c r="D167" t="s">
+        <v>528</v>
+      </c>
+      <c r="E167" t="s">
+        <v>714</v>
+      </c>
+      <c r="F167">
+        <v>1</v>
+      </c>
+      <c r="G167" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="168" spans="1:7">
+      <c r="A168">
+        <v>167</v>
+      </c>
+      <c r="B168" t="s">
+        <v>173</v>
+      </c>
+      <c r="C168" t="s">
+        <v>343</v>
+      </c>
+      <c r="D168" t="s">
+        <v>529</v>
+      </c>
+      <c r="E168" t="s">
+        <v>715</v>
+      </c>
+      <c r="F168">
+        <v>1</v>
+      </c>
+      <c r="G168" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="169" spans="1:7">
+      <c r="A169">
+        <v>168</v>
+      </c>
+      <c r="B169" t="s">
+        <v>174</v>
+      </c>
+      <c r="C169" t="s">
+        <v>344</v>
+      </c>
+      <c r="D169" t="s">
+        <v>530</v>
+      </c>
+      <c r="E169" t="s">
+        <v>716</v>
+      </c>
+      <c r="F169">
+        <v>1</v>
+      </c>
+      <c r="G169" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="170" spans="1:7">
+      <c r="A170">
+        <v>169</v>
+      </c>
+      <c r="B170" t="s">
+        <v>175</v>
+      </c>
+      <c r="C170" t="s">
+        <v>345</v>
+      </c>
+      <c r="D170" t="s">
+        <v>531</v>
+      </c>
+      <c r="E170" t="s">
+        <v>717</v>
+      </c>
+      <c r="F170">
+        <v>1</v>
+      </c>
+      <c r="G170" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="171" spans="1:7">
+      <c r="A171">
+        <v>170</v>
+      </c>
+      <c r="B171" t="s">
+        <v>176</v>
+      </c>
+      <c r="C171" t="s">
+        <v>346</v>
+      </c>
+      <c r="D171" t="s">
+        <v>532</v>
+      </c>
+      <c r="E171" t="s">
+        <v>718</v>
+      </c>
+      <c r="F171">
+        <v>1</v>
+      </c>
+      <c r="G171" t="s">
+        <v>779</v>
+      </c>
+    </row>
+    <row r="172" spans="1:7">
+      <c r="A172">
+        <v>171</v>
+      </c>
+      <c r="B172" t="s">
+        <v>177</v>
+      </c>
+      <c r="C172" t="s">
+        <v>347</v>
+      </c>
+      <c r="D172" t="s">
+        <v>533</v>
+      </c>
+      <c r="E172" t="s">
+        <v>719</v>
+      </c>
+      <c r="F172">
+        <v>1</v>
+      </c>
+      <c r="G172" t="s">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="173" spans="1:7">
+      <c r="A173">
+        <v>172</v>
+      </c>
+      <c r="B173" t="s">
+        <v>178</v>
+      </c>
+      <c r="C173" t="s">
+        <v>348</v>
+      </c>
+      <c r="D173" t="s">
+        <v>534</v>
+      </c>
+      <c r="E173" t="s">
+        <v>720</v>
+      </c>
+      <c r="F173">
+        <v>1</v>
+      </c>
+      <c r="G173" t="s">
+        <v>781</v>
+      </c>
+    </row>
+    <row r="174" spans="1:7">
+      <c r="A174">
+        <v>173</v>
+      </c>
+      <c r="B174" t="s">
+        <v>179</v>
+      </c>
+      <c r="C174" t="s">
+        <v>349</v>
+      </c>
+      <c r="D174" t="s">
+        <v>535</v>
+      </c>
+      <c r="E174" t="s">
+        <v>721</v>
+      </c>
+      <c r="F174">
+        <v>1</v>
+      </c>
+      <c r="G174" t="s">
+        <v>782</v>
+      </c>
+    </row>
+    <row r="175" spans="1:7">
+      <c r="A175">
+        <v>174</v>
+      </c>
+      <c r="B175" t="s">
+        <v>180</v>
+      </c>
+      <c r="C175" t="s">
+        <v>350</v>
+      </c>
+      <c r="D175" t="s">
+        <v>536</v>
+      </c>
+      <c r="E175" t="s">
+        <v>722</v>
+      </c>
+      <c r="F175">
+        <v>1</v>
+      </c>
+      <c r="G175" t="s">
+        <v>782</v>
+      </c>
+    </row>
+    <row r="176" spans="1:7">
+      <c r="A176">
+        <v>175</v>
+      </c>
+      <c r="B176" t="s">
+        <v>178</v>
+      </c>
+      <c r="C176" t="s">
+        <v>351</v>
+      </c>
+      <c r="D176" t="s">
+        <v>537</v>
+      </c>
+      <c r="E176" t="s">
+        <v>723</v>
+      </c>
+      <c r="F176">
+        <v>1</v>
+      </c>
+      <c r="G176" t="s">
+        <v>782</v>
+      </c>
+    </row>
+    <row r="177" spans="1:7">
+      <c r="A177">
+        <v>176</v>
+      </c>
+      <c r="B177" t="s">
+        <v>178</v>
+      </c>
+      <c r="C177" t="s">
+        <v>352</v>
+      </c>
+      <c r="D177" t="s">
+        <v>538</v>
+      </c>
+      <c r="E177" t="s">
+        <v>724</v>
+      </c>
+      <c r="F177">
+        <v>1</v>
+      </c>
+      <c r="G177" t="s">
+        <v>782</v>
+      </c>
+    </row>
+    <row r="178" spans="1:7">
+      <c r="A178">
+        <v>177</v>
+      </c>
+      <c r="B178" t="s">
+        <v>181</v>
+      </c>
+      <c r="C178" t="s">
+        <v>353</v>
+      </c>
+      <c r="D178" t="s">
+        <v>539</v>
+      </c>
+      <c r="E178" t="s">
+        <v>725</v>
+      </c>
+      <c r="F178">
+        <v>1</v>
+      </c>
+      <c r="G178" t="s">
+        <v>782</v>
+      </c>
+    </row>
+    <row r="179" spans="1:7">
+      <c r="A179">
+        <v>178</v>
+      </c>
+      <c r="B179" t="s">
+        <v>182</v>
+      </c>
+      <c r="C179" t="s">
+        <v>354</v>
+      </c>
+      <c r="D179" t="s">
+        <v>540</v>
+      </c>
+      <c r="E179" t="s">
+        <v>726</v>
+      </c>
+      <c r="F179">
+        <v>1</v>
+      </c>
+      <c r="G179" t="s">
+        <v>782</v>
+      </c>
+    </row>
+    <row r="180" spans="1:7">
+      <c r="A180">
+        <v>179</v>
+      </c>
+      <c r="B180" t="s">
+        <v>183</v>
+      </c>
+      <c r="C180" t="s">
+        <v>355</v>
+      </c>
+      <c r="D180" t="s">
+        <v>541</v>
+      </c>
+      <c r="E180" t="s">
+        <v>727</v>
+      </c>
+      <c r="F180">
+        <v>1</v>
+      </c>
+      <c r="G180" t="s">
+        <v>782</v>
+      </c>
+    </row>
+    <row r="181" spans="1:7">
+      <c r="A181">
+        <v>180</v>
+      </c>
+      <c r="B181" t="s">
+        <v>184</v>
+      </c>
+      <c r="C181" t="s">
+        <v>356</v>
+      </c>
+      <c r="D181" t="s">
+        <v>542</v>
+      </c>
+      <c r="E181" t="s">
+        <v>728</v>
+      </c>
+      <c r="F181">
+        <v>1</v>
+      </c>
+      <c r="G181" t="s">
+        <v>783</v>
+      </c>
+    </row>
+    <row r="182" spans="1:7">
+      <c r="A182">
+        <v>181</v>
+      </c>
+      <c r="B182" t="s">
+        <v>185</v>
+      </c>
+      <c r="C182" t="s">
+        <v>357</v>
+      </c>
+      <c r="D182" t="s">
+        <v>543</v>
+      </c>
+      <c r="E182" t="s">
+        <v>729</v>
+      </c>
+      <c r="F182">
+        <v>1</v>
+      </c>
+      <c r="G182" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="183" spans="1:7">
+      <c r="A183">
+        <v>182</v>
+      </c>
+      <c r="B183" t="s">
+        <v>186</v>
+      </c>
+      <c r="C183" t="s">
+        <v>358</v>
+      </c>
+      <c r="D183" t="s">
+        <v>544</v>
+      </c>
+      <c r="E183" t="s">
+        <v>730</v>
+      </c>
+      <c r="F183">
+        <v>1</v>
+      </c>
+      <c r="G183" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="184" spans="1:7">
+      <c r="A184">
+        <v>183</v>
+      </c>
+      <c r="B184" t="s">
+        <v>187</v>
+      </c>
+      <c r="C184" t="s">
+        <v>359</v>
+      </c>
+      <c r="D184" t="s">
+        <v>545</v>
+      </c>
+      <c r="E184" t="s">
+        <v>731</v>
+      </c>
+      <c r="F184">
+        <v>1</v>
+      </c>
+      <c r="G184" t="s">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="185" spans="1:7">
+      <c r="A185">
+        <v>184</v>
+      </c>
+      <c r="B185" t="s">
+        <v>188</v>
+      </c>
+      <c r="C185" t="s">
+        <v>360</v>
+      </c>
+      <c r="D185" t="s">
+        <v>546</v>
+      </c>
+      <c r="E185" t="s">
+        <v>732</v>
+      </c>
+      <c r="F185">
+        <v>1</v>
+      </c>
+      <c r="G185" t="s">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="186" spans="1:7">
+      <c r="A186">
+        <v>185</v>
+      </c>
+      <c r="B186" t="s">
+        <v>189</v>
+      </c>
+      <c r="C186" t="s">
+        <v>361</v>
+      </c>
+      <c r="D186" t="s">
+        <v>547</v>
+      </c>
+      <c r="E186" t="s">
+        <v>733</v>
+      </c>
+      <c r="F186">
+        <v>1</v>
+      </c>
+      <c r="G186" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="187" spans="1:7">
+      <c r="A187">
+        <v>186</v>
+      </c>
+      <c r="B187" t="s">
+        <v>190</v>
+      </c>
+      <c r="C187" t="s">
+        <v>362</v>
+      </c>
+      <c r="D187" t="s">
+        <v>548</v>
+      </c>
+      <c r="E187" t="s">
+        <v>734</v>
+      </c>
+      <c r="F187">
+        <v>1</v>
+      </c>
+      <c r="G187" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="188" spans="1:7">
+      <c r="A188">
+        <v>187</v>
+      </c>
+      <c r="B188" t="s">
+        <v>191</v>
+      </c>
+      <c r="C188" t="s">
+        <v>363</v>
+      </c>
+      <c r="D188" t="s">
+        <v>549</v>
+      </c>
+      <c r="E188" t="s">
+        <v>735</v>
+      </c>
+      <c r="F188">
+        <v>1</v>
+      </c>
+      <c r="G188" t="s">
+        <v>736</v>
       </c>
     </row>
   </sheetData>

--- a/data/target_dispatch/파보겔_실제발송_최종정제명단.xlsx
+++ b/data/target_dispatch/파보겔_실제발송_최종정제명단.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="940" uniqueCount="787">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="970" uniqueCount="813">
   <si>
     <t>순번</t>
   </si>
@@ -592,6 +592,24 @@
     <t>강아지대공원</t>
   </si>
   <si>
+    <t>유앤미펫</t>
+  </si>
+  <si>
+    <t>슈팅가이 켄넬</t>
+  </si>
+  <si>
+    <t>탑퍼피</t>
+  </si>
+  <si>
+    <t>청주강아지분양 리몽드켄넬</t>
+  </si>
+  <si>
+    <t>강아지농장</t>
+  </si>
+  <si>
+    <t>강해성</t>
+  </si>
+  <si>
     <t>정원정</t>
   </si>
   <si>
@@ -1108,6 +1126,21 @@
     <t>이완구</t>
   </si>
   <si>
+    <t>김승기</t>
+  </si>
+  <si>
+    <t>신연재</t>
+  </si>
+  <si>
+    <t>김보송</t>
+  </si>
+  <si>
+    <t>이정년</t>
+  </si>
+  <si>
+    <t>이인옥</t>
+  </si>
+  <si>
     <t>010-3114-1100</t>
   </si>
   <si>
@@ -1666,6 +1699,24 @@
     <t>010-2828-9779</t>
   </si>
   <si>
+    <t>010-7158-7801</t>
+  </si>
+  <si>
+    <t>010-4803-8787</t>
+  </si>
+  <si>
+    <t>010-2445-4445</t>
+  </si>
+  <si>
+    <t>010-2447-8264</t>
+  </si>
+  <si>
+    <t>010-3797-8689</t>
+  </si>
+  <si>
+    <t>010-3350-5188</t>
+  </si>
+  <si>
     <t>원주시 태장동 흥양로30  대흥아파트202-1202</t>
   </si>
   <si>
@@ -2224,6 +2275,24 @@
     <t>경기도 양주시 옥정동로7다길 62 대길프라자 강아지대공원</t>
   </si>
   <si>
+    <t>인천광역시 남동구 간석동 210-9번지</t>
+  </si>
+  <si>
+    <t>경북 포항시 북구 청하면 미남리 72번지 C동 (슈팅가이 켄넬)</t>
+  </si>
+  <si>
+    <t>경기도 화성시 꽃내음1길 19-26 101호 TOPPUPPY</t>
+  </si>
+  <si>
+    <t>충청북도 청주시 청원구 율량로 38, 102호(주중동)</t>
+  </si>
+  <si>
+    <t>경기도 포천시 신북면 호국로 1887-1</t>
+  </si>
+  <si>
+    <t>경기도 화성시 장안면 포승장안로 1290-30</t>
+  </si>
+  <si>
     <t>[MMS 문자 유입] 펫샵 본품 1병 무료 샘플 신청</t>
   </si>
   <si>
@@ -2375,6 +2444,15 @@
   </si>
   <si>
     <t>[MMS 문자 유입] 펫샵·켄넬 본품 1병 무료 샘플 신청 (동일 주소지 청통농장 인접 분리 배송)</t>
+  </si>
+  <si>
+    <t>[사업자등록증 사진 인증 접수] 동물판매업 본품 1병 무료 샘플 신청 (231-97-01826)</t>
+  </si>
+  <si>
+    <t>[문자 직통 신청] 브리더/농장 본품 1병 무료 샘플 신청</t>
+  </si>
+  <si>
+    <t>[현장 직접 전달] 에스앤제이 동물병원 현장에서 직접 샘플 전달 완료</t>
   </si>
 </sst>
 </file>
@@ -2706,7 +2784,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G188"/>
+  <dimension ref="A1:G194"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -2740,19 +2818,19 @@
         <v>7</v>
       </c>
       <c r="C2" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="D2" t="s">
-        <v>364</v>
+        <v>375</v>
       </c>
       <c r="E2" t="s">
-        <v>550</v>
+        <v>567</v>
       </c>
       <c r="F2">
         <v>1</v>
       </c>
       <c r="G2" t="s">
-        <v>736</v>
+        <v>759</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -2763,19 +2841,19 @@
         <v>8</v>
       </c>
       <c r="C3" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="D3" t="s">
-        <v>365</v>
+        <v>376</v>
       </c>
       <c r="E3" t="s">
-        <v>551</v>
+        <v>568</v>
       </c>
       <c r="F3">
         <v>1</v>
       </c>
       <c r="G3" t="s">
-        <v>736</v>
+        <v>759</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -2786,19 +2864,19 @@
         <v>9</v>
       </c>
       <c r="C4" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="D4" t="s">
-        <v>366</v>
+        <v>377</v>
       </c>
       <c r="E4" t="s">
-        <v>552</v>
+        <v>569</v>
       </c>
       <c r="F4">
         <v>1</v>
       </c>
       <c r="G4" t="s">
-        <v>736</v>
+        <v>759</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -2809,19 +2887,19 @@
         <v>10</v>
       </c>
       <c r="C5" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="D5" t="s">
-        <v>367</v>
+        <v>378</v>
       </c>
       <c r="E5" t="s">
-        <v>553</v>
+        <v>570</v>
       </c>
       <c r="F5">
         <v>1</v>
       </c>
       <c r="G5" t="s">
-        <v>736</v>
+        <v>759</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -2832,19 +2910,19 @@
         <v>11</v>
       </c>
       <c r="C6" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="D6" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="E6" t="s">
-        <v>554</v>
+        <v>571</v>
       </c>
       <c r="F6">
         <v>1</v>
       </c>
       <c r="G6" t="s">
-        <v>736</v>
+        <v>759</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -2855,19 +2933,19 @@
         <v>12</v>
       </c>
       <c r="C7" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="D7" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="E7" t="s">
-        <v>555</v>
+        <v>572</v>
       </c>
       <c r="F7">
         <v>1</v>
       </c>
       <c r="G7" t="s">
-        <v>736</v>
+        <v>759</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -2878,19 +2956,19 @@
         <v>13</v>
       </c>
       <c r="C8" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="D8" t="s">
-        <v>370</v>
+        <v>381</v>
       </c>
       <c r="E8" t="s">
-        <v>556</v>
+        <v>573</v>
       </c>
       <c r="F8">
         <v>1</v>
       </c>
       <c r="G8" t="s">
-        <v>736</v>
+        <v>759</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -2901,19 +2979,19 @@
         <v>14</v>
       </c>
       <c r="C9" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="D9" t="s">
-        <v>371</v>
+        <v>382</v>
       </c>
       <c r="E9" t="s">
-        <v>557</v>
+        <v>574</v>
       </c>
       <c r="F9">
         <v>1</v>
       </c>
       <c r="G9" t="s">
-        <v>736</v>
+        <v>759</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -2924,19 +3002,19 @@
         <v>15</v>
       </c>
       <c r="C10" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="D10" t="s">
-        <v>372</v>
+        <v>383</v>
       </c>
       <c r="E10" t="s">
-        <v>558</v>
+        <v>575</v>
       </c>
       <c r="F10">
         <v>1</v>
       </c>
       <c r="G10" t="s">
-        <v>736</v>
+        <v>759</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -2947,13 +3025,13 @@
         <v>16</v>
       </c>
       <c r="C11" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="D11" t="s">
-        <v>373</v>
+        <v>384</v>
       </c>
       <c r="E11" t="s">
-        <v>559</v>
+        <v>576</v>
       </c>
       <c r="F11">
         <v>1</v>
@@ -2967,19 +3045,19 @@
         <v>17</v>
       </c>
       <c r="C12" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="D12" t="s">
-        <v>374</v>
+        <v>385</v>
       </c>
       <c r="E12" t="s">
-        <v>560</v>
+        <v>577</v>
       </c>
       <c r="F12">
         <v>1</v>
       </c>
       <c r="G12" t="s">
-        <v>736</v>
+        <v>759</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -2990,19 +3068,19 @@
         <v>18</v>
       </c>
       <c r="C13" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="D13" t="s">
-        <v>375</v>
+        <v>386</v>
       </c>
       <c r="E13" t="s">
-        <v>561</v>
+        <v>578</v>
       </c>
       <c r="F13">
         <v>1</v>
       </c>
       <c r="G13" t="s">
-        <v>736</v>
+        <v>759</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -3013,19 +3091,19 @@
         <v>19</v>
       </c>
       <c r="C14" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="D14" t="s">
-        <v>376</v>
+        <v>387</v>
       </c>
       <c r="E14" t="s">
-        <v>562</v>
+        <v>579</v>
       </c>
       <c r="F14">
         <v>1</v>
       </c>
       <c r="G14" t="s">
-        <v>736</v>
+        <v>759</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -3036,19 +3114,19 @@
         <v>20</v>
       </c>
       <c r="C15" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="D15" t="s">
-        <v>377</v>
+        <v>388</v>
       </c>
       <c r="E15" t="s">
-        <v>563</v>
+        <v>580</v>
       </c>
       <c r="F15">
         <v>1</v>
       </c>
       <c r="G15" t="s">
-        <v>736</v>
+        <v>759</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -3059,19 +3137,19 @@
         <v>21</v>
       </c>
       <c r="C16" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="D16" t="s">
-        <v>378</v>
+        <v>389</v>
       </c>
       <c r="E16" t="s">
-        <v>564</v>
+        <v>581</v>
       </c>
       <c r="F16">
         <v>1</v>
       </c>
       <c r="G16" t="s">
-        <v>737</v>
+        <v>760</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -3082,19 +3160,19 @@
         <v>22</v>
       </c>
       <c r="C17" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="D17" t="s">
-        <v>379</v>
+        <v>390</v>
       </c>
       <c r="E17" t="s">
-        <v>565</v>
+        <v>582</v>
       </c>
       <c r="F17">
         <v>1</v>
       </c>
       <c r="G17" t="s">
-        <v>736</v>
+        <v>759</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -3105,19 +3183,19 @@
         <v>23</v>
       </c>
       <c r="C18" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="D18" t="s">
-        <v>380</v>
+        <v>391</v>
       </c>
       <c r="E18" t="s">
-        <v>566</v>
+        <v>583</v>
       </c>
       <c r="F18">
         <v>1</v>
       </c>
       <c r="G18" t="s">
-        <v>736</v>
+        <v>759</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -3128,19 +3206,19 @@
         <v>24</v>
       </c>
       <c r="C19" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="D19" t="s">
-        <v>381</v>
+        <v>392</v>
       </c>
       <c r="E19" t="s">
-        <v>567</v>
+        <v>584</v>
       </c>
       <c r="F19">
         <v>1</v>
       </c>
       <c r="G19" t="s">
-        <v>736</v>
+        <v>759</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -3151,19 +3229,19 @@
         <v>25</v>
       </c>
       <c r="C20" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="D20" t="s">
-        <v>382</v>
+        <v>393</v>
       </c>
       <c r="E20" t="s">
-        <v>568</v>
+        <v>585</v>
       </c>
       <c r="F20">
         <v>1</v>
       </c>
       <c r="G20" t="s">
-        <v>736</v>
+        <v>759</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -3174,19 +3252,19 @@
         <v>26</v>
       </c>
       <c r="C21" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="D21" t="s">
-        <v>383</v>
+        <v>394</v>
       </c>
       <c r="E21" t="s">
-        <v>569</v>
+        <v>586</v>
       </c>
       <c r="F21">
         <v>1</v>
       </c>
       <c r="G21" t="s">
-        <v>736</v>
+        <v>759</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -3197,19 +3275,19 @@
         <v>27</v>
       </c>
       <c r="C22" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="D22" t="s">
-        <v>384</v>
+        <v>395</v>
       </c>
       <c r="E22" t="s">
-        <v>570</v>
+        <v>587</v>
       </c>
       <c r="F22">
         <v>1</v>
       </c>
       <c r="G22" t="s">
-        <v>736</v>
+        <v>759</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -3220,19 +3298,19 @@
         <v>28</v>
       </c>
       <c r="C23" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="D23" t="s">
-        <v>385</v>
+        <v>396</v>
       </c>
       <c r="E23" t="s">
-        <v>571</v>
+        <v>588</v>
       </c>
       <c r="F23">
         <v>1</v>
       </c>
       <c r="G23" t="s">
-        <v>736</v>
+        <v>759</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -3243,19 +3321,19 @@
         <v>29</v>
       </c>
       <c r="C24" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="D24" t="s">
-        <v>386</v>
+        <v>397</v>
       </c>
       <c r="E24" t="s">
-        <v>572</v>
+        <v>589</v>
       </c>
       <c r="F24">
         <v>1</v>
       </c>
       <c r="G24" t="s">
-        <v>736</v>
+        <v>759</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -3266,19 +3344,19 @@
         <v>30</v>
       </c>
       <c r="C25" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="D25" t="s">
-        <v>387</v>
+        <v>398</v>
       </c>
       <c r="E25" t="s">
-        <v>573</v>
+        <v>590</v>
       </c>
       <c r="F25">
         <v>1</v>
       </c>
       <c r="G25" t="s">
-        <v>736</v>
+        <v>759</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -3289,19 +3367,19 @@
         <v>31</v>
       </c>
       <c r="C26" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="D26" t="s">
-        <v>388</v>
+        <v>399</v>
       </c>
       <c r="E26" t="s">
-        <v>574</v>
+        <v>591</v>
       </c>
       <c r="F26">
         <v>1</v>
       </c>
       <c r="G26" t="s">
-        <v>736</v>
+        <v>759</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -3312,19 +3390,19 @@
         <v>32</v>
       </c>
       <c r="C27" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="D27" t="s">
-        <v>389</v>
+        <v>400</v>
       </c>
       <c r="E27" t="s">
-        <v>575</v>
+        <v>592</v>
       </c>
       <c r="F27">
         <v>1</v>
       </c>
       <c r="G27" t="s">
-        <v>736</v>
+        <v>759</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -3335,19 +3413,19 @@
         <v>33</v>
       </c>
       <c r="C28" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="D28" t="s">
-        <v>390</v>
+        <v>401</v>
       </c>
       <c r="E28" t="s">
-        <v>576</v>
+        <v>593</v>
       </c>
       <c r="F28">
         <v>1</v>
       </c>
       <c r="G28" t="s">
-        <v>736</v>
+        <v>759</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -3358,19 +3436,19 @@
         <v>34</v>
       </c>
       <c r="C29" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="D29" t="s">
-        <v>391</v>
+        <v>402</v>
       </c>
       <c r="E29" t="s">
-        <v>577</v>
+        <v>594</v>
       </c>
       <c r="F29">
         <v>1</v>
       </c>
       <c r="G29" t="s">
-        <v>736</v>
+        <v>759</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -3381,19 +3459,19 @@
         <v>35</v>
       </c>
       <c r="C30" t="s">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="D30" t="s">
-        <v>392</v>
+        <v>403</v>
       </c>
       <c r="E30" t="s">
-        <v>578</v>
+        <v>595</v>
       </c>
       <c r="F30">
         <v>1</v>
       </c>
       <c r="G30" t="s">
-        <v>736</v>
+        <v>759</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -3404,19 +3482,19 @@
         <v>36</v>
       </c>
       <c r="C31" t="s">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="D31" t="s">
-        <v>393</v>
+        <v>404</v>
       </c>
       <c r="E31" t="s">
-        <v>579</v>
+        <v>596</v>
       </c>
       <c r="F31">
         <v>1</v>
       </c>
       <c r="G31" t="s">
-        <v>736</v>
+        <v>759</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -3427,19 +3505,19 @@
         <v>37</v>
       </c>
       <c r="C32" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="D32" t="s">
-        <v>394</v>
+        <v>405</v>
       </c>
       <c r="E32" t="s">
-        <v>580</v>
+        <v>597</v>
       </c>
       <c r="F32">
         <v>1</v>
       </c>
       <c r="G32" t="s">
-        <v>736</v>
+        <v>759</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -3450,19 +3528,19 @@
         <v>38</v>
       </c>
       <c r="C33" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="D33" t="s">
-        <v>395</v>
+        <v>406</v>
       </c>
       <c r="E33" t="s">
-        <v>581</v>
+        <v>598</v>
       </c>
       <c r="F33">
         <v>1</v>
       </c>
       <c r="G33" t="s">
-        <v>736</v>
+        <v>759</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -3473,19 +3551,19 @@
         <v>39</v>
       </c>
       <c r="C34" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="D34" t="s">
-        <v>396</v>
+        <v>407</v>
       </c>
       <c r="E34" t="s">
-        <v>582</v>
+        <v>599</v>
       </c>
       <c r="F34">
         <v>1</v>
       </c>
       <c r="G34" t="s">
-        <v>736</v>
+        <v>759</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -3496,19 +3574,19 @@
         <v>40</v>
       </c>
       <c r="C35" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="D35" t="s">
-        <v>397</v>
+        <v>408</v>
       </c>
       <c r="E35" t="s">
-        <v>583</v>
+        <v>600</v>
       </c>
       <c r="F35">
         <v>1</v>
       </c>
       <c r="G35" t="s">
-        <v>736</v>
+        <v>759</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -3519,19 +3597,19 @@
         <v>41</v>
       </c>
       <c r="C36" t="s">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="D36" t="s">
-        <v>398</v>
+        <v>409</v>
       </c>
       <c r="E36" t="s">
-        <v>584</v>
+        <v>601</v>
       </c>
       <c r="F36">
         <v>1</v>
       </c>
       <c r="G36" t="s">
-        <v>736</v>
+        <v>759</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -3542,19 +3620,19 @@
         <v>42</v>
       </c>
       <c r="C37" t="s">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="D37" t="s">
-        <v>399</v>
+        <v>410</v>
       </c>
       <c r="E37" t="s">
-        <v>585</v>
+        <v>602</v>
       </c>
       <c r="F37">
         <v>1</v>
       </c>
       <c r="G37" t="s">
-        <v>736</v>
+        <v>759</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -3565,19 +3643,19 @@
         <v>43</v>
       </c>
       <c r="C38" t="s">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="D38" t="s">
-        <v>400</v>
+        <v>411</v>
       </c>
       <c r="E38" t="s">
-        <v>586</v>
+        <v>603</v>
       </c>
       <c r="F38">
         <v>1</v>
       </c>
       <c r="G38" t="s">
-        <v>736</v>
+        <v>759</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -3588,19 +3666,19 @@
         <v>44</v>
       </c>
       <c r="C39" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="D39" t="s">
-        <v>401</v>
+        <v>412</v>
       </c>
       <c r="E39" t="s">
-        <v>587</v>
+        <v>604</v>
       </c>
       <c r="F39">
         <v>1</v>
       </c>
       <c r="G39" t="s">
-        <v>736</v>
+        <v>759</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -3611,19 +3689,19 @@
         <v>45</v>
       </c>
       <c r="C40" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="D40" t="s">
-        <v>402</v>
+        <v>413</v>
       </c>
       <c r="E40" t="s">
-        <v>588</v>
+        <v>605</v>
       </c>
       <c r="F40">
         <v>1</v>
       </c>
       <c r="G40" t="s">
-        <v>738</v>
+        <v>761</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -3634,19 +3712,19 @@
         <v>46</v>
       </c>
       <c r="C41" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="D41" t="s">
-        <v>403</v>
+        <v>414</v>
       </c>
       <c r="E41" t="s">
-        <v>589</v>
+        <v>606</v>
       </c>
       <c r="F41">
         <v>1</v>
       </c>
       <c r="G41" t="s">
-        <v>737</v>
+        <v>760</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -3657,19 +3735,19 @@
         <v>47</v>
       </c>
       <c r="C42" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="D42" t="s">
-        <v>404</v>
+        <v>415</v>
       </c>
       <c r="E42" t="s">
-        <v>590</v>
+        <v>607</v>
       </c>
       <c r="F42">
         <v>1</v>
       </c>
       <c r="G42" t="s">
-        <v>736</v>
+        <v>759</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -3680,19 +3758,19 @@
         <v>48</v>
       </c>
       <c r="C43" t="s">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="D43" t="s">
-        <v>405</v>
+        <v>416</v>
       </c>
       <c r="E43" t="s">
-        <v>591</v>
+        <v>608</v>
       </c>
       <c r="F43">
         <v>1</v>
       </c>
       <c r="G43" t="s">
-        <v>736</v>
+        <v>759</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -3703,19 +3781,19 @@
         <v>49</v>
       </c>
       <c r="C44" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="D44" t="s">
-        <v>406</v>
+        <v>417</v>
       </c>
       <c r="E44" t="s">
-        <v>592</v>
+        <v>609</v>
       </c>
       <c r="F44">
         <v>1</v>
       </c>
       <c r="G44" t="s">
-        <v>736</v>
+        <v>759</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -3726,19 +3804,19 @@
         <v>50</v>
       </c>
       <c r="C45" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="D45" t="s">
-        <v>407</v>
+        <v>418</v>
       </c>
       <c r="E45" t="s">
-        <v>593</v>
+        <v>610</v>
       </c>
       <c r="F45">
         <v>1</v>
       </c>
       <c r="G45" t="s">
-        <v>736</v>
+        <v>759</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -3749,19 +3827,19 @@
         <v>51</v>
       </c>
       <c r="C46" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="D46" t="s">
-        <v>408</v>
+        <v>419</v>
       </c>
       <c r="E46" t="s">
-        <v>594</v>
+        <v>611</v>
       </c>
       <c r="F46">
         <v>1</v>
       </c>
       <c r="G46" t="s">
-        <v>736</v>
+        <v>759</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -3772,19 +3850,19 @@
         <v>52</v>
       </c>
       <c r="C47" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="D47" t="s">
-        <v>409</v>
+        <v>420</v>
       </c>
       <c r="E47" t="s">
-        <v>595</v>
+        <v>612</v>
       </c>
       <c r="F47">
         <v>1</v>
       </c>
       <c r="G47" t="s">
-        <v>736</v>
+        <v>759</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -3795,19 +3873,19 @@
         <v>53</v>
       </c>
       <c r="C48" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="D48" t="s">
-        <v>410</v>
+        <v>421</v>
       </c>
       <c r="E48" t="s">
-        <v>596</v>
+        <v>613</v>
       </c>
       <c r="F48">
         <v>1</v>
       </c>
       <c r="G48" t="s">
-        <v>736</v>
+        <v>759</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -3818,19 +3896,19 @@
         <v>54</v>
       </c>
       <c r="C49" t="s">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="D49" t="s">
-        <v>411</v>
+        <v>422</v>
       </c>
       <c r="E49" t="s">
-        <v>597</v>
+        <v>614</v>
       </c>
       <c r="F49">
         <v>1</v>
       </c>
       <c r="G49" t="s">
-        <v>736</v>
+        <v>759</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -3841,19 +3919,19 @@
         <v>55</v>
       </c>
       <c r="C50" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="D50" t="s">
-        <v>412</v>
+        <v>423</v>
       </c>
       <c r="E50" t="s">
-        <v>598</v>
+        <v>615</v>
       </c>
       <c r="F50">
         <v>1</v>
       </c>
       <c r="G50" t="s">
-        <v>736</v>
+        <v>759</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -3864,19 +3942,19 @@
         <v>56</v>
       </c>
       <c r="C51" t="s">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="D51" t="s">
-        <v>413</v>
+        <v>424</v>
       </c>
       <c r="E51" t="s">
-        <v>599</v>
+        <v>616</v>
       </c>
       <c r="F51">
         <v>1</v>
       </c>
       <c r="G51" t="s">
-        <v>736</v>
+        <v>759</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -3887,19 +3965,19 @@
         <v>57</v>
       </c>
       <c r="C52" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="D52" t="s">
-        <v>414</v>
+        <v>425</v>
       </c>
       <c r="E52" t="s">
-        <v>600</v>
+        <v>617</v>
       </c>
       <c r="F52">
         <v>1</v>
       </c>
       <c r="G52" t="s">
-        <v>736</v>
+        <v>759</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -3910,19 +3988,19 @@
         <v>58</v>
       </c>
       <c r="C53" t="s">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="D53" t="s">
-        <v>415</v>
+        <v>426</v>
       </c>
       <c r="E53" t="s">
-        <v>601</v>
+        <v>618</v>
       </c>
       <c r="F53">
         <v>1</v>
       </c>
       <c r="G53" t="s">
-        <v>736</v>
+        <v>759</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -3933,19 +4011,19 @@
         <v>59</v>
       </c>
       <c r="C54" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="D54" t="s">
-        <v>416</v>
+        <v>427</v>
       </c>
       <c r="E54" t="s">
-        <v>602</v>
+        <v>619</v>
       </c>
       <c r="F54">
         <v>1</v>
       </c>
       <c r="G54" t="s">
-        <v>736</v>
+        <v>759</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -3956,19 +4034,19 @@
         <v>60</v>
       </c>
       <c r="C55" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="D55" t="s">
-        <v>417</v>
+        <v>428</v>
       </c>
       <c r="E55" t="s">
-        <v>603</v>
+        <v>620</v>
       </c>
       <c r="F55">
         <v>1</v>
       </c>
       <c r="G55" t="s">
-        <v>736</v>
+        <v>759</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -3979,19 +4057,19 @@
         <v>61</v>
       </c>
       <c r="C56" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="D56" t="s">
-        <v>418</v>
+        <v>429</v>
       </c>
       <c r="E56" t="s">
-        <v>604</v>
+        <v>621</v>
       </c>
       <c r="F56">
         <v>1</v>
       </c>
       <c r="G56" t="s">
-        <v>736</v>
+        <v>759</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -4002,19 +4080,19 @@
         <v>62</v>
       </c>
       <c r="C57" t="s">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="D57" t="s">
-        <v>419</v>
+        <v>430</v>
       </c>
       <c r="E57" t="s">
-        <v>605</v>
+        <v>622</v>
       </c>
       <c r="F57">
         <v>1</v>
       </c>
       <c r="G57" t="s">
-        <v>739</v>
+        <v>762</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -4025,19 +4103,19 @@
         <v>63</v>
       </c>
       <c r="C58" t="s">
-        <v>248</v>
+        <v>254</v>
       </c>
       <c r="D58" t="s">
-        <v>420</v>
+        <v>431</v>
       </c>
       <c r="E58" t="s">
-        <v>606</v>
+        <v>623</v>
       </c>
       <c r="F58">
         <v>1</v>
       </c>
       <c r="G58" t="s">
-        <v>736</v>
+        <v>759</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -4048,19 +4126,19 @@
         <v>64</v>
       </c>
       <c r="C59" t="s">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="D59" t="s">
-        <v>421</v>
+        <v>432</v>
       </c>
       <c r="E59" t="s">
-        <v>607</v>
+        <v>624</v>
       </c>
       <c r="F59">
         <v>1</v>
       </c>
       <c r="G59" t="s">
-        <v>736</v>
+        <v>759</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -4071,19 +4149,19 @@
         <v>65</v>
       </c>
       <c r="C60" t="s">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="D60" t="s">
-        <v>422</v>
+        <v>433</v>
       </c>
       <c r="E60" t="s">
-        <v>608</v>
+        <v>625</v>
       </c>
       <c r="F60">
         <v>1</v>
       </c>
       <c r="G60" t="s">
-        <v>736</v>
+        <v>759</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -4094,19 +4172,19 @@
         <v>66</v>
       </c>
       <c r="C61" t="s">
-        <v>251</v>
+        <v>257</v>
       </c>
       <c r="D61" t="s">
-        <v>423</v>
+        <v>434</v>
       </c>
       <c r="E61" t="s">
-        <v>609</v>
+        <v>626</v>
       </c>
       <c r="F61">
         <v>1</v>
       </c>
       <c r="G61" t="s">
-        <v>736</v>
+        <v>759</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -4117,19 +4195,19 @@
         <v>67</v>
       </c>
       <c r="C62" t="s">
-        <v>252</v>
+        <v>258</v>
       </c>
       <c r="D62" t="s">
-        <v>424</v>
+        <v>435</v>
       </c>
       <c r="E62" t="s">
-        <v>610</v>
+        <v>627</v>
       </c>
       <c r="F62">
         <v>1</v>
       </c>
       <c r="G62" t="s">
-        <v>736</v>
+        <v>759</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -4140,19 +4218,19 @@
         <v>68</v>
       </c>
       <c r="C63" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="D63" t="s">
-        <v>425</v>
+        <v>436</v>
       </c>
       <c r="E63" t="s">
-        <v>611</v>
+        <v>628</v>
       </c>
       <c r="F63">
         <v>1</v>
       </c>
       <c r="G63" t="s">
-        <v>736</v>
+        <v>759</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -4163,19 +4241,19 @@
         <v>69</v>
       </c>
       <c r="C64" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="D64" t="s">
-        <v>426</v>
+        <v>437</v>
       </c>
       <c r="E64" t="s">
-        <v>612</v>
+        <v>629</v>
       </c>
       <c r="F64">
         <v>1</v>
       </c>
       <c r="G64" t="s">
-        <v>736</v>
+        <v>759</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -4186,19 +4264,19 @@
         <v>70</v>
       </c>
       <c r="C65" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>427</v>
+        <v>438</v>
       </c>
       <c r="E65" t="s">
-        <v>613</v>
+        <v>630</v>
       </c>
       <c r="F65">
         <v>3</v>
       </c>
       <c r="G65" t="s">
-        <v>740</v>
+        <v>763</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -4209,19 +4287,19 @@
         <v>71</v>
       </c>
       <c r="C66" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="D66" t="s">
-        <v>428</v>
+        <v>439</v>
       </c>
       <c r="E66" t="s">
-        <v>614</v>
+        <v>631</v>
       </c>
       <c r="F66">
         <v>1</v>
       </c>
       <c r="G66" t="s">
-        <v>736</v>
+        <v>759</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -4232,19 +4310,19 @@
         <v>72</v>
       </c>
       <c r="C67" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="D67" t="s">
-        <v>429</v>
+        <v>440</v>
       </c>
       <c r="E67" t="s">
-        <v>615</v>
+        <v>632</v>
       </c>
       <c r="F67">
         <v>1</v>
       </c>
       <c r="G67" t="s">
-        <v>736</v>
+        <v>759</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -4255,19 +4333,19 @@
         <v>73</v>
       </c>
       <c r="C68" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="D68" t="s">
-        <v>430</v>
+        <v>441</v>
       </c>
       <c r="E68" t="s">
-        <v>616</v>
+        <v>633</v>
       </c>
       <c r="F68">
         <v>1</v>
       </c>
       <c r="G68" t="s">
-        <v>736</v>
+        <v>759</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -4278,19 +4356,19 @@
         <v>74</v>
       </c>
       <c r="C69" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D69" t="s">
-        <v>431</v>
+        <v>442</v>
       </c>
       <c r="E69" t="s">
-        <v>617</v>
+        <v>634</v>
       </c>
       <c r="F69">
         <v>1</v>
       </c>
       <c r="G69" t="s">
-        <v>736</v>
+        <v>759</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -4301,19 +4379,19 @@
         <v>75</v>
       </c>
       <c r="C70" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="D70" t="s">
-        <v>432</v>
+        <v>443</v>
       </c>
       <c r="E70" t="s">
-        <v>618</v>
+        <v>635</v>
       </c>
       <c r="F70">
         <v>1</v>
       </c>
       <c r="G70" t="s">
-        <v>736</v>
+        <v>759</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -4324,19 +4402,19 @@
         <v>76</v>
       </c>
       <c r="C71" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="D71" t="s">
-        <v>433</v>
+        <v>444</v>
       </c>
       <c r="E71" t="s">
-        <v>619</v>
+        <v>636</v>
       </c>
       <c r="F71">
         <v>1</v>
       </c>
       <c r="G71" t="s">
-        <v>736</v>
+        <v>759</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -4347,19 +4425,19 @@
         <v>77</v>
       </c>
       <c r="C72" t="s">
-        <v>262</v>
+        <v>268</v>
       </c>
       <c r="D72" t="s">
-        <v>434</v>
+        <v>445</v>
       </c>
       <c r="E72" t="s">
-        <v>620</v>
+        <v>637</v>
       </c>
       <c r="F72">
         <v>1</v>
       </c>
       <c r="G72" t="s">
-        <v>736</v>
+        <v>759</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -4370,19 +4448,19 @@
         <v>78</v>
       </c>
       <c r="C73" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="D73" t="s">
-        <v>435</v>
+        <v>446</v>
       </c>
       <c r="E73" t="s">
-        <v>621</v>
+        <v>638</v>
       </c>
       <c r="F73">
         <v>1</v>
       </c>
       <c r="G73" t="s">
-        <v>736</v>
+        <v>759</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -4393,19 +4471,19 @@
         <v>79</v>
       </c>
       <c r="C74" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="D74" t="s">
-        <v>436</v>
+        <v>447</v>
       </c>
       <c r="E74" t="s">
-        <v>622</v>
+        <v>639</v>
       </c>
       <c r="F74">
         <v>1</v>
       </c>
       <c r="G74" t="s">
-        <v>736</v>
+        <v>759</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -4416,19 +4494,19 @@
         <v>80</v>
       </c>
       <c r="C75" t="s">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="D75" t="s">
-        <v>437</v>
+        <v>448</v>
       </c>
       <c r="E75" t="s">
-        <v>623</v>
+        <v>640</v>
       </c>
       <c r="F75">
         <v>1</v>
       </c>
       <c r="G75" t="s">
-        <v>736</v>
+        <v>759</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -4439,19 +4517,19 @@
         <v>81</v>
       </c>
       <c r="C76" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="D76" t="s">
-        <v>438</v>
+        <v>449</v>
       </c>
       <c r="E76" t="s">
-        <v>624</v>
+        <v>641</v>
       </c>
       <c r="F76">
         <v>1</v>
       </c>
       <c r="G76" t="s">
-        <v>736</v>
+        <v>759</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -4465,16 +4543,16 @@
         <v>82</v>
       </c>
       <c r="D77" t="s">
-        <v>439</v>
+        <v>450</v>
       </c>
       <c r="E77" t="s">
-        <v>625</v>
+        <v>642</v>
       </c>
       <c r="F77">
         <v>1</v>
       </c>
       <c r="G77" t="s">
-        <v>741</v>
+        <v>764</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -4488,16 +4566,16 @@
         <v>83</v>
       </c>
       <c r="D78" t="s">
-        <v>440</v>
+        <v>451</v>
       </c>
       <c r="E78" t="s">
-        <v>626</v>
+        <v>643</v>
       </c>
       <c r="F78">
         <v>1</v>
       </c>
       <c r="G78" t="s">
-        <v>741</v>
+        <v>764</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -4511,16 +4589,16 @@
         <v>84</v>
       </c>
       <c r="D79" t="s">
-        <v>441</v>
+        <v>452</v>
       </c>
       <c r="E79" t="s">
-        <v>627</v>
+        <v>644</v>
       </c>
       <c r="F79">
         <v>1</v>
       </c>
       <c r="G79" t="s">
-        <v>741</v>
+        <v>764</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -4534,16 +4612,16 @@
         <v>85</v>
       </c>
       <c r="D80" t="s">
-        <v>442</v>
+        <v>453</v>
       </c>
       <c r="E80" t="s">
-        <v>628</v>
+        <v>645</v>
       </c>
       <c r="F80">
         <v>1</v>
       </c>
       <c r="G80" t="s">
-        <v>741</v>
+        <v>764</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -4557,16 +4635,16 @@
         <v>86</v>
       </c>
       <c r="D81" t="s">
-        <v>443</v>
+        <v>454</v>
       </c>
       <c r="E81" t="s">
-        <v>629</v>
+        <v>646</v>
       </c>
       <c r="F81">
         <v>1</v>
       </c>
       <c r="G81" t="s">
-        <v>742</v>
+        <v>765</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -4580,16 +4658,16 @@
         <v>87</v>
       </c>
       <c r="D82" t="s">
-        <v>444</v>
+        <v>455</v>
       </c>
       <c r="E82" t="s">
-        <v>630</v>
+        <v>647</v>
       </c>
       <c r="F82">
         <v>1</v>
       </c>
       <c r="G82" t="s">
-        <v>743</v>
+        <v>766</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -4603,16 +4681,16 @@
         <v>88</v>
       </c>
       <c r="D83" t="s">
-        <v>445</v>
+        <v>456</v>
       </c>
       <c r="E83" t="s">
-        <v>631</v>
+        <v>648</v>
       </c>
       <c r="F83">
         <v>1</v>
       </c>
       <c r="G83" t="s">
-        <v>741</v>
+        <v>764</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -4626,16 +4704,16 @@
         <v>89</v>
       </c>
       <c r="D84" t="s">
-        <v>446</v>
+        <v>457</v>
       </c>
       <c r="E84" t="s">
-        <v>632</v>
+        <v>649</v>
       </c>
       <c r="F84">
         <v>1</v>
       </c>
       <c r="G84" t="s">
-        <v>741</v>
+        <v>764</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -4649,16 +4727,16 @@
         <v>90</v>
       </c>
       <c r="D85" t="s">
-        <v>447</v>
+        <v>458</v>
       </c>
       <c r="E85" t="s">
-        <v>633</v>
+        <v>650</v>
       </c>
       <c r="F85">
         <v>1</v>
       </c>
       <c r="G85" t="s">
-        <v>741</v>
+        <v>764</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -4669,19 +4747,19 @@
         <v>91</v>
       </c>
       <c r="C86" t="s">
-        <v>267</v>
+        <v>273</v>
       </c>
       <c r="D86" t="s">
-        <v>448</v>
+        <v>459</v>
       </c>
       <c r="E86" t="s">
-        <v>634</v>
+        <v>651</v>
       </c>
       <c r="F86">
         <v>1</v>
       </c>
       <c r="G86" t="s">
-        <v>741</v>
+        <v>764</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -4695,16 +4773,16 @@
         <v>92</v>
       </c>
       <c r="D87" t="s">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="E87" t="s">
-        <v>635</v>
+        <v>652</v>
       </c>
       <c r="F87">
         <v>1</v>
       </c>
       <c r="G87" t="s">
-        <v>744</v>
+        <v>767</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -4718,16 +4796,16 @@
         <v>93</v>
       </c>
       <c r="D88" t="s">
-        <v>449</v>
+        <v>460</v>
       </c>
       <c r="E88" t="s">
-        <v>636</v>
+        <v>653</v>
       </c>
       <c r="F88">
         <v>1</v>
       </c>
       <c r="G88" t="s">
-        <v>741</v>
+        <v>764</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -4738,19 +4816,19 @@
         <v>94</v>
       </c>
       <c r="C89" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="D89" t="s">
-        <v>450</v>
+        <v>461</v>
       </c>
       <c r="E89" t="s">
-        <v>637</v>
+        <v>654</v>
       </c>
       <c r="F89">
         <v>1</v>
       </c>
       <c r="G89" t="s">
-        <v>739</v>
+        <v>762</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -4761,19 +4839,19 @@
         <v>95</v>
       </c>
       <c r="C90" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="D90" t="s">
-        <v>451</v>
+        <v>462</v>
       </c>
       <c r="E90" t="s">
-        <v>638</v>
+        <v>655</v>
       </c>
       <c r="F90">
         <v>1</v>
       </c>
       <c r="G90" t="s">
-        <v>736</v>
+        <v>759</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -4784,19 +4862,19 @@
         <v>96</v>
       </c>
       <c r="C91" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="D91" t="s">
-        <v>452</v>
+        <v>463</v>
       </c>
       <c r="E91" t="s">
-        <v>639</v>
+        <v>656</v>
       </c>
       <c r="F91">
         <v>1</v>
       </c>
       <c r="G91" t="s">
-        <v>736</v>
+        <v>759</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -4807,19 +4885,19 @@
         <v>97</v>
       </c>
       <c r="C92" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="D92" t="s">
-        <v>453</v>
+        <v>464</v>
       </c>
       <c r="E92" t="s">
-        <v>640</v>
+        <v>657</v>
       </c>
       <c r="F92">
         <v>1</v>
       </c>
       <c r="G92" t="s">
-        <v>736</v>
+        <v>759</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -4830,19 +4908,19 @@
         <v>98</v>
       </c>
       <c r="C93" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="D93" t="s">
-        <v>454</v>
+        <v>465</v>
       </c>
       <c r="E93" t="s">
-        <v>641</v>
+        <v>658</v>
       </c>
       <c r="F93">
         <v>1</v>
       </c>
       <c r="G93" t="s">
-        <v>736</v>
+        <v>759</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -4853,19 +4931,19 @@
         <v>99</v>
       </c>
       <c r="C94" t="s">
-        <v>273</v>
+        <v>279</v>
       </c>
       <c r="D94" t="s">
-        <v>455</v>
+        <v>466</v>
       </c>
       <c r="E94" t="s">
-        <v>642</v>
+        <v>659</v>
       </c>
       <c r="F94">
         <v>1</v>
       </c>
       <c r="G94" t="s">
-        <v>736</v>
+        <v>759</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -4876,19 +4954,19 @@
         <v>100</v>
       </c>
       <c r="C95" t="s">
-        <v>274</v>
+        <v>280</v>
       </c>
       <c r="D95" t="s">
-        <v>456</v>
+        <v>467</v>
       </c>
       <c r="E95" t="s">
-        <v>643</v>
+        <v>660</v>
       </c>
       <c r="F95">
         <v>1</v>
       </c>
       <c r="G95" t="s">
-        <v>745</v>
+        <v>768</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -4899,10 +4977,10 @@
         <v>101</v>
       </c>
       <c r="C96" t="s">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="D96" t="s">
-        <v>457</v>
+        <v>468</v>
       </c>
       <c r="E96" t="s">
         <v>101</v>
@@ -4911,7 +4989,7 @@
         <v>1</v>
       </c>
       <c r="G96" t="s">
-        <v>736</v>
+        <v>759</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -4922,19 +5000,19 @@
         <v>102</v>
       </c>
       <c r="C97" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="D97" t="s">
-        <v>458</v>
+        <v>469</v>
       </c>
       <c r="E97" t="s">
-        <v>644</v>
+        <v>661</v>
       </c>
       <c r="F97">
         <v>1</v>
       </c>
       <c r="G97" t="s">
-        <v>736</v>
+        <v>759</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -4945,19 +5023,19 @@
         <v>103</v>
       </c>
       <c r="C98" t="s">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="D98" t="s">
-        <v>459</v>
+        <v>470</v>
       </c>
       <c r="E98" t="s">
-        <v>645</v>
+        <v>662</v>
       </c>
       <c r="F98">
         <v>1</v>
       </c>
       <c r="G98" t="s">
-        <v>736</v>
+        <v>759</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -4968,19 +5046,19 @@
         <v>104</v>
       </c>
       <c r="C99" t="s">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c r="D99" t="s">
-        <v>460</v>
+        <v>471</v>
       </c>
       <c r="E99" t="s">
-        <v>646</v>
+        <v>663</v>
       </c>
       <c r="F99">
         <v>1</v>
       </c>
       <c r="G99" t="s">
-        <v>736</v>
+        <v>759</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -4991,19 +5069,19 @@
         <v>105</v>
       </c>
       <c r="C100" t="s">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="D100" t="s">
-        <v>461</v>
+        <v>472</v>
       </c>
       <c r="E100" t="s">
-        <v>647</v>
+        <v>664</v>
       </c>
       <c r="F100">
         <v>1</v>
       </c>
       <c r="G100" t="s">
-        <v>736</v>
+        <v>759</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -5014,19 +5092,19 @@
         <v>106</v>
       </c>
       <c r="C101" t="s">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="D101" t="s">
-        <v>462</v>
+        <v>473</v>
       </c>
       <c r="E101" t="s">
-        <v>648</v>
+        <v>665</v>
       </c>
       <c r="F101">
         <v>1</v>
       </c>
       <c r="G101" t="s">
-        <v>736</v>
+        <v>759</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -5037,19 +5115,19 @@
         <v>107</v>
       </c>
       <c r="C102" t="s">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c r="D102" t="s">
-        <v>463</v>
+        <v>474</v>
       </c>
       <c r="E102" t="s">
-        <v>649</v>
+        <v>666</v>
       </c>
       <c r="F102">
         <v>1</v>
       </c>
       <c r="G102" t="s">
-        <v>736</v>
+        <v>759</v>
       </c>
     </row>
     <row r="103" spans="1:7">
@@ -5060,19 +5138,19 @@
         <v>108</v>
       </c>
       <c r="C103" t="s">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="D103" t="s">
-        <v>464</v>
+        <v>475</v>
       </c>
       <c r="E103" t="s">
-        <v>650</v>
+        <v>667</v>
       </c>
       <c r="F103">
         <v>1</v>
       </c>
       <c r="G103" t="s">
-        <v>736</v>
+        <v>759</v>
       </c>
     </row>
     <row r="104" spans="1:7">
@@ -5083,19 +5161,19 @@
         <v>109</v>
       </c>
       <c r="C104" t="s">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="D104" t="s">
-        <v>465</v>
+        <v>476</v>
       </c>
       <c r="E104" t="s">
-        <v>651</v>
+        <v>668</v>
       </c>
       <c r="F104">
         <v>1</v>
       </c>
       <c r="G104" t="s">
-        <v>736</v>
+        <v>759</v>
       </c>
     </row>
     <row r="105" spans="1:7">
@@ -5106,19 +5184,19 @@
         <v>110</v>
       </c>
       <c r="C105" t="s">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c r="D105" t="s">
-        <v>466</v>
+        <v>477</v>
       </c>
       <c r="E105" t="s">
-        <v>652</v>
+        <v>669</v>
       </c>
       <c r="F105">
         <v>1</v>
       </c>
       <c r="G105" t="s">
-        <v>736</v>
+        <v>759</v>
       </c>
     </row>
     <row r="106" spans="1:7">
@@ -5129,19 +5207,19 @@
         <v>111</v>
       </c>
       <c r="C106" t="s">
-        <v>284</v>
+        <v>290</v>
       </c>
       <c r="D106" t="s">
-        <v>467</v>
+        <v>478</v>
       </c>
       <c r="E106" t="s">
-        <v>653</v>
+        <v>670</v>
       </c>
       <c r="F106">
         <v>1</v>
       </c>
       <c r="G106" t="s">
-        <v>736</v>
+        <v>759</v>
       </c>
     </row>
     <row r="107" spans="1:7">
@@ -5155,16 +5233,16 @@
         <v>112</v>
       </c>
       <c r="D107" t="s">
-        <v>468</v>
+        <v>479</v>
       </c>
       <c r="E107" t="s">
-        <v>654</v>
+        <v>671</v>
       </c>
       <c r="F107">
         <v>1</v>
       </c>
       <c r="G107" t="s">
-        <v>741</v>
+        <v>764</v>
       </c>
     </row>
     <row r="108" spans="1:7">
@@ -5178,16 +5256,16 @@
         <v>113</v>
       </c>
       <c r="D108" t="s">
-        <v>469</v>
+        <v>480</v>
       </c>
       <c r="E108" t="s">
-        <v>655</v>
+        <v>672</v>
       </c>
       <c r="F108">
         <v>1</v>
       </c>
       <c r="G108" t="s">
-        <v>741</v>
+        <v>764</v>
       </c>
     </row>
     <row r="109" spans="1:7">
@@ -5201,16 +5279,16 @@
         <v>114</v>
       </c>
       <c r="D109" t="s">
-        <v>470</v>
+        <v>481</v>
       </c>
       <c r="E109" t="s">
-        <v>656</v>
+        <v>673</v>
       </c>
       <c r="F109">
         <v>1</v>
       </c>
       <c r="G109" t="s">
-        <v>741</v>
+        <v>764</v>
       </c>
     </row>
     <row r="110" spans="1:7">
@@ -5221,19 +5299,19 @@
         <v>115</v>
       </c>
       <c r="C110" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="D110" t="s">
-        <v>471</v>
+        <v>482</v>
       </c>
       <c r="E110" t="s">
-        <v>657</v>
+        <v>674</v>
       </c>
       <c r="F110">
         <v>1</v>
       </c>
       <c r="G110" t="s">
-        <v>736</v>
+        <v>759</v>
       </c>
     </row>
     <row r="111" spans="1:7">
@@ -5244,19 +5322,19 @@
         <v>116</v>
       </c>
       <c r="C111" t="s">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="D111" t="s">
-        <v>472</v>
+        <v>483</v>
       </c>
       <c r="E111" t="s">
-        <v>658</v>
+        <v>675</v>
       </c>
       <c r="F111">
         <v>1</v>
       </c>
       <c r="G111" t="s">
-        <v>736</v>
+        <v>759</v>
       </c>
     </row>
     <row r="112" spans="1:7">
@@ -5267,19 +5345,19 @@
         <v>117</v>
       </c>
       <c r="C112" t="s">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="D112" t="s">
-        <v>473</v>
+        <v>484</v>
       </c>
       <c r="E112" t="s">
-        <v>659</v>
+        <v>676</v>
       </c>
       <c r="F112">
         <v>1</v>
       </c>
       <c r="G112" t="s">
-        <v>746</v>
+        <v>769</v>
       </c>
     </row>
     <row r="113" spans="1:7">
@@ -5290,19 +5368,19 @@
         <v>118</v>
       </c>
       <c r="C113" t="s">
-        <v>288</v>
+        <v>294</v>
       </c>
       <c r="D113" t="s">
-        <v>474</v>
+        <v>485</v>
       </c>
       <c r="E113" t="s">
-        <v>660</v>
+        <v>677</v>
       </c>
       <c r="F113">
         <v>1</v>
       </c>
       <c r="G113" t="s">
-        <v>736</v>
+        <v>759</v>
       </c>
     </row>
     <row r="114" spans="1:7">
@@ -5313,19 +5391,19 @@
         <v>119</v>
       </c>
       <c r="C114" t="s">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="D114" t="s">
-        <v>475</v>
+        <v>486</v>
       </c>
       <c r="E114" t="s">
-        <v>661</v>
+        <v>678</v>
       </c>
       <c r="F114">
         <v>1</v>
       </c>
       <c r="G114" t="s">
-        <v>747</v>
+        <v>770</v>
       </c>
     </row>
     <row r="115" spans="1:7">
@@ -5336,19 +5414,19 @@
         <v>120</v>
       </c>
       <c r="C115" t="s">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="D115" t="s">
-        <v>476</v>
+        <v>487</v>
       </c>
       <c r="E115" t="s">
-        <v>662</v>
+        <v>679</v>
       </c>
       <c r="F115">
         <v>1</v>
       </c>
       <c r="G115" t="s">
-        <v>748</v>
+        <v>771</v>
       </c>
     </row>
     <row r="116" spans="1:7">
@@ -5359,19 +5437,19 @@
         <v>121</v>
       </c>
       <c r="C116" t="s">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="D116" t="s">
-        <v>477</v>
+        <v>488</v>
       </c>
       <c r="E116" t="s">
-        <v>663</v>
+        <v>680</v>
       </c>
       <c r="F116">
         <v>1</v>
       </c>
       <c r="G116" t="s">
-        <v>736</v>
+        <v>759</v>
       </c>
     </row>
     <row r="117" spans="1:7">
@@ -5382,19 +5460,19 @@
         <v>122</v>
       </c>
       <c r="C117" t="s">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="D117" t="s">
-        <v>478</v>
+        <v>489</v>
       </c>
       <c r="E117" t="s">
-        <v>664</v>
+        <v>681</v>
       </c>
       <c r="F117">
         <v>1</v>
       </c>
       <c r="G117" t="s">
-        <v>749</v>
+        <v>772</v>
       </c>
     </row>
     <row r="118" spans="1:7">
@@ -5405,19 +5483,19 @@
         <v>123</v>
       </c>
       <c r="C118" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="D118" t="s">
-        <v>479</v>
+        <v>490</v>
       </c>
       <c r="E118" t="s">
-        <v>665</v>
+        <v>682</v>
       </c>
       <c r="F118">
         <v>1</v>
       </c>
       <c r="G118" t="s">
-        <v>750</v>
+        <v>773</v>
       </c>
     </row>
     <row r="119" spans="1:7">
@@ -5428,19 +5506,19 @@
         <v>124</v>
       </c>
       <c r="C119" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="D119" t="s">
-        <v>480</v>
+        <v>491</v>
       </c>
       <c r="E119" t="s">
-        <v>666</v>
+        <v>683</v>
       </c>
       <c r="F119">
         <v>1</v>
       </c>
       <c r="G119" t="s">
-        <v>751</v>
+        <v>774</v>
       </c>
     </row>
     <row r="120" spans="1:7">
@@ -5451,19 +5529,19 @@
         <v>125</v>
       </c>
       <c r="C120" t="s">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="D120" t="s">
-        <v>481</v>
+        <v>492</v>
       </c>
       <c r="E120" t="s">
-        <v>667</v>
+        <v>684</v>
       </c>
       <c r="F120">
         <v>1</v>
       </c>
       <c r="G120" t="s">
-        <v>752</v>
+        <v>775</v>
       </c>
     </row>
     <row r="121" spans="1:7">
@@ -5474,19 +5552,19 @@
         <v>126</v>
       </c>
       <c r="C121" t="s">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="D121" t="s">
-        <v>482</v>
+        <v>493</v>
       </c>
       <c r="E121" t="s">
-        <v>668</v>
+        <v>685</v>
       </c>
       <c r="F121">
         <v>1</v>
       </c>
       <c r="G121" t="s">
-        <v>753</v>
+        <v>776</v>
       </c>
     </row>
     <row r="122" spans="1:7">
@@ -5497,19 +5575,19 @@
         <v>127</v>
       </c>
       <c r="C122" t="s">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="D122" t="s">
-        <v>483</v>
+        <v>494</v>
       </c>
       <c r="E122" t="s">
-        <v>669</v>
+        <v>686</v>
       </c>
       <c r="F122">
         <v>1</v>
       </c>
       <c r="G122" t="s">
-        <v>754</v>
+        <v>777</v>
       </c>
     </row>
     <row r="123" spans="1:7">
@@ -5520,19 +5598,19 @@
         <v>128</v>
       </c>
       <c r="C123" t="s">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="D123" t="s">
-        <v>484</v>
+        <v>495</v>
       </c>
       <c r="E123" t="s">
-        <v>670</v>
+        <v>687</v>
       </c>
       <c r="F123">
         <v>1</v>
       </c>
       <c r="G123" t="s">
-        <v>755</v>
+        <v>778</v>
       </c>
     </row>
     <row r="124" spans="1:7">
@@ -5543,19 +5621,19 @@
         <v>129</v>
       </c>
       <c r="C124" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="D124" t="s">
-        <v>485</v>
+        <v>496</v>
       </c>
       <c r="E124" t="s">
-        <v>671</v>
+        <v>688</v>
       </c>
       <c r="F124">
         <v>1</v>
       </c>
       <c r="G124" t="s">
-        <v>756</v>
+        <v>779</v>
       </c>
     </row>
     <row r="125" spans="1:7">
@@ -5566,19 +5644,19 @@
         <v>130</v>
       </c>
       <c r="C125" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="D125" t="s">
-        <v>486</v>
+        <v>497</v>
       </c>
       <c r="E125" t="s">
-        <v>672</v>
+        <v>689</v>
       </c>
       <c r="F125">
         <v>1</v>
       </c>
       <c r="G125" t="s">
-        <v>757</v>
+        <v>780</v>
       </c>
     </row>
     <row r="126" spans="1:7">
@@ -5589,19 +5667,19 @@
         <v>131</v>
       </c>
       <c r="C126" t="s">
-        <v>301</v>
+        <v>307</v>
       </c>
       <c r="D126" t="s">
-        <v>487</v>
+        <v>498</v>
       </c>
       <c r="E126" t="s">
-        <v>673</v>
+        <v>690</v>
       </c>
       <c r="F126">
         <v>1</v>
       </c>
       <c r="G126" t="s">
-        <v>758</v>
+        <v>781</v>
       </c>
     </row>
     <row r="127" spans="1:7">
@@ -5612,19 +5690,19 @@
         <v>132</v>
       </c>
       <c r="C127" t="s">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="D127" t="s">
-        <v>488</v>
+        <v>499</v>
       </c>
       <c r="E127" t="s">
-        <v>674</v>
+        <v>691</v>
       </c>
       <c r="F127">
         <v>1</v>
       </c>
       <c r="G127" t="s">
-        <v>759</v>
+        <v>782</v>
       </c>
     </row>
     <row r="128" spans="1:7">
@@ -5635,19 +5713,19 @@
         <v>133</v>
       </c>
       <c r="C128" t="s">
-        <v>303</v>
+        <v>309</v>
       </c>
       <c r="D128" t="s">
-        <v>489</v>
+        <v>500</v>
       </c>
       <c r="E128" t="s">
-        <v>675</v>
+        <v>692</v>
       </c>
       <c r="F128">
         <v>1</v>
       </c>
       <c r="G128" t="s">
-        <v>760</v>
+        <v>783</v>
       </c>
     </row>
     <row r="129" spans="1:7">
@@ -5658,19 +5736,19 @@
         <v>134</v>
       </c>
       <c r="C129" t="s">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c r="D129" t="s">
-        <v>490</v>
+        <v>501</v>
       </c>
       <c r="E129" t="s">
-        <v>676</v>
+        <v>693</v>
       </c>
       <c r="F129">
         <v>1</v>
       </c>
       <c r="G129" t="s">
-        <v>761</v>
+        <v>784</v>
       </c>
     </row>
     <row r="130" spans="1:7">
@@ -5681,19 +5759,19 @@
         <v>135</v>
       </c>
       <c r="C130" t="s">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="D130" t="s">
-        <v>491</v>
+        <v>502</v>
       </c>
       <c r="E130" t="s">
-        <v>677</v>
+        <v>694</v>
       </c>
       <c r="F130">
         <v>1</v>
       </c>
       <c r="G130" t="s">
-        <v>762</v>
+        <v>785</v>
       </c>
     </row>
     <row r="131" spans="1:7">
@@ -5704,19 +5782,19 @@
         <v>136</v>
       </c>
       <c r="C131" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="D131" t="s">
-        <v>492</v>
+        <v>503</v>
       </c>
       <c r="E131" t="s">
-        <v>678</v>
+        <v>695</v>
       </c>
       <c r="F131">
         <v>1</v>
       </c>
       <c r="G131" t="s">
-        <v>763</v>
+        <v>786</v>
       </c>
     </row>
     <row r="132" spans="1:7">
@@ -5727,19 +5805,19 @@
         <v>137</v>
       </c>
       <c r="C132" t="s">
-        <v>307</v>
+        <v>313</v>
       </c>
       <c r="D132" t="s">
-        <v>493</v>
+        <v>504</v>
       </c>
       <c r="E132" t="s">
-        <v>679</v>
+        <v>696</v>
       </c>
       <c r="F132">
         <v>1</v>
       </c>
       <c r="G132" t="s">
-        <v>764</v>
+        <v>787</v>
       </c>
     </row>
     <row r="133" spans="1:7">
@@ -5750,19 +5828,19 @@
         <v>138</v>
       </c>
       <c r="C133" t="s">
-        <v>308</v>
+        <v>314</v>
       </c>
       <c r="D133" t="s">
-        <v>494</v>
+        <v>505</v>
       </c>
       <c r="E133" t="s">
-        <v>680</v>
+        <v>697</v>
       </c>
       <c r="F133">
         <v>1</v>
       </c>
       <c r="G133" t="s">
-        <v>765</v>
+        <v>788</v>
       </c>
     </row>
     <row r="134" spans="1:7">
@@ -5773,19 +5851,19 @@
         <v>139</v>
       </c>
       <c r="C134" t="s">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="D134" t="s">
-        <v>495</v>
+        <v>506</v>
       </c>
       <c r="E134" t="s">
-        <v>681</v>
+        <v>698</v>
       </c>
       <c r="F134">
         <v>1</v>
       </c>
       <c r="G134" t="s">
-        <v>766</v>
+        <v>789</v>
       </c>
     </row>
     <row r="135" spans="1:7">
@@ -5796,19 +5874,19 @@
         <v>140</v>
       </c>
       <c r="C135" t="s">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="D135" t="s">
-        <v>496</v>
+        <v>507</v>
       </c>
       <c r="E135" t="s">
-        <v>682</v>
+        <v>699</v>
       </c>
       <c r="F135">
         <v>1</v>
       </c>
       <c r="G135" t="s">
-        <v>767</v>
+        <v>790</v>
       </c>
     </row>
     <row r="136" spans="1:7">
@@ -5819,19 +5897,19 @@
         <v>141</v>
       </c>
       <c r="C136" t="s">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="D136" t="s">
-        <v>497</v>
+        <v>508</v>
       </c>
       <c r="E136" t="s">
-        <v>683</v>
+        <v>700</v>
       </c>
       <c r="F136">
         <v>1</v>
       </c>
       <c r="G136" t="s">
-        <v>768</v>
+        <v>791</v>
       </c>
     </row>
     <row r="137" spans="1:7">
@@ -5842,19 +5920,19 @@
         <v>142</v>
       </c>
       <c r="C137" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="D137" t="s">
-        <v>498</v>
+        <v>509</v>
       </c>
       <c r="E137" t="s">
-        <v>684</v>
+        <v>701</v>
       </c>
       <c r="F137">
         <v>1</v>
       </c>
       <c r="G137" t="s">
-        <v>769</v>
+        <v>792</v>
       </c>
     </row>
     <row r="138" spans="1:7">
@@ -5865,19 +5943,19 @@
         <v>143</v>
       </c>
       <c r="C138" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="D138" t="s">
-        <v>499</v>
+        <v>510</v>
       </c>
       <c r="E138" t="s">
-        <v>685</v>
+        <v>702</v>
       </c>
       <c r="F138">
         <v>1</v>
       </c>
       <c r="G138" t="s">
-        <v>770</v>
+        <v>793</v>
       </c>
     </row>
     <row r="139" spans="1:7">
@@ -5888,19 +5966,19 @@
         <v>144</v>
       </c>
       <c r="C139" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="D139" t="s">
-        <v>500</v>
+        <v>511</v>
       </c>
       <c r="E139" t="s">
-        <v>686</v>
+        <v>703</v>
       </c>
       <c r="F139">
         <v>1</v>
       </c>
       <c r="G139" t="s">
-        <v>771</v>
+        <v>794</v>
       </c>
     </row>
     <row r="140" spans="1:7">
@@ -5911,19 +5989,19 @@
         <v>145</v>
       </c>
       <c r="C140" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="D140" t="s">
-        <v>501</v>
+        <v>512</v>
       </c>
       <c r="E140" t="s">
-        <v>687</v>
+        <v>704</v>
       </c>
       <c r="F140">
         <v>1</v>
       </c>
       <c r="G140" t="s">
-        <v>772</v>
+        <v>795</v>
       </c>
     </row>
     <row r="141" spans="1:7">
@@ -5934,19 +6012,19 @@
         <v>146</v>
       </c>
       <c r="C141" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="D141" t="s">
-        <v>502</v>
+        <v>513</v>
       </c>
       <c r="E141" t="s">
-        <v>688</v>
+        <v>705</v>
       </c>
       <c r="F141">
         <v>1</v>
       </c>
       <c r="G141" t="s">
-        <v>773</v>
+        <v>796</v>
       </c>
     </row>
     <row r="142" spans="1:7">
@@ -5957,19 +6035,19 @@
         <v>147</v>
       </c>
       <c r="C142" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="D142" t="s">
-        <v>503</v>
+        <v>514</v>
       </c>
       <c r="E142" t="s">
-        <v>689</v>
+        <v>706</v>
       </c>
       <c r="F142">
         <v>1</v>
       </c>
       <c r="G142" t="s">
-        <v>774</v>
+        <v>797</v>
       </c>
     </row>
     <row r="143" spans="1:7">
@@ -5980,19 +6058,19 @@
         <v>148</v>
       </c>
       <c r="C143" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="D143" t="s">
-        <v>504</v>
+        <v>515</v>
       </c>
       <c r="E143" t="s">
-        <v>690</v>
+        <v>707</v>
       </c>
       <c r="F143">
         <v>1</v>
       </c>
       <c r="G143" t="s">
-        <v>775</v>
+        <v>798</v>
       </c>
     </row>
     <row r="144" spans="1:7">
@@ -6003,19 +6081,19 @@
         <v>149</v>
       </c>
       <c r="C144" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="D144" t="s">
-        <v>505</v>
+        <v>516</v>
       </c>
       <c r="E144" t="s">
-        <v>691</v>
+        <v>708</v>
       </c>
       <c r="F144">
         <v>1</v>
       </c>
       <c r="G144" t="s">
-        <v>776</v>
+        <v>799</v>
       </c>
     </row>
     <row r="145" spans="1:7">
@@ -6026,13 +6104,13 @@
         <v>150</v>
       </c>
       <c r="C145" t="s">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="D145" t="s">
-        <v>506</v>
+        <v>517</v>
       </c>
       <c r="E145" t="s">
-        <v>692</v>
+        <v>709</v>
       </c>
       <c r="F145">
         <v>1</v>
@@ -6046,19 +6124,19 @@
         <v>151</v>
       </c>
       <c r="C146" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="D146" t="s">
-        <v>507</v>
+        <v>518</v>
       </c>
       <c r="E146" t="s">
-        <v>693</v>
+        <v>710</v>
       </c>
       <c r="F146">
         <v>1</v>
       </c>
       <c r="G146" t="s">
-        <v>777</v>
+        <v>800</v>
       </c>
     </row>
     <row r="147" spans="1:7">
@@ -6069,19 +6147,19 @@
         <v>152</v>
       </c>
       <c r="C147" t="s">
-        <v>322</v>
+        <v>328</v>
       </c>
       <c r="D147" t="s">
-        <v>508</v>
+        <v>519</v>
       </c>
       <c r="E147" t="s">
-        <v>694</v>
+        <v>711</v>
       </c>
       <c r="F147">
         <v>1</v>
       </c>
       <c r="G147" t="s">
-        <v>739</v>
+        <v>762</v>
       </c>
     </row>
     <row r="148" spans="1:7">
@@ -6092,19 +6170,19 @@
         <v>153</v>
       </c>
       <c r="C148" t="s">
-        <v>323</v>
+        <v>329</v>
       </c>
       <c r="D148" t="s">
-        <v>509</v>
+        <v>520</v>
       </c>
       <c r="E148" t="s">
-        <v>695</v>
+        <v>712</v>
       </c>
       <c r="F148">
         <v>1</v>
       </c>
       <c r="G148" t="s">
-        <v>736</v>
+        <v>759</v>
       </c>
     </row>
     <row r="149" spans="1:7">
@@ -6115,19 +6193,19 @@
         <v>154</v>
       </c>
       <c r="C149" t="s">
-        <v>324</v>
+        <v>330</v>
       </c>
       <c r="D149" t="s">
-        <v>510</v>
+        <v>521</v>
       </c>
       <c r="E149" t="s">
-        <v>696</v>
+        <v>713</v>
       </c>
       <c r="F149">
         <v>1</v>
       </c>
       <c r="G149" t="s">
-        <v>736</v>
+        <v>759</v>
       </c>
     </row>
     <row r="150" spans="1:7">
@@ -6138,19 +6216,19 @@
         <v>155</v>
       </c>
       <c r="C150" t="s">
-        <v>325</v>
+        <v>331</v>
       </c>
       <c r="D150" t="s">
-        <v>511</v>
+        <v>522</v>
       </c>
       <c r="E150" t="s">
-        <v>697</v>
+        <v>714</v>
       </c>
       <c r="F150">
         <v>1</v>
       </c>
       <c r="G150" t="s">
-        <v>736</v>
+        <v>759</v>
       </c>
     </row>
     <row r="151" spans="1:7">
@@ -6161,19 +6239,19 @@
         <v>156</v>
       </c>
       <c r="C151" t="s">
-        <v>326</v>
+        <v>332</v>
       </c>
       <c r="D151" t="s">
-        <v>512</v>
+        <v>523</v>
       </c>
       <c r="E151" t="s">
-        <v>698</v>
+        <v>715</v>
       </c>
       <c r="F151">
         <v>1</v>
       </c>
       <c r="G151" t="s">
-        <v>736</v>
+        <v>759</v>
       </c>
     </row>
     <row r="152" spans="1:7">
@@ -6184,19 +6262,19 @@
         <v>157</v>
       </c>
       <c r="C152" t="s">
-        <v>327</v>
+        <v>333</v>
       </c>
       <c r="D152" t="s">
-        <v>513</v>
+        <v>524</v>
       </c>
       <c r="E152" t="s">
-        <v>699</v>
+        <v>716</v>
       </c>
       <c r="F152">
         <v>1</v>
       </c>
       <c r="G152" t="s">
-        <v>736</v>
+        <v>759</v>
       </c>
     </row>
     <row r="153" spans="1:7">
@@ -6207,19 +6285,19 @@
         <v>158</v>
       </c>
       <c r="C153" t="s">
-        <v>328</v>
+        <v>334</v>
       </c>
       <c r="D153" t="s">
-        <v>514</v>
+        <v>525</v>
       </c>
       <c r="E153" t="s">
-        <v>700</v>
+        <v>717</v>
       </c>
       <c r="F153">
         <v>1</v>
       </c>
       <c r="G153" t="s">
-        <v>736</v>
+        <v>759</v>
       </c>
     </row>
     <row r="154" spans="1:7">
@@ -6230,19 +6308,19 @@
         <v>159</v>
       </c>
       <c r="C154" t="s">
-        <v>329</v>
+        <v>335</v>
       </c>
       <c r="D154" t="s">
-        <v>515</v>
+        <v>526</v>
       </c>
       <c r="E154" t="s">
-        <v>701</v>
+        <v>718</v>
       </c>
       <c r="F154">
         <v>1</v>
       </c>
       <c r="G154" t="s">
-        <v>739</v>
+        <v>762</v>
       </c>
     </row>
     <row r="155" spans="1:7">
@@ -6253,19 +6331,19 @@
         <v>160</v>
       </c>
       <c r="C155" t="s">
-        <v>330</v>
+        <v>336</v>
       </c>
       <c r="D155" t="s">
-        <v>516</v>
+        <v>527</v>
       </c>
       <c r="E155" t="s">
-        <v>702</v>
+        <v>719</v>
       </c>
       <c r="F155">
         <v>1</v>
       </c>
       <c r="G155" t="s">
-        <v>736</v>
+        <v>759</v>
       </c>
     </row>
     <row r="156" spans="1:7">
@@ -6276,19 +6354,19 @@
         <v>161</v>
       </c>
       <c r="C156" t="s">
-        <v>331</v>
+        <v>337</v>
       </c>
       <c r="D156" t="s">
-        <v>517</v>
+        <v>528</v>
       </c>
       <c r="E156" t="s">
-        <v>703</v>
+        <v>720</v>
       </c>
       <c r="F156">
         <v>1</v>
       </c>
       <c r="G156" t="s">
-        <v>736</v>
+        <v>759</v>
       </c>
     </row>
     <row r="157" spans="1:7">
@@ -6299,19 +6377,19 @@
         <v>162</v>
       </c>
       <c r="C157" t="s">
-        <v>332</v>
+        <v>338</v>
       </c>
       <c r="D157" t="s">
-        <v>518</v>
+        <v>529</v>
       </c>
       <c r="E157" t="s">
-        <v>704</v>
+        <v>721</v>
       </c>
       <c r="F157">
         <v>1</v>
       </c>
       <c r="G157" t="s">
-        <v>736</v>
+        <v>759</v>
       </c>
     </row>
     <row r="158" spans="1:7">
@@ -6322,19 +6400,19 @@
         <v>163</v>
       </c>
       <c r="C158" t="s">
-        <v>333</v>
+        <v>339</v>
       </c>
       <c r="D158" t="s">
-        <v>519</v>
+        <v>530</v>
       </c>
       <c r="E158" t="s">
-        <v>705</v>
+        <v>722</v>
       </c>
       <c r="F158">
         <v>1</v>
       </c>
       <c r="G158" t="s">
-        <v>736</v>
+        <v>759</v>
       </c>
     </row>
     <row r="159" spans="1:7">
@@ -6345,19 +6423,19 @@
         <v>164</v>
       </c>
       <c r="C159" t="s">
-        <v>334</v>
+        <v>340</v>
       </c>
       <c r="D159" t="s">
-        <v>520</v>
+        <v>531</v>
       </c>
       <c r="E159" t="s">
-        <v>706</v>
+        <v>723</v>
       </c>
       <c r="F159">
         <v>1</v>
       </c>
       <c r="G159" t="s">
-        <v>736</v>
+        <v>759</v>
       </c>
     </row>
     <row r="160" spans="1:7">
@@ -6368,19 +6446,19 @@
         <v>165</v>
       </c>
       <c r="C160" t="s">
-        <v>335</v>
+        <v>341</v>
       </c>
       <c r="D160" t="s">
-        <v>521</v>
+        <v>532</v>
       </c>
       <c r="E160" t="s">
-        <v>707</v>
+        <v>724</v>
       </c>
       <c r="F160">
         <v>1</v>
       </c>
       <c r="G160" t="s">
-        <v>736</v>
+        <v>759</v>
       </c>
     </row>
     <row r="161" spans="1:7">
@@ -6391,19 +6469,19 @@
         <v>166</v>
       </c>
       <c r="C161" t="s">
-        <v>336</v>
+        <v>342</v>
       </c>
       <c r="D161" t="s">
-        <v>522</v>
+        <v>533</v>
       </c>
       <c r="E161" t="s">
-        <v>708</v>
+        <v>725</v>
       </c>
       <c r="F161">
         <v>1</v>
       </c>
       <c r="G161" t="s">
-        <v>736</v>
+        <v>759</v>
       </c>
     </row>
     <row r="162" spans="1:7">
@@ -6414,19 +6492,19 @@
         <v>167</v>
       </c>
       <c r="C162" t="s">
-        <v>337</v>
+        <v>343</v>
       </c>
       <c r="D162" t="s">
-        <v>523</v>
+        <v>534</v>
       </c>
       <c r="E162" t="s">
-        <v>709</v>
+        <v>726</v>
       </c>
       <c r="F162">
         <v>1</v>
       </c>
       <c r="G162" t="s">
-        <v>736</v>
+        <v>759</v>
       </c>
     </row>
     <row r="163" spans="1:7">
@@ -6437,19 +6515,19 @@
         <v>168</v>
       </c>
       <c r="C163" t="s">
-        <v>338</v>
+        <v>344</v>
       </c>
       <c r="D163" t="s">
-        <v>524</v>
+        <v>535</v>
       </c>
       <c r="E163" t="s">
-        <v>710</v>
+        <v>727</v>
       </c>
       <c r="F163">
         <v>1</v>
       </c>
       <c r="G163" t="s">
-        <v>778</v>
+        <v>801</v>
       </c>
     </row>
     <row r="164" spans="1:7">
@@ -6460,19 +6538,19 @@
         <v>169</v>
       </c>
       <c r="C164" t="s">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="D164" t="s">
-        <v>525</v>
+        <v>536</v>
       </c>
       <c r="E164" t="s">
-        <v>711</v>
+        <v>728</v>
       </c>
       <c r="F164">
         <v>1</v>
       </c>
       <c r="G164" t="s">
-        <v>736</v>
+        <v>759</v>
       </c>
     </row>
     <row r="165" spans="1:7">
@@ -6483,19 +6561,19 @@
         <v>170</v>
       </c>
       <c r="C165" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="D165" t="s">
-        <v>526</v>
+        <v>537</v>
       </c>
       <c r="E165" t="s">
-        <v>712</v>
+        <v>729</v>
       </c>
       <c r="F165">
         <v>1</v>
       </c>
       <c r="G165" t="s">
-        <v>736</v>
+        <v>759</v>
       </c>
     </row>
     <row r="166" spans="1:7">
@@ -6506,19 +6584,19 @@
         <v>171</v>
       </c>
       <c r="C166" t="s">
-        <v>341</v>
+        <v>347</v>
       </c>
       <c r="D166" t="s">
-        <v>527</v>
+        <v>538</v>
       </c>
       <c r="E166" t="s">
-        <v>713</v>
+        <v>730</v>
       </c>
       <c r="F166">
         <v>1</v>
       </c>
       <c r="G166" t="s">
-        <v>736</v>
+        <v>759</v>
       </c>
     </row>
     <row r="167" spans="1:7">
@@ -6529,19 +6607,19 @@
         <v>172</v>
       </c>
       <c r="C167" t="s">
-        <v>342</v>
+        <v>348</v>
       </c>
       <c r="D167" t="s">
-        <v>528</v>
+        <v>539</v>
       </c>
       <c r="E167" t="s">
-        <v>714</v>
+        <v>731</v>
       </c>
       <c r="F167">
         <v>1</v>
       </c>
       <c r="G167" t="s">
-        <v>736</v>
+        <v>759</v>
       </c>
     </row>
     <row r="168" spans="1:7">
@@ -6552,19 +6630,19 @@
         <v>173</v>
       </c>
       <c r="C168" t="s">
-        <v>343</v>
+        <v>349</v>
       </c>
       <c r="D168" t="s">
-        <v>529</v>
+        <v>540</v>
       </c>
       <c r="E168" t="s">
-        <v>715</v>
+        <v>732</v>
       </c>
       <c r="F168">
         <v>1</v>
       </c>
       <c r="G168" t="s">
-        <v>736</v>
+        <v>759</v>
       </c>
     </row>
     <row r="169" spans="1:7">
@@ -6575,19 +6653,19 @@
         <v>174</v>
       </c>
       <c r="C169" t="s">
-        <v>344</v>
+        <v>350</v>
       </c>
       <c r="D169" t="s">
-        <v>530</v>
+        <v>541</v>
       </c>
       <c r="E169" t="s">
-        <v>716</v>
+        <v>733</v>
       </c>
       <c r="F169">
         <v>1</v>
       </c>
       <c r="G169" t="s">
-        <v>736</v>
+        <v>759</v>
       </c>
     </row>
     <row r="170" spans="1:7">
@@ -6598,19 +6676,19 @@
         <v>175</v>
       </c>
       <c r="C170" t="s">
-        <v>345</v>
+        <v>351</v>
       </c>
       <c r="D170" t="s">
-        <v>531</v>
+        <v>542</v>
       </c>
       <c r="E170" t="s">
-        <v>717</v>
+        <v>734</v>
       </c>
       <c r="F170">
         <v>1</v>
       </c>
       <c r="G170" t="s">
-        <v>736</v>
+        <v>759</v>
       </c>
     </row>
     <row r="171" spans="1:7">
@@ -6621,19 +6699,19 @@
         <v>176</v>
       </c>
       <c r="C171" t="s">
-        <v>346</v>
+        <v>352</v>
       </c>
       <c r="D171" t="s">
-        <v>532</v>
+        <v>543</v>
       </c>
       <c r="E171" t="s">
-        <v>718</v>
+        <v>735</v>
       </c>
       <c r="F171">
         <v>1</v>
       </c>
       <c r="G171" t="s">
-        <v>779</v>
+        <v>802</v>
       </c>
     </row>
     <row r="172" spans="1:7">
@@ -6644,19 +6722,19 @@
         <v>177</v>
       </c>
       <c r="C172" t="s">
-        <v>347</v>
+        <v>353</v>
       </c>
       <c r="D172" t="s">
-        <v>533</v>
+        <v>544</v>
       </c>
       <c r="E172" t="s">
-        <v>719</v>
+        <v>736</v>
       </c>
       <c r="F172">
         <v>1</v>
       </c>
       <c r="G172" t="s">
-        <v>780</v>
+        <v>803</v>
       </c>
     </row>
     <row r="173" spans="1:7">
@@ -6667,19 +6745,19 @@
         <v>178</v>
       </c>
       <c r="C173" t="s">
-        <v>348</v>
+        <v>354</v>
       </c>
       <c r="D173" t="s">
-        <v>534</v>
+        <v>545</v>
       </c>
       <c r="E173" t="s">
-        <v>720</v>
+        <v>737</v>
       </c>
       <c r="F173">
         <v>1</v>
       </c>
       <c r="G173" t="s">
-        <v>781</v>
+        <v>804</v>
       </c>
     </row>
     <row r="174" spans="1:7">
@@ -6690,19 +6768,19 @@
         <v>179</v>
       </c>
       <c r="C174" t="s">
-        <v>349</v>
+        <v>355</v>
       </c>
       <c r="D174" t="s">
-        <v>535</v>
+        <v>546</v>
       </c>
       <c r="E174" t="s">
-        <v>721</v>
+        <v>738</v>
       </c>
       <c r="F174">
         <v>1</v>
       </c>
       <c r="G174" t="s">
-        <v>782</v>
+        <v>805</v>
       </c>
     </row>
     <row r="175" spans="1:7">
@@ -6713,19 +6791,19 @@
         <v>180</v>
       </c>
       <c r="C175" t="s">
-        <v>350</v>
+        <v>356</v>
       </c>
       <c r="D175" t="s">
-        <v>536</v>
+        <v>547</v>
       </c>
       <c r="E175" t="s">
-        <v>722</v>
+        <v>739</v>
       </c>
       <c r="F175">
         <v>1</v>
       </c>
       <c r="G175" t="s">
-        <v>782</v>
+        <v>805</v>
       </c>
     </row>
     <row r="176" spans="1:7">
@@ -6736,19 +6814,19 @@
         <v>178</v>
       </c>
       <c r="C176" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="D176" t="s">
-        <v>537</v>
+        <v>548</v>
       </c>
       <c r="E176" t="s">
-        <v>723</v>
+        <v>740</v>
       </c>
       <c r="F176">
         <v>1</v>
       </c>
       <c r="G176" t="s">
-        <v>782</v>
+        <v>805</v>
       </c>
     </row>
     <row r="177" spans="1:7">
@@ -6759,19 +6837,19 @@
         <v>178</v>
       </c>
       <c r="C177" t="s">
-        <v>352</v>
+        <v>358</v>
       </c>
       <c r="D177" t="s">
-        <v>538</v>
+        <v>549</v>
       </c>
       <c r="E177" t="s">
-        <v>724</v>
+        <v>741</v>
       </c>
       <c r="F177">
         <v>1</v>
       </c>
       <c r="G177" t="s">
-        <v>782</v>
+        <v>805</v>
       </c>
     </row>
     <row r="178" spans="1:7">
@@ -6782,19 +6860,19 @@
         <v>181</v>
       </c>
       <c r="C178" t="s">
-        <v>353</v>
+        <v>359</v>
       </c>
       <c r="D178" t="s">
-        <v>539</v>
+        <v>550</v>
       </c>
       <c r="E178" t="s">
-        <v>725</v>
+        <v>742</v>
       </c>
       <c r="F178">
         <v>1</v>
       </c>
       <c r="G178" t="s">
-        <v>782</v>
+        <v>805</v>
       </c>
     </row>
     <row r="179" spans="1:7">
@@ -6805,19 +6883,19 @@
         <v>182</v>
       </c>
       <c r="C179" t="s">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="D179" t="s">
-        <v>540</v>
+        <v>551</v>
       </c>
       <c r="E179" t="s">
-        <v>726</v>
+        <v>743</v>
       </c>
       <c r="F179">
         <v>1</v>
       </c>
       <c r="G179" t="s">
-        <v>782</v>
+        <v>805</v>
       </c>
     </row>
     <row r="180" spans="1:7">
@@ -6828,19 +6906,19 @@
         <v>183</v>
       </c>
       <c r="C180" t="s">
-        <v>355</v>
+        <v>361</v>
       </c>
       <c r="D180" t="s">
-        <v>541</v>
+        <v>552</v>
       </c>
       <c r="E180" t="s">
-        <v>727</v>
+        <v>744</v>
       </c>
       <c r="F180">
         <v>1</v>
       </c>
       <c r="G180" t="s">
-        <v>782</v>
+        <v>805</v>
       </c>
     </row>
     <row r="181" spans="1:7">
@@ -6851,19 +6929,19 @@
         <v>184</v>
       </c>
       <c r="C181" t="s">
-        <v>356</v>
+        <v>362</v>
       </c>
       <c r="D181" t="s">
-        <v>542</v>
+        <v>553</v>
       </c>
       <c r="E181" t="s">
-        <v>728</v>
+        <v>745</v>
       </c>
       <c r="F181">
         <v>1</v>
       </c>
       <c r="G181" t="s">
-        <v>783</v>
+        <v>806</v>
       </c>
     </row>
     <row r="182" spans="1:7">
@@ -6874,19 +6952,19 @@
         <v>185</v>
       </c>
       <c r="C182" t="s">
-        <v>357</v>
+        <v>363</v>
       </c>
       <c r="D182" t="s">
-        <v>543</v>
+        <v>554</v>
       </c>
       <c r="E182" t="s">
-        <v>729</v>
+        <v>746</v>
       </c>
       <c r="F182">
         <v>1</v>
       </c>
       <c r="G182" t="s">
-        <v>736</v>
+        <v>759</v>
       </c>
     </row>
     <row r="183" spans="1:7">
@@ -6897,19 +6975,19 @@
         <v>186</v>
       </c>
       <c r="C183" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="D183" t="s">
-        <v>544</v>
+        <v>555</v>
       </c>
       <c r="E183" t="s">
-        <v>730</v>
+        <v>747</v>
       </c>
       <c r="F183">
         <v>1</v>
       </c>
       <c r="G183" t="s">
-        <v>736</v>
+        <v>759</v>
       </c>
     </row>
     <row r="184" spans="1:7">
@@ -6920,19 +6998,19 @@
         <v>187</v>
       </c>
       <c r="C184" t="s">
-        <v>359</v>
+        <v>365</v>
       </c>
       <c r="D184" t="s">
-        <v>545</v>
+        <v>556</v>
       </c>
       <c r="E184" t="s">
-        <v>731</v>
+        <v>748</v>
       </c>
       <c r="F184">
         <v>1</v>
       </c>
       <c r="G184" t="s">
-        <v>784</v>
+        <v>807</v>
       </c>
     </row>
     <row r="185" spans="1:7">
@@ -6943,19 +7021,19 @@
         <v>188</v>
       </c>
       <c r="C185" t="s">
-        <v>360</v>
+        <v>366</v>
       </c>
       <c r="D185" t="s">
-        <v>546</v>
+        <v>557</v>
       </c>
       <c r="E185" t="s">
-        <v>732</v>
+        <v>749</v>
       </c>
       <c r="F185">
         <v>1</v>
       </c>
       <c r="G185" t="s">
-        <v>785</v>
+        <v>808</v>
       </c>
     </row>
     <row r="186" spans="1:7">
@@ -6966,19 +7044,19 @@
         <v>189</v>
       </c>
       <c r="C186" t="s">
-        <v>361</v>
+        <v>367</v>
       </c>
       <c r="D186" t="s">
-        <v>547</v>
+        <v>558</v>
       </c>
       <c r="E186" t="s">
-        <v>733</v>
+        <v>750</v>
       </c>
       <c r="F186">
         <v>1</v>
       </c>
       <c r="G186" t="s">
-        <v>736</v>
+        <v>759</v>
       </c>
     </row>
     <row r="187" spans="1:7">
@@ -6989,19 +7067,19 @@
         <v>190</v>
       </c>
       <c r="C187" t="s">
-        <v>362</v>
+        <v>368</v>
       </c>
       <c r="D187" t="s">
-        <v>548</v>
+        <v>559</v>
       </c>
       <c r="E187" t="s">
-        <v>734</v>
+        <v>751</v>
       </c>
       <c r="F187">
         <v>1</v>
       </c>
       <c r="G187" t="s">
-        <v>786</v>
+        <v>809</v>
       </c>
     </row>
     <row r="188" spans="1:7">
@@ -7012,19 +7090,157 @@
         <v>191</v>
       </c>
       <c r="C188" t="s">
-        <v>363</v>
+        <v>369</v>
       </c>
       <c r="D188" t="s">
-        <v>549</v>
+        <v>560</v>
       </c>
       <c r="E188" t="s">
-        <v>735</v>
+        <v>752</v>
       </c>
       <c r="F188">
         <v>1</v>
       </c>
       <c r="G188" t="s">
-        <v>736</v>
+        <v>759</v>
+      </c>
+    </row>
+    <row r="189" spans="1:7">
+      <c r="A189">
+        <v>188</v>
+      </c>
+      <c r="B189" t="s">
+        <v>192</v>
+      </c>
+      <c r="C189" t="s">
+        <v>370</v>
+      </c>
+      <c r="D189" t="s">
+        <v>561</v>
+      </c>
+      <c r="E189" t="s">
+        <v>753</v>
+      </c>
+      <c r="F189">
+        <v>1</v>
+      </c>
+      <c r="G189" t="s">
+        <v>759</v>
+      </c>
+    </row>
+    <row r="190" spans="1:7">
+      <c r="A190">
+        <v>189</v>
+      </c>
+      <c r="B190" t="s">
+        <v>193</v>
+      </c>
+      <c r="C190" t="s">
+        <v>371</v>
+      </c>
+      <c r="D190" t="s">
+        <v>562</v>
+      </c>
+      <c r="E190" t="s">
+        <v>754</v>
+      </c>
+      <c r="F190">
+        <v>1</v>
+      </c>
+      <c r="G190" t="s">
+        <v>759</v>
+      </c>
+    </row>
+    <row r="191" spans="1:7">
+      <c r="A191">
+        <v>190</v>
+      </c>
+      <c r="B191" t="s">
+        <v>194</v>
+      </c>
+      <c r="C191" t="s">
+        <v>372</v>
+      </c>
+      <c r="D191" t="s">
+        <v>563</v>
+      </c>
+      <c r="E191" t="s">
+        <v>755</v>
+      </c>
+      <c r="F191">
+        <v>1</v>
+      </c>
+      <c r="G191" t="s">
+        <v>759</v>
+      </c>
+    </row>
+    <row r="192" spans="1:7">
+      <c r="A192">
+        <v>191</v>
+      </c>
+      <c r="B192" t="s">
+        <v>195</v>
+      </c>
+      <c r="C192" t="s">
+        <v>373</v>
+      </c>
+      <c r="D192" t="s">
+        <v>564</v>
+      </c>
+      <c r="E192" t="s">
+        <v>756</v>
+      </c>
+      <c r="F192">
+        <v>1</v>
+      </c>
+      <c r="G192" t="s">
+        <v>810</v>
+      </c>
+    </row>
+    <row r="193" spans="1:7">
+      <c r="A193">
+        <v>192</v>
+      </c>
+      <c r="B193" t="s">
+        <v>196</v>
+      </c>
+      <c r="C193" t="s">
+        <v>374</v>
+      </c>
+      <c r="D193" t="s">
+        <v>565</v>
+      </c>
+      <c r="E193" t="s">
+        <v>757</v>
+      </c>
+      <c r="F193">
+        <v>1</v>
+      </c>
+      <c r="G193" t="s">
+        <v>811</v>
+      </c>
+    </row>
+    <row r="194" spans="1:7">
+      <c r="A194">
+        <v>193</v>
+      </c>
+      <c r="B194" t="s">
+        <v>197</v>
+      </c>
+      <c r="C194" t="s">
+        <v>197</v>
+      </c>
+      <c r="D194" t="s">
+        <v>566</v>
+      </c>
+      <c r="E194" t="s">
+        <v>758</v>
+      </c>
+      <c r="F194">
+        <v>1</v>
+      </c>
+      <c r="G194" t="s">
+        <v>812</v>
       </c>
     </row>
   </sheetData>

--- a/data/target_dispatch/파보겔_실제발송_최종정제명단.xlsx
+++ b/data/target_dispatch/파보겔_실제발송_최종정제명단.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="970" uniqueCount="813">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="975" uniqueCount="818">
   <si>
     <t>순번</t>
   </si>
@@ -610,6 +610,9 @@
     <t>강해성</t>
   </si>
   <si>
+    <t>사랑하개켄넬</t>
+  </si>
+  <si>
     <t>정원정</t>
   </si>
   <si>
@@ -1141,6 +1144,9 @@
     <t>이인옥</t>
   </si>
   <si>
+    <t>선문규</t>
+  </si>
+  <si>
     <t>010-3114-1100</t>
   </si>
   <si>
@@ -1717,6 +1723,9 @@
     <t>010-3350-5188</t>
   </si>
   <si>
+    <t>010-3740-0729</t>
+  </si>
+  <si>
     <t>원주시 태장동 흥양로30  대흥아파트202-1202</t>
   </si>
   <si>
@@ -2293,6 +2302,9 @@
     <t>경기도 화성시 장안면 포승장안로 1290-30</t>
   </si>
   <si>
+    <t>인천 검단구 이음3로220 엘에이치20단지 2001동1812호</t>
+  </si>
+  <si>
     <t>[MMS 문자 유입] 펫샵 본품 1병 무료 샘플 신청</t>
   </si>
   <si>
@@ -2453,6 +2465,9 @@
   </si>
   <si>
     <t>[현장 직접 전달] 에스앤제이 동물병원 현장에서 직접 샘플 전달 완료</t>
+  </si>
+  <si>
+    <t>[MMS 문자 유입] 켄넬/브리더 본품 1병 무료 샘플 신청</t>
   </si>
 </sst>
 </file>
@@ -2784,7 +2799,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G194"/>
+  <dimension ref="A1:G195"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -2818,19 +2833,19 @@
         <v>7</v>
       </c>
       <c r="C2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D2" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="E2" t="s">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="F2">
         <v>1</v>
       </c>
       <c r="G2" t="s">
-        <v>759</v>
+        <v>763</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -2841,19 +2856,19 @@
         <v>8</v>
       </c>
       <c r="C3" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D3" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="E3" t="s">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="F3">
         <v>1</v>
       </c>
       <c r="G3" t="s">
-        <v>759</v>
+        <v>763</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -2864,19 +2879,19 @@
         <v>9</v>
       </c>
       <c r="C4" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D4" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="E4" t="s">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="F4">
         <v>1</v>
       </c>
       <c r="G4" t="s">
-        <v>759</v>
+        <v>763</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -2887,19 +2902,19 @@
         <v>10</v>
       </c>
       <c r="C5" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D5" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="E5" t="s">
-        <v>570</v>
+        <v>573</v>
       </c>
       <c r="F5">
         <v>1</v>
       </c>
       <c r="G5" t="s">
-        <v>759</v>
+        <v>763</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -2910,19 +2925,19 @@
         <v>11</v>
       </c>
       <c r="C6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D6" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="E6" t="s">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="F6">
         <v>1</v>
       </c>
       <c r="G6" t="s">
-        <v>759</v>
+        <v>763</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -2933,19 +2948,19 @@
         <v>12</v>
       </c>
       <c r="C7" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D7" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="E7" t="s">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="F7">
         <v>1</v>
       </c>
       <c r="G7" t="s">
-        <v>759</v>
+        <v>763</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -2956,19 +2971,19 @@
         <v>13</v>
       </c>
       <c r="C8" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D8" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="E8" t="s">
-        <v>573</v>
+        <v>576</v>
       </c>
       <c r="F8">
         <v>1</v>
       </c>
       <c r="G8" t="s">
-        <v>759</v>
+        <v>763</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -2979,19 +2994,19 @@
         <v>14</v>
       </c>
       <c r="C9" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D9" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="E9" t="s">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="F9">
         <v>1</v>
       </c>
       <c r="G9" t="s">
-        <v>759</v>
+        <v>763</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -3002,19 +3017,19 @@
         <v>15</v>
       </c>
       <c r="C10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="D10" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="E10" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="F10">
         <v>1</v>
       </c>
       <c r="G10" t="s">
-        <v>759</v>
+        <v>763</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -3025,13 +3040,13 @@
         <v>16</v>
       </c>
       <c r="C11" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D11" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="E11" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="F11">
         <v>1</v>
@@ -3045,19 +3060,19 @@
         <v>17</v>
       </c>
       <c r="C12" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D12" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="E12" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="F12">
         <v>1</v>
       </c>
       <c r="G12" t="s">
-        <v>759</v>
+        <v>763</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -3068,19 +3083,19 @@
         <v>18</v>
       </c>
       <c r="C13" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="D13" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="E13" t="s">
-        <v>578</v>
+        <v>581</v>
       </c>
       <c r="F13">
         <v>1</v>
       </c>
       <c r="G13" t="s">
-        <v>759</v>
+        <v>763</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -3091,19 +3106,19 @@
         <v>19</v>
       </c>
       <c r="C14" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D14" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="E14" t="s">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="F14">
         <v>1</v>
       </c>
       <c r="G14" t="s">
-        <v>759</v>
+        <v>763</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -3114,19 +3129,19 @@
         <v>20</v>
       </c>
       <c r="C15" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="D15" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="E15" t="s">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="F15">
         <v>1</v>
       </c>
       <c r="G15" t="s">
-        <v>759</v>
+        <v>763</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -3137,19 +3152,19 @@
         <v>21</v>
       </c>
       <c r="C16" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="D16" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="E16" t="s">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="F16">
         <v>1</v>
       </c>
       <c r="G16" t="s">
-        <v>760</v>
+        <v>764</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -3160,19 +3175,19 @@
         <v>22</v>
       </c>
       <c r="C17" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D17" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="E17" t="s">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="F17">
         <v>1</v>
       </c>
       <c r="G17" t="s">
-        <v>759</v>
+        <v>763</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -3183,19 +3198,19 @@
         <v>23</v>
       </c>
       <c r="C18" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="D18" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="E18" t="s">
-        <v>583</v>
+        <v>586</v>
       </c>
       <c r="F18">
         <v>1</v>
       </c>
       <c r="G18" t="s">
-        <v>759</v>
+        <v>763</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -3206,19 +3221,19 @@
         <v>24</v>
       </c>
       <c r="C19" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="D19" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="E19" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="F19">
         <v>1</v>
       </c>
       <c r="G19" t="s">
-        <v>759</v>
+        <v>763</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -3229,19 +3244,19 @@
         <v>25</v>
       </c>
       <c r="C20" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="D20" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="E20" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="F20">
         <v>1</v>
       </c>
       <c r="G20" t="s">
-        <v>759</v>
+        <v>763</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -3252,19 +3267,19 @@
         <v>26</v>
       </c>
       <c r="C21" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D21" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="E21" t="s">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="F21">
         <v>1</v>
       </c>
       <c r="G21" t="s">
-        <v>759</v>
+        <v>763</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -3275,19 +3290,19 @@
         <v>27</v>
       </c>
       <c r="C22" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D22" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="E22" t="s">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="F22">
         <v>1</v>
       </c>
       <c r="G22" t="s">
-        <v>759</v>
+        <v>763</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -3298,19 +3313,19 @@
         <v>28</v>
       </c>
       <c r="C23" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D23" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="E23" t="s">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="F23">
         <v>1</v>
       </c>
       <c r="G23" t="s">
-        <v>759</v>
+        <v>763</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -3321,19 +3336,19 @@
         <v>29</v>
       </c>
       <c r="C24" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="D24" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="E24" t="s">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="F24">
         <v>1</v>
       </c>
       <c r="G24" t="s">
-        <v>759</v>
+        <v>763</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -3344,19 +3359,19 @@
         <v>30</v>
       </c>
       <c r="C25" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D25" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="E25" t="s">
-        <v>590</v>
+        <v>593</v>
       </c>
       <c r="F25">
         <v>1</v>
       </c>
       <c r="G25" t="s">
-        <v>759</v>
+        <v>763</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -3367,19 +3382,19 @@
         <v>31</v>
       </c>
       <c r="C26" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D26" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="E26" t="s">
-        <v>591</v>
+        <v>594</v>
       </c>
       <c r="F26">
         <v>1</v>
       </c>
       <c r="G26" t="s">
-        <v>759</v>
+        <v>763</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -3390,19 +3405,19 @@
         <v>32</v>
       </c>
       <c r="C27" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D27" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="E27" t="s">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="F27">
         <v>1</v>
       </c>
       <c r="G27" t="s">
-        <v>759</v>
+        <v>763</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -3413,19 +3428,19 @@
         <v>33</v>
       </c>
       <c r="C28" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="D28" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="E28" t="s">
-        <v>593</v>
+        <v>596</v>
       </c>
       <c r="F28">
         <v>1</v>
       </c>
       <c r="G28" t="s">
-        <v>759</v>
+        <v>763</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -3436,19 +3451,19 @@
         <v>34</v>
       </c>
       <c r="C29" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="D29" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="E29" t="s">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="F29">
         <v>1</v>
       </c>
       <c r="G29" t="s">
-        <v>759</v>
+        <v>763</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -3459,19 +3474,19 @@
         <v>35</v>
       </c>
       <c r="C30" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D30" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="E30" t="s">
-        <v>595</v>
+        <v>598</v>
       </c>
       <c r="F30">
         <v>1</v>
       </c>
       <c r="G30" t="s">
-        <v>759</v>
+        <v>763</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -3482,19 +3497,19 @@
         <v>36</v>
       </c>
       <c r="C31" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="D31" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="E31" t="s">
-        <v>596</v>
+        <v>599</v>
       </c>
       <c r="F31">
         <v>1</v>
       </c>
       <c r="G31" t="s">
-        <v>759</v>
+        <v>763</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -3505,19 +3520,19 @@
         <v>37</v>
       </c>
       <c r="C32" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D32" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="E32" t="s">
-        <v>597</v>
+        <v>600</v>
       </c>
       <c r="F32">
         <v>1</v>
       </c>
       <c r="G32" t="s">
-        <v>759</v>
+        <v>763</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -3528,19 +3543,19 @@
         <v>38</v>
       </c>
       <c r="C33" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="D33" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="E33" t="s">
-        <v>598</v>
+        <v>601</v>
       </c>
       <c r="F33">
         <v>1</v>
       </c>
       <c r="G33" t="s">
-        <v>759</v>
+        <v>763</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -3551,19 +3566,19 @@
         <v>39</v>
       </c>
       <c r="C34" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="D34" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="E34" t="s">
-        <v>599</v>
+        <v>602</v>
       </c>
       <c r="F34">
         <v>1</v>
       </c>
       <c r="G34" t="s">
-        <v>759</v>
+        <v>763</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -3574,19 +3589,19 @@
         <v>40</v>
       </c>
       <c r="C35" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="D35" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="E35" t="s">
-        <v>600</v>
+        <v>603</v>
       </c>
       <c r="F35">
         <v>1</v>
       </c>
       <c r="G35" t="s">
-        <v>759</v>
+        <v>763</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -3597,19 +3612,19 @@
         <v>41</v>
       </c>
       <c r="C36" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="D36" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="E36" t="s">
-        <v>601</v>
+        <v>604</v>
       </c>
       <c r="F36">
         <v>1</v>
       </c>
       <c r="G36" t="s">
-        <v>759</v>
+        <v>763</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -3620,19 +3635,19 @@
         <v>42</v>
       </c>
       <c r="C37" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="D37" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="E37" t="s">
-        <v>602</v>
+        <v>605</v>
       </c>
       <c r="F37">
         <v>1</v>
       </c>
       <c r="G37" t="s">
-        <v>759</v>
+        <v>763</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -3643,19 +3658,19 @@
         <v>43</v>
       </c>
       <c r="C38" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="D38" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="E38" t="s">
-        <v>603</v>
+        <v>606</v>
       </c>
       <c r="F38">
         <v>1</v>
       </c>
       <c r="G38" t="s">
-        <v>759</v>
+        <v>763</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -3666,19 +3681,19 @@
         <v>44</v>
       </c>
       <c r="C39" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D39" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="E39" t="s">
-        <v>604</v>
+        <v>607</v>
       </c>
       <c r="F39">
         <v>1</v>
       </c>
       <c r="G39" t="s">
-        <v>759</v>
+        <v>763</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -3689,19 +3704,19 @@
         <v>45</v>
       </c>
       <c r="C40" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="D40" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="E40" t="s">
-        <v>605</v>
+        <v>608</v>
       </c>
       <c r="F40">
         <v>1</v>
       </c>
       <c r="G40" t="s">
-        <v>761</v>
+        <v>765</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -3712,19 +3727,19 @@
         <v>46</v>
       </c>
       <c r="C41" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="D41" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="E41" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="F41">
         <v>1</v>
       </c>
       <c r="G41" t="s">
-        <v>760</v>
+        <v>764</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -3735,19 +3750,19 @@
         <v>47</v>
       </c>
       <c r="C42" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D42" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="E42" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="F42">
         <v>1</v>
       </c>
       <c r="G42" t="s">
-        <v>759</v>
+        <v>763</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -3758,19 +3773,19 @@
         <v>48</v>
       </c>
       <c r="C43" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D43" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E43" t="s">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="F43">
         <v>1</v>
       </c>
       <c r="G43" t="s">
-        <v>759</v>
+        <v>763</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -3781,19 +3796,19 @@
         <v>49</v>
       </c>
       <c r="C44" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D44" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="E44" t="s">
-        <v>609</v>
+        <v>612</v>
       </c>
       <c r="F44">
         <v>1</v>
       </c>
       <c r="G44" t="s">
-        <v>759</v>
+        <v>763</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -3804,19 +3819,19 @@
         <v>50</v>
       </c>
       <c r="C45" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D45" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="E45" t="s">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="F45">
         <v>1</v>
       </c>
       <c r="G45" t="s">
-        <v>759</v>
+        <v>763</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -3827,19 +3842,19 @@
         <v>51</v>
       </c>
       <c r="C46" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D46" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="E46" t="s">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="F46">
         <v>1</v>
       </c>
       <c r="G46" t="s">
-        <v>759</v>
+        <v>763</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -3850,19 +3865,19 @@
         <v>52</v>
       </c>
       <c r="C47" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="D47" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="E47" t="s">
-        <v>612</v>
+        <v>615</v>
       </c>
       <c r="F47">
         <v>1</v>
       </c>
       <c r="G47" t="s">
-        <v>759</v>
+        <v>763</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -3873,19 +3888,19 @@
         <v>53</v>
       </c>
       <c r="C48" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="D48" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="E48" t="s">
-        <v>613</v>
+        <v>616</v>
       </c>
       <c r="F48">
         <v>1</v>
       </c>
       <c r="G48" t="s">
-        <v>759</v>
+        <v>763</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -3896,19 +3911,19 @@
         <v>54</v>
       </c>
       <c r="C49" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="D49" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="E49" t="s">
-        <v>614</v>
+        <v>617</v>
       </c>
       <c r="F49">
         <v>1</v>
       </c>
       <c r="G49" t="s">
-        <v>759</v>
+        <v>763</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -3919,19 +3934,19 @@
         <v>55</v>
       </c>
       <c r="C50" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="D50" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="E50" t="s">
-        <v>615</v>
+        <v>618</v>
       </c>
       <c r="F50">
         <v>1</v>
       </c>
       <c r="G50" t="s">
-        <v>759</v>
+        <v>763</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -3942,19 +3957,19 @@
         <v>56</v>
       </c>
       <c r="C51" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D51" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="E51" t="s">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="F51">
         <v>1</v>
       </c>
       <c r="G51" t="s">
-        <v>759</v>
+        <v>763</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -3965,19 +3980,19 @@
         <v>57</v>
       </c>
       <c r="C52" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D52" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="E52" t="s">
-        <v>617</v>
+        <v>620</v>
       </c>
       <c r="F52">
         <v>1</v>
       </c>
       <c r="G52" t="s">
-        <v>759</v>
+        <v>763</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -3988,19 +4003,19 @@
         <v>58</v>
       </c>
       <c r="C53" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D53" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="E53" t="s">
-        <v>618</v>
+        <v>621</v>
       </c>
       <c r="F53">
         <v>1</v>
       </c>
       <c r="G53" t="s">
-        <v>759</v>
+        <v>763</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -4011,19 +4026,19 @@
         <v>59</v>
       </c>
       <c r="C54" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D54" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="E54" t="s">
-        <v>619</v>
+        <v>622</v>
       </c>
       <c r="F54">
         <v>1</v>
       </c>
       <c r="G54" t="s">
-        <v>759</v>
+        <v>763</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -4034,19 +4049,19 @@
         <v>60</v>
       </c>
       <c r="C55" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D55" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="E55" t="s">
-        <v>620</v>
+        <v>623</v>
       </c>
       <c r="F55">
         <v>1</v>
       </c>
       <c r="G55" t="s">
-        <v>759</v>
+        <v>763</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -4057,19 +4072,19 @@
         <v>61</v>
       </c>
       <c r="C56" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D56" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="E56" t="s">
-        <v>621</v>
+        <v>624</v>
       </c>
       <c r="F56">
         <v>1</v>
       </c>
       <c r="G56" t="s">
-        <v>759</v>
+        <v>763</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -4080,19 +4095,19 @@
         <v>62</v>
       </c>
       <c r="C57" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D57" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="E57" t="s">
-        <v>622</v>
+        <v>625</v>
       </c>
       <c r="F57">
         <v>1</v>
       </c>
       <c r="G57" t="s">
-        <v>762</v>
+        <v>766</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -4103,19 +4118,19 @@
         <v>63</v>
       </c>
       <c r="C58" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D58" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="E58" t="s">
-        <v>623</v>
+        <v>626</v>
       </c>
       <c r="F58">
         <v>1</v>
       </c>
       <c r="G58" t="s">
-        <v>759</v>
+        <v>763</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -4126,19 +4141,19 @@
         <v>64</v>
       </c>
       <c r="C59" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D59" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="E59" t="s">
-        <v>624</v>
+        <v>627</v>
       </c>
       <c r="F59">
         <v>1</v>
       </c>
       <c r="G59" t="s">
-        <v>759</v>
+        <v>763</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -4149,19 +4164,19 @@
         <v>65</v>
       </c>
       <c r="C60" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D60" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="E60" t="s">
-        <v>625</v>
+        <v>628</v>
       </c>
       <c r="F60">
         <v>1</v>
       </c>
       <c r="G60" t="s">
-        <v>759</v>
+        <v>763</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -4172,19 +4187,19 @@
         <v>66</v>
       </c>
       <c r="C61" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D61" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="E61" t="s">
-        <v>626</v>
+        <v>629</v>
       </c>
       <c r="F61">
         <v>1</v>
       </c>
       <c r="G61" t="s">
-        <v>759</v>
+        <v>763</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -4195,19 +4210,19 @@
         <v>67</v>
       </c>
       <c r="C62" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="E62" t="s">
-        <v>627</v>
+        <v>630</v>
       </c>
       <c r="F62">
         <v>1</v>
       </c>
       <c r="G62" t="s">
-        <v>759</v>
+        <v>763</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -4218,19 +4233,19 @@
         <v>68</v>
       </c>
       <c r="C63" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D63" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="E63" t="s">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="F63">
         <v>1</v>
       </c>
       <c r="G63" t="s">
-        <v>759</v>
+        <v>763</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -4241,19 +4256,19 @@
         <v>69</v>
       </c>
       <c r="C64" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="E64" t="s">
-        <v>629</v>
+        <v>632</v>
       </c>
       <c r="F64">
         <v>1</v>
       </c>
       <c r="G64" t="s">
-        <v>759</v>
+        <v>763</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -4264,19 +4279,19 @@
         <v>70</v>
       </c>
       <c r="C65" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D65" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="E65" t="s">
-        <v>630</v>
+        <v>633</v>
       </c>
       <c r="F65">
         <v>3</v>
       </c>
       <c r="G65" t="s">
-        <v>763</v>
+        <v>767</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -4287,19 +4302,19 @@
         <v>71</v>
       </c>
       <c r="C66" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="E66" t="s">
-        <v>631</v>
+        <v>634</v>
       </c>
       <c r="F66">
         <v>1</v>
       </c>
       <c r="G66" t="s">
-        <v>759</v>
+        <v>763</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -4310,19 +4325,19 @@
         <v>72</v>
       </c>
       <c r="C67" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D67" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="E67" t="s">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="F67">
         <v>1</v>
       </c>
       <c r="G67" t="s">
-        <v>759</v>
+        <v>763</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -4333,19 +4348,19 @@
         <v>73</v>
       </c>
       <c r="C68" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D68" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="E68" t="s">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="F68">
         <v>1</v>
       </c>
       <c r="G68" t="s">
-        <v>759</v>
+        <v>763</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -4356,19 +4371,19 @@
         <v>74</v>
       </c>
       <c r="C69" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D69" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="E69" t="s">
-        <v>634</v>
+        <v>637</v>
       </c>
       <c r="F69">
         <v>1</v>
       </c>
       <c r="G69" t="s">
-        <v>759</v>
+        <v>763</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -4379,19 +4394,19 @@
         <v>75</v>
       </c>
       <c r="C70" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D70" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E70" t="s">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="F70">
         <v>1</v>
       </c>
       <c r="G70" t="s">
-        <v>759</v>
+        <v>763</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -4402,19 +4417,19 @@
         <v>76</v>
       </c>
       <c r="C71" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D71" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="E71" t="s">
-        <v>636</v>
+        <v>639</v>
       </c>
       <c r="F71">
         <v>1</v>
       </c>
       <c r="G71" t="s">
-        <v>759</v>
+        <v>763</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -4425,19 +4440,19 @@
         <v>77</v>
       </c>
       <c r="C72" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D72" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="E72" t="s">
-        <v>637</v>
+        <v>640</v>
       </c>
       <c r="F72">
         <v>1</v>
       </c>
       <c r="G72" t="s">
-        <v>759</v>
+        <v>763</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -4448,19 +4463,19 @@
         <v>78</v>
       </c>
       <c r="C73" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D73" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="E73" t="s">
-        <v>638</v>
+        <v>641</v>
       </c>
       <c r="F73">
         <v>1</v>
       </c>
       <c r="G73" t="s">
-        <v>759</v>
+        <v>763</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -4471,19 +4486,19 @@
         <v>79</v>
       </c>
       <c r="C74" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D74" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="E74" t="s">
-        <v>639</v>
+        <v>642</v>
       </c>
       <c r="F74">
         <v>1</v>
       </c>
       <c r="G74" t="s">
-        <v>759</v>
+        <v>763</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -4494,19 +4509,19 @@
         <v>80</v>
       </c>
       <c r="C75" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D75" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="E75" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="F75">
         <v>1</v>
       </c>
       <c r="G75" t="s">
-        <v>759</v>
+        <v>763</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -4517,19 +4532,19 @@
         <v>81</v>
       </c>
       <c r="C76" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="D76" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="E76" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="F76">
         <v>1</v>
       </c>
       <c r="G76" t="s">
-        <v>759</v>
+        <v>763</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -4543,16 +4558,16 @@
         <v>82</v>
       </c>
       <c r="D77" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="E77" t="s">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="F77">
         <v>1</v>
       </c>
       <c r="G77" t="s">
-        <v>764</v>
+        <v>768</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -4566,16 +4581,16 @@
         <v>83</v>
       </c>
       <c r="D78" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="E78" t="s">
-        <v>643</v>
+        <v>646</v>
       </c>
       <c r="F78">
         <v>1</v>
       </c>
       <c r="G78" t="s">
-        <v>764</v>
+        <v>768</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -4589,16 +4604,16 @@
         <v>84</v>
       </c>
       <c r="D79" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="E79" t="s">
-        <v>644</v>
+        <v>647</v>
       </c>
       <c r="F79">
         <v>1</v>
       </c>
       <c r="G79" t="s">
-        <v>764</v>
+        <v>768</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -4612,16 +4627,16 @@
         <v>85</v>
       </c>
       <c r="D80" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="E80" t="s">
-        <v>645</v>
+        <v>648</v>
       </c>
       <c r="F80">
         <v>1</v>
       </c>
       <c r="G80" t="s">
-        <v>764</v>
+        <v>768</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -4635,16 +4650,16 @@
         <v>86</v>
       </c>
       <c r="D81" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="E81" t="s">
-        <v>646</v>
+        <v>649</v>
       </c>
       <c r="F81">
         <v>1</v>
       </c>
       <c r="G81" t="s">
-        <v>765</v>
+        <v>769</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -4658,16 +4673,16 @@
         <v>87</v>
       </c>
       <c r="D82" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="E82" t="s">
-        <v>647</v>
+        <v>650</v>
       </c>
       <c r="F82">
         <v>1</v>
       </c>
       <c r="G82" t="s">
-        <v>766</v>
+        <v>770</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -4681,16 +4696,16 @@
         <v>88</v>
       </c>
       <c r="D83" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="E83" t="s">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="F83">
         <v>1</v>
       </c>
       <c r="G83" t="s">
-        <v>764</v>
+        <v>768</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -4704,16 +4719,16 @@
         <v>89</v>
       </c>
       <c r="D84" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="E84" t="s">
-        <v>649</v>
+        <v>652</v>
       </c>
       <c r="F84">
         <v>1</v>
       </c>
       <c r="G84" t="s">
-        <v>764</v>
+        <v>768</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -4727,16 +4742,16 @@
         <v>90</v>
       </c>
       <c r="D85" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="E85" t="s">
-        <v>650</v>
+        <v>653</v>
       </c>
       <c r="F85">
         <v>1</v>
       </c>
       <c r="G85" t="s">
-        <v>764</v>
+        <v>768</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -4747,19 +4762,19 @@
         <v>91</v>
       </c>
       <c r="C86" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="D86" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="E86" t="s">
-        <v>651</v>
+        <v>654</v>
       </c>
       <c r="F86">
         <v>1</v>
       </c>
       <c r="G86" t="s">
-        <v>764</v>
+        <v>768</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -4773,16 +4788,16 @@
         <v>92</v>
       </c>
       <c r="D87" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="E87" t="s">
-        <v>652</v>
+        <v>655</v>
       </c>
       <c r="F87">
         <v>1</v>
       </c>
       <c r="G87" t="s">
-        <v>767</v>
+        <v>771</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -4796,16 +4811,16 @@
         <v>93</v>
       </c>
       <c r="D88" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="E88" t="s">
-        <v>653</v>
+        <v>656</v>
       </c>
       <c r="F88">
         <v>1</v>
       </c>
       <c r="G88" t="s">
-        <v>764</v>
+        <v>768</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -4816,19 +4831,19 @@
         <v>94</v>
       </c>
       <c r="C89" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D89" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="E89" t="s">
-        <v>654</v>
+        <v>657</v>
       </c>
       <c r="F89">
         <v>1</v>
       </c>
       <c r="G89" t="s">
-        <v>762</v>
+        <v>766</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -4839,19 +4854,19 @@
         <v>95</v>
       </c>
       <c r="C90" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="D90" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="E90" t="s">
-        <v>655</v>
+        <v>658</v>
       </c>
       <c r="F90">
         <v>1</v>
       </c>
       <c r="G90" t="s">
-        <v>759</v>
+        <v>763</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -4862,19 +4877,19 @@
         <v>96</v>
       </c>
       <c r="C91" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="D91" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="E91" t="s">
-        <v>656</v>
+        <v>659</v>
       </c>
       <c r="F91">
         <v>1</v>
       </c>
       <c r="G91" t="s">
-        <v>759</v>
+        <v>763</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -4885,19 +4900,19 @@
         <v>97</v>
       </c>
       <c r="C92" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="D92" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="E92" t="s">
-        <v>657</v>
+        <v>660</v>
       </c>
       <c r="F92">
         <v>1</v>
       </c>
       <c r="G92" t="s">
-        <v>759</v>
+        <v>763</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -4908,19 +4923,19 @@
         <v>98</v>
       </c>
       <c r="C93" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="D93" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="E93" t="s">
-        <v>658</v>
+        <v>661</v>
       </c>
       <c r="F93">
         <v>1</v>
       </c>
       <c r="G93" t="s">
-        <v>759</v>
+        <v>763</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -4931,19 +4946,19 @@
         <v>99</v>
       </c>
       <c r="C94" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="D94" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="E94" t="s">
-        <v>659</v>
+        <v>662</v>
       </c>
       <c r="F94">
         <v>1</v>
       </c>
       <c r="G94" t="s">
-        <v>759</v>
+        <v>763</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -4954,19 +4969,19 @@
         <v>100</v>
       </c>
       <c r="C95" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D95" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="E95" t="s">
-        <v>660</v>
+        <v>663</v>
       </c>
       <c r="F95">
         <v>1</v>
       </c>
       <c r="G95" t="s">
-        <v>768</v>
+        <v>772</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -4977,10 +4992,10 @@
         <v>101</v>
       </c>
       <c r="C96" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="D96" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="E96" t="s">
         <v>101</v>
@@ -4989,7 +5004,7 @@
         <v>1</v>
       </c>
       <c r="G96" t="s">
-        <v>759</v>
+        <v>763</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -5000,19 +5015,19 @@
         <v>102</v>
       </c>
       <c r="C97" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D97" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="E97" t="s">
-        <v>661</v>
+        <v>664</v>
       </c>
       <c r="F97">
         <v>1</v>
       </c>
       <c r="G97" t="s">
-        <v>759</v>
+        <v>763</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -5023,19 +5038,19 @@
         <v>103</v>
       </c>
       <c r="C98" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="D98" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="E98" t="s">
-        <v>662</v>
+        <v>665</v>
       </c>
       <c r="F98">
         <v>1</v>
       </c>
       <c r="G98" t="s">
-        <v>759</v>
+        <v>763</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -5046,19 +5061,19 @@
         <v>104</v>
       </c>
       <c r="C99" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="D99" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="E99" t="s">
-        <v>663</v>
+        <v>666</v>
       </c>
       <c r="F99">
         <v>1</v>
       </c>
       <c r="G99" t="s">
-        <v>759</v>
+        <v>763</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -5069,19 +5084,19 @@
         <v>105</v>
       </c>
       <c r="C100" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="D100" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="E100" t="s">
-        <v>664</v>
+        <v>667</v>
       </c>
       <c r="F100">
         <v>1</v>
       </c>
       <c r="G100" t="s">
-        <v>759</v>
+        <v>763</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -5092,19 +5107,19 @@
         <v>106</v>
       </c>
       <c r="C101" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D101" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="E101" t="s">
-        <v>665</v>
+        <v>668</v>
       </c>
       <c r="F101">
         <v>1</v>
       </c>
       <c r="G101" t="s">
-        <v>759</v>
+        <v>763</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -5115,19 +5130,19 @@
         <v>107</v>
       </c>
       <c r="C102" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="D102" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="E102" t="s">
-        <v>666</v>
+        <v>669</v>
       </c>
       <c r="F102">
         <v>1</v>
       </c>
       <c r="G102" t="s">
-        <v>759</v>
+        <v>763</v>
       </c>
     </row>
     <row r="103" spans="1:7">
@@ -5138,19 +5153,19 @@
         <v>108</v>
       </c>
       <c r="C103" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="D103" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="E103" t="s">
-        <v>667</v>
+        <v>670</v>
       </c>
       <c r="F103">
         <v>1</v>
       </c>
       <c r="G103" t="s">
-        <v>759</v>
+        <v>763</v>
       </c>
     </row>
     <row r="104" spans="1:7">
@@ -5161,19 +5176,19 @@
         <v>109</v>
       </c>
       <c r="C104" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D104" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="E104" t="s">
-        <v>668</v>
+        <v>671</v>
       </c>
       <c r="F104">
         <v>1</v>
       </c>
       <c r="G104" t="s">
-        <v>759</v>
+        <v>763</v>
       </c>
     </row>
     <row r="105" spans="1:7">
@@ -5184,19 +5199,19 @@
         <v>110</v>
       </c>
       <c r="C105" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D105" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="E105" t="s">
-        <v>669</v>
+        <v>672</v>
       </c>
       <c r="F105">
         <v>1</v>
       </c>
       <c r="G105" t="s">
-        <v>759</v>
+        <v>763</v>
       </c>
     </row>
     <row r="106" spans="1:7">
@@ -5207,19 +5222,19 @@
         <v>111</v>
       </c>
       <c r="C106" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="D106" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="E106" t="s">
-        <v>670</v>
+        <v>673</v>
       </c>
       <c r="F106">
         <v>1</v>
       </c>
       <c r="G106" t="s">
-        <v>759</v>
+        <v>763</v>
       </c>
     </row>
     <row r="107" spans="1:7">
@@ -5233,16 +5248,16 @@
         <v>112</v>
       </c>
       <c r="D107" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="E107" t="s">
-        <v>671</v>
+        <v>674</v>
       </c>
       <c r="F107">
         <v>1</v>
       </c>
       <c r="G107" t="s">
-        <v>764</v>
+        <v>768</v>
       </c>
     </row>
     <row r="108" spans="1:7">
@@ -5256,16 +5271,16 @@
         <v>113</v>
       </c>
       <c r="D108" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="E108" t="s">
-        <v>672</v>
+        <v>675</v>
       </c>
       <c r="F108">
         <v>1</v>
       </c>
       <c r="G108" t="s">
-        <v>764</v>
+        <v>768</v>
       </c>
     </row>
     <row r="109" spans="1:7">
@@ -5279,16 +5294,16 @@
         <v>114</v>
       </c>
       <c r="D109" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="E109" t="s">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="F109">
         <v>1</v>
       </c>
       <c r="G109" t="s">
-        <v>764</v>
+        <v>768</v>
       </c>
     </row>
     <row r="110" spans="1:7">
@@ -5299,19 +5314,19 @@
         <v>115</v>
       </c>
       <c r="C110" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="D110" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="E110" t="s">
-        <v>674</v>
+        <v>677</v>
       </c>
       <c r="F110">
         <v>1</v>
       </c>
       <c r="G110" t="s">
-        <v>759</v>
+        <v>763</v>
       </c>
     </row>
     <row r="111" spans="1:7">
@@ -5322,19 +5337,19 @@
         <v>116</v>
       </c>
       <c r="C111" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="D111" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="E111" t="s">
-        <v>675</v>
+        <v>678</v>
       </c>
       <c r="F111">
         <v>1</v>
       </c>
       <c r="G111" t="s">
-        <v>759</v>
+        <v>763</v>
       </c>
     </row>
     <row r="112" spans="1:7">
@@ -5345,19 +5360,19 @@
         <v>117</v>
       </c>
       <c r="C112" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="D112" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="E112" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="F112">
         <v>1</v>
       </c>
       <c r="G112" t="s">
-        <v>769</v>
+        <v>773</v>
       </c>
     </row>
     <row r="113" spans="1:7">
@@ -5368,19 +5383,19 @@
         <v>118</v>
       </c>
       <c r="C113" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="D113" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="E113" t="s">
-        <v>677</v>
+        <v>680</v>
       </c>
       <c r="F113">
         <v>1</v>
       </c>
       <c r="G113" t="s">
-        <v>759</v>
+        <v>763</v>
       </c>
     </row>
     <row r="114" spans="1:7">
@@ -5391,19 +5406,19 @@
         <v>119</v>
       </c>
       <c r="C114" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D114" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="E114" t="s">
-        <v>678</v>
+        <v>681</v>
       </c>
       <c r="F114">
         <v>1</v>
       </c>
       <c r="G114" t="s">
-        <v>770</v>
+        <v>774</v>
       </c>
     </row>
     <row r="115" spans="1:7">
@@ -5414,19 +5429,19 @@
         <v>120</v>
       </c>
       <c r="C115" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="D115" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="E115" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="F115">
         <v>1</v>
       </c>
       <c r="G115" t="s">
-        <v>771</v>
+        <v>775</v>
       </c>
     </row>
     <row r="116" spans="1:7">
@@ -5437,19 +5452,19 @@
         <v>121</v>
       </c>
       <c r="C116" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="D116" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="E116" t="s">
-        <v>680</v>
+        <v>683</v>
       </c>
       <c r="F116">
         <v>1</v>
       </c>
       <c r="G116" t="s">
-        <v>759</v>
+        <v>763</v>
       </c>
     </row>
     <row r="117" spans="1:7">
@@ -5460,19 +5475,19 @@
         <v>122</v>
       </c>
       <c r="C117" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="D117" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="E117" t="s">
-        <v>681</v>
+        <v>684</v>
       </c>
       <c r="F117">
         <v>1</v>
       </c>
       <c r="G117" t="s">
-        <v>772</v>
+        <v>776</v>
       </c>
     </row>
     <row r="118" spans="1:7">
@@ -5483,19 +5498,19 @@
         <v>123</v>
       </c>
       <c r="C118" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="D118" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="E118" t="s">
-        <v>682</v>
+        <v>685</v>
       </c>
       <c r="F118">
         <v>1</v>
       </c>
       <c r="G118" t="s">
-        <v>773</v>
+        <v>777</v>
       </c>
     </row>
     <row r="119" spans="1:7">
@@ -5506,19 +5521,19 @@
         <v>124</v>
       </c>
       <c r="C119" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="D119" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="E119" t="s">
-        <v>683</v>
+        <v>686</v>
       </c>
       <c r="F119">
         <v>1</v>
       </c>
       <c r="G119" t="s">
-        <v>774</v>
+        <v>778</v>
       </c>
     </row>
     <row r="120" spans="1:7">
@@ -5529,19 +5544,19 @@
         <v>125</v>
       </c>
       <c r="C120" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="D120" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="E120" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="F120">
         <v>1</v>
       </c>
       <c r="G120" t="s">
-        <v>775</v>
+        <v>779</v>
       </c>
     </row>
     <row r="121" spans="1:7">
@@ -5552,19 +5567,19 @@
         <v>126</v>
       </c>
       <c r="C121" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="D121" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="E121" t="s">
-        <v>685</v>
+        <v>688</v>
       </c>
       <c r="F121">
         <v>1</v>
       </c>
       <c r="G121" t="s">
-        <v>776</v>
+        <v>780</v>
       </c>
     </row>
     <row r="122" spans="1:7">
@@ -5575,19 +5590,19 @@
         <v>127</v>
       </c>
       <c r="C122" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D122" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="E122" t="s">
-        <v>686</v>
+        <v>689</v>
       </c>
       <c r="F122">
         <v>1</v>
       </c>
       <c r="G122" t="s">
-        <v>777</v>
+        <v>781</v>
       </c>
     </row>
     <row r="123" spans="1:7">
@@ -5598,19 +5613,19 @@
         <v>128</v>
       </c>
       <c r="C123" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D123" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="E123" t="s">
-        <v>687</v>
+        <v>690</v>
       </c>
       <c r="F123">
         <v>1</v>
       </c>
       <c r="G123" t="s">
-        <v>778</v>
+        <v>782</v>
       </c>
     </row>
     <row r="124" spans="1:7">
@@ -5621,19 +5636,19 @@
         <v>129</v>
       </c>
       <c r="C124" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="D124" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="E124" t="s">
-        <v>688</v>
+        <v>691</v>
       </c>
       <c r="F124">
         <v>1</v>
       </c>
       <c r="G124" t="s">
-        <v>779</v>
+        <v>783</v>
       </c>
     </row>
     <row r="125" spans="1:7">
@@ -5644,19 +5659,19 @@
         <v>130</v>
       </c>
       <c r="C125" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="D125" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="E125" t="s">
-        <v>689</v>
+        <v>692</v>
       </c>
       <c r="F125">
         <v>1</v>
       </c>
       <c r="G125" t="s">
-        <v>780</v>
+        <v>784</v>
       </c>
     </row>
     <row r="126" spans="1:7">
@@ -5667,19 +5682,19 @@
         <v>131</v>
       </c>
       <c r="C126" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="D126" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="E126" t="s">
-        <v>690</v>
+        <v>693</v>
       </c>
       <c r="F126">
         <v>1</v>
       </c>
       <c r="G126" t="s">
-        <v>781</v>
+        <v>785</v>
       </c>
     </row>
     <row r="127" spans="1:7">
@@ -5690,19 +5705,19 @@
         <v>132</v>
       </c>
       <c r="C127" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D127" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="E127" t="s">
-        <v>691</v>
+        <v>694</v>
       </c>
       <c r="F127">
         <v>1</v>
       </c>
       <c r="G127" t="s">
-        <v>782</v>
+        <v>786</v>
       </c>
     </row>
     <row r="128" spans="1:7">
@@ -5713,19 +5728,19 @@
         <v>133</v>
       </c>
       <c r="C128" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="D128" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="E128" t="s">
-        <v>692</v>
+        <v>695</v>
       </c>
       <c r="F128">
         <v>1</v>
       </c>
       <c r="G128" t="s">
-        <v>783</v>
+        <v>787</v>
       </c>
     </row>
     <row r="129" spans="1:7">
@@ -5736,19 +5751,19 @@
         <v>134</v>
       </c>
       <c r="C129" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="D129" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="E129" t="s">
-        <v>693</v>
+        <v>696</v>
       </c>
       <c r="F129">
         <v>1</v>
       </c>
       <c r="G129" t="s">
-        <v>784</v>
+        <v>788</v>
       </c>
     </row>
     <row r="130" spans="1:7">
@@ -5759,19 +5774,19 @@
         <v>135</v>
       </c>
       <c r="C130" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="D130" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="E130" t="s">
-        <v>694</v>
+        <v>697</v>
       </c>
       <c r="F130">
         <v>1</v>
       </c>
       <c r="G130" t="s">
-        <v>785</v>
+        <v>789</v>
       </c>
     </row>
     <row r="131" spans="1:7">
@@ -5782,19 +5797,19 @@
         <v>136</v>
       </c>
       <c r="C131" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="D131" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="E131" t="s">
-        <v>695</v>
+        <v>698</v>
       </c>
       <c r="F131">
         <v>1</v>
       </c>
       <c r="G131" t="s">
-        <v>786</v>
+        <v>790</v>
       </c>
     </row>
     <row r="132" spans="1:7">
@@ -5805,19 +5820,19 @@
         <v>137</v>
       </c>
       <c r="C132" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="D132" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="E132" t="s">
-        <v>696</v>
+        <v>699</v>
       </c>
       <c r="F132">
         <v>1</v>
       </c>
       <c r="G132" t="s">
-        <v>787</v>
+        <v>791</v>
       </c>
     </row>
     <row r="133" spans="1:7">
@@ -5828,19 +5843,19 @@
         <v>138</v>
       </c>
       <c r="C133" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="D133" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="E133" t="s">
-        <v>697</v>
+        <v>700</v>
       </c>
       <c r="F133">
         <v>1</v>
       </c>
       <c r="G133" t="s">
-        <v>788</v>
+        <v>792</v>
       </c>
     </row>
     <row r="134" spans="1:7">
@@ -5851,19 +5866,19 @@
         <v>139</v>
       </c>
       <c r="C134" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="D134" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="E134" t="s">
-        <v>698</v>
+        <v>701</v>
       </c>
       <c r="F134">
         <v>1</v>
       </c>
       <c r="G134" t="s">
-        <v>789</v>
+        <v>793</v>
       </c>
     </row>
     <row r="135" spans="1:7">
@@ -5874,19 +5889,19 @@
         <v>140</v>
       </c>
       <c r="C135" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="D135" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="E135" t="s">
-        <v>699</v>
+        <v>702</v>
       </c>
       <c r="F135">
         <v>1</v>
       </c>
       <c r="G135" t="s">
-        <v>790</v>
+        <v>794</v>
       </c>
     </row>
     <row r="136" spans="1:7">
@@ -5897,19 +5912,19 @@
         <v>141</v>
       </c>
       <c r="C136" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="D136" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="E136" t="s">
-        <v>700</v>
+        <v>703</v>
       </c>
       <c r="F136">
         <v>1</v>
       </c>
       <c r="G136" t="s">
-        <v>791</v>
+        <v>795</v>
       </c>
     </row>
     <row r="137" spans="1:7">
@@ -5920,19 +5935,19 @@
         <v>142</v>
       </c>
       <c r="C137" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="D137" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="E137" t="s">
-        <v>701</v>
+        <v>704</v>
       </c>
       <c r="F137">
         <v>1</v>
       </c>
       <c r="G137" t="s">
-        <v>792</v>
+        <v>796</v>
       </c>
     </row>
     <row r="138" spans="1:7">
@@ -5943,19 +5958,19 @@
         <v>143</v>
       </c>
       <c r="C138" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="D138" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="E138" t="s">
-        <v>702</v>
+        <v>705</v>
       </c>
       <c r="F138">
         <v>1</v>
       </c>
       <c r="G138" t="s">
-        <v>793</v>
+        <v>797</v>
       </c>
     </row>
     <row r="139" spans="1:7">
@@ -5966,19 +5981,19 @@
         <v>144</v>
       </c>
       <c r="C139" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="D139" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="E139" t="s">
-        <v>703</v>
+        <v>706</v>
       </c>
       <c r="F139">
         <v>1</v>
       </c>
       <c r="G139" t="s">
-        <v>794</v>
+        <v>798</v>
       </c>
     </row>
     <row r="140" spans="1:7">
@@ -5989,19 +6004,19 @@
         <v>145</v>
       </c>
       <c r="C140" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="D140" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="E140" t="s">
-        <v>704</v>
+        <v>707</v>
       </c>
       <c r="F140">
         <v>1</v>
       </c>
       <c r="G140" t="s">
-        <v>795</v>
+        <v>799</v>
       </c>
     </row>
     <row r="141" spans="1:7">
@@ -6012,19 +6027,19 @@
         <v>146</v>
       </c>
       <c r="C141" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D141" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="E141" t="s">
-        <v>705</v>
+        <v>708</v>
       </c>
       <c r="F141">
         <v>1</v>
       </c>
       <c r="G141" t="s">
-        <v>796</v>
+        <v>800</v>
       </c>
     </row>
     <row r="142" spans="1:7">
@@ -6035,19 +6050,19 @@
         <v>147</v>
       </c>
       <c r="C142" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="D142" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="E142" t="s">
-        <v>706</v>
+        <v>709</v>
       </c>
       <c r="F142">
         <v>1</v>
       </c>
       <c r="G142" t="s">
-        <v>797</v>
+        <v>801</v>
       </c>
     </row>
     <row r="143" spans="1:7">
@@ -6058,19 +6073,19 @@
         <v>148</v>
       </c>
       <c r="C143" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="D143" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="E143" t="s">
-        <v>707</v>
+        <v>710</v>
       </c>
       <c r="F143">
         <v>1</v>
       </c>
       <c r="G143" t="s">
-        <v>798</v>
+        <v>802</v>
       </c>
     </row>
     <row r="144" spans="1:7">
@@ -6081,19 +6096,19 @@
         <v>149</v>
       </c>
       <c r="C144" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="D144" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="E144" t="s">
-        <v>708</v>
+        <v>711</v>
       </c>
       <c r="F144">
         <v>1</v>
       </c>
       <c r="G144" t="s">
-        <v>799</v>
+        <v>803</v>
       </c>
     </row>
     <row r="145" spans="1:7">
@@ -6104,13 +6119,13 @@
         <v>150</v>
       </c>
       <c r="C145" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="D145" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="E145" t="s">
-        <v>709</v>
+        <v>712</v>
       </c>
       <c r="F145">
         <v>1</v>
@@ -6124,19 +6139,19 @@
         <v>151</v>
       </c>
       <c r="C146" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="D146" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="E146" t="s">
-        <v>710</v>
+        <v>713</v>
       </c>
       <c r="F146">
         <v>1</v>
       </c>
       <c r="G146" t="s">
-        <v>800</v>
+        <v>804</v>
       </c>
     </row>
     <row r="147" spans="1:7">
@@ -6147,19 +6162,19 @@
         <v>152</v>
       </c>
       <c r="C147" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="D147" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="E147" t="s">
-        <v>711</v>
+        <v>714</v>
       </c>
       <c r="F147">
         <v>1</v>
       </c>
       <c r="G147" t="s">
-        <v>762</v>
+        <v>766</v>
       </c>
     </row>
     <row r="148" spans="1:7">
@@ -6170,19 +6185,19 @@
         <v>153</v>
       </c>
       <c r="C148" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="D148" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="E148" t="s">
-        <v>712</v>
+        <v>715</v>
       </c>
       <c r="F148">
         <v>1</v>
       </c>
       <c r="G148" t="s">
-        <v>759</v>
+        <v>763</v>
       </c>
     </row>
     <row r="149" spans="1:7">
@@ -6193,19 +6208,19 @@
         <v>154</v>
       </c>
       <c r="C149" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="D149" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="E149" t="s">
-        <v>713</v>
+        <v>716</v>
       </c>
       <c r="F149">
         <v>1</v>
       </c>
       <c r="G149" t="s">
-        <v>759</v>
+        <v>763</v>
       </c>
     </row>
     <row r="150" spans="1:7">
@@ -6216,19 +6231,19 @@
         <v>155</v>
       </c>
       <c r="C150" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="D150" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="E150" t="s">
-        <v>714</v>
+        <v>717</v>
       </c>
       <c r="F150">
         <v>1</v>
       </c>
       <c r="G150" t="s">
-        <v>759</v>
+        <v>763</v>
       </c>
     </row>
     <row r="151" spans="1:7">
@@ -6239,19 +6254,19 @@
         <v>156</v>
       </c>
       <c r="C151" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="D151" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="E151" t="s">
-        <v>715</v>
+        <v>718</v>
       </c>
       <c r="F151">
         <v>1</v>
       </c>
       <c r="G151" t="s">
-        <v>759</v>
+        <v>763</v>
       </c>
     </row>
     <row r="152" spans="1:7">
@@ -6262,19 +6277,19 @@
         <v>157</v>
       </c>
       <c r="C152" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="D152" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="E152" t="s">
-        <v>716</v>
+        <v>719</v>
       </c>
       <c r="F152">
         <v>1</v>
       </c>
       <c r="G152" t="s">
-        <v>759</v>
+        <v>763</v>
       </c>
     </row>
     <row r="153" spans="1:7">
@@ -6285,19 +6300,19 @@
         <v>158</v>
       </c>
       <c r="C153" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="D153" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="E153" t="s">
-        <v>717</v>
+        <v>720</v>
       </c>
       <c r="F153">
         <v>1</v>
       </c>
       <c r="G153" t="s">
-        <v>759</v>
+        <v>763</v>
       </c>
     </row>
     <row r="154" spans="1:7">
@@ -6308,19 +6323,19 @@
         <v>159</v>
       </c>
       <c r="C154" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="D154" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="E154" t="s">
-        <v>718</v>
+        <v>721</v>
       </c>
       <c r="F154">
         <v>1</v>
       </c>
       <c r="G154" t="s">
-        <v>762</v>
+        <v>766</v>
       </c>
     </row>
     <row r="155" spans="1:7">
@@ -6331,19 +6346,19 @@
         <v>160</v>
       </c>
       <c r="C155" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="D155" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="E155" t="s">
-        <v>719</v>
+        <v>722</v>
       </c>
       <c r="F155">
         <v>1</v>
       </c>
       <c r="G155" t="s">
-        <v>759</v>
+        <v>763</v>
       </c>
     </row>
     <row r="156" spans="1:7">
@@ -6354,19 +6369,19 @@
         <v>161</v>
       </c>
       <c r="C156" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="D156" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="E156" t="s">
-        <v>720</v>
+        <v>723</v>
       </c>
       <c r="F156">
         <v>1</v>
       </c>
       <c r="G156" t="s">
-        <v>759</v>
+        <v>763</v>
       </c>
     </row>
     <row r="157" spans="1:7">
@@ -6377,19 +6392,19 @@
         <v>162</v>
       </c>
       <c r="C157" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="D157" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="E157" t="s">
-        <v>721</v>
+        <v>724</v>
       </c>
       <c r="F157">
         <v>1</v>
       </c>
       <c r="G157" t="s">
-        <v>759</v>
+        <v>763</v>
       </c>
     </row>
     <row r="158" spans="1:7">
@@ -6400,19 +6415,19 @@
         <v>163</v>
       </c>
       <c r="C158" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="D158" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="E158" t="s">
-        <v>722</v>
+        <v>725</v>
       </c>
       <c r="F158">
         <v>1</v>
       </c>
       <c r="G158" t="s">
-        <v>759</v>
+        <v>763</v>
       </c>
     </row>
     <row r="159" spans="1:7">
@@ -6423,19 +6438,19 @@
         <v>164</v>
       </c>
       <c r="C159" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="D159" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="E159" t="s">
-        <v>723</v>
+        <v>726</v>
       </c>
       <c r="F159">
         <v>1</v>
       </c>
       <c r="G159" t="s">
-        <v>759</v>
+        <v>763</v>
       </c>
     </row>
     <row r="160" spans="1:7">
@@ -6446,19 +6461,19 @@
         <v>165</v>
       </c>
       <c r="C160" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="D160" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="E160" t="s">
-        <v>724</v>
+        <v>727</v>
       </c>
       <c r="F160">
         <v>1</v>
       </c>
       <c r="G160" t="s">
-        <v>759</v>
+        <v>763</v>
       </c>
     </row>
     <row r="161" spans="1:7">
@@ -6469,19 +6484,19 @@
         <v>166</v>
       </c>
       <c r="C161" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="D161" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="E161" t="s">
-        <v>725</v>
+        <v>728</v>
       </c>
       <c r="F161">
         <v>1</v>
       </c>
       <c r="G161" t="s">
-        <v>759</v>
+        <v>763</v>
       </c>
     </row>
     <row r="162" spans="1:7">
@@ -6492,19 +6507,19 @@
         <v>167</v>
       </c>
       <c r="C162" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="D162" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="E162" t="s">
-        <v>726</v>
+        <v>729</v>
       </c>
       <c r="F162">
         <v>1</v>
       </c>
       <c r="G162" t="s">
-        <v>759</v>
+        <v>763</v>
       </c>
     </row>
     <row r="163" spans="1:7">
@@ -6515,19 +6530,19 @@
         <v>168</v>
       </c>
       <c r="C163" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="D163" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="E163" t="s">
-        <v>727</v>
+        <v>730</v>
       </c>
       <c r="F163">
         <v>1</v>
       </c>
       <c r="G163" t="s">
-        <v>801</v>
+        <v>805</v>
       </c>
     </row>
     <row r="164" spans="1:7">
@@ -6538,19 +6553,19 @@
         <v>169</v>
       </c>
       <c r="C164" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="D164" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="E164" t="s">
-        <v>728</v>
+        <v>731</v>
       </c>
       <c r="F164">
         <v>1</v>
       </c>
       <c r="G164" t="s">
-        <v>759</v>
+        <v>763</v>
       </c>
     </row>
     <row r="165" spans="1:7">
@@ -6561,19 +6576,19 @@
         <v>170</v>
       </c>
       <c r="C165" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="D165" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="E165" t="s">
-        <v>729</v>
+        <v>732</v>
       </c>
       <c r="F165">
         <v>1</v>
       </c>
       <c r="G165" t="s">
-        <v>759</v>
+        <v>763</v>
       </c>
     </row>
     <row r="166" spans="1:7">
@@ -6584,19 +6599,19 @@
         <v>171</v>
       </c>
       <c r="C166" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="D166" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="E166" t="s">
-        <v>730</v>
+        <v>733</v>
       </c>
       <c r="F166">
         <v>1</v>
       </c>
       <c r="G166" t="s">
-        <v>759</v>
+        <v>763</v>
       </c>
     </row>
     <row r="167" spans="1:7">
@@ -6607,19 +6622,19 @@
         <v>172</v>
       </c>
       <c r="C167" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="D167" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="E167" t="s">
-        <v>731</v>
+        <v>734</v>
       </c>
       <c r="F167">
         <v>1</v>
       </c>
       <c r="G167" t="s">
-        <v>759</v>
+        <v>763</v>
       </c>
     </row>
     <row r="168" spans="1:7">
@@ -6630,19 +6645,19 @@
         <v>173</v>
       </c>
       <c r="C168" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="D168" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="E168" t="s">
-        <v>732</v>
+        <v>735</v>
       </c>
       <c r="F168">
         <v>1</v>
       </c>
       <c r="G168" t="s">
-        <v>759</v>
+        <v>763</v>
       </c>
     </row>
     <row r="169" spans="1:7">
@@ -6653,19 +6668,19 @@
         <v>174</v>
       </c>
       <c r="C169" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="D169" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="E169" t="s">
-        <v>733</v>
+        <v>736</v>
       </c>
       <c r="F169">
         <v>1</v>
       </c>
       <c r="G169" t="s">
-        <v>759</v>
+        <v>763</v>
       </c>
     </row>
     <row r="170" spans="1:7">
@@ -6676,19 +6691,19 @@
         <v>175</v>
       </c>
       <c r="C170" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="D170" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="E170" t="s">
-        <v>734</v>
+        <v>737</v>
       </c>
       <c r="F170">
         <v>1</v>
       </c>
       <c r="G170" t="s">
-        <v>759</v>
+        <v>763</v>
       </c>
     </row>
     <row r="171" spans="1:7">
@@ -6699,19 +6714,19 @@
         <v>176</v>
       </c>
       <c r="C171" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="D171" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="E171" t="s">
-        <v>735</v>
+        <v>738</v>
       </c>
       <c r="F171">
         <v>1</v>
       </c>
       <c r="G171" t="s">
-        <v>802</v>
+        <v>806</v>
       </c>
     </row>
     <row r="172" spans="1:7">
@@ -6722,19 +6737,19 @@
         <v>177</v>
       </c>
       <c r="C172" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D172" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="E172" t="s">
-        <v>736</v>
+        <v>739</v>
       </c>
       <c r="F172">
         <v>1</v>
       </c>
       <c r="G172" t="s">
-        <v>803</v>
+        <v>807</v>
       </c>
     </row>
     <row r="173" spans="1:7">
@@ -6745,19 +6760,19 @@
         <v>178</v>
       </c>
       <c r="C173" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="D173" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="E173" t="s">
-        <v>737</v>
+        <v>740</v>
       </c>
       <c r="F173">
         <v>1</v>
       </c>
       <c r="G173" t="s">
-        <v>804</v>
+        <v>808</v>
       </c>
     </row>
     <row r="174" spans="1:7">
@@ -6768,19 +6783,19 @@
         <v>179</v>
       </c>
       <c r="C174" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="D174" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="E174" t="s">
-        <v>738</v>
+        <v>741</v>
       </c>
       <c r="F174">
         <v>1</v>
       </c>
       <c r="G174" t="s">
-        <v>805</v>
+        <v>809</v>
       </c>
     </row>
     <row r="175" spans="1:7">
@@ -6791,19 +6806,19 @@
         <v>180</v>
       </c>
       <c r="C175" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="D175" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="E175" t="s">
-        <v>739</v>
+        <v>742</v>
       </c>
       <c r="F175">
         <v>1</v>
       </c>
       <c r="G175" t="s">
-        <v>805</v>
+        <v>809</v>
       </c>
     </row>
     <row r="176" spans="1:7">
@@ -6814,19 +6829,19 @@
         <v>178</v>
       </c>
       <c r="C176" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="D176" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="E176" t="s">
-        <v>740</v>
+        <v>743</v>
       </c>
       <c r="F176">
         <v>1</v>
       </c>
       <c r="G176" t="s">
-        <v>805</v>
+        <v>809</v>
       </c>
     </row>
     <row r="177" spans="1:7">
@@ -6837,19 +6852,19 @@
         <v>178</v>
       </c>
       <c r="C177" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="D177" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="E177" t="s">
-        <v>741</v>
+        <v>744</v>
       </c>
       <c r="F177">
         <v>1</v>
       </c>
       <c r="G177" t="s">
-        <v>805</v>
+        <v>809</v>
       </c>
     </row>
     <row r="178" spans="1:7">
@@ -6860,19 +6875,19 @@
         <v>181</v>
       </c>
       <c r="C178" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="D178" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="E178" t="s">
-        <v>742</v>
+        <v>745</v>
       </c>
       <c r="F178">
         <v>1</v>
       </c>
       <c r="G178" t="s">
-        <v>805</v>
+        <v>809</v>
       </c>
     </row>
     <row r="179" spans="1:7">
@@ -6883,19 +6898,19 @@
         <v>182</v>
       </c>
       <c r="C179" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="D179" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="E179" t="s">
-        <v>743</v>
+        <v>746</v>
       </c>
       <c r="F179">
         <v>1</v>
       </c>
       <c r="G179" t="s">
-        <v>805</v>
+        <v>809</v>
       </c>
     </row>
     <row r="180" spans="1:7">
@@ -6906,19 +6921,19 @@
         <v>183</v>
       </c>
       <c r="C180" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D180" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="E180" t="s">
-        <v>744</v>
+        <v>747</v>
       </c>
       <c r="F180">
         <v>1</v>
       </c>
       <c r="G180" t="s">
-        <v>805</v>
+        <v>809</v>
       </c>
     </row>
     <row r="181" spans="1:7">
@@ -6929,19 +6944,19 @@
         <v>184</v>
       </c>
       <c r="C181" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="D181" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="E181" t="s">
-        <v>745</v>
+        <v>748</v>
       </c>
       <c r="F181">
         <v>1</v>
       </c>
       <c r="G181" t="s">
-        <v>806</v>
+        <v>810</v>
       </c>
     </row>
     <row r="182" spans="1:7">
@@ -6952,19 +6967,19 @@
         <v>185</v>
       </c>
       <c r="C182" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="D182" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="E182" t="s">
-        <v>746</v>
+        <v>749</v>
       </c>
       <c r="F182">
         <v>1</v>
       </c>
       <c r="G182" t="s">
-        <v>759</v>
+        <v>763</v>
       </c>
     </row>
     <row r="183" spans="1:7">
@@ -6975,19 +6990,19 @@
         <v>186</v>
       </c>
       <c r="C183" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="D183" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="E183" t="s">
-        <v>747</v>
+        <v>750</v>
       </c>
       <c r="F183">
         <v>1</v>
       </c>
       <c r="G183" t="s">
-        <v>759</v>
+        <v>763</v>
       </c>
     </row>
     <row r="184" spans="1:7">
@@ -6998,19 +7013,19 @@
         <v>187</v>
       </c>
       <c r="C184" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="D184" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="E184" t="s">
-        <v>748</v>
+        <v>751</v>
       </c>
       <c r="F184">
         <v>1</v>
       </c>
       <c r="G184" t="s">
-        <v>807</v>
+        <v>811</v>
       </c>
     </row>
     <row r="185" spans="1:7">
@@ -7021,19 +7036,19 @@
         <v>188</v>
       </c>
       <c r="C185" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="D185" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="E185" t="s">
-        <v>749</v>
+        <v>752</v>
       </c>
       <c r="F185">
         <v>1</v>
       </c>
       <c r="G185" t="s">
-        <v>808</v>
+        <v>812</v>
       </c>
     </row>
     <row r="186" spans="1:7">
@@ -7044,19 +7059,19 @@
         <v>189</v>
       </c>
       <c r="C186" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="D186" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="E186" t="s">
-        <v>750</v>
+        <v>753</v>
       </c>
       <c r="F186">
         <v>1</v>
       </c>
       <c r="G186" t="s">
-        <v>759</v>
+        <v>763</v>
       </c>
     </row>
     <row r="187" spans="1:7">
@@ -7067,19 +7082,19 @@
         <v>190</v>
       </c>
       <c r="C187" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="D187" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="E187" t="s">
-        <v>751</v>
+        <v>754</v>
       </c>
       <c r="F187">
         <v>1</v>
       </c>
       <c r="G187" t="s">
-        <v>809</v>
+        <v>813</v>
       </c>
     </row>
     <row r="188" spans="1:7">
@@ -7090,19 +7105,19 @@
         <v>191</v>
       </c>
       <c r="C188" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="D188" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="E188" t="s">
-        <v>752</v>
+        <v>755</v>
       </c>
       <c r="F188">
         <v>1</v>
       </c>
       <c r="G188" t="s">
-        <v>759</v>
+        <v>763</v>
       </c>
     </row>
     <row r="189" spans="1:7">
@@ -7113,19 +7128,19 @@
         <v>192</v>
       </c>
       <c r="C189" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="D189" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="E189" t="s">
-        <v>753</v>
+        <v>756</v>
       </c>
       <c r="F189">
         <v>1</v>
       </c>
       <c r="G189" t="s">
-        <v>759</v>
+        <v>763</v>
       </c>
     </row>
     <row r="190" spans="1:7">
@@ -7136,19 +7151,19 @@
         <v>193</v>
       </c>
       <c r="C190" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="D190" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="E190" t="s">
-        <v>754</v>
+        <v>757</v>
       </c>
       <c r="F190">
         <v>1</v>
       </c>
       <c r="G190" t="s">
-        <v>759</v>
+        <v>763</v>
       </c>
     </row>
     <row r="191" spans="1:7">
@@ -7159,19 +7174,19 @@
         <v>194</v>
       </c>
       <c r="C191" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="D191" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="E191" t="s">
-        <v>755</v>
+        <v>758</v>
       </c>
       <c r="F191">
         <v>1</v>
       </c>
       <c r="G191" t="s">
-        <v>759</v>
+        <v>763</v>
       </c>
     </row>
     <row r="192" spans="1:7">
@@ -7182,19 +7197,19 @@
         <v>195</v>
       </c>
       <c r="C192" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="D192" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="E192" t="s">
-        <v>756</v>
+        <v>759</v>
       </c>
       <c r="F192">
         <v>1</v>
       </c>
       <c r="G192" t="s">
-        <v>810</v>
+        <v>814</v>
       </c>
     </row>
     <row r="193" spans="1:7">
@@ -7205,19 +7220,19 @@
         <v>196</v>
       </c>
       <c r="C193" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="D193" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="E193" t="s">
-        <v>757</v>
+        <v>760</v>
       </c>
       <c r="F193">
         <v>1</v>
       </c>
       <c r="G193" t="s">
-        <v>811</v>
+        <v>815</v>
       </c>
     </row>
     <row r="194" spans="1:7">
@@ -7231,16 +7246,39 @@
         <v>197</v>
       </c>
       <c r="D194" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="E194" t="s">
-        <v>758</v>
+        <v>761</v>
       </c>
       <c r="F194">
         <v>1</v>
       </c>
       <c r="G194" t="s">
-        <v>812</v>
+        <v>816</v>
+      </c>
+    </row>
+    <row r="195" spans="1:7">
+      <c r="A195">
+        <v>194</v>
+      </c>
+      <c r="B195" t="s">
+        <v>198</v>
+      </c>
+      <c r="C195" t="s">
+        <v>376</v>
+      </c>
+      <c r="D195" t="s">
+        <v>569</v>
+      </c>
+      <c r="E195" t="s">
+        <v>762</v>
+      </c>
+      <c r="F195">
+        <v>1</v>
+      </c>
+      <c r="G195" t="s">
+        <v>817</v>
       </c>
     </row>
   </sheetData>
